--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2210,8 +2210,162 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>ARDL/VECM spread test</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>9 CSE stocks + rates</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>monthly (171)</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>ARDL bounds + VECM</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>ARDL/VECM</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>long-run vs short-run</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>ARDL bounds F (banks)</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>No long-run link (spread is I(0)); effect is short-run only; banks -, finance + but weak long-run</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>ardl_vecm_summary.md</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>spread_ardl_vecm.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Direction Step 1 baseline</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>80/20 chrono</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>next-day Buy/Sell/Hold</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Accuracy %</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>Price+technical only: no edge, loses to persistence (43%). Honest baseline to beat.</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>step1_summary.md</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>direction_step1_baseline.py</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P22"/>
+  <autoFilter ref="A1:P24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2364,8 +2364,320 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Phase A multi-horizon direction</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>80/20 chrono + h-bar purge</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons (1d-252d)</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Horizons beating baseline</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0 of 9</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>majority / persistence</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>NO EDGE AT ANY HORIZON. Best model always below best baseline; gap widens with horizon (-3.5pp @1d -&gt; -47.1pp @1yr) because long-horizon drift makes the dumb baseline huge (maj 78% @6mo, pers 77% @1yr).</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>results/direction/multi_horizon/mh_summary.md</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>direction_multi_horizon.py; Tier-1 only; dead-zone +/-0.5%*sqrt(h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Phase A best single horizon</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>80/20 chrono + h-bar purge</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Logistic</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>direct, h=22d (1 month)</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Accuracy %</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>Best model result of the sweep (1-month Logistic 40.1%) still loses to persistence 42.1%. Logistic &gt; XGBoost at every horizon -&gt; no nonlinear structure to find.</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>mh_direction_table.csv</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>edge -2.0pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Return forecast</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Phase A multi-horizon return %</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>80/20 chrono + h-bar purge</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Ridge + XGBoost</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons (1d-252d)</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>RMSE ratio vs train-mean</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>Ridge beats naive-0 at 8/9 horizons BUT is only ~1% better than train-mean drift -&gt; it learned drift, NOT signal. XGBoost worse than naive everywhere (ratio 1.01-1.14).</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>mh_return_table.csv</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>train-mean is the honest null, not naive-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Return forecast</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Phase A return sign accuracy</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>80/20 chrono + h-bar purge</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>direct, sign of h-day return</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Horizons beating sign null</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>2 of 9</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>always-guess-winning-side</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>TRAP CHECK: 55-57% sign accuracy @1-3mo looks like the 52-58% target but 'always guess up' matches/beats it (test window drifted up 59-95%). Both 'wins' are +0.2pp = noise.</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>mh_edge_vs_horizon.png</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>up-share null added to stop false positive</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P24"/>
+  <autoFilter ref="A1:P28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2676,8 +2676,238 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Phase B ablation (+Tier-2)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>identical rows/split/seeds, A vs B</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons, ablation</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Mean gain from Tier-2 (pp)</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>RSI+MACD+volume add NOTHING. Mean -1.1pp, positive at only 1/9 horizons, 0/9 beat baseline. Technical indicators exhausted.</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>results/direction/phase_ablation/ablation_summary.md</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>direction_phase_ablation.py; 9 -&gt; 15 features</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Phase B feature attention check</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>identical rows/split/seeds</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>XGBoost importance</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Tier-2 share of importance %</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>XGBoost spends 41% of importance on Tier-2 (macd_signal is top feature at 6/9 horizons) yet accuracy does not improve -&gt; the model USES them but they carry no signal.</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>ablation_tier2_importance.csv</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>strong evidence indicators are redundant with price</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Return forecast</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Phase B return % (+Tier-2)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>identical rows/split/seeds</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Ridge + XGBoost</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>RMSE ratio vs train-mean (B)</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>Tier-2 made return RMSE slightly WORSE at 9/9 horizons (ratio gain +0.000 to +0.046). Sign edge stays negative everywhere.</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>ablation_return_table.csv</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>A ratio 0.991 -&gt; B ratio 0.991-1.034</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P28"/>
+  <autoFilter ref="A1:P31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="K29" s="2" t="n">
-        <v>-1.1</v>
+        <v>-0.9</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>RSI+MACD+volume add NOTHING. Mean -1.1pp, positive at only 1/9 horizons, 0/9 beat baseline. Technical indicators exhausted.</t>
+          <t>RSI+MACD+volume add NOTHING. Mean -0.9pp, 0/9 beat baseline. Technical indicators exhausted.</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_ablation.py; 9 -&gt; 15 features</t>
+          <t>direction_phase_ablation.py; 9 -&gt; 16 features; value restated on the 4-phase run (macro availability trims early rows)</t>
         </is>
       </c>
     </row>
@@ -2906,8 +2906,314 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Phase C ablation (+macro rates)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>identical rows/split/seeds, 35d publication lag</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons, ablation</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Mean gain from macro (pp)</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>Macro rates make it WORSE and unstable: gain swings -22.3 to +10.3 pp, 0/9 beat baseline. Not weak signal - overfitting.</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>results/direction/phase_ablation/ablation_summary.md</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>direction_phase_ablation.py; 16 -&gt; 29 features; inflation/FX/M2 still uncollected</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Phase C2 diagnostic (macro changes only)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>identical rows/split/seeds</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons, ablation</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Mean gain from macro d (pp)</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>DROPPING RATE LEVELS FIXES THE DAMAGE (-2.8 -&gt; +3.4 pp; 1yr 4.5% -&gt; 49.7%). Non-stationary levels were being memorised. Still 0/9 beat baseline -&gt; form was wrong AND no signal.</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>ablation_gain_table.csv</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>key methodology lesson: feed macro as changes, never levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Phase C feature attention check</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>identical rows/split/seeds</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>XGBoost importance</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Macro share of importance %</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>Macro importance rises 46% (1d) -&gt; 80% (1yr) while accuracy FALLS. Model fits rates as a trend proxy, not signal. tb_12m/spread/policy_rate are top features at 8/9 horizons.</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>ablation_feature_importance.csv</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>fingerprint of trending-variable overfit</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Return forecast</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Phase C return % (+macro)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>identical rows/split/seeds</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Ridge + XGBoost</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>RMSE ratio vs train-mean (C)</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>Macro blows out return RMSE to 1.29-1.37x the train-mean null (A/B sat at ~0.99). Clear damage, confirms the overfit reading.</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>ablation_return_table.csv</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>worst at 2-3 month horizons</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P31"/>
+  <autoFilter ref="A1:P35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3212,8 +3212,318 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Phase D ablation (+sector)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>identical rows/split/seeds</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons, ablation</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Mean gain from sector (pp)</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>FIRST consistently POSITIVE step: +2.6pp mean, positive at 6/9 horizons. Built on C2 (macro changes only). But still 0/9 beat baseline.</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>results/direction/phase_ablation/ablation_summary.md</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>direction_phase_ablation.py; C2 16+7 -&gt; D 39 features; ASPI + COMB/SAMP + LOFC/LOLC/LFIN/CFIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Phase D best single horizon</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>identical rows/split/seeds</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>direct, h=5d (1 week)</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Edge over baseline (pp)</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>Closest call of the whole study: 1-week Phase D 37.3% vs baseline 37.4%. Near-parity at short horizons (1d -1.7, 1wk -0.2, 2wk -1.6) but never crosses.</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>ablation_gain_table.csv</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>not a win; single split, one stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Return forecast</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Phase D return sign edge (+sector)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>identical rows/split/seeds</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Ridge + XGBoost</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>direct, sign of h-day return</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Sign edge 1wk/2wk/3wk (pp)</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>+1.7 / +1.7 / +1.1</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>always-guess-winning-side</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>First POSITIVE sign edges in the study, and at 3 adjacent horizons (1-3 weeks). Tiny (~1-2pp) and one split only -&gt; flag as worth re-testing, NOT a finding.</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>ablation_return_table.csv</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>check on other tickers before claiming anything</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Phase D feature attention check</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>HNB</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>identical rows/split/seeds</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>XGBoost importance</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Sector share of importance %</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>Sector takes 34% avg (42% at 1 day, falling to 27% at 1yr) - mirror image of macro, which rises with horizon. Sector matters short, macro long, neither enough.</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>ablation_feature_importance.csv</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>vol_20 is top feature at 1d/1wk; d_tb3m dominates long</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P35"/>
+  <autoFilter ref="A1:P39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3522,8 +3522,320 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Sector sweep - replication test</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>11 CSE stocks (3 banks, 4 finance, 4 control)</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>80/20 chrono + h-bar purge, per stock</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons x 11 stocks</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Cells beating baseline</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>27 of 99</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>14 of 99 (Phase A)</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>Sector features nearly DOUBLE the win rate vs Tier-1 (14-&gt;27 of 99) but wins sit at exactly coin-flip at short horizons and collapse at long ones. No real edge.</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>results/direction/sector_sweep/sweep_summary.md</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>direction_sector_sweep.py; peer composites exclude the target stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Sector gain replication (HNB claim 3)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>11 CSE stocks</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>identical protocol per stock</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Phase D - Phase A</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons x 11 stocks</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Mean sector gain (pp)</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>REPLICATES: +3.8pp mean, positive in 66/99 cells (67%), 9 of 11 stocks positive. HNB was not a fluke - sector context genuinely helps the model. Best: LFIN +13.2, SAMP +9.4, LOFC +8.2. Worst: CTC -11.0.</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>sweep_gain_by_ticker.csv</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>helping is not the same as winning</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Sector sweep significance screen</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>11 CSE stocks</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>sign test + Wilcoxon across stocks, per horizon</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>binomial sign test (H0 p=0.5)</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Best sign-test p</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>NOTHING SIGNIFICANT AT ANY HORIZON. Best cells (1 day, 1 week) are 6/11 stocks positive = p=0.500, exactly a coin flip. Long horizons far worse (1yr 0/11).</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>sweep_significance.csv</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>stocks share a market factor so p-values are already optimistic</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>HNB sign-edge claim retest (claim 2)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>11 CSE stocks</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>identical protocol per stock</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Ridge + XGBoost</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>direct, sign of h-day return, 1-3 week horizons</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Cells with positive sign edge</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>6 of 33</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>~17 of 33 (coin flip)</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>REFUTED. HNB's positive 1-3 week sign edge did NOT replicate - 18% vs the ~50% chance would give. It was luck. Flagged as provisional when found, now closed.</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>sweep_all_results.csv</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>value of naming a claim before retesting it</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P39"/>
+  <autoFilter ref="A1:P43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3834,8 +3834,864 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Phase E - daily USD/LKR</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>11 CSE stocks</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>80/20 chrono + h-bar purge, 2015-2026 window</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons x 11 stocks</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Mean gain from daily FX (pp)</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>FREQUENCY WAS NOT THE PROBLEM. Daily FX gain is exactly 0.0pp (positive in 57/99 cells = coin flip). Macro fails daily exactly as it failed monthly.</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>results/direction/daily_macro/daily_macro_summary.md</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>direction_daily_macro.py; new cleaned_data/usd_lkr_daily.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Phase E2 - daily global + CPI</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>11 CSE stocks</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>identical rows/split/seeds</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons x 11 stocks</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Mean gain from global+CPI (pp)</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>Oil, US 10Y, DXY and inflation make it WORSE (-1.9pp), worst at long horizons (-6.0pp at 1yr). Same trending-variable overfit as Phase C.</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>daily_macro_gain.csv</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>CPI spliced across 4 base years; money supply excluded (ends 2024-08, inside test window)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Phase E significance screen</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>11 CSE stocks</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>sign test across stocks, 4 phases x 9 horizons</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>binomial sign test (H0 p=0.5)</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Combinations with p&lt;0.05</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>0 of 36</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>NOTHING SIGNIFICANT ANYWHERE. Best cell is 1 day (6/11 stocks, p=0.500) - exact coin flip, same as the sector sweep. Cells beating baseline: A 17, D 27, E 24, E2 25 of 99.</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>daily_macro_significance.csv</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>macro information source now closed at both frequencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Phase E feature attention check</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>11 CSE stocks</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>identical rows/split/seeds</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>XGBoost importance</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons x 11 stocks</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>New-data share of importance %</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>Model spends 27% of importance on the new data (FX 7%, global 11%, CPI 9%) and gains nothing - third time this fingerprint has appeared (Tier-2 41%, macro 64%, now 27%).</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>daily_macro_all_results.csv</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>using a feature is not the same as profiting from it</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Phase F - money supply (M1/M2/M2b/M4)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>11 CSE stocks</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>80/20 chrono, sample cut at 2024-08; test 2022-03 to 2024-08</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons x 11 stocks</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Mean gain from money supply (pp)</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>Money supply adds NOTHING even on a crisis-era test window (positive in 50/99 cells = exact coin flip). Window moved back so M1/M2 could be tested fairly rather than excluded.</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>results/direction/money_supply/money_summary.md</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>direction_money_supply.py; 65-day publication lag per CBSL's own note; reserve money dropped (ends 2024-02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Phase F - full classic macro set</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>11 CSE stocks</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>identical rows/split/seeds</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons x 11 stocks</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Mean gain money-&gt;full macro (pp)</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>Full classic set (money + rates + FX + inflation) = 4 of the 5 Naik-Padhi variables. Still 42/99 cells, below the money-only phase (51/99). Only industrial production remains uncollected.</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>money_gain.csv</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>closes the macro chapter apart from IIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Crisis-window effect (window sensitivity)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>11 CSE stocks</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>2022-03 to 2024-08 vs 2024-2026</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons x 11 stocks</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Cells beating baseline</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>43-51 of 99</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>17-27 of 99 (calm window)</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>IMPORTANT METHOD FINDING: moving the test window into the 2022 crisis roughly DOUBLES the win rate for ALL phases including price-only. Results are window-dependent, not model-dependent.</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>money_by_horizon.csv</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>argues for walk-forward / multi-window evaluation in the write-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>1-day significance - macro ruled out</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>11 CSE stocks</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>sign test across stocks, 4 phases x 9 horizons</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>binomial sign test (H0 p=0.5)</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Cells with p&lt;0.05</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>2 of 36</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>1.8 expected by chance</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>Both hits are at 1 day, and the STRONGEST is Phase A (price only, 9/11, +3.9pp, p=0.033). Adding money supply SHRINKS it to +3.2pp. So it is the crisis window, not macro - and 2/36 is chance anyway.</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>money_significance.csv</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>checking the null model is what prevented a false claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Phase G - industrial production (IIP)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>11 CSE stocks</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>80/20 chrono, sample 2016-2026 (IIP coverage)</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons x 11 stocks</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Mean gain from IIP (pp)</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>IIP makes it WORSE (-6.4pp, positive in only 25/99 cells, 0/36 significant). It was the STRONGEST variable in the Naik-Padhi reference paper, and it still does not predict direction.</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>results/direction/industrial_production/iip_summary.md</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>direction_industrial_production.py; DCS index entered by hand, 2016-01 to 2026-05; 50-day publication lag</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Phase G - full classic macro set complete</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>11 CSE stocks</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>identical rows/split/seeds</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons x 11 stocks</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Cells beating baseline</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>25 of 99</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>27 of 99 (no macro)</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>ALL FIVE Naik-Padhi macro variables now tested (IIP, money supply, T-bill rate, exchange rate, inflation). NONE beats plain price history. Macro chapter complete.</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>iip_gain.csv</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>adding all macro is WORSE than sector-only (27/99)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>IIP seasonality guard</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Sri Lanka DCS IIP</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>monthly (125)</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>2016-01 to 2026-05</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>seasonal inspection</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>April vs March gap (pts)</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>-10 to -34</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>IIP is NOT seasonally adjusted - April falls 10-34 pts EVERY year (Sinhala/Tamil New Year), March always peaks. Month-on-month would be a calendar signal, so YoY-only features were used.</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>cleaned_data/industrial_production_monthly.csv</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>clean_macro_sources.py; mom column deliberately named _DO_NOT_USE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P43"/>
+  <autoFilter ref="A1:P54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,7 +44,7 @@
       <color rgb="00C00000"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -117,6 +122,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -493,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P54"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4690,8 +4698,400 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Correlation</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Co-movement lift table (no model)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks (22,677 stock-days)</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>full panel, 15 indicators x 9 horizons</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>conditional probability + 2-proportion z</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Median |lift| short horizons (pp)</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>'If indicator up, does stock go up?' answered by pure counting. Market/peer indicators give a real +6 to +10pp lift at 1d-1mo on huge samples. Macro lifts are near zero at short horizons.</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>results/direction/pooled_rules/comovement_table.csv</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>direction_pooled_and_rules.py; lift = P(up|ind up) - P(up|ind down)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Correlation</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Co-movement - long-horizon lifts are artifacts</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>panel, |lift|&gt;=10pp cells</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>independent-window audit</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Independent windows behind biggest lifts</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>7-24</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>hundreds needed</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>All 19 large lifts (T-bill -19.3, M2 +17.0, USD/LKR -15.3) sit at 3mo-1yr where only 7-24 INDEPENDENT windows exist. Overlapping windows inflate the z-test. Discard them.</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>comovement_table.csv</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>median |lift| long 4.2pp vs short 2.5pp is a sample-size illusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Pooled panel model (sector-wide)</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks pooled</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>split by DATE not row, 17,770 train rows</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons, one model for whole sector</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Horizons beating pooled baseline</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>2 of 9</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>majority / persistence</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>7x more training data (17,770 vs ~2,700 per stock). Beats the POOLED baseline at 1 day (+3.3pp) and 1 week (+2.7pp) only.</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>results/direction/pooled_rules/pooled_model_results.csv</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>direction_pooled_and_rules.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Pooled model fairness check</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>pooled model scored vs each stock's OWN baseline</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>binomial sign test (H0 p=0.5)</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>direct, 9 horizons</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>1-day: stocks positive</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>6 of 7</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>p=0.062</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>STRONGEST RESULT OF THE PROJECT but still not significant. The 1-week +2.7pp was a POOLING ARTIFACT (-0.5pp vs own baselines). Only 1 day survives: median +2.5pp, p=0.062, 1 of 9 horizons, single window.</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>pooled_vs_own_baseline.csv</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>pooling stocks with different class balance weakens the majority baseline and fakes an edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Readable rules extracted</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks pooled</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>depth-3 tree, scored on unseen test set</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Decision tree (depth 3)</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>direct, h=1/5/22</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Best 1-day rule accuracy %</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="M59" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>17 plain-English rules with out-of-sample hit rates. Best 1-day rule: calm market + flat ASPI + no big drop -&gt; Hold, 49.3% (+11.3pp). Shows WHAT the model believes, not just that it fails.</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>readable_rules.csv</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>1-month rule at 68.5% fires only 317 times - treat as noise</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P54"/>
+  <autoFilter ref="A1:P59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4710,16 +5110,16 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>RESULTS MASTER LOG — how to use</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr"/>
+      <c r="B1" s="10" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
-      <c r="B2" s="9" t="inlineStr"/>
+      <c r="B2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4727,7 +5127,7 @@
           <t>Purpose</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>One tidy row per reported test result, across ALL test types (forecasting, regression, event study, correlation, baseline). Filter/sort by any column.</t>
         </is>
@@ -4735,195 +5135,195 @@
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
-      <c r="B4" s="9" t="inlineStr"/>
+      <c r="B4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Sequential row number</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>When the test was run (approx.)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Price forecast / Baseline / Correlation / Event study / Regression / Method study / (new types allowed)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Test / Experiment</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Short test name</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>What data (S&amp;P SL20, HNB, 10 CSE stocks, ...)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Freq</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>daily / hourly / monthly / event</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Split / Setup</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>80/20, 50/50, 40/60, walk-forward, full-sample, event-study, n specifications, ...</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Model / Method</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>ARIMA, LSTM, Hybrid, Prophet, XGBoost, GRU, TFT, OLS, event-study, ...</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Protocol</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>one-step / multi-step / recursive / direct / n/a</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Name of the reported number (MAPE %, accuracy, interaction p, CAR, correlation, ...)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>The metric value</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Baseline value</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>The naive / comparison value (leave '—' if not applicable)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Beats baseline?</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Yes / No / Tie / —  (drives the colour)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Verdict / Key finding</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>One-line human takeaway</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Output files</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Where the detailed results live</t>
         </is>
@@ -4935,7 +5335,7 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Anything else (caveats, script name)</t>
         </is>
@@ -4943,15 +5343,15 @@
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" s="9" t="inlineStr"/>
+      <c r="B22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>RULE</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Update this log after EVERY test run (this chat or Claude Code): add a new row to ROWS in src/build_results_log.py and re-run it, OR append a row directly in Excel. Never leave a completed test unlogged.</t>
         </is>
@@ -4963,7 +5363,7 @@
           <t>To regenerate</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>python src/build_results_log.py</t>
         </is>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:P62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5090,8 +5090,248 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>1-day claim re-test (walk-forward)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>21 non-overlapping 6-month windows, expanding train</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost (reported separately)</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>direct, walk-forward, h=1</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Folds with positive median edge</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>6-7 of 21</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>10.5 expected by chance</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>CLAIM REFUTED. Median of fold medians -1.8pp (Logistic) / -1.9pp (XGBoost), sign-test p=0.96 and 0.99. The single-split +2.5pp did not survive 21 independent windows.</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>results/direction/retest_1day/retest_summary.md</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>direction_1day_retest.py; verdict rule fixed IN ADVANCE; 1-week carried as control, also negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>1-day re-test - window regime effect</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>21 walk-forward folds</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>direct, h=1</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Positive folds 2016-2020 vs 2021-2024</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>1 of 10 vs 6 of 8</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M61" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>Confirms the crisis-window finding a second time: folds in 2021-2024 are mostly POSITIVE, 2016-2020 mostly negative. Apparent skill is a property of the period, not the model.</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>retest_by_fold.csv</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>strong argument for walk-forward reporting in the dissertation</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>1-day re-test - per stock consistency</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>21 walk-forward folds each</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>direct, h=1</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Stocks positive in &gt;50% of folds</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>2 of 7</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>No consistency: LOFC and CFIN positive in 62% of folds, HNB in only 19%. A real edge would show across the sector, not in two names.</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>retest_by_stock.csv</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>median edge per stock ranges +4.9 (LOFC) to -4.9 (SAMP)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P59"/>
+  <autoFilter ref="A1:P62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P62"/>
+  <dimension ref="A1:P65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5330,8 +5330,248 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>LSTM/GRU for direction</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks pooled</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>daily (30-day sequences)</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>7 walk-forward 12-month folds, 3 seeds</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>LSTM + GRU (PyTorch)</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>direct, sequence input, h=1/5/22</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Folds positive (LSTM, h=1)</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>5 of 7</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>p=0.227</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>Recurrent nets do NOT beat the naive baseline at any horizon. Closes the 'did you try deep learning on direction?' question. LSTM finally applied to the direction target (project is named after it).</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>results/direction/lstm_gru/lstm_gru_summary.md</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>direction_lstm_gru.py; monthly macro excluded (flat inside a 30-day window)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Sequence vs flat control (LSTM value)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks pooled</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>identical sequences, flattened for the control</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>LSTM vs Logistic on flattened sequences</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>direct, h=1/5/22</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Median edge LSTM vs flat (pp)</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>+2.9 vs -1.7</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Logistic(flat)</t>
+        </is>
+      </c>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>REAL NUANCE: LSTM beats the FLATTENED same data at ALL 3 horizons (1d +2.9 vs -1.7, 1wk -0.4 vs -2.1, 1mo -5.4 vs -9.9). Order of recent days carries a little signal that summary features discard - first time added complexity helped. Still not enough to reach the baseline.</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>lstm_gru_by_fold.csv</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>the flat control is what makes this interpretable</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Regime effect - THIRD confirmation</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>7 walk-forward folds, LSTM h=1</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Positive folds 2019-2020 vs 2021-2025</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>0 of 2 vs 5 of 5</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>Same window/regime pattern found for a THIRD time (after money supply and the 1-day retest). Every model looks skilled post-2021 and useless before, with identical code and features. Explains why 5/7 folds here is not convincing.</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>lstm_gru_by_fold.csv</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>strongest methodological finding of the project</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P62"/>
+  <autoFilter ref="A1:P65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5570,8 +5570,320 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Phase H - news sentiment</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>7 walk-forward 6-month folds, 2016-2022</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>direct, h=1/5/10/22</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Mean gain from sentiment (pp)</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>News sentiment does NOT improve direction. Gain positive at 2 of 4 horizons (-0.8, -0.7, +2.4, +1.6), nothing near significance (all p&gt;=0.50). No phase beats the naive baseline.</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>results/direction/sentiment/sentiment_summary.md</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>direction_phase_h_sentiment.py; 149k Dailymirror/Newsfirst articles, 9,785 market-relevant</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Phase H - lexicon disagreement</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Dailymirror + Newsfirst news</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>9,785 market-relevant articles 2016-2022</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>VADER vs Loughran-McDonald style</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>sentiment scoring</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Correlation between lexicons</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>Two reasonable sentiment measures on the SAME articles correlate only 0.42. Direct evidence the sentiment signal is fragile, not merely weak. Running one lexicon alone would have hidden this.</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>sentiment_verdict.csv</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>finance_lexicon.py; full LM dictionary can be dropped in without code change</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Phase H - regime confound ruled out</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>folds split calm vs crisis</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Sentiment gain calm vs crisis (pp)</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>+0.85 vs -0.45</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="4" t="inlineStr">
+        <is>
+          <t>Expected sentiment to 'work' only in the 2022 crisis; the OPPOSITE happened (calm 9/16 folds positive, crisis 3/12). So this null is NOT a regime artifact - cleaner than the other phases.</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>sentiment_regime_split.csv</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>first phase where the regime effect did not appear</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>News look-ahead guard</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Dailymirror + Newsfirst news</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>publication timestamps vs 14:30 CSE close</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>time-of-day assignment</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Articles pushed to next trading day %</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>36% of articles were published AFTER the 14:30 close and were reassigned to the next trading day. Without this rule those articles report the very move being predicted and sentiment would look excellent and be worthless.</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>cleaned_data/news_sentiment_daily.csv</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>only 75 of 149,240 rows lacked a timestamp</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P65"/>
+  <autoFilter ref="A1:P69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P69"/>
+  <dimension ref="A1:P80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5882,8 +5882,858 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>POSITIVE CONTROL - pipeline validation</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>19 walk-forward folds, same-day vs lagged info</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>contemporaneous vs predictive</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Edge over baseline (pp)</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="M70" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>DECISIVE: same code finds +8.2pp (17/19 folds, p=0.0004) using TODAY's market/macro/news, and -4.1pp using the SAME info one day earlier. Gap 13.7pp. The pipeline is NOT blind - this information EXPLAINS returns but does not PREDICT them.</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>results/direction/diagnostics/diagnostics_summary.md</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>direction_diagnostics.py; own-stock return excluded from contemporaneous features</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Binary up/down reformulation</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>19 walk-forward folds</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>binary, h=1/5/22</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Edge over baseline (pp)</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>3-class dead-zone was NOT hiding a signal. Binary edge -4.8/-1.1/-2.1pp at 1d/1wk/1mo, positive in only 1/19, 7/19, 4/19 folds.</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>diagnostics_verdict.csv</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>rules out the Hold-majority explanation</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>MAGNITUDE-WEIGHTED edge (survives)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>19 walk-forward folds</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>binary, |return|-weighted</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Weighted edge 1d / 1wk (pp)</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>+7.9 / +13.2</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>FIRST RESULT TO SURVIVE. Model is WRONG more often than baseline on plain accuracy (-4.3pp) but RIGHT on the big moves: weighted edge +7.9pp (15/19 folds, p=0.0096) at 1 day and +13.2pp (15/19, p=0.0096) at 1 week. Accuracy was the wrong metric.</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>diagnostics_magnitude.csv</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>1-month +9.5pp but p=0.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Trading backtest with costs</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>19 walk-forward folds, h=1 only (non-overlapping)</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>long/short on model signal</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>economic evaluation</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Net return @50bps (%)</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>THE EDGE IS REAL BUT NOT EXPLOITABLE. Gross +22.19% vs buy-and-hold +6.49%, but median 40 position flips per 6-month fold: net +17.35% @10bps, +11.24% @25bps, +0.05% @50bps. At realistic CSE costs the edge is exactly zero (8/19 folds, p=0.82).</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>diagnostics_backtest_h1.csv</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>h=5 and h=22 backtests omitted - overlapping returns cannot be summed</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Price forecast</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Price + macro + news vs naive</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>walk-forward 6-month folds, per stock</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>naive / ARIMA(1,1,1) / Ridge / XGBoost</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>1-day and 5-day, return-then-reconstruct</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Cases beating naive (MAPE)</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>0 of 133</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>NAIVE UNBEATEN. Best model ARIMA(1,1,1) at 1.004x naive MAPE. Stage 1's univariate conclusion survives the multivariate test - adding macro and news does not rescue price forecasting.</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>results/price_macro_news/price_summary.md</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>price_with_macro_news.py; models predict RETURN then reconstruct price to stop them echoing today's price</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Price forecast</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Does macro/news improve price forecasting?</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>nested feature sets P / P+M / P+M+N</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Ridge + XGBoost</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>ablation on MAPE</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Median MAPE improvement (pp)</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>ALL EIGHT combinations NEGATIVE (-0.008 to -0.078pp). Adding macro and news makes price forecasting WORSE, consistently across both algorithms and both horizons.</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>price_ablation_gain.csv</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>mirrors the direction chapter exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>CSE flat-day share (illiquidity)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>7 bank/finance stocks</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>2017-2026</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>share of zero-return days</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Flat days at 1 day (%)</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>~10% of bank/finance trading days close EXACTLY unchanged; LOFC 36.0%, HNB 12.9%, LOLC 7.2%. Illiquidity is part of why the naive baseline is so hard to beat and why the Hold class dominates.</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>price_all_results.csv</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>surfaced as an artefact of the naive model's directional-accuracy column</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>LEAK CAUGHT - ASPI forward-fill</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 index</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>feature vs same-day and next-day return</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>correlation audit</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>leak detection</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>corr with next-day vs same-day</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="M77" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>SPSL20 and ASPI do not share a trading calendar (207 / 962 mismatched dates). Forward-filling ASPI across the gaps let it carry a move SPSL20 only recorded on its NEXT row. Halved MAPE for free: ratio 0.496 vs a true 0.970.</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>results/price_macro_news/leak_scan.csv</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>fix: no ffill across calendars + no ASPI features for index targets</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Automated leak scan added</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>all 9 targets</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>every feature, every run</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>corr(feature, future) vs corr(feature, present)</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>guard</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Features flagged after fix</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
+          <t>Permanent guard: any feature correlating MORE with the future than the present is flagged. Would have caught the ASPI bug instantly. Runs on every target automatically. THIRD leak-class bug in this project - all three flattered the model.</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>price_with_macro_news.py</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>previous two: persistence baseline lookback, pooled baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Price forecast</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 with macro + news (corrected)</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 index</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>17 walk-forward 6-month folds</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>naive / ARIMA / Ridge / XGBoost</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>direct 1-day and 5-day</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>MAPE ratio vs naive (best)</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>After the leak fix: best is Ridge price-only at 0.970 (1d) and 0.959 (5d), beating naive in only 10/17 and 9/17 folds. Macro and news make it WORSE (ratios 1.00-1.10).</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>results/price_macro_news/price_summary.md</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>pre-fix figure was 0.496 - entirely the ASPI leak</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Price forecast</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Index vs stock autocorrelation</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>SPSL20, ASPI vs 7 stocks</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>full sample</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>lag-1 return autocorrelation</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>descriptive</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Lag-1 autocorr (index vs stock)</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>+0.24 vs +0.04</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>REAL EFFECT: indices show +0.237 (SPSL20) and +0.233 (ASPI) lag-1 return autocorrelation vs +0.038 for HNB. Non-synchronous trading - illiquid constituents (LOFC 37.8% flat days) reprice a day late, smearing shocks. A 1-parameter AR(1) captures the entire index 'edge'.</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>price_all_results.csv</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>statistically real, economically useless - capturing it means trading the illiquid names that cause it</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P69"/>
+  <autoFilter ref="A1:P80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:P85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6732,8 +6732,400 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Price forecast</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid ARIMA+LSTM (Zhang 2003)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + HNB</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>fixed 80/20 + 7 walk-forward folds</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>ARIMA(2,1,0) + LSTM on residuals</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>one-step-ahead, rolling ARIMA state</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Theil U2 (fixed split)</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N81" s="4" t="inlineStr">
+        <is>
+          <t>Hybrid built properly (Y=L+N, LSTM on ARIMA residuals, 3 seeds averaged) and it does NOT beat the naive random walk. SPSL20 U2=1.012, HNB U2=1.005. Marginally WORSE than plain ARIMA on both targets.</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>results/hybrid_comparable/hybrid_summary.md</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>hybrid_arima_lstm_macro_news.py; supervisor-committed architecture, now tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Price forecast</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid + macro + news (extension)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + HNB</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>fixed 80/20 + 7 walk-forward folds</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>ARIMA + LSTM on residuals WITH exogenous macro/news</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>one-step-ahead</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Folds better than naive (HNB)</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0 of 7</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>THE PROJECT'S EXTENSION: macro+news fed into the residual model - the part ARIMA provably cannot explain. It makes things WORSE. SPSL20 U2 1.032, HNB U2 1.011, HNB walk-forward 0/7 folds.</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>hybrid_walkforward_table.csv</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>best place to put macro if it carried information; it does not</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Diebold-Mariano + Theil U added</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + HNB</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>fixed 80/20</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>DM test (Newey-West HAC) + Theil U2</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>forecast comparison</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Models significantly better than naive</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>0 of 8</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>COMPARABILITY GAP CLOSED. Papers claim superiority with the DM test; this project had only baseline-relative edge. DM run vs naive AND vs ARIMA: ZERO models significant at p&lt;0.05. Only 1 of 8 has Theil U2&lt;1.</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>hybrid_fixed_split_table.csv</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>the standard test reviewers expect; previously missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>R-squared on price levels is meaningless</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + HNB</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>fixed 80/20</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>all models incl. naive</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>descriptive</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>R2 of the NAIVE model</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0.9979</v>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M84" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>IMPORTANT FOR THE WRITE-UP: every model scores R2 0.9977-0.9980 - INCLUDING the naive random walk. Papers reporting R2~0.99 on price levels are reporting nothing. R2 on a level only measures being in the right magnitude.</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>hybrid_fixed_split_table.csv</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>direct rebuttal to a common claim in this literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Fixed split vs walk-forward disagreement</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + HNB</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>both protocols, same models</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>ARIMA / LSTM / Hybrid</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>one-step-ahead</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>ARIMA SPSL20 U2 (fixed vs WF)</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>1.005 vs 0.985</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M85" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>The two protocols DISAGREE: ARIMA is worse than naive on the SPSL20 fixed split (6/7 folds better in walk-forward), and the reverse pattern on HNB. Reporting only one protocol would mislead - hence both are published.</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>hybrid_all_results.csv</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>4th demonstration that the test window drives the result</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P80"/>
+  <autoFilter ref="A1:P85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P85"/>
+  <dimension ref="A1:P103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7124,8 +7124,1424 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Sector composite autocorrelation</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>BANKS/FINANCE/SECTOR composites</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>full sample</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>lag-1 autocorrelation</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>descriptive</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Composite vs constituent autocorr</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>BANKS +0.178 vs ~0.07</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M86" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>Averaging HELPS for banks (composite 0.178 &gt; every constituent) but FAILS for finance (0.017 - constituents have negative autocorrs that cancel). Mixing them is worse (0.078). SYSTEM DESIGN: build a BANKS index, not a banks+finance index.</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>results/sector_direction/autocorrelation.csv</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>sector_direction.py; the '6x more predictable' estimate was too strong - 1.2x on average</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Sector direction (the product target)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>BANKS/FINANCE/SECTOR composites</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>19 walk-forward 6-month folds</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>direct, h=1/5/10/22, binary + 3-class</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Configurations beating baseline</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>0 of 24</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>majority / persistence</t>
+        </is>
+      </c>
+      <c r="M87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>The target the SYSTEM actually predicts, never tested before. Sector-level direction is NOT predictable on plain accuracy at any horizon or grouping. Leak scan clean.</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>results/sector_direction/sector_direction_summary.md</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>sector_direction.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Magnitude edge on BANKS composite</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>BANKS composite</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>19 walk-forward folds, binary</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>|return|-weighted accuracy</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>Weighted edge 1d/1wk/2wk (pp)</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>+10.2 / +8.1 / +11.5</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>THIRD independent replication of the magnitude edge (after single stocks and pooled panel). Consistent across 4 horizons, 14-15 of 19 folds each, while plain accuracy edge is NEGATIVE. Product: flag big-move periods, do not emit daily direction calls.</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>sector_direction_all.csv</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>3-class magnitude figures (+34/+39pp) are INFLATED by a degenerate weighted-majority baseline - use the binary ones</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>PROBABILITY CALIBRATION (product-critical)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>BANKS + SECTOR composites</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>19 walk-forward folds, calibrator fitted inside training window only</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Logistic/XGBoost x raw/Platt/isotonic</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>binary, h=5/10/22</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>Configurations usable (skill&gt;0 &amp; ECE&lt;0.10)</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>0 of 36</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>climatology (base rate)</t>
+        </is>
+      </c>
+      <c r="M89" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>THE DASHBOARD CANNOT SHOW A MODEL CONFIDENCE NUMBER. Every Brier skill score is NEGATIVE; AUC 0.41-0.56 = coin flip. Calibration cannot fix a model that cannot rank.</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>results/sector_calibration/calibration_summary.md</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>sector_calibration.py; sklearn 1.9 removed cv='prefit', FrozenEstimator required</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Calibration removes error by removing information</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>BANKS + SECTOR composites</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>19 walk-forward folds</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Platt vs raw probabilities</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>prob_std Platt vs raw</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0.012-0.054 vs 0.164-0.232</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>Platt roughly HALVES calibration error by collapsing the forecast to near-constant. A model that says '54%' every day is perfectly calibrated and useless - no resolution. Calibration alone is not evidence of a usable forecast.</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>calibration_all_folds.csv</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>product answer: replace model confidence with a realised track record</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>News isolated - macro removed</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>BANKS composite + S&amp;P SL 20</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>6 walk-forward folds, 2016-2022 (news window)</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Logistic + XGBoost</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>direct, h=1/5/10, P vs P+N</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Horizons where news helps</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>0 of 6</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>CLEAN ISOLATION TEST. In Phase H news competed with ~30 other columns incl. macro, which Phase C showed can actively hurt. Stripped back to price+news only: news gain -1.25 to +2.60pp, nothing significant. Macro was NOT masking news.</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>results/price_news_hybrid/news_gain.csv</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>price_news_hybrid.py; window 2016-2022 not comparable to other phases</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Price forecast</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid + news, no macro</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>BANKS composite + S&amp;P SL 20</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>6 walk-forward folds</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>naive / ARIMA(2,1,0) / Hybrid / Hybrid+News</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>one-step-ahead</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Theil U2 (Hybrid+News, BANKS)</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>1.0003</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>Adding news to the hybrid makes it WORSE on both targets (BANKS 0.989-&gt;1.000, SPSL20 0.987-&gt;1.017). Plain ARIMA is the best model in the table and even it is not significant (DM p=0.30/0.46). Simplest wins again.</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>results/price_news_hybrid/price_summary.csv</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>supports cutting BOTH the news and hybrid stages from the production system</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Data quality</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>LEAK #4 - SPSL20 calendar vs ASPI (again)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>feature vs same-day and next-day return</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>correlation audit</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>leak detection</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>corr with next-day vs same-day</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="M93" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>The 'clean' SPSL20 file DELETED every flat day, misaligning it against ASPI (352 of 1505 rows drop). Removing .ffill() was NOT enough. Faked 82.8% accuracy / +20.7pp edge; a trivial 'copy sign of ASPI' rule scored 84.3%. Fixed by using the ASPI-calendar SPSL20 file AND dropping ASPI features for index targets.</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>results/price_news_hybrid/leak_scan.csv</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>corrected result: 56.8% accuracy, -5.5pp edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Leak guard now HALTS the run</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>all targets</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>every feature set</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>automated leak scan</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>guard</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Runs aborted on leak detection</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>1 of 1</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>The guard previously only wrote a CSV and the run continued, reporting a fake +20.7pp edge while the summary line claimed 'clean'. A guard that does not stop the run is not a guard. Now raises SystemExit.</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>price_news_hybrid.py</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>4th leak caught in this project; all four flattered the model</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Late fusion (one model per source)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>BANKS composite + HNB</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>6 walk-forward folds, chronological base/meta split</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>XGBoost bases + Logistic meta-learner</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>stacking, h=1/5/10</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Configurations beating baseline</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>0 of 6</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>majority / persistence</t>
+        </is>
+      </c>
+      <c r="M95" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>ARCHITECTURE WAS NOT THE CONSTRAINT. Separate models for price/news/macro combined by a meta-learner: 0/6 beat the baseline. Late fusion IS less bad than early fusion (better in 5/6) but beats it significantly in only 1/6 = chance.</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>results/late_fusion/late_fusion_summary.md</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>late_fusion_stacking.py; meta-learner trained on OUT-OF-FOLD base predictions</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Meta-learner weight allocation</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>BANKS composite + HNB</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>6 walk-forward folds</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Logistic meta-learner on 3 base models</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>stacking</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Median weight share price/news/macro</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>29% / 38% / 33%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>CLEANEST VERSION OF THE CENTRAL FINDING. A model free to weight the three sources however it likes splits ~1/3 each and leans MOST on news. If price carried signal and news did not, it would load onto price. Even allocation = nothing to prefer.</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>results/late_fusion/meta_weights_summary.csv</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>resolves the ambiguous early-fusion result (high importance, zero gain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Early vs late fusion ruled out as explanation</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>BANKS composite + HNB</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>identical folds, both architectures</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>early (concatenated) vs late (stacked)</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Late beats early significantly</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>1 of 6</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M97" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>Rules out one candidate explanation for why published papers report gains: 'early fusion drowned the weak signals'. Giving news and macro dedicated models surfaces nothing. Still open: missing naive baselines, no publication lag, single favourable split, decomposition hybrids.</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>late_fusion_folds.csv</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>late_fusion_stacking.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Reproduce-then-break ladder</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>L0 paper-style -&gt; L3 walk-forward, one guard at a time</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Ridge + XGBoost (best reported)</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>next-day price</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>L0 'macro improvement' %</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>+0.17 / -0.04</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>REPRODUCTION FAILED - and that is the finding. Removing the publication lag, leaking the scaler and using a single split move the number by FRACTIONS OF A PERCENT. These three shortcuts are NOT the mechanism behind published macro gains.</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>results/reproduce_then_break/ladder_summary.md</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>reproduce_then_break.py; hypothesis was wrong, reported as such</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>The likely real mechanism: no naive baseline</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>all ladder levels</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>all configs incl. naive</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>next-day price</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>R2 across every level</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0.9979</v>
+      </c>
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N99" s="4" t="inlineStr">
+        <is>
+          <t>R2 is 0.9978-0.9984 at EVERY level for EVERY config - and naive scores 0.9979. A paper running this exact setup would truthfully report 'R2=0.998, MAPE=0.83%, outperforms benchmark'. The gain is model-vs-weaker-model, reported with metrics that cannot distinguish either from a random walk.</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>ladder_summary.csv</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>DM p = 0.48-0.86 throughout; nothing significant</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Single split is the shortcut that matters most</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>L0-L2 single split vs L3 walk-forward</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Ridge + XGBoost</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>next-day price</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>MAPE(macro)/MAPE(naive)</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>0.96-0.98 -&gt; 1.027</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="M100" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>Under single-split levels price+macro sits BELOW naive (0.964-0.980); under walk-forward it crosses ABOVE 1.0 on both targets. Of the three shortcuts tested, the single split changes the conclusion; the other two do not. 4th confirmation of the window effect.</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>ladder_all.csv</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>argues for walk-forward as the default reporting protocol</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>DECOMPOSITION LEAK - the mechanism found</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>fixed 80/20, identical model/data, only pipeline ORDER differs</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>wavelet(db4,3) + CEEMDAN -&gt; Ridge/XGBoost</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>one-step-ahead price</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Improvement over naive: leaky vs honest</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>+19.2% vs -6.9%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>★ THE MECHANISM. Decomposing the FULL series BEFORE splitting creates a 13-26pp improvement out of nothing. Wavelet/CEEMDAN are GLOBAL transforms: component values at time t are computed from the whole series, so training components carry test-period information and test components were built from their own future.</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>results/decomposition_leak/decomposition_summary.md</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>decomposition_leak_test.py; explains the gap between published hybrid results and this project</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Leaky decomposition is highly significant</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>fixed 80/20</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>wavelet + CEEMDAN, leaky pipeline</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>one-step-ahead price</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>DM p vs naive (4 configs)</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>0.0000-0.0199</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M102" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N102" s="4" t="inlineStr">
+        <is>
+          <t>ALL FOUR leaky configurations beat naive significantly (Theil U2 0.794-0.871, DM p&lt;0.02, two at p&lt;0.0001). These are exactly the numbers decomposition-hybrid papers report.</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>decomposition_results.csv</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>the result is real as computed - it is the pipeline that is wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Honest decomposition loses to naive</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>fixed 80/20, decompose only series[:t] at each t</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>wavelet + CEEMDAN, honest pipeline</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>one-step-ahead price</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Theil U2 (4 configs)</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>1.008-1.028</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M103" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N103" s="4" t="inlineStr">
+        <is>
+          <t>Same models, same data, decomposition restricted to past data only: ALL FOUR configs are WORSE than a random walk and none significant (DM p 0.35-0.84). The decomposition advantage does not survive an honest pipeline.</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>decomposition_results.csv</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>honest CEEMDAN re-decomposes every 3rd point for runtime; wavelet every point</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P85"/>
+  <autoFilter ref="A1:P103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P103"/>
+  <dimension ref="A1:P105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2383,12 +2383,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Multi-horizon</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Phase A multi-horizon direction</t>
+          <t>MH ARIMAX/RF/CNN-LSTM</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2403,52 +2403,52 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge</t>
+          <t>80/20 direct, 11 horizons</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>ARIMAX / RandomForest / CNN-LSTM</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons (1d-252d)</t>
+          <t>direction + price %</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Horizons beating baseline</t>
+          <t>dir acc / price MAPE</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0 of 9</t>
+          <t>see CSV</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>majority / persistence</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>NO EDGE AT ANY HORIZON. Best model always below best baseline; gap widens with horizon (-3.5pp @1d -&gt; -47.1pp @1yr) because long-horizon drift makes the dumb baseline huge (maj 78% @6mo, pers 77% @1yr).</t>
+          <t>No model beats naive on DIRECTION (long-horizon 'up'=trend). ARIMAX small PRICE edge at 1-6mo. Caught+fixed ARIMAX leak.</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>results/direction/multi_horizon/mh_summary.md</t>
+          <t>results/mh_models/HNB_results.csv</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>direction_multi_horizon.py; Tier-1 only; dead-zone +/-0.5%*sqrt(h)</t>
+          <t>mh_multimodel.py HNB</t>
         </is>
       </c>
     </row>
@@ -2458,22 +2458,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Multi-horizon</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Phase A best single horizon</t>
+          <t>MH ARIMAX/RF/CNN-LSTM</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>HNB</t>
+          <t>JKH</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2483,48 +2483,52 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge</t>
+          <t>80/20 direct, 11 horizons</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Logistic</t>
+          <t>ARIMAX / RandomForest / CNN-LSTM</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>direct, h=22d (1 month)</t>
+          <t>direction + price %</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Accuracy %</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>dir acc / price MAPE</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>see CSV</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Best model result of the sweep (1-month Logistic 40.1%) still loses to persistence 42.1%. Logistic &gt; XGBoost at every horizon -&gt; no nonlinear structure to find.</t>
+          <t>Non-bank (John Keells). PRICE: ARIMAX lowest MAPE at 1mo-3mo (4.1/7.1/9.7 vs naive 5.7/8.9/10.4) then loses at 6mo-1yr. Short 1d-5d nobody beats naive (~1-2.4%). CNN-LSTM noisy/worst. DIRECTION: RF best but marginal; naive huge at long horizon (81% @6mo=uptrend). Error grows 1%@1d -&gt; ~14-16%@1yr.</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>mh_direction_table.csv</t>
+          <t>results/mh_models/JKH_results.csv + JKH_decay_chart.png</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>edge -2.0pp</t>
+          <t>mh_multimodel.py JKH; mh_decay_chart.py JKH</t>
         </is>
       </c>
     </row>
@@ -2539,12 +2543,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Phase A multi-horizon return %</t>
+          <t>Phase A multi-horizon direction</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2564,7 +2568,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2574,33 +2578,37 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>RMSE ratio vs train-mean</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>Tie</t>
+          <t>Horizons beating baseline</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0 of 9</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>majority / persistence</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>Ridge beats naive-0 at 8/9 horizons BUT is only ~1% better than train-mean drift -&gt; it learned drift, NOT signal. XGBoost worse than naive everywhere (ratio 1.01-1.14).</t>
+          <t>NO EDGE AT ANY HORIZON. Best model always below best baseline; gap widens with horizon (-3.5pp @1d -&gt; -47.1pp @1yr) because long-horizon drift makes the dumb baseline huge (maj 78% @6mo, pers 77% @1yr).</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>mh_return_table.csv</t>
+          <t>results/direction/multi_horizon/mh_summary.md</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>train-mean is the honest null, not naive-0</t>
+          <t>direction_multi_horizon.py; Tier-1 only; dead-zone +/-0.5%*sqrt(h)</t>
         </is>
       </c>
     </row>
@@ -2615,12 +2623,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Phase A return sign accuracy</t>
+          <t>Phase A best single horizon</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2640,28 +2648,24 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Logistic</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>direct, sign of h-day return</t>
+          <t>direct, h=22d (1 month)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Horizons beating sign null</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2 of 9</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>always-guess-winning-side</t>
-        </is>
+          <t>Accuracy %</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>42.1</v>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
@@ -2670,17 +2674,17 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>TRAP CHECK: 55-57% sign accuracy @1-3mo looks like the 52-58% target but 'always guess up' matches/beats it (test window drifted up 59-95%). Both 'wins' are +0.2pp = noise.</t>
+          <t>Best model result of the sweep (1-month Logistic 40.1%) still loses to persistence 42.1%. Logistic &gt; XGBoost at every horizon -&gt; no nonlinear structure to find.</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>mh_edge_vs_horizon.png</t>
+          <t>mh_direction_table.csv</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>up-share null added to stop false positive</t>
+          <t>edge -2.0pp</t>
         </is>
       </c>
     </row>
@@ -2695,12 +2699,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Phase B ablation (+Tier-2)</t>
+          <t>Phase A multi-horizon return %</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2715,48 +2719,48 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds, A vs B</t>
+          <t>80/20 chrono + h-bar purge</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, ablation</t>
+          <t>direct, 9 horizons (1d-252d)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from Tier-2 (pp)</t>
+          <t>RMSE ratio vs train-mean</t>
         </is>
       </c>
       <c r="K29" s="2" t="n">
-        <v>-0.9</v>
+        <v>0.99</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>1</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Tie</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>RSI+MACD+volume add NOTHING. Mean -0.9pp, 0/9 beat baseline. Technical indicators exhausted.</t>
+          <t>Ridge beats naive-0 at 8/9 horizons BUT is only ~1% better than train-mean drift -&gt; it learned drift, NOT signal. XGBoost worse than naive everywhere (ratio 1.01-1.14).</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>results/direction/phase_ablation/ablation_summary.md</t>
+          <t>mh_return_table.csv</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_ablation.py; 9 -&gt; 16 features; value restated on the 4-phase run (macro availability trims early rows)</t>
+          <t>train-mean is the honest null, not naive-0</t>
         </is>
       </c>
     </row>
@@ -2771,12 +2775,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Phase B feature attention check</t>
+          <t>Phase A return sign accuracy</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2791,50 +2795,52 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>80/20 chrono + h-bar purge</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>XGBoost importance</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, sign of h-day return</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Tier-2 share of importance %</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>41</v>
+          <t>Horizons beating sign null</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2 of 9</t>
+        </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M30" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>always-guess-winning-side</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>XGBoost spends 41% of importance on Tier-2 (macd_signal is top feature at 6/9 horizons) yet accuracy does not improve -&gt; the model USES them but they carry no signal.</t>
+          <t>TRAP CHECK: 55-57% sign accuracy @1-3mo looks like the 52-58% target but 'always guess up' matches/beats it (test window drifted up 59-95%). Both 'wins' are +0.2pp = noise.</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ablation_tier2_importance.csv</t>
+          <t>mh_edge_vs_horizon.png</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>strong evidence indicators are redundant with price</t>
+          <t>up-share null added to stop false positive</t>
         </is>
       </c>
     </row>
@@ -2849,12 +2855,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Phase B return % (+Tier-2)</t>
+          <t>Phase B ablation (+Tier-2)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2869,48 +2875,48 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>identical rows/split/seeds, A vs B</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, 9 horizons, ablation</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>RMSE ratio vs train-mean (B)</t>
+          <t>Mean gain from Tier-2 (pp)</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.991</v>
+        <v>-0.9</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>Tie</t>
+        <v>0</v>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>Tier-2 made return RMSE slightly WORSE at 9/9 horizons (ratio gain +0.000 to +0.046). Sign edge stays negative everywhere.</t>
+          <t>RSI+MACD+volume add NOTHING. Mean -0.9pp, 0/9 beat baseline. Technical indicators exhausted.</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ablation_return_table.csv</t>
+          <t>results/direction/phase_ablation/ablation_summary.md</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>A ratio 0.991 -&gt; B ratio 0.991-1.034</t>
+          <t>direction_phase_ablation.py; 9 -&gt; 16 features; value restated on the 4-phase run (macro availability trims early rows)</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2936,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Phase C ablation (+macro rates)</t>
+          <t>Phase B feature attention check</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2945,48 +2951,50 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds, 35d publication lag</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>XGBoost importance</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, ablation</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from macro (pp)</t>
+          <t>Tier-2 share of importance %</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>41</v>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Macro rates make it WORSE and unstable: gain swings -22.3 to +10.3 pp, 0/9 beat baseline. Not weak signal - overfitting.</t>
+          <t>XGBoost spends 41% of importance on Tier-2 (macd_signal is top feature at 6/9 horizons) yet accuracy does not improve -&gt; the model USES them but they carry no signal.</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>results/direction/phase_ablation/ablation_summary.md</t>
+          <t>ablation_tier2_importance.csv</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_ablation.py; 16 -&gt; 29 features; inflation/FX/M2 still uncollected</t>
+          <t>strong evidence indicators are redundant with price</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3009,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Phase C2 diagnostic (macro changes only)</t>
+          <t>Phase B return % (+Tier-2)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3026,43 +3034,43 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, ablation</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from macro d (pp)</t>
+          <t>RMSE ratio vs train-mean (B)</t>
         </is>
       </c>
       <c r="K33" s="2" t="n">
-        <v>3.4</v>
+        <v>0.991</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="M33" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.991</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Tie</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>DROPPING RATE LEVELS FIXES THE DAMAGE (-2.8 -&gt; +3.4 pp; 1yr 4.5% -&gt; 49.7%). Non-stationary levels were being memorised. Still 0/9 beat baseline -&gt; form was wrong AND no signal.</t>
+          <t>Tier-2 made return RMSE slightly WORSE at 9/9 horizons (ratio gain +0.000 to +0.046). Sign edge stays negative everywhere.</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ablation_gain_table.csv</t>
+          <t>ablation_return_table.csv</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>key methodology lesson: feed macro as changes, never levels</t>
+          <t>A ratio 0.991 -&gt; B ratio 0.991-1.034</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3090,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Phase C feature attention check</t>
+          <t>Phase C ablation (+macro rates)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3097,50 +3105,48 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>identical rows/split/seeds, 35d publication lag</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>XGBoost importance</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, 9 horizons, ablation</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Macro share of importance %</t>
+          <t>Mean gain from macro (pp)</t>
         </is>
       </c>
       <c r="K34" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M34" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>-2.8</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>Macro importance rises 46% (1d) -&gt; 80% (1yr) while accuracy FALLS. Model fits rates as a trend proxy, not signal. tb_12m/spread/policy_rate are top features at 8/9 horizons.</t>
+          <t>Macro rates make it WORSE and unstable: gain swings -22.3 to +10.3 pp, 0/9 beat baseline. Not weak signal - overfitting.</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ablation_feature_importance.csv</t>
+          <t>results/direction/phase_ablation/ablation_summary.md</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>fingerprint of trending-variable overfit</t>
+          <t>direction_phase_ablation.py; 16 -&gt; 29 features; inflation/FX/M2 still uncollected</t>
         </is>
       </c>
     </row>
@@ -3155,12 +3161,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Phase C return % (+macro)</t>
+          <t>Phase C2 diagnostic (macro changes only)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3180,43 +3186,43 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, 9 horizons, ablation</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>RMSE ratio vs train-mean (C)</t>
+          <t>Mean gain from macro d (pp)</t>
         </is>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1.37</v>
+        <v>3.4</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>-2.8</v>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>Macro blows out return RMSE to 1.29-1.37x the train-mean null (A/B sat at ~0.99). Clear damage, confirms the overfit reading.</t>
+          <t>DROPPING RATE LEVELS FIXES THE DAMAGE (-2.8 -&gt; +3.4 pp; 1yr 4.5% -&gt; 49.7%). Non-stationary levels were being memorised. Still 0/9 beat baseline -&gt; form was wrong AND no signal.</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ablation_return_table.csv</t>
+          <t>ablation_gain_table.csv</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>worst at 2-3 month horizons</t>
+          <t>key methodology lesson: feed macro as changes, never levels</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3242,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Phase D ablation (+sector)</t>
+          <t>Phase C feature attention check</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3256,43 +3262,45 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>XGBoost importance</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, ablation</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from sector (pp)</t>
+          <t>Macro share of importance %</t>
         </is>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>64</v>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>FIRST consistently POSITIVE step: +2.6pp mean, positive at 6/9 horizons. Built on C2 (macro changes only). But still 0/9 beat baseline.</t>
+          <t>Macro importance rises 46% (1d) -&gt; 80% (1yr) while accuracy FALLS. Model fits rates as a trend proxy, not signal. tb_12m/spread/policy_rate are top features at 8/9 horizons.</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>results/direction/phase_ablation/ablation_summary.md</t>
+          <t>ablation_feature_importance.csv</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_ablation.py; C2 16+7 -&gt; D 39 features; ASPI + COMB/SAMP + LOFC/LOLC/LFIN/CFIN</t>
+          <t>fingerprint of trending-variable overfit</t>
         </is>
       </c>
     </row>
@@ -3307,12 +3315,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Phase D best single horizon</t>
+          <t>Phase C return % (+macro)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3332,24 +3340,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>direct, h=5d (1 week)</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Edge over baseline (pp)</t>
+          <t>RMSE ratio vs train-mean (C)</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>-0.2</v>
+        <v>1.37</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>0.995</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
@@ -3358,17 +3366,17 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>Closest call of the whole study: 1-week Phase D 37.3% vs baseline 37.4%. Near-parity at short horizons (1d -1.7, 1wk -0.2, 2wk -1.6) but never crosses.</t>
+          <t>Macro blows out return RMSE to 1.29-1.37x the train-mean null (A/B sat at ~0.99). Clear damage, confirms the overfit reading.</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ablation_gain_table.csv</t>
+          <t>ablation_return_table.csv</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>not a win; single split, one stock</t>
+          <t>worst at 2-3 month horizons</t>
         </is>
       </c>
     </row>
@@ -3383,12 +3391,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Phase D return sign edge (+sector)</t>
+          <t>Phase D ablation (+sector)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3408,47 +3416,43 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>direct, sign of h-day return</t>
+          <t>direct, 9 horizons, ablation</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Sign edge 1wk/2wk/3wk (pp)</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>+1.7 / +1.7 / +1.1</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>always-guess-winning-side</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>Tie</t>
+          <t>Mean gain from sector (pp)</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>First POSITIVE sign edges in the study, and at 3 adjacent horizons (1-3 weeks). Tiny (~1-2pp) and one split only -&gt; flag as worth re-testing, NOT a finding.</t>
+          <t>FIRST consistently POSITIVE step: +2.6pp mean, positive at 6/9 horizons. Built on C2 (macro changes only). But still 0/9 beat baseline.</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ablation_return_table.csv</t>
+          <t>results/direction/phase_ablation/ablation_summary.md</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>check on other tickers before claiming anything</t>
+          <t>direction_phase_ablation.py; C2 16+7 -&gt; D 39 features; ASPI + COMB/SAMP + LOFC/LOLC/LFIN/CFIN</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3472,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Phase D feature attention check</t>
+          <t>Phase D best single horizon</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3488,45 +3492,43 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>XGBoost importance</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, h=5d (1 week)</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Sector share of importance %</t>
+          <t>Edge over baseline (pp)</t>
         </is>
       </c>
       <c r="K39" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>-0.2</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>Sector takes 34% avg (42% at 1 day, falling to 27% at 1yr) - mirror image of macro, which rises with horizon. Sector matters short, macro long, neither enough.</t>
+          <t>Closest call of the whole study: 1-week Phase D 37.3% vs baseline 37.4%. Near-parity at short horizons (1d -1.7, 1wk -0.2, 2wk -1.6) but never crosses.</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ablation_feature_importance.csv</t>
+          <t>ablation_gain_table.csv</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>vol_20 is top feature at 1d/1wk; d_tb3m dominates long</t>
+          <t>not a win; single split, one stock</t>
         </is>
       </c>
     </row>
@@ -3541,17 +3543,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Sector sweep - replication test</t>
+          <t>Phase D return sign edge (+sector)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks (3 banks, 4 finance, 4 control)</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3561,52 +3563,52 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge, per stock</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, sign of h-day return</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Cells beating baseline</t>
+          <t>Sign edge 1wk/2wk/3wk (pp)</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>27 of 99</t>
+          <t>+1.7 / +1.7 / +1.1</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>14 of 99 (Phase A)</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>always-guess-winning-side</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Tie</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>Sector features nearly DOUBLE the win rate vs Tier-1 (14-&gt;27 of 99) but wins sit at exactly coin-flip at short horizons and collapse at long ones. No real edge.</t>
+          <t>First POSITIVE sign edges in the study, and at 3 adjacent horizons (1-3 weeks). Tiny (~1-2pp) and one split only -&gt; flag as worth re-testing, NOT a finding.</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>results/direction/sector_sweep/sweep_summary.md</t>
+          <t>ablation_return_table.csv</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>direction_sector_sweep.py; peer composites exclude the target stock</t>
+          <t>check on other tickers before claiming anything</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3628,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Sector gain replication (HNB claim 3)</t>
+          <t>Phase D feature attention check</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3641,29 +3643,31 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>identical protocol per stock</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Phase D - Phase A</t>
+          <t>XGBoost importance</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Mean sector gain (pp)</t>
+          <t>Sector share of importance %</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -3672,17 +3676,17 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>REPLICATES: +3.8pp mean, positive in 66/99 cells (67%), 9 of 11 stocks positive. HNB was not a fluke - sector context genuinely helps the model. Best: LFIN +13.2, SAMP +9.4, LOFC +8.2. Worst: CTC -11.0.</t>
+          <t>Sector takes 34% avg (42% at 1 day, falling to 27% at 1yr) - mirror image of macro, which rises with horizon. Sector matters short, macro long, neither enough.</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>sweep_gain_by_ticker.csv</t>
+          <t>ablation_feature_importance.csv</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>helping is not the same as winning</t>
+          <t>vol_20 is top feature at 1d/1wk; d_tb3m dominates long</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3706,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Sector sweep significance screen</t>
+          <t>Sector sweep - replication test</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>11 CSE stocks (3 banks, 4 finance, 4 control)</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3717,29 +3721,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>sign test + Wilcoxon across stocks, per horizon</t>
+          <t>80/20 chrono + h-bar purge, per stock</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>binomial sign test (H0 p=0.5)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Best sign-test p</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0.05</v>
+          <t>Cells beating baseline</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>27 of 99</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>14 of 99 (Phase A)</t>
+        </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
@@ -3748,17 +3756,17 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>NOTHING SIGNIFICANT AT ANY HORIZON. Best cells (1 day, 1 week) are 6/11 stocks positive = p=0.500, exactly a coin flip. Long horizons far worse (1yr 0/11).</t>
+          <t>Sector features nearly DOUBLE the win rate vs Tier-1 (14-&gt;27 of 99) but wins sit at exactly coin-flip at short horizons and collapse at long ones. No real edge.</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>sweep_significance.csv</t>
+          <t>results/direction/sector_sweep/sweep_summary.md</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>stocks share a market factor so p-values are already optimistic</t>
+          <t>direction_sector_sweep.py; peer composites exclude the target stock</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3786,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>HNB sign-edge claim retest (claim 2)</t>
+          <t>Sector gain replication (HNB claim 3)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3798,47 +3806,43 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Phase D - Phase A</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>direct, sign of h-day return, 1-3 week horizons</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Cells with positive sign edge</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>6 of 33</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>~17 of 33 (coin flip)</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Mean sector gain (pp)</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>REFUTED. HNB's positive 1-3 week sign edge did NOT replicate - 18% vs the ~50% chance would give. It was luck. Flagged as provisional when found, now closed.</t>
+          <t>REPLICATES: +3.8pp mean, positive in 66/99 cells (67%), 9 of 11 stocks positive. HNB was not a fluke - sector context genuinely helps the model. Best: LFIN +13.2, SAMP +9.4, LOFC +8.2. Worst: CTC -11.0.</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>sweep_all_results.csv</t>
+          <t>sweep_gain_by_ticker.csv</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>value of naming a claim before retesting it</t>
+          <t>helping is not the same as winning</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3862,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Phase E - daily USD/LKR</t>
+          <t>Sector sweep significance screen</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3873,29 +3877,29 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge, 2015-2026 window</t>
+          <t>sign test + Wilcoxon across stocks, per horizon</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>binomial sign test (H0 p=0.5)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from daily FX (pp)</t>
+          <t>Best sign-test p</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
@@ -3904,17 +3908,17 @@
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>FREQUENCY WAS NOT THE PROBLEM. Daily FX gain is exactly 0.0pp (positive in 57/99 cells = coin flip). Macro fails daily exactly as it failed monthly.</t>
+          <t>NOTHING SIGNIFICANT AT ANY HORIZON. Best cells (1 day, 1 week) are 6/11 stocks positive = p=0.500, exactly a coin flip. Long horizons far worse (1yr 0/11).</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>results/direction/daily_macro/daily_macro_summary.md</t>
+          <t>sweep_significance.csv</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>direction_daily_macro.py; new cleaned_data/usd_lkr_daily.csv</t>
+          <t>stocks share a market factor so p-values are already optimistic</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3938,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Phase E2 - daily global + CPI</t>
+          <t>HNB sign-edge claim retest (claim 2)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3949,29 +3953,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>identical protocol per stock</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, sign of h-day return, 1-3 week horizons</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from global+CPI (pp)</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>Cells with positive sign edge</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>6 of 33</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>~17 of 33 (coin flip)</t>
+        </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
@@ -3980,17 +3988,17 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>Oil, US 10Y, DXY and inflation make it WORSE (-1.9pp), worst at long horizons (-6.0pp at 1yr). Same trending-variable overfit as Phase C.</t>
+          <t>REFUTED. HNB's positive 1-3 week sign edge did NOT replicate - 18% vs the ~50% chance would give. It was luck. Flagged as provisional when found, now closed.</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>daily_macro_gain.csv</t>
+          <t>sweep_all_results.csv</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>CPI spliced across 4 base years; money supply excluded (ends 2024-08, inside test window)</t>
+          <t>value of naming a claim before retesting it</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4018,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Phase E significance screen</t>
+          <t>Phase E - daily USD/LKR</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4025,31 +4033,29 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>sign test across stocks, 4 phases x 9 horizons</t>
+          <t>80/20 chrono + h-bar purge, 2015-2026 window</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>binomial sign test (H0 p=0.5)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Combinations with p&lt;0.05</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>0 of 36</t>
-        </is>
+          <t>Mean gain from daily FX (pp)</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
@@ -4058,17 +4064,17 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>NOTHING SIGNIFICANT ANYWHERE. Best cell is 1 day (6/11 stocks, p=0.500) - exact coin flip, same as the sector sweep. Cells beating baseline: A 17, D 27, E 24, E2 25 of 99.</t>
+          <t>FREQUENCY WAS NOT THE PROBLEM. Daily FX gain is exactly 0.0pp (positive in 57/99 cells = coin flip). Macro fails daily exactly as it failed monthly.</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>daily_macro_significance.csv</t>
+          <t>results/direction/daily_macro/daily_macro_summary.md</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>macro information source now closed at both frequencies</t>
+          <t>direction_daily_macro.py; new cleaned_data/usd_lkr_daily.csv</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4094,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Phase E feature attention check</t>
+          <t>Phase E2 - daily global + CPI</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4108,7 +4114,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>XGBoost importance</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -4118,35 +4124,33 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>New-data share of importance %</t>
+          <t>Mean gain from global+CPI (pp)</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M47" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>-1.9</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>Model spends 27% of importance on the new data (FX 7%, global 11%, CPI 9%) and gains nothing - third time this fingerprint has appeared (Tier-2 41%, macro 64%, now 27%).</t>
+          <t>Oil, US 10Y, DXY and inflation make it WORSE (-1.9pp), worst at long horizons (-6.0pp at 1yr). Same trending-variable overfit as Phase C.</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>daily_macro_all_results.csv</t>
+          <t>daily_macro_gain.csv</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>using a feature is not the same as profiting from it</t>
+          <t>CPI spliced across 4 base years; money supply excluded (ends 2024-08, inside test window)</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4170,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Phase F - money supply (M1/M2/M2b/M4)</t>
+          <t>Phase E significance screen</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4181,29 +4185,31 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono, sample cut at 2024-08; test 2022-03 to 2024-08</t>
+          <t>sign test across stocks, 4 phases x 9 horizons</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>binomial sign test (H0 p=0.5)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from money supply (pp)</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>-0.7</v>
+          <t>Combinations with p&lt;0.05</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>0 of 36</t>
+        </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
@@ -4212,17 +4218,17 @@
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>Money supply adds NOTHING even on a crisis-era test window (positive in 50/99 cells = exact coin flip). Window moved back so M1/M2 could be tested fairly rather than excluded.</t>
+          <t>NOTHING SIGNIFICANT ANYWHERE. Best cell is 1 day (6/11 stocks, p=0.500) - exact coin flip, same as the sector sweep. Cells beating baseline: A 17, D 27, E 24, E2 25 of 99.</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>results/direction/money_supply/money_summary.md</t>
+          <t>daily_macro_significance.csv</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>direction_money_supply.py; 65-day publication lag per CBSL's own note; reserve money dropped (ends 2024-02)</t>
+          <t>macro information source now closed at both frequencies</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4248,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Phase F - full classic macro set</t>
+          <t>Phase E feature attention check</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4262,7 +4268,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>XGBoost importance</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -4272,33 +4278,35 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Mean gain money-&gt;full macro (pp)</t>
+          <t>New-data share of importance %</t>
         </is>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>27</v>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>Full classic set (money + rates + FX + inflation) = 4 of the 5 Naik-Padhi variables. Still 42/99 cells, below the money-only phase (51/99). Only industrial production remains uncollected.</t>
+          <t>Model spends 27% of importance on the new data (FX 7%, global 11%, CPI 9%) and gains nothing - third time this fingerprint has appeared (Tier-2 41%, macro 64%, now 27%).</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>money_gain.csv</t>
+          <t>daily_macro_all_results.csv</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>closes the macro chapter apart from IIP</t>
+          <t>using a feature is not the same as profiting from it</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4326,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Crisis-window effect (window sensitivity)</t>
+          <t>Phase F - money supply (M1/M2/M2b/M4)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4333,7 +4341,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2022-03 to 2024-08 vs 2024-2026</t>
+          <t>80/20 chrono, sample cut at 2024-08; test 2022-03 to 2024-08</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4348,37 +4356,33 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Cells beating baseline</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>43-51 of 99</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>17-27 of 99 (calm window)</t>
-        </is>
-      </c>
-      <c r="M50" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Mean gain from money supply (pp)</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>IMPORTANT METHOD FINDING: moving the test window into the 2022 crisis roughly DOUBLES the win rate for ALL phases including price-only. Results are window-dependent, not model-dependent.</t>
+          <t>Money supply adds NOTHING even on a crisis-era test window (positive in 50/99 cells = exact coin flip). Window moved back so M1/M2 could be tested fairly rather than excluded.</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>money_by_horizon.csv</t>
+          <t>results/direction/money_supply/money_summary.md</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>argues for walk-forward / multi-window evaluation in the write-up</t>
+          <t>direction_money_supply.py; 65-day publication lag per CBSL's own note; reserve money dropped (ends 2024-02)</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4402,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>1-day significance - macro ruled out</t>
+          <t>Phase F - full classic macro set</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4413,33 +4417,29 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>sign test across stocks, 4 phases x 9 horizons</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>binomial sign test (H0 p=0.5)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Cells with p&lt;0.05</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>2 of 36</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>1.8 expected by chance</t>
-        </is>
+          <t>Mean gain money-&gt;full macro (pp)</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
@@ -4448,17 +4448,17 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>Both hits are at 1 day, and the STRONGEST is Phase A (price only, 9/11, +3.9pp, p=0.033). Adding money supply SHRINKS it to +3.2pp. So it is the crisis window, not macro - and 2/36 is chance anyway.</t>
+          <t>Full classic set (money + rates + FX + inflation) = 4 of the 5 Naik-Padhi variables. Still 42/99 cells, below the money-only phase (51/99). Only industrial production remains uncollected.</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>money_significance.csv</t>
+          <t>money_gain.csv</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>checking the null model is what prevented a false claim</t>
+          <t>closes the macro chapter apart from IIP</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Phase G - industrial production (IIP)</t>
+          <t>Crisis-window effect (window sensitivity)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono, sample 2016-2026 (IIP coverage)</t>
+          <t>2022-03 to 2024-08 vs 2024-2026</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4508,33 +4508,37 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from IIP (pp)</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Cells beating baseline</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>43-51 of 99</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>17-27 of 99 (calm window)</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>IIP makes it WORSE (-6.4pp, positive in only 25/99 cells, 0/36 significant). It was the STRONGEST variable in the Naik-Padhi reference paper, and it still does not predict direction.</t>
+          <t>IMPORTANT METHOD FINDING: moving the test window into the 2022 crisis roughly DOUBLES the win rate for ALL phases including price-only. Results are window-dependent, not model-dependent.</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>results/direction/industrial_production/iip_summary.md</t>
+          <t>money_by_horizon.csv</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>direction_industrial_production.py; DCS index entered by hand, 2016-01 to 2026-05; 50-day publication lag</t>
+          <t>argues for walk-forward / multi-window evaluation in the write-up</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4548,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4554,7 +4558,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Phase G - full classic macro set complete</t>
+          <t>1-day significance - macro ruled out</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -4569,32 +4573,32 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>sign test across stocks, 4 phases x 9 horizons</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>binomial sign test (H0 p=0.5)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Cells beating baseline</t>
+          <t>Cells with p&lt;0.05</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>25 of 99</t>
+          <t>2 of 36</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>27 of 99 (no macro)</t>
+          <t>1.8 expected by chance</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
@@ -4604,17 +4608,17 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>ALL FIVE Naik-Padhi macro variables now tested (IIP, money supply, T-bill rate, exchange rate, inflation). NONE beats plain price history. Macro chapter complete.</t>
+          <t>Both hits are at 1 day, and the STRONGEST is Phase A (price only, 9/11, +3.9pp, p=0.033). Adding money supply SHRINKS it to +3.2pp. So it is the crisis window, not macro - and 2/36 is chance anyway.</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>iip_gain.csv</t>
+          <t>money_significance.csv</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>adding all macro is WORSE than sector-only (27/99)</t>
+          <t>checking the null model is what prevented a false claim</t>
         </is>
       </c>
     </row>
@@ -4629,72 +4633,68 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>IIP seasonality guard</t>
+          <t>Phase G - industrial production (IIP)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sri Lanka DCS IIP</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>monthly (125)</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>2016-01 to 2026-05</t>
+          <t>80/20 chrono, sample 2016-2026 (IIP coverage)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>seasonal inspection</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>April vs March gap (pts)</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>-10 to -34</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M54" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Mean gain from IIP (pp)</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>IIP is NOT seasonally adjusted - April falls 10-34 pts EVERY year (Sinhala/Tamil New Year), March always peaks. Month-on-month would be a calendar signal, so YoY-only features were used.</t>
+          <t>IIP makes it WORSE (-6.4pp, positive in only 25/99 cells, 0/36 significant). It was the STRONGEST variable in the Naik-Padhi reference paper, and it still does not predict direction.</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>cleaned_data/industrial_production_monthly.csv</t>
+          <t>results/direction/industrial_production/iip_summary.md</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>clean_macro_sources.py; mom column deliberately named _DO_NOT_USE</t>
+          <t>direction_industrial_production.py; DCS index entered by hand, 2016-01 to 2026-05; 50-day publication lag</t>
         </is>
       </c>
     </row>
@@ -4709,17 +4709,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Correlation</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Co-movement lift table (no model)</t>
+          <t>Phase G - full classic macro set complete</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks (22,677 stock-days)</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -4729,48 +4729,52 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>full panel, 15 indicators x 9 horizons</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>conditional probability + 2-proportion z</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Median |lift| short horizons (pp)</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Cells beating baseline</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>25 of 99</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>27 of 99 (no macro)</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>'If indicator up, does stock go up?' answered by pure counting. Market/peer indicators give a real +6 to +10pp lift at 1d-1mo on huge samples. Macro lifts are near zero at short horizons.</t>
+          <t>ALL FIVE Naik-Padhi macro variables now tested (IIP, money supply, T-bill rate, exchange rate, inflation). NONE beats plain price history. Macro chapter complete.</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>results/direction/pooled_rules/comovement_table.csv</t>
+          <t>iip_gain.csv</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>direction_pooled_and_rules.py; lift = P(up|ind up) - P(up|ind down)</t>
+          <t>adding all macro is WORSE than sector-only (27/99)</t>
         </is>
       </c>
     </row>
@@ -4785,72 +4789,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Correlation</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Co-movement - long-horizon lifts are artifacts</t>
+          <t>IIP seasonality guard</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>Sri Lanka DCS IIP</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly (125)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>panel, |lift|&gt;=10pp cells</t>
+          <t>2016-01 to 2026-05</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>independent-window audit</t>
+          <t>seasonal inspection</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Independent windows behind biggest lifts</t>
+          <t>April vs March gap (pts)</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>7-24</t>
+          <t>-10 to -34</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>hundreds needed</t>
-        </is>
-      </c>
-      <c r="M56" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>All 19 large lifts (T-bill -19.3, M2 +17.0, USD/LKR -15.3) sit at 3mo-1yr where only 7-24 INDEPENDENT windows exist. Overlapping windows inflate the z-test. Discard them.</t>
+          <t>IIP is NOT seasonally adjusted - April falls 10-34 pts EVERY year (Sinhala/Tamil New Year), March always peaks. Month-on-month would be a calendar signal, so YoY-only features were used.</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>comovement_table.csv</t>
+          <t>cleaned_data/industrial_production_monthly.csv</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>median |lift| long 4.2pp vs short 2.5pp is a sample-size illusion</t>
+          <t>clean_macro_sources.py; mom column deliberately named _DO_NOT_USE</t>
         </is>
       </c>
     </row>
@@ -4865,17 +4869,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Correlation</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Pooled panel model (sector-wide)</t>
+          <t>Co-movement lift table (no model)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks pooled</t>
+          <t>7 bank/finance stocks (22,677 stock-days)</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -4885,52 +4889,48 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>split by DATE not row, 17,770 train rows</t>
+          <t>full panel, 15 indicators x 9 horizons</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>conditional probability + 2-proportion z</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, one model for whole sector</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Horizons beating pooled baseline</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>2 of 9</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>majority / persistence</t>
-        </is>
-      </c>
-      <c r="M57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Median |lift| short horizons (pp)</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>7x more training data (17,770 vs ~2,700 per stock). Beats the POOLED baseline at 1 day (+3.3pp) and 1 week (+2.7pp) only.</t>
+          <t>'If indicator up, does stock go up?' answered by pure counting. Market/peer indicators give a real +6 to +10pp lift at 1d-1mo on huge samples. Macro lifts are near zero at short horizons.</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>results/direction/pooled_rules/pooled_model_results.csv</t>
+          <t>results/direction/pooled_rules/comovement_table.csv</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>direction_pooled_and_rules.py</t>
+          <t>direction_pooled_and_rules.py; lift = P(up|ind up) - P(up|ind down)</t>
         </is>
       </c>
     </row>
@@ -4945,12 +4945,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Correlation</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Pooled model fairness check</t>
+          <t>Co-movement - long-horizon lifts are artifacts</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>pooled model scored vs each stock's OWN baseline</t>
+          <t>panel, |lift|&gt;=10pp cells</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>binomial sign test (H0 p=0.5)</t>
+          <t>independent-window audit</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>1-day: stocks positive</t>
+          <t>Independent windows behind biggest lifts</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>6 of 7</t>
+          <t>7-24</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>p=0.062</t>
+          <t>hundreds needed</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
@@ -5000,17 +5000,17 @@
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>STRONGEST RESULT OF THE PROJECT but still not significant. The 1-week +2.7pp was a POOLING ARTIFACT (-0.5pp vs own baselines). Only 1 day survives: median +2.5pp, p=0.062, 1 of 9 horizons, single window.</t>
+          <t>All 19 large lifts (T-bill -19.3, M2 +17.0, USD/LKR -15.3) sit at 3mo-1yr where only 7-24 INDEPENDENT windows exist. Overlapping windows inflate the z-test. Discard them.</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>pooled_vs_own_baseline.csv</t>
+          <t>comovement_table.csv</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>pooling stocks with different class balance weakens the majority baseline and fakes an edge</t>
+          <t>median |lift| long 4.2pp vs short 2.5pp is a sample-size illusion</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Readable rules extracted</t>
+          <t>Pooled panel model (sector-wide)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -5045,48 +5045,52 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>depth-3 tree, scored on unseen test set</t>
+          <t>split by DATE not row, 17,770 train rows</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Decision tree (depth 3)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/22</t>
+          <t>direct, 9 horizons, one model for whole sector</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Best 1-day rule accuracy %</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="M59" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Horizons beating pooled baseline</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>2 of 9</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>majority / persistence</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>17 plain-English rules with out-of-sample hit rates. Best 1-day rule: calm market + flat ASPI + no big drop -&gt; Hold, 49.3% (+11.3pp). Shows WHAT the model believes, not just that it fails.</t>
+          <t>7x more training data (17,770 vs ~2,700 per stock). Beats the POOLED baseline at 1 day (+3.3pp) and 1 week (+2.7pp) only.</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>readable_rules.csv</t>
+          <t>results/direction/pooled_rules/pooled_model_results.csv</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>1-month rule at 68.5% fires only 317 times - treat as noise</t>
+          <t>direction_pooled_and_rules.py</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5110,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>1-day claim re-test (walk-forward)</t>
+          <t>Pooled model fairness check</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5121,32 +5125,32 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>21 non-overlapping 6-month windows, expanding train</t>
+          <t>pooled model scored vs each stock's OWN baseline</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost (reported separately)</t>
+          <t>binomial sign test (H0 p=0.5)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>direct, walk-forward, h=1</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Folds with positive median edge</t>
+          <t>1-day: stocks positive</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>6-7 of 21</t>
+          <t>6 of 7</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>10.5 expected by chance</t>
+          <t>p=0.062</t>
         </is>
       </c>
       <c r="M60" s="5" t="inlineStr">
@@ -5156,17 +5160,17 @@
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>CLAIM REFUTED. Median of fold medians -1.8pp (Logistic) / -1.9pp (XGBoost), sign-test p=0.96 and 0.99. The single-split +2.5pp did not survive 21 independent windows.</t>
+          <t>STRONGEST RESULT OF THE PROJECT but still not significant. The 1-week +2.7pp was a POOLING ARTIFACT (-0.5pp vs own baselines). Only 1 day survives: median +2.5pp, p=0.062, 1 of 9 horizons, single window.</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>results/direction/retest_1day/retest_summary.md</t>
+          <t>pooled_vs_own_baseline.csv</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>direction_1day_retest.py; verdict rule fixed IN ADVANCE; 1-week carried as control, also negative</t>
+          <t>pooling stocks with different class balance weakens the majority baseline and fakes an edge</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5190,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>1-day re-test - window regime effect</t>
+          <t>Readable rules extracted</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>7 bank/finance stocks pooled</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -5201,52 +5205,48 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>21 walk-forward folds</t>
+          <t>depth-3 tree, scored on unseen test set</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Decision tree (depth 3)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1</t>
+          <t>direct, h=1/5/22</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Positive folds 2016-2020 vs 2021-2024</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>1 of 10 vs 6 of 8</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M61" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Best 1-day rule accuracy %</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="M61" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>Confirms the crisis-window finding a second time: folds in 2021-2024 are mostly POSITIVE, 2016-2020 mostly negative. Apparent skill is a property of the period, not the model.</t>
+          <t>17 plain-English rules with out-of-sample hit rates. Best 1-day rule: calm market + flat ASPI + no big drop -&gt; Hold, 49.3% (+11.3pp). Shows WHAT the model believes, not just that it fails.</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>retest_by_fold.csv</t>
+          <t>readable_rules.csv</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>strong argument for walk-forward reporting in the dissertation</t>
+          <t>1-month rule at 68.5% fires only 317 times - treat as noise</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1-day re-test - per stock consistency</t>
+          <t>1-day claim re-test (walk-forward)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5281,32 +5281,32 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>21 walk-forward folds each</t>
+          <t>21 non-overlapping 6-month windows, expanding train</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Logistic + XGBoost (reported separately)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1</t>
+          <t>direct, walk-forward, h=1</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Stocks positive in &gt;50% of folds</t>
+          <t>Folds with positive median edge</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>2 of 7</t>
+          <t>6-7 of 21</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.5 expected by chance</t>
         </is>
       </c>
       <c r="M62" s="5" t="inlineStr">
@@ -5316,17 +5316,17 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>No consistency: LOFC and CFIN positive in 62% of folds, HNB in only 19%. A real edge would show across the sector, not in two names.</t>
+          <t>CLAIM REFUTED. Median of fold medians -1.8pp (Logistic) / -1.9pp (XGBoost), sign-test p=0.96 and 0.99. The single-split +2.5pp did not survive 21 independent windows.</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>retest_by_stock.csv</t>
+          <t>results/direction/retest_1day/retest_summary.md</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>median edge per stock ranges +4.9 (LOFC) to -4.9 (SAMP)</t>
+          <t>direction_1day_retest.py; verdict rule fixed IN ADVANCE; 1-week carried as control, also negative</t>
         </is>
       </c>
     </row>
@@ -5346,67 +5346,67 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>LSTM/GRU for direction</t>
+          <t>1-day re-test - window regime effect</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks pooled</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>daily (30-day sequences)</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>7 walk-forward 12-month folds, 3 seeds</t>
+          <t>21 walk-forward folds</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>LSTM + GRU (PyTorch)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>direct, sequence input, h=1/5/22</t>
+          <t>direct, h=1</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Folds positive (LSTM, h=1)</t>
+          <t>Positive folds 2016-2020 vs 2021-2024</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>5 of 7</t>
+          <t>1 of 10 vs 6 of 8</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>p=0.227</t>
-        </is>
-      </c>
-      <c r="M63" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>Recurrent nets do NOT beat the naive baseline at any horizon. Closes the 'did you try deep learning on direction?' question. LSTM finally applied to the direction target (project is named after it).</t>
+          <t>Confirms the crisis-window finding a second time: folds in 2021-2024 are mostly POSITIVE, 2016-2020 mostly negative. Apparent skill is a property of the period, not the model.</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>results/direction/lstm_gru/lstm_gru_summary.md</t>
+          <t>retest_by_fold.csv</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>direction_lstm_gru.py; monthly macro excluded (flat inside a 30-day window)</t>
+          <t>strong argument for walk-forward reporting in the dissertation</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Sequence vs flat control (LSTM value)</t>
+          <t>1-day re-test - per stock consistency</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks pooled</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -5441,52 +5441,52 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>identical sequences, flattened for the control</t>
+          <t>21 walk-forward folds each</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>LSTM vs Logistic on flattened sequences</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/22</t>
+          <t>direct, h=1</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Median edge LSTM vs flat (pp)</t>
+          <t>Stocks positive in &gt;50% of folds</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>+2.9 vs -1.7</t>
+          <t>2 of 7</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>Logistic(flat)</t>
-        </is>
-      </c>
-      <c r="M64" s="6" t="inlineStr">
-        <is>
           <t>—</t>
         </is>
       </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>REAL NUANCE: LSTM beats the FLATTENED same data at ALL 3 horizons (1d +2.9 vs -1.7, 1wk -0.4 vs -2.1, 1mo -5.4 vs -9.9). Order of recent days carries a little signal that summary features discard - first time added complexity helped. Still not enough to reach the baseline.</t>
+          <t>No consistency: LOFC and CFIN positive in 62% of folds, HNB in only 19%. A real edge would show across the sector, not in two names.</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>lstm_gru_by_fold.csv</t>
+          <t>retest_by_stock.csv</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>the flat control is what makes this interpretable</t>
+          <t>median edge per stock ranges +4.9 (LOFC) to -4.9 (SAMP)</t>
         </is>
       </c>
     </row>
@@ -5506,67 +5506,67 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Regime effect - THIRD confirmation</t>
+          <t>LSTM/GRU for direction</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>7 bank/finance stocks pooled</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>daily (30-day sequences)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>7 walk-forward folds, LSTM h=1</t>
+          <t>7 walk-forward 12-month folds, 3 seeds</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM + GRU (PyTorch)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, sequence input, h=1/5/22</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Positive folds 2019-2020 vs 2021-2025</t>
+          <t>Folds positive (LSTM, h=1)</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0 of 2 vs 5 of 5</t>
+          <t>5 of 7</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M65" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>p=0.227</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>Same window/regime pattern found for a THIRD time (after money supply and the 1-day retest). Every model looks skilled post-2021 and useless before, with identical code and features. Explains why 5/7 folds here is not convincing.</t>
+          <t>Recurrent nets do NOT beat the naive baseline at any horizon. Closes the 'did you try deep learning on direction?' question. LSTM finally applied to the direction target (project is named after it).</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>lstm_gru_by_fold.csv</t>
+          <t>results/direction/lstm_gru/lstm_gru_summary.md</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>strongest methodological finding of the project</t>
+          <t>direction_lstm_gru.py; monthly macro excluded (flat inside a 30-day window)</t>
         </is>
       </c>
     </row>
@@ -5586,12 +5586,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Phase H - news sentiment</t>
+          <t>Sequence vs flat control (LSTM value)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>7 bank/finance stocks pooled</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -5601,48 +5601,52 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>7 walk-forward 6-month folds, 2016-2022</t>
+          <t>identical sequences, flattened for the control</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>LSTM vs Logistic on flattened sequences</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/10/22</t>
+          <t>direct, h=1/5/22</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from sentiment (pp)</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Median edge LSTM vs flat (pp)</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>+2.9 vs -1.7</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Logistic(flat)</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>News sentiment does NOT improve direction. Gain positive at 2 of 4 horizons (-0.8, -0.7, +2.4, +1.6), nothing near significance (all p&gt;=0.50). No phase beats the naive baseline.</t>
+          <t>REAL NUANCE: LSTM beats the FLATTENED same data at ALL 3 horizons (1d +2.9 vs -1.7, 1wk -0.4 vs -2.1, 1mo -5.4 vs -9.9). Order of recent days carries a little signal that summary features discard - first time added complexity helped. Still not enough to reach the baseline.</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>results/direction/sentiment/sentiment_summary.md</t>
+          <t>lstm_gru_by_fold.csv</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_h_sentiment.py; 149k Dailymirror/Newsfirst articles, 9,785 market-relevant</t>
+          <t>the flat control is what makes this interpretable</t>
         </is>
       </c>
     </row>
@@ -5662,12 +5666,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Phase H - lexicon disagreement</t>
+          <t>Regime effect - THIRD confirmation</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Dailymirror + Newsfirst news</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -5677,26 +5681,28 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>9,785 market-relevant articles 2016-2022</t>
+          <t>7 walk-forward folds, LSTM h=1</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>VADER vs Loughran-McDonald style</t>
+          <t>LSTM</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>sentiment scoring</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Correlation between lexicons</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="n">
-        <v>0.416</v>
+          <t>Positive folds 2019-2020 vs 2021-2025</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>0 of 2 vs 5 of 5</t>
+        </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
@@ -5710,17 +5716,17 @@
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>Two reasonable sentiment measures on the SAME articles correlate only 0.42. Direct evidence the sentiment signal is fragile, not merely weak. Running one lexicon alone would have hidden this.</t>
+          <t>Same window/regime pattern found for a THIRD time (after money supply and the 1-day retest). Every model looks skilled post-2021 and useless before, with identical code and features. Explains why 5/7 folds here is not convincing.</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>sentiment_verdict.csv</t>
+          <t>lstm_gru_by_fold.csv</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>finance_lexicon.py; full LM dictionary can be dropped in without code change</t>
+          <t>strongest methodological finding of the project</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5746,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Phase H - regime confound ruled out</t>
+          <t>Phase H - news sentiment</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5755,7 +5761,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>folds split calm vs crisis</t>
+          <t>7 walk-forward 6-month folds, 2016-2022</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5765,42 +5771,38 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, h=1/5/10/22</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Sentiment gain calm vs crisis (pp)</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>+0.85 vs -0.45</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Mean gain from sentiment (pp)</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>Expected sentiment to 'work' only in the 2022 crisis; the OPPOSITE happened (calm 9/16 folds positive, crisis 3/12). So this null is NOT a regime artifact - cleaner than the other phases.</t>
+          <t>News sentiment does NOT improve direction. Gain positive at 2 of 4 horizons (-0.8, -0.7, +2.4, +1.6), nothing near significance (all p&gt;=0.50). No phase beats the naive baseline.</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>sentiment_regime_split.csv</t>
+          <t>results/direction/sentiment/sentiment_summary.md</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>first phase where the regime effect did not appear</t>
+          <t>direction_phase_h_sentiment.py; 149k Dailymirror/Newsfirst articles, 9,785 market-relevant</t>
         </is>
       </c>
     </row>
@@ -5815,12 +5817,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>News look-ahead guard</t>
+          <t>Phase H - lexicon disagreement</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -5835,26 +5837,26 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>publication timestamps vs 14:30 CSE close</t>
+          <t>9,785 market-relevant articles 2016-2022</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>time-of-day assignment</t>
+          <t>VADER vs Loughran-McDonald style</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>sentiment scoring</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Articles pushed to next trading day %</t>
+          <t>Correlation between lexicons</t>
         </is>
       </c>
       <c r="K69" s="2" t="n">
-        <v>36</v>
+        <v>0.416</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
@@ -5868,17 +5870,17 @@
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>36% of articles were published AFTER the 14:30 close and were reassigned to the next trading day. Without this rule those articles report the very move being predicted and sentiment would look excellent and be worthless.</t>
+          <t>Two reasonable sentiment measures on the SAME articles correlate only 0.42. Direct evidence the sentiment signal is fragile, not merely weak. Running one lexicon alone would have hidden this.</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>cleaned_data/news_sentiment_daily.csv</t>
+          <t>sentiment_verdict.csv</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>only 75 of 149,240 rows lacked a timestamp</t>
+          <t>finance_lexicon.py; full LM dictionary can be dropped in without code change</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5900,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>POSITIVE CONTROL - pipeline validation</t>
+          <t>Phase H - regime confound ruled out</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5913,7 +5915,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, same-day vs lagged info</t>
+          <t>folds split calm vs crisis</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5923,38 +5925,42 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>contemporaneous vs predictive</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Edge over baseline (pp)</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="M70" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Sentiment gain calm vs crisis (pp)</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>+0.85 vs -0.45</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>DECISIVE: same code finds +8.2pp (17/19 folds, p=0.0004) using TODAY's market/macro/news, and -4.1pp using the SAME info one day earlier. Gap 13.7pp. The pipeline is NOT blind - this information EXPLAINS returns but does not PREDICT them.</t>
+          <t>Expected sentiment to 'work' only in the 2022 crisis; the OPPOSITE happened (calm 9/16 folds positive, crisis 3/12). So this null is NOT a regime artifact - cleaner than the other phases.</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>results/direction/diagnostics/diagnostics_summary.md</t>
+          <t>sentiment_regime_split.csv</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>direction_diagnostics.py; own-stock return excluded from contemporaneous features</t>
+          <t>first phase where the regime effect did not appear</t>
         </is>
       </c>
     </row>
@@ -5969,17 +5975,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Binary up/down reformulation</t>
+          <t>News look-ahead guard</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>Dailymirror + Newsfirst news</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -5989,48 +5995,50 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds</t>
+          <t>publication timestamps vs 14:30 CSE close</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>time-of-day assignment</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>binary, h=1/5/22</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Edge over baseline (pp)</t>
+          <t>Articles pushed to next trading day %</t>
         </is>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>36</v>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>3-class dead-zone was NOT hiding a signal. Binary edge -4.8/-1.1/-2.1pp at 1d/1wk/1mo, positive in only 1/19, 7/19, 4/19 folds.</t>
+          <t>36% of articles were published AFTER the 14:30 close and were reassigned to the next trading day. Without this rule those articles report the very move being predicted and sentiment would look excellent and be worthless.</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>diagnostics_verdict.csv</t>
+          <t>cleaned_data/news_sentiment_daily.csv</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>rules out the Hold-majority explanation</t>
+          <t>only 75 of 149,240 rows lacked a timestamp</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6058,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>MAGNITUDE-WEIGHTED edge (survives)</t>
+          <t>POSITIVE CONTROL - pipeline validation</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -6065,7 +6073,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds</t>
+          <t>19 walk-forward folds, same-day vs lagged info</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -6075,21 +6083,19 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>binary, |return|-weighted</t>
+          <t>contemporaneous vs predictive</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Weighted edge 1d / 1wk (pp)</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>+7.9 / +13.2</t>
-        </is>
+          <t>Edge over baseline (pp)</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>-4.1</v>
       </c>
       <c r="M72" s="8" t="inlineStr">
         <is>
@@ -6098,17 +6104,17 @@
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>FIRST RESULT TO SURVIVE. Model is WRONG more often than baseline on plain accuracy (-4.3pp) but RIGHT on the big moves: weighted edge +7.9pp (15/19 folds, p=0.0096) at 1 day and +13.2pp (15/19, p=0.0096) at 1 week. Accuracy was the wrong metric.</t>
+          <t>DECISIVE: same code finds +8.2pp (17/19 folds, p=0.0004) using TODAY's market/macro/news, and -4.1pp using the SAME info one day earlier. Gap 13.7pp. The pipeline is NOT blind - this information EXPLAINS returns but does not PREDICT them.</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>diagnostics_magnitude.csv</t>
+          <t>results/direction/diagnostics/diagnostics_summary.md</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>1-month +9.5pp but p=0.18</t>
+          <t>direction_diagnostics.py; own-stock return excluded from contemporaneous features</t>
         </is>
       </c>
     </row>
@@ -6128,7 +6134,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Trading backtest with costs</t>
+          <t>Binary up/down reformulation</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -6143,29 +6149,29 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, h=1 only (non-overlapping)</t>
+          <t>19 walk-forward folds</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>long/short on model signal</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>economic evaluation</t>
+          <t>binary, h=1/5/22</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Net return @50bps (%)</t>
+          <t>Edge over baseline (pp)</t>
         </is>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.05</v>
+        <v>-4.8</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
@@ -6174,17 +6180,17 @@
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>THE EDGE IS REAL BUT NOT EXPLOITABLE. Gross +22.19% vs buy-and-hold +6.49%, but median 40 position flips per 6-month fold: net +17.35% @10bps, +11.24% @25bps, +0.05% @50bps. At realistic CSE costs the edge is exactly zero (8/19 folds, p=0.82).</t>
+          <t>3-class dead-zone was NOT hiding a signal. Binary edge -4.8/-1.1/-2.1pp at 1d/1wk/1mo, positive in only 1/19, 7/19, 4/19 folds.</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>diagnostics_backtest_h1.csv</t>
+          <t>diagnostics_verdict.csv</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>h=5 and h=22 backtests omitted - overlapping returns cannot be summed</t>
+          <t>rules out the Hold-majority explanation</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6205,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Price + macro + news vs naive</t>
+          <t>MAGNITUDE-WEIGHTED edge (survives)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -6219,52 +6225,50 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>walk-forward 6-month folds, per stock</t>
+          <t>19 walk-forward folds</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>naive / ARIMA(1,1,1) / Ridge / XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>1-day and 5-day, return-then-reconstruct</t>
+          <t>binary, |return|-weighted</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Cases beating naive (MAPE)</t>
+          <t>Weighted edge 1d / 1wk (pp)</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0 of 133</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>naive</t>
-        </is>
-      </c>
-      <c r="M74" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>+7.9 / +13.2</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>NAIVE UNBEATEN. Best model ARIMA(1,1,1) at 1.004x naive MAPE. Stage 1's univariate conclusion survives the multivariate test - adding macro and news does not rescue price forecasting.</t>
+          <t>FIRST RESULT TO SURVIVE. Model is WRONG more often than baseline on plain accuracy (-4.3pp) but RIGHT on the big moves: weighted edge +7.9pp (15/19 folds, p=0.0096) at 1 day and +13.2pp (15/19, p=0.0096) at 1 week. Accuracy was the wrong metric.</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>results/price_macro_news/price_summary.md</t>
+          <t>diagnostics_magnitude.csv</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>price_with_macro_news.py; models predict RETURN then reconstruct price to stop them echoing today's price</t>
+          <t>1-month +9.5pp but p=0.18</t>
         </is>
       </c>
     </row>
@@ -6279,12 +6283,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Does macro/news improve price forecasting?</t>
+          <t>Trading backtest with costs</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -6299,29 +6303,29 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>nested feature sets P / P+M / P+M+N</t>
+          <t>19 walk-forward folds, h=1 only (non-overlapping)</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>long/short on model signal</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>ablation on MAPE</t>
+          <t>economic evaluation</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Median MAPE improvement (pp)</t>
+          <t>Net return @50bps (%)</t>
         </is>
       </c>
       <c r="K75" s="2" t="n">
-        <v>-0.019</v>
+        <v>0.05</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>6.49</v>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
@@ -6330,17 +6334,17 @@
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>ALL EIGHT combinations NEGATIVE (-0.008 to -0.078pp). Adding macro and news makes price forecasting WORSE, consistently across both algorithms and both horizons.</t>
+          <t>THE EDGE IS REAL BUT NOT EXPLOITABLE. Gross +22.19% vs buy-and-hold +6.49%, but median 40 position flips per 6-month fold: net +17.35% @10bps, +11.24% @25bps, +0.05% @50bps. At realistic CSE costs the edge is exactly zero (8/19 folds, p=0.82).</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>price_ablation_gain.csv</t>
+          <t>diagnostics_backtest_h1.csv</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>mirrors the direction chapter exactly</t>
+          <t>h=5 and h=22 backtests omitted - overlapping returns cannot be summed</t>
         </is>
       </c>
     </row>
@@ -6355,12 +6359,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>CSE flat-day share (illiquidity)</t>
+          <t>Price + macro + news vs naive</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6375,50 +6379,52 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>2017-2026</t>
+          <t>walk-forward 6-month folds, per stock</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>share of zero-return days</t>
+          <t>naive / ARIMA(1,1,1) / Ridge / XGBoost</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>1-day and 5-day, return-then-reconstruct</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Flat days at 1 day (%)</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="n">
-        <v>10.5</v>
+          <t>Cases beating naive (MAPE)</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>0 of 133</t>
+        </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>~10% of bank/finance trading days close EXACTLY unchanged; LOFC 36.0%, HNB 12.9%, LOLC 7.2%. Illiquidity is part of why the naive baseline is so hard to beat and why the Hold class dominates.</t>
+          <t>NAIVE UNBEATEN. Best model ARIMA(1,1,1) at 1.004x naive MAPE. Stage 1's univariate conclusion survives the multivariate test - adding macro and news does not rescue price forecasting.</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>price_all_results.csv</t>
+          <t>results/price_macro_news/price_summary.md</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>surfaced as an artefact of the naive model's directional-accuracy column</t>
+          <t>price_with_macro_news.py; models predict RETURN then reconstruct price to stop them echoing today's price</t>
         </is>
       </c>
     </row>
@@ -6433,17 +6439,17 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>LEAK CAUGHT - ASPI forward-fill</t>
+          <t>Does macro/news improve price forecasting?</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 index</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -6453,48 +6459,48 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>feature vs same-day and next-day return</t>
+          <t>nested feature sets P / P+M / P+M+N</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>correlation audit</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>leak detection</t>
+          <t>ablation on MAPE</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>corr with next-day vs same-day</t>
+          <t>Median MAPE improvement (pp)</t>
         </is>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.742</v>
+        <v>-0.019</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="M77" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0</v>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>SPSL20 and ASPI do not share a trading calendar (207 / 962 mismatched dates). Forward-filling ASPI across the gaps let it carry a move SPSL20 only recorded on its NEXT row. Halved MAPE for free: ratio 0.496 vs a true 0.970.</t>
+          <t>ALL EIGHT combinations NEGATIVE (-0.008 to -0.078pp). Adding macro and news makes price forecasting WORSE, consistently across both algorithms and both horizons.</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>results/price_macro_news/leak_scan.csv</t>
+          <t>price_ablation_gain.csv</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>fix: no ffill across calendars + no ASPI features for index targets</t>
+          <t>mirrors the direction chapter exactly</t>
         </is>
       </c>
     </row>
@@ -6509,17 +6515,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Automated leak scan added</t>
+          <t>CSE flat-day share (illiquidity)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>all 9 targets</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -6529,26 +6535,26 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>every feature, every run</t>
+          <t>2017-2026</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>corr(feature, future) vs corr(feature, present)</t>
+          <t>share of zero-return days</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>guard</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Features flagged after fix</t>
+          <t>Flat days at 1 day (%)</t>
         </is>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
@@ -6562,17 +6568,17 @@
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>Permanent guard: any feature correlating MORE with the future than the present is flagged. Would have caught the ASPI bug instantly. Runs on every target automatically. THIRD leak-class bug in this project - all three flattered the model.</t>
+          <t>~10% of bank/finance trading days close EXACTLY unchanged; LOFC 36.0%, HNB 12.9%, LOLC 7.2%. Illiquidity is part of why the naive baseline is so hard to beat and why the Hold class dominates.</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>price_with_macro_news.py</t>
+          <t>price_all_results.csv</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>previous two: persistence baseline lookback, pooled baseline</t>
+          <t>surfaced as an artefact of the naive model's directional-accuracy column</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6593,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 with macro + news (corrected)</t>
+          <t>LEAK CAUGHT - ASPI forward-fill</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -6607,48 +6613,48 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>17 walk-forward 6-month folds</t>
+          <t>feature vs same-day and next-day return</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>naive / ARIMA / Ridge / XGBoost</t>
+          <t>correlation audit</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>direct 1-day and 5-day</t>
+          <t>leak detection</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>MAPE ratio vs naive (best)</t>
+          <t>corr with next-day vs same-day</t>
         </is>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.97</v>
+        <v>0.742</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M79" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>0.374</v>
+      </c>
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>After the leak fix: best is Ridge price-only at 0.970 (1d) and 0.959 (5d), beating naive in only 10/17 and 9/17 folds. Macro and news make it WORSE (ratios 1.00-1.10).</t>
+          <t>SPSL20 and ASPI do not share a trading calendar (207 / 962 mismatched dates). Forward-filling ASPI across the gaps let it carry a move SPSL20 only recorded on its NEXT row. Halved MAPE for free: ratio 0.496 vs a true 0.970.</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>results/price_macro_news/price_summary.md</t>
+          <t>results/price_macro_news/leak_scan.csv</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>pre-fix figure was 0.496 - entirely the ASPI leak</t>
+          <t>fix: no ffill across calendars + no ASPI features for index targets</t>
         </is>
       </c>
     </row>
@@ -6663,17 +6669,17 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Method study</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Index vs stock autocorrelation</t>
+          <t>Automated leak scan added</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>SPSL20, ASPI vs 7 stocks</t>
+          <t>all 9 targets</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -6683,28 +6689,26 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>full sample</t>
+          <t>every feature, every run</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>lag-1 return autocorrelation</t>
+          <t>corr(feature, future) vs corr(feature, present)</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>guard</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Lag-1 autocorr (index vs stock)</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>+0.24 vs +0.04</t>
-        </is>
+          <t>Features flagged after fix</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
@@ -6718,17 +6722,17 @@
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>REAL EFFECT: indices show +0.237 (SPSL20) and +0.233 (ASPI) lag-1 return autocorrelation vs +0.038 for HNB. Non-synchronous trading - illiquid constituents (LOFC 37.8% flat days) reprice a day late, smearing shocks. A 1-parameter AR(1) captures the entire index 'edge'.</t>
+          <t>Permanent guard: any feature correlating MORE with the future than the present is flagged. Would have caught the ASPI bug instantly. Runs on every target automatically. THIRD leak-class bug in this project - all three flattered the model.</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>price_all_results.csv</t>
+          <t>price_with_macro_news.py</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>statistically real, economically useless - capturing it means trading the illiquid names that cause it</t>
+          <t>previous two: persistence baseline lookback, pooled baseline</t>
         </is>
       </c>
     </row>
@@ -6748,12 +6752,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Hybrid ARIMA+LSTM (Zhang 2003)</t>
+          <t>S&amp;P SL 20 with macro + news (corrected)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + HNB</t>
+          <t>S&amp;P SL 20 index</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -6763,26 +6767,26 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20 + 7 walk-forward folds</t>
+          <t>17 walk-forward 6-month folds</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>ARIMA(2,1,0) + LSTM on residuals</t>
+          <t>naive / ARIMA / Ridge / XGBoost</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead, rolling ARIMA state</t>
+          <t>direct 1-day and 5-day</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Theil U2 (fixed split)</t>
+          <t>MAPE ratio vs naive (best)</t>
         </is>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1.012</v>
+        <v>0.97</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>1</v>
@@ -6794,17 +6798,17 @@
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>Hybrid built properly (Y=L+N, LSTM on ARIMA residuals, 3 seeds averaged) and it does NOT beat the naive random walk. SPSL20 U2=1.012, HNB U2=1.005. Marginally WORSE than plain ARIMA on both targets.</t>
+          <t>After the leak fix: best is Ridge price-only at 0.970 (1d) and 0.959 (5d), beating naive in only 10/17 and 9/17 folds. Macro and news make it WORSE (ratios 1.00-1.10).</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>results/hybrid_comparable/hybrid_summary.md</t>
+          <t>results/price_macro_news/price_summary.md</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>hybrid_arima_lstm_macro_news.py; supervisor-committed architecture, now tested</t>
+          <t>pre-fix figure was 0.496 - entirely the ASPI leak</t>
         </is>
       </c>
     </row>
@@ -6824,12 +6828,12 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Hybrid + macro + news (extension)</t>
+          <t>Index vs stock autocorrelation</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + HNB</t>
+          <t>SPSL20, ASPI vs 7 stocks</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -6839,52 +6843,52 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20 + 7 walk-forward folds</t>
+          <t>full sample</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>ARIMA + LSTM on residuals WITH exogenous macro/news</t>
+          <t>lag-1 return autocorrelation</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Folds better than naive (HNB)</t>
+          <t>Lag-1 autocorr (index vs stock)</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0 of 7</t>
+          <t>+0.24 vs +0.04</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>naive</t>
-        </is>
-      </c>
-      <c r="M82" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>THE PROJECT'S EXTENSION: macro+news fed into the residual model - the part ARIMA provably cannot explain. It makes things WORSE. SPSL20 U2 1.032, HNB U2 1.011, HNB walk-forward 0/7 folds.</t>
+          <t>REAL EFFECT: indices show +0.237 (SPSL20) and +0.233 (ASPI) lag-1 return autocorrelation vs +0.038 for HNB. Non-synchronous trading - illiquid constituents (LOFC 37.8% flat days) reprice a day late, smearing shocks. A 1-parameter AR(1) captures the entire index 'edge'.</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>hybrid_walkforward_table.csv</t>
+          <t>price_all_results.csv</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>best place to put macro if it carried information; it does not</t>
+          <t>statistically real, economically useless - capturing it means trading the illiquid names that cause it</t>
         </is>
       </c>
     </row>
@@ -6899,12 +6903,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Diebold-Mariano + Theil U added</t>
+          <t>Hybrid ARIMA+LSTM (Zhang 2003)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -6919,31 +6923,29 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20</t>
+          <t>fixed 80/20 + 7 walk-forward folds</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>DM test (Newey-West HAC) + Theil U2</t>
+          <t>ARIMA(2,1,0) + LSTM on residuals</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>forecast comparison</t>
+          <t>one-step-ahead, rolling ARIMA state</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Models significantly better than naive</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>0 of 8</t>
-        </is>
+          <t>Theil U2 (fixed split)</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>1.012</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
@@ -6952,17 +6954,17 @@
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>COMPARABILITY GAP CLOSED. Papers claim superiority with the DM test; this project had only baseline-relative edge. DM run vs naive AND vs ARIMA: ZERO models significant at p&lt;0.05. Only 1 of 8 has Theil U2&lt;1.</t>
+          <t>Hybrid built properly (Y=L+N, LSTM on ARIMA residuals, 3 seeds averaged) and it does NOT beat the naive random walk. SPSL20 U2=1.012, HNB U2=1.005. Marginally WORSE than plain ARIMA on both targets.</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>hybrid_fixed_split_table.csv</t>
+          <t>results/hybrid_comparable/hybrid_summary.md</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>the standard test reviewers expect; previously missing</t>
+          <t>hybrid_arima_lstm_macro_news.py; supervisor-committed architecture, now tested</t>
         </is>
       </c>
     </row>
@@ -6977,12 +6979,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>R-squared on price levels is meaningless</t>
+          <t>Hybrid + macro + news (extension)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -6997,50 +6999,52 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20</t>
+          <t>fixed 80/20 + 7 walk-forward folds</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>all models incl. naive</t>
+          <t>ARIMA + LSTM on residuals WITH exogenous macro/news</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>one-step-ahead</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>R2 of the NAIVE model</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="n">
-        <v>0.9979</v>
+          <t>Folds better than naive (HNB)</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>0 of 7</t>
+        </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M84" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>IMPORTANT FOR THE WRITE-UP: every model scores R2 0.9977-0.9980 - INCLUDING the naive random walk. Papers reporting R2~0.99 on price levels are reporting nothing. R2 on a level only measures being in the right magnitude.</t>
+          <t>THE PROJECT'S EXTENSION: macro+news fed into the residual model - the part ARIMA provably cannot explain. It makes things WORSE. SPSL20 U2 1.032, HNB U2 1.011, HNB walk-forward 0/7 folds.</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>hybrid_fixed_split_table.csv</t>
+          <t>hybrid_walkforward_table.csv</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>direct rebuttal to a common claim in this literature</t>
+          <t>best place to put macro if it carried information; it does not</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7064,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Fixed split vs walk-forward disagreement</t>
+          <t>Diebold-Mariano + Theil U added</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -7075,52 +7079,50 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>both protocols, same models</t>
+          <t>fixed 80/20</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>ARIMA / LSTM / Hybrid</t>
+          <t>DM test (Newey-West HAC) + Theil U2</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead</t>
+          <t>forecast comparison</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>ARIMA SPSL20 U2 (fixed vs WF)</t>
+          <t>Models significantly better than naive</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>1.005 vs 0.985</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M85" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>0 of 8</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>The two protocols DISAGREE: ARIMA is worse than naive on the SPSL20 fixed split (6/7 folds better in walk-forward), and the reverse pattern on HNB. Reporting only one protocol would mislead - hence both are published.</t>
+          <t>COMPARABILITY GAP CLOSED. Papers claim superiority with the DM test; this project had only baseline-relative edge. DM run vs naive AND vs ARIMA: ZERO models significant at p&lt;0.05. Only 1 of 8 has Theil U2&lt;1.</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>hybrid_all_results.csv</t>
+          <t>hybrid_fixed_split_table.csv</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>4th demonstration that the test window drives the result</t>
+          <t>the standard test reviewers expect; previously missing</t>
         </is>
       </c>
     </row>
@@ -7135,17 +7137,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Method study</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Sector composite autocorrelation</t>
+          <t>R-squared on price levels is meaningless</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>BANKS/FINANCE/SECTOR composites</t>
+          <t>S&amp;P SL 20 + HNB</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -7155,12 +7157,12 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>full sample</t>
+          <t>fixed 80/20</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>lag-1 autocorrelation</t>
+          <t>all models incl. naive</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -7170,13 +7172,11 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Composite vs constituent autocorr</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>BANKS +0.178 vs ~0.07</t>
-        </is>
+          <t>R2 of the NAIVE model</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0.9979</v>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
@@ -7190,17 +7190,17 @@
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>Averaging HELPS for banks (composite 0.178 &gt; every constituent) but FAILS for finance (0.017 - constituents have negative autocorrs that cancel). Mixing them is worse (0.078). SYSTEM DESIGN: build a BANKS index, not a banks+finance index.</t>
+          <t>IMPORTANT FOR THE WRITE-UP: every model scores R2 0.9977-0.9980 - INCLUDING the naive random walk. Papers reporting R2~0.99 on price levels are reporting nothing. R2 on a level only measures being in the right magnitude.</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>results/sector_direction/autocorrelation.csv</t>
+          <t>hybrid_fixed_split_table.csv</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>sector_direction.py; the '6x more predictable' estimate was too strong - 1.2x on average</t>
+          <t>direct rebuttal to a common claim in this literature</t>
         </is>
       </c>
     </row>
@@ -7215,17 +7215,17 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Method study</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Sector direction (the product target)</t>
+          <t>Fixed split vs walk-forward disagreement</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>BANKS/FINANCE/SECTOR composites</t>
+          <t>S&amp;P SL 20 + HNB</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -7235,52 +7235,52 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward 6-month folds</t>
+          <t>both protocols, same models</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>ARIMA / LSTM / Hybrid</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/10/22, binary + 3-class</t>
+          <t>one-step-ahead</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Configurations beating baseline</t>
+          <t>ARIMA SPSL20 U2 (fixed vs WF)</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0 of 24</t>
+          <t>1.005 vs 0.985</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>majority / persistence</t>
-        </is>
-      </c>
-      <c r="M87" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>The target the SYSTEM actually predicts, never tested before. Sector-level direction is NOT predictable on plain accuracy at any horizon or grouping. Leak scan clean.</t>
+          <t>The two protocols DISAGREE: ARIMA is worse than naive on the SPSL20 fixed split (6/7 folds better in walk-forward), and the reverse pattern on HNB. Reporting only one protocol would mislead - hence both are published.</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>results/sector_direction/sector_direction_summary.md</t>
+          <t>hybrid_all_results.csv</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>sector_direction.py</t>
+          <t>4th demonstration that the test window drives the result</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Magnitude edge on BANKS composite</t>
+          <t>Sector composite autocorrelation</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite</t>
+          <t>BANKS/FINANCE/SECTOR composites</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -7315,50 +7315,52 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, binary</t>
+          <t>full sample</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>lag-1 autocorrelation</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>|return|-weighted accuracy</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Weighted edge 1d/1wk/2wk (pp)</t>
+          <t>Composite vs constituent autocorr</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>+10.2 / +8.1 / +11.5</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>BANKS +0.178 vs ~0.07</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M88" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>THIRD independent replication of the magnitude edge (after single stocks and pooled panel). Consistent across 4 horizons, 14-15 of 19 folds each, while plain accuracy edge is NEGATIVE. Product: flag big-move periods, do not emit daily direction calls.</t>
+          <t>Averaging HELPS for banks (composite 0.178 &gt; every constituent) but FAILS for finance (0.017 - constituents have negative autocorrs that cancel). Mixing them is worse (0.078). SYSTEM DESIGN: build a BANKS index, not a banks+finance index.</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>sector_direction_all.csv</t>
+          <t>results/sector_direction/autocorrelation.csv</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>3-class magnitude figures (+34/+39pp) are INFLATED by a degenerate weighted-majority baseline - use the binary ones</t>
+          <t>sector_direction.py; the '6x more predictable' estimate was too strong - 1.2x on average</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7380,12 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>PROBABILITY CALIBRATION (product-critical)</t>
+          <t>Sector direction (the product target)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>BANKS + SECTOR composites</t>
+          <t>BANKS/FINANCE/SECTOR composites</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -7393,32 +7395,32 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, calibrator fitted inside training window only</t>
+          <t>19 walk-forward 6-month folds</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Logistic/XGBoost x raw/Platt/isotonic</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>binary, h=5/10/22</t>
+          <t>direct, h=1/5/10/22, binary + 3-class</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Configurations usable (skill&gt;0 &amp; ECE&lt;0.10)</t>
+          <t>Configurations beating baseline</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0 of 36</t>
+          <t>0 of 24</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>climatology (base rate)</t>
+          <t>majority / persistence</t>
         </is>
       </c>
       <c r="M89" s="5" t="inlineStr">
@@ -7428,17 +7430,17 @@
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>THE DASHBOARD CANNOT SHOW A MODEL CONFIDENCE NUMBER. Every Brier skill score is NEGATIVE; AUC 0.41-0.56 = coin flip. Calibration cannot fix a model that cannot rank.</t>
+          <t>The target the SYSTEM actually predicts, never tested before. Sector-level direction is NOT predictable on plain accuracy at any horizon or grouping. Leak scan clean.</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>results/sector_calibration/calibration_summary.md</t>
+          <t>results/sector_direction/sector_direction_summary.md</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>sector_calibration.py; sklearn 1.9 removed cv='prefit', FrozenEstimator required</t>
+          <t>sector_direction.py</t>
         </is>
       </c>
     </row>
@@ -7458,12 +7460,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Calibration removes error by removing information</t>
+          <t>Magnitude edge on BANKS composite</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>BANKS + SECTOR composites</t>
+          <t>BANKS composite</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -7473,52 +7475,50 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds</t>
+          <t>19 walk-forward folds, binary</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Platt vs raw probabilities</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>|return|-weighted accuracy</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>prob_std Platt vs raw</t>
+          <t>Weighted edge 1d/1wk/2wk (pp)</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0.012-0.054 vs 0.164-0.232</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M90" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>+10.2 / +8.1 / +11.5</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>Platt roughly HALVES calibration error by collapsing the forecast to near-constant. A model that says '54%' every day is perfectly calibrated and useless - no resolution. Calibration alone is not evidence of a usable forecast.</t>
+          <t>THIRD independent replication of the magnitude edge (after single stocks and pooled panel). Consistent across 4 horizons, 14-15 of 19 folds each, while plain accuracy edge is NEGATIVE. Product: flag big-move periods, do not emit daily direction calls.</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>calibration_all_folds.csv</t>
+          <t>sector_direction_all.csv</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>product answer: replace model confidence with a realised track record</t>
+          <t>3-class magnitude figures (+34/+39pp) are INFLATED by a degenerate weighted-majority baseline - use the binary ones</t>
         </is>
       </c>
     </row>
@@ -7538,12 +7538,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>News isolated - macro removed</t>
+          <t>PROBABILITY CALIBRATION (product-critical)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + S&amp;P SL 20</t>
+          <t>BANKS + SECTOR composites</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -7553,31 +7553,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds, 2016-2022 (news window)</t>
+          <t>19 walk-forward folds, calibrator fitted inside training window only</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Logistic/XGBoost x raw/Platt/isotonic</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/10, P vs P+N</t>
+          <t>binary, h=5/10/22</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Horizons where news helps</t>
+          <t>Configurations usable (skill&gt;0 &amp; ECE&lt;0.10)</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0 of 6</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0.05</v>
+          <t>0 of 36</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>climatology (base rate)</t>
+        </is>
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
@@ -7586,17 +7588,17 @@
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>CLEAN ISOLATION TEST. In Phase H news competed with ~30 other columns incl. macro, which Phase C showed can actively hurt. Stripped back to price+news only: news gain -1.25 to +2.60pp, nothing significant. Macro was NOT masking news.</t>
+          <t>THE DASHBOARD CANNOT SHOW A MODEL CONFIDENCE NUMBER. Every Brier skill score is NEGATIVE; AUC 0.41-0.56 = coin flip. Calibration cannot fix a model that cannot rank.</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>results/price_news_hybrid/news_gain.csv</t>
+          <t>results/sector_calibration/calibration_summary.md</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>price_news_hybrid.py; window 2016-2022 not comparable to other phases</t>
+          <t>sector_calibration.py; sklearn 1.9 removed cv='prefit', FrozenEstimator required</t>
         </is>
       </c>
     </row>
@@ -7611,17 +7613,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Hybrid + news, no macro</t>
+          <t>Calibration removes error by removing information</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + S&amp;P SL 20</t>
+          <t>BANKS + SECTOR composites</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -7631,48 +7633,52 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds</t>
+          <t>19 walk-forward folds</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>naive / ARIMA(2,1,0) / Hybrid / Hybrid+News</t>
+          <t>Platt vs raw probabilities</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Theil U2 (Hybrid+News, BANKS)</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>1.0003</v>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M92" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>prob_std Platt vs raw</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>0.012-0.054 vs 0.164-0.232</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M92" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>Adding news to the hybrid makes it WORSE on both targets (BANKS 0.989-&gt;1.000, SPSL20 0.987-&gt;1.017). Plain ARIMA is the best model in the table and even it is not significant (DM p=0.30/0.46). Simplest wins again.</t>
+          <t>Platt roughly HALVES calibration error by collapsing the forecast to near-constant. A model that says '54%' every day is perfectly calibrated and useless - no resolution. Calibration alone is not evidence of a usable forecast.</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>results/price_news_hybrid/price_summary.csv</t>
+          <t>calibration_all_folds.csv</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>supports cutting BOTH the news and hybrid stages from the production system</t>
+          <t>product answer: replace model confidence with a realised track record</t>
         </is>
       </c>
     </row>
@@ -7687,17 +7693,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>LEAK #4 - SPSL20 calendar vs ASPI (again)</t>
+          <t>News isolated - macro removed</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20</t>
+          <t>BANKS composite + S&amp;P SL 20</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -7707,48 +7713,50 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>feature vs same-day and next-day return</t>
+          <t>6 walk-forward folds, 2016-2022 (news window)</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>correlation audit</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>leak detection</t>
+          <t>direct, h=1/5/10, P vs P+N</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>corr with next-day vs same-day</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="n">
-        <v>0.871</v>
+          <t>Horizons where news helps</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>0 of 6</t>
+        </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="M93" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.05</v>
+      </c>
+      <c r="M93" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>The 'clean' SPSL20 file DELETED every flat day, misaligning it against ASPI (352 of 1505 rows drop). Removing .ffill() was NOT enough. Faked 82.8% accuracy / +20.7pp edge; a trivial 'copy sign of ASPI' rule scored 84.3%. Fixed by using the ASPI-calendar SPSL20 file AND dropping ASPI features for index targets.</t>
+          <t>CLEAN ISOLATION TEST. In Phase H news competed with ~30 other columns incl. macro, which Phase C showed can actively hurt. Stripped back to price+news only: news gain -1.25 to +2.60pp, nothing significant. Macro was NOT masking news.</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>results/price_news_hybrid/leak_scan.csv</t>
+          <t>results/price_news_hybrid/news_gain.csv</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>corrected result: 56.8% accuracy, -5.5pp edge</t>
+          <t>price_news_hybrid.py; window 2016-2022 not comparable to other phases</t>
         </is>
       </c>
     </row>
@@ -7763,17 +7771,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Leak guard now HALTS the run</t>
+          <t>Hybrid + news, no macro</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>all targets</t>
+          <t>BANKS composite + S&amp;P SL 20</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -7783,52 +7791,48 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>every feature set</t>
+          <t>6 walk-forward folds</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>automated leak scan</t>
+          <t>naive / ARIMA(2,1,0) / Hybrid / Hybrid+News</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>guard</t>
+          <t>one-step-ahead</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Runs aborted on leak detection</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>1 of 1</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M94" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Theil U2 (Hybrid+News, BANKS)</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>1.0003</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M94" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>The guard previously only wrote a CSV and the run continued, reporting a fake +20.7pp edge while the summary line claimed 'clean'. A guard that does not stop the run is not a guard. Now raises SystemExit.</t>
+          <t>Adding news to the hybrid makes it WORSE on both targets (BANKS 0.989-&gt;1.000, SPSL20 0.987-&gt;1.017). Plain ARIMA is the best model in the table and even it is not significant (DM p=0.30/0.46). Simplest wins again.</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>price_news_hybrid.py</t>
+          <t>results/price_news_hybrid/price_summary.csv</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>4th leak caught in this project; all four flattered the model</t>
+          <t>supports cutting BOTH the news and hybrid stages from the production system</t>
         </is>
       </c>
     </row>
@@ -7843,17 +7847,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Late fusion (one model per source)</t>
+          <t>LEAK #4 - SPSL20 calendar vs ASPI (again)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + HNB</t>
+          <t>S&amp;P SL 20</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -7863,52 +7867,48 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds, chronological base/meta split</t>
+          <t>feature vs same-day and next-day return</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>XGBoost bases + Logistic meta-learner</t>
+          <t>correlation audit</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>stacking, h=1/5/10</t>
+          <t>leak detection</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Configurations beating baseline</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>0 of 6</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>majority / persistence</t>
-        </is>
-      </c>
-      <c r="M95" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>corr with next-day vs same-day</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>ARCHITECTURE WAS NOT THE CONSTRAINT. Separate models for price/news/macro combined by a meta-learner: 0/6 beat the baseline. Late fusion IS less bad than early fusion (better in 5/6) but beats it significantly in only 1/6 = chance.</t>
+          <t>The 'clean' SPSL20 file DELETED every flat day, misaligning it against ASPI (352 of 1505 rows drop). Removing .ffill() was NOT enough. Faked 82.8% accuracy / +20.7pp edge; a trivial 'copy sign of ASPI' rule scored 84.3%. Fixed by using the ASPI-calendar SPSL20 file AND dropping ASPI features for index targets.</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>results/late_fusion/late_fusion_summary.md</t>
+          <t>results/price_news_hybrid/leak_scan.csv</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>late_fusion_stacking.py; meta-learner trained on OUT-OF-FOLD base predictions</t>
+          <t>corrected result: 56.8% accuracy, -5.5pp edge</t>
         </is>
       </c>
     </row>
@@ -7923,17 +7923,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Method study</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Meta-learner weight allocation</t>
+          <t>Leak guard now HALTS the run</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + HNB</t>
+          <t>all targets</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -7943,27 +7943,27 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds</t>
+          <t>every feature set</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Logistic meta-learner on 3 base models</t>
+          <t>automated leak scan</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>stacking</t>
+          <t>guard</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Median weight share price/news/macro</t>
+          <t>Runs aborted on leak detection</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>29% / 38% / 33%</t>
+          <t>1 of 1</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -7978,17 +7978,17 @@
       </c>
       <c r="N96" s="4" t="inlineStr">
         <is>
-          <t>CLEANEST VERSION OF THE CENTRAL FINDING. A model free to weight the three sources however it likes splits ~1/3 each and leans MOST on news. If price carried signal and news did not, it would load onto price. Even allocation = nothing to prefer.</t>
+          <t>The guard previously only wrote a CSV and the run continued, reporting a fake +20.7pp edge while the summary line claimed 'clean'. A guard that does not stop the run is not a guard. Now raises SystemExit.</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>results/late_fusion/meta_weights_summary.csv</t>
+          <t>price_news_hybrid.py</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>resolves the ambiguous early-fusion result (high importance, zero gain)</t>
+          <t>4th leak caught in this project; all four flattered the model</t>
         </is>
       </c>
     </row>
@@ -8003,12 +8003,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Early vs late fusion ruled out as explanation</t>
+          <t>Late fusion (one model per source)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -8023,31 +8023,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>identical folds, both architectures</t>
+          <t>6 walk-forward folds, chronological base/meta split</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>early (concatenated) vs late (stacked)</t>
+          <t>XGBoost bases + Logistic meta-learner</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>stacking, h=1/5/10</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Late beats early significantly</t>
+          <t>Configurations beating baseline</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>1 of 6</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0.05</v>
+          <t>0 of 6</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>majority / persistence</t>
+        </is>
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
@@ -8056,17 +8058,17 @@
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>Rules out one candidate explanation for why published papers report gains: 'early fusion drowned the weak signals'. Giving news and macro dedicated models surfaces nothing. Still open: missing naive baselines, no publication lag, single favourable split, decomposition hybrids.</t>
+          <t>ARCHITECTURE WAS NOT THE CONSTRAINT. Separate models for price/news/macro combined by a meta-learner: 0/6 beat the baseline. Late fusion IS less bad than early fusion (better in 5/6) but beats it significantly in only 1/6 = chance.</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>late_fusion_folds.csv</t>
+          <t>results/late_fusion/late_fusion_summary.md</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>late_fusion_stacking.py</t>
+          <t>late_fusion_stacking.py; meta-learner trained on OUT-OF-FOLD base predictions</t>
         </is>
       </c>
     </row>
@@ -8081,17 +8083,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Reproduce-then-break ladder</t>
+          <t>Meta-learner weight allocation</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + BANKS composite</t>
+          <t>BANKS composite + HNB</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -8101,31 +8103,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>L0 paper-style -&gt; L3 walk-forward, one guard at a time</t>
+          <t>6 walk-forward folds</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost (best reported)</t>
+          <t>Logistic meta-learner on 3 base models</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>next-day price</t>
+          <t>stacking</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>L0 'macro improvement' %</t>
+          <t>Median weight share price/news/macro</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>+0.17 / -0.04</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
+          <t>29% / 38% / 33%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -8134,17 +8138,17 @@
       </c>
       <c r="N98" s="4" t="inlineStr">
         <is>
-          <t>REPRODUCTION FAILED - and that is the finding. Removing the publication lag, leaking the scaler and using a single split move the number by FRACTIONS OF A PERCENT. These three shortcuts are NOT the mechanism behind published macro gains.</t>
+          <t>CLEANEST VERSION OF THE CENTRAL FINDING. A model free to weight the three sources however it likes splits ~1/3 each and leans MOST on news. If price carried signal and news did not, it would load onto price. Even allocation = nothing to prefer.</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>results/reproduce_then_break/ladder_summary.md</t>
+          <t>results/late_fusion/meta_weights_summary.csv</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>reproduce_then_break.py; hypothesis was wrong, reported as such</t>
+          <t>resolves the ambiguous early-fusion result (high importance, zero gain)</t>
         </is>
       </c>
     </row>
@@ -8164,12 +8168,12 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>The likely real mechanism: no naive baseline</t>
+          <t>Early vs late fusion ruled out as explanation</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + BANKS composite</t>
+          <t>BANKS composite + HNB</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -8179,48 +8183,50 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>all ladder levels</t>
+          <t>identical folds, both architectures</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>all configs incl. naive</t>
+          <t>early (concatenated) vs late (stacked)</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>next-day price</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>R2 across every level</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="n">
-        <v>0.998</v>
+          <t>Late beats early significantly</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>1 of 6</t>
+        </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>0.9979</v>
-      </c>
-      <c r="M99" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.05</v>
+      </c>
+      <c r="M99" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>R2 is 0.9978-0.9984 at EVERY level for EVERY config - and naive scores 0.9979. A paper running this exact setup would truthfully report 'R2=0.998, MAPE=0.83%, outperforms benchmark'. The gain is model-vs-weaker-model, reported with metrics that cannot distinguish either from a random walk.</t>
+          <t>Rules out one candidate explanation for why published papers report gains: 'early fusion drowned the weak signals'. Giving news and macro dedicated models surfaces nothing. Still open: missing naive baselines, no publication lag, single favourable split, decomposition hybrids.</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ladder_summary.csv</t>
+          <t>late_fusion_folds.csv</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>DM p = 0.48-0.86 throughout; nothing significant</t>
+          <t>late_fusion_stacking.py</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8246,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Single split is the shortcut that matters most</t>
+          <t>Reproduce-then-break ladder</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -8255,12 +8261,12 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>L0-L2 single split vs L3 walk-forward</t>
+          <t>L0 paper-style -&gt; L3 walk-forward, one guard at a time</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Ridge + XGBoost (best reported)</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -8270,37 +8276,35 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>MAPE(macro)/MAPE(naive)</t>
+          <t>L0 'macro improvement' %</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0.96-0.98 -&gt; 1.027</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="M100" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>+0.17 / -0.04</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N100" s="4" t="inlineStr">
         <is>
-          <t>Under single-split levels price+macro sits BELOW naive (0.964-0.980); under walk-forward it crosses ABOVE 1.0 on both targets. Of the three shortcuts tested, the single split changes the conclusion; the other two do not. 4th confirmation of the window effect.</t>
+          <t>REPRODUCTION FAILED - and that is the finding. Removing the publication lag, leaking the scaler and using a single split move the number by FRACTIONS OF A PERCENT. These three shortcuts are NOT the mechanism behind published macro gains.</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ladder_all.csv</t>
+          <t>results/reproduce_then_break/ladder_summary.md</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>argues for walk-forward as the default reporting protocol</t>
+          <t>reproduce_then_break.py; hypothesis was wrong, reported as such</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8324,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>DECOMPOSITION LEAK - the mechanism found</t>
+          <t>The likely real mechanism: no naive baseline</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -8335,33 +8339,29 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20, identical model/data, only pipeline ORDER differs</t>
+          <t>all ladder levels</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>wavelet(db4,3) + CEEMDAN -&gt; Ridge/XGBoost</t>
+          <t>all configs incl. naive</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead price</t>
+          <t>next-day price</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Improvement over naive: leaky vs honest</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>+19.2% vs -6.9%</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>naive</t>
-        </is>
+          <t>R2 across every level</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0.9979</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -8370,17 +8370,17 @@
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>★ THE MECHANISM. Decomposing the FULL series BEFORE splitting creates a 13-26pp improvement out of nothing. Wavelet/CEEMDAN are GLOBAL transforms: component values at time t are computed from the whole series, so training components carry test-period information and test components were built from their own future.</t>
+          <t>R2 is 0.9978-0.9984 at EVERY level for EVERY config - and naive scores 0.9979. A paper running this exact setup would truthfully report 'R2=0.998, MAPE=0.83%, outperforms benchmark'. The gain is model-vs-weaker-model, reported with metrics that cannot distinguish either from a random walk.</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>results/decomposition_leak/decomposition_summary.md</t>
+          <t>ladder_summary.csv</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>decomposition_leak_test.py; explains the gap between published hybrid results and this project</t>
+          <t>DM p = 0.48-0.86 throughout; nothing significant</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Leaky decomposition is highly significant</t>
+          <t>Single split is the shortcut that matters most</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -8415,50 +8415,52 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20</t>
+          <t>L0-L2 single split vs L3 walk-forward</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>wavelet + CEEMDAN, leaky pipeline</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead price</t>
+          <t>next-day price</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>DM p vs naive (4 configs)</t>
+          <t>MAPE(macro)/MAPE(naive)</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0.0000-0.0199</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M102" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>0.96-0.98 -&gt; 1.027</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="M102" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
-          <t>ALL FOUR leaky configurations beat naive significantly (Theil U2 0.794-0.871, DM p&lt;0.02, two at p&lt;0.0001). These are exactly the numbers decomposition-hybrid papers report.</t>
+          <t>Under single-split levels price+macro sits BELOW naive (0.964-0.980); under walk-forward it crosses ABOVE 1.0 on both targets. Of the three shortcuts tested, the single split changes the conclusion; the other two do not. 4th confirmation of the window effect.</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>decomposition_results.csv</t>
+          <t>ladder_all.csv</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>the result is real as computed - it is the pipeline that is wrong</t>
+          <t>argues for walk-forward as the default reporting protocol</t>
         </is>
       </c>
     </row>
@@ -8478,70 +8480,228 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
+          <t>DECOMPOSITION LEAK - the mechanism found</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>fixed 80/20, identical model/data, only pipeline ORDER differs</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>wavelet(db4,3) + CEEMDAN -&gt; Ridge/XGBoost</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>one-step-ahead price</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Improvement over naive: leaky vs honest</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>+19.2% vs -6.9%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M103" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N103" s="4" t="inlineStr">
+        <is>
+          <t>★ THE MECHANISM. Decomposing the FULL series BEFORE splitting creates a 13-26pp improvement out of nothing. Wavelet/CEEMDAN are GLOBAL transforms: component values at time t are computed from the whole series, so training components carry test-period information and test components were built from their own future.</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>results/decomposition_leak/decomposition_summary.md</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>decomposition_leak_test.py; explains the gap between published hybrid results and this project</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Leaky decomposition is highly significant</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>fixed 80/20</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>wavelet + CEEMDAN, leaky pipeline</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>one-step-ahead price</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>DM p vs naive (4 configs)</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>0.0000-0.0199</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M104" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N104" s="4" t="inlineStr">
+        <is>
+          <t>ALL FOUR leaky configurations beat naive significantly (Theil U2 0.794-0.871, DM p&lt;0.02, two at p&lt;0.0001). These are exactly the numbers decomposition-hybrid papers report.</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>decomposition_results.csv</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>the result is real as computed - it is the pipeline that is wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
           <t>Honest decomposition loses to naive</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>S&amp;P SL 20 + BANKS composite</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>fixed 80/20, decompose only series[:t] at each t</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>wavelet + CEEMDAN, honest pipeline</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr">
         <is>
           <t>one-step-ahead price</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr">
+      <c r="J105" s="2" t="inlineStr">
         <is>
           <t>Theil U2 (4 configs)</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="K105" s="2" t="inlineStr">
         <is>
           <t>1.008-1.028</t>
         </is>
       </c>
-      <c r="L103" s="2" t="n">
+      <c r="L105" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M103" s="5" t="inlineStr">
+      <c r="M105" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N103" s="4" t="inlineStr">
+      <c r="N105" s="4" t="inlineStr">
         <is>
           <t>Same models, same data, decomposition restricted to past data only: ALL FOUR configs are WORSE than a random walk and none significant (DM p 0.35-0.84). The decomposition advantage does not survive an honest pipeline.</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="O105" s="2" t="inlineStr">
         <is>
           <t>decomposition_results.csv</t>
         </is>
       </c>
-      <c r="P103" s="2" t="inlineStr">
+      <c r="P105" s="2" t="inlineStr">
         <is>
           <t>honest CEEMDAN re-decomposes every 3rd point for runtime; wavelet every point</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P103"/>
+  <autoFilter ref="A1:P105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P105"/>
+  <dimension ref="A1:P108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2538,17 +2538,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Ensemble</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Phase A multi-horizon direction</t>
+          <t>MH combine (AVG2/AVG3/SWITCH)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2563,52 +2563,52 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge</t>
+          <t>80/20 blind, val-tail weights</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>AVG2(AR+RF) / AVG3 / SWITCH</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons (1d-252d)</t>
+          <t>direct, 11 horizons, price MAPE</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Horizons beating baseline</t>
+          <t>horizons beating naive (of 11)</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0 of 9</t>
+          <t>AVG2: 6/11</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>majority / persistence</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>Yes (long horizon)</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>NO EDGE AT ANY HORIZON. Best model always below best baseline; gap widens with horizon (-3.5pp @1d -&gt; -47.1pp @1yr) because long-horizon drift makes the dumb baseline huge (maj 78% @6mo, pers 77% @1yr).</t>
+          <t>AVG2=mean(ARIMAX,RF) beats naive 6/11, esp long: 1yr 25.6 vs 34.7, 6mo 16.4 vs 19.5. Single models beat naive 0-4/11. Errors cancel (ARIMAX too flat + RF too wild). CNN-LSTM drags AVG3 down. SWITCH=RF (no gain). Short 1d-5d still naive.</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>results/direction/multi_horizon/mh_summary.md</t>
+          <t>results/mh_models/HNB_ensemble.csv</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>direction_multi_horizon.py; Tier-1 only; dead-zone +/-0.5%*sqrt(h)</t>
+          <t>mh_ensemble.py HNB</t>
         </is>
       </c>
     </row>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Ensemble</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Phase A best single horizon</t>
+          <t>MH combine (AVG2/AVG3/SWITCH)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>HNB</t>
+          <t>JKH</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2643,48 +2643,52 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge</t>
+          <t>80/20 blind, val-tail weights</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Logistic</t>
+          <t>AVG2(AR+RF) / AVG3 / SWITCH</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>direct, h=22d (1 month)</t>
+          <t>direct, 11 horizons, price MAPE</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Accuracy %</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>horizons beating naive (of 11)</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>AVG2: 6/11</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>Yes (long horizon)</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>Best model result of the sweep (1-month Logistic 40.1%) still loses to persistence 42.1%. Logistic &gt; XGBoost at every horizon -&gt; no nonlinear structure to find.</t>
+          <t>Confirms HNB. AVG2 beats naive 6/11: 1mo 3.85 vs 3.99, 3mo 8.68 vs 9.57, 6mo 10.80 vs 12.81, 1yr 15.12 vs 16.50. Short 1d-5d still naive. First result to consistently beat naive at long range across 2 tickers.</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>mh_direction_table.csv</t>
+          <t>results/mh_models/JKH_ensemble.csv</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>edge -2.0pp</t>
+          <t>mh_ensemble.py JKH</t>
         </is>
       </c>
     </row>
@@ -2694,22 +2698,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Ensemble</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Phase A multi-horizon return %</t>
+          <t>AVG2 combo robustness (7 tickers)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>HNB</t>
+          <t>HNB/JKH/COMB/SAMP/LOLC/DIAL/CTC</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2719,48 +2723,52 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge</t>
+          <t>80/20 blind</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>AVG2 = mean(ARIMAX,RF)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons (1d-252d)</t>
+          <t>direct, 11 horizons, price MAPE vs naive</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>RMSE ratio vs train-mean</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>Tie</t>
+          <t>1-year: combo beats naive?</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>7 of 7 tickers</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>Yes — robust at long horizon</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>Ridge beats naive-0 at 8/9 horizons BUT is only ~1% better than train-mean drift -&gt; it learned drift, NOT signal. XGBoost worse than naive everywhere (ratio 1.01-1.14).</t>
+          <t>LUCK CHECK across 7 stocks / 5 sectors. At 1yr combo beats naive in ALL 7 (e.g. HNB 25.6vs34.6, COMB 24.1vs33.1, CTC 15.1vs24.2). 6mo blue for all 7. SHORT 1d-1mo = tie (near 0). MID 2-3mo mixed: wins banks+CTC, LOSES on DIAL (-7.8@6mo... recovers) and LOLC. Honest claim: averaging ARIMAX+RF reliably cuts 6-12mo price error below naive across sectors; short/mid not reliable.</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>mh_return_table.csv</t>
+          <t>results/mh_models/ensemble_robustness_heatmap.png</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>train-mean is the honest null, not naive-0</t>
+          <t>mh_ensemble.py x7</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2783,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Phase A return sign accuracy</t>
+          <t>Phase A multi-horizon direction</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2800,27 +2808,27 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>direct, sign of h-day return</t>
+          <t>direct, 9 horizons (1d-252d)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Horizons beating sign null</t>
+          <t>Horizons beating baseline</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2 of 9</t>
+          <t>0 of 9</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>always-guess-winning-side</t>
+          <t>majority / persistence</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
@@ -2830,17 +2838,17 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>TRAP CHECK: 55-57% sign accuracy @1-3mo looks like the 52-58% target but 'always guess up' matches/beats it (test window drifted up 59-95%). Both 'wins' are +0.2pp = noise.</t>
+          <t>NO EDGE AT ANY HORIZON. Best model always below best baseline; gap widens with horizon (-3.5pp @1d -&gt; -47.1pp @1yr) because long-horizon drift makes the dumb baseline huge (maj 78% @6mo, pers 77% @1yr).</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>mh_edge_vs_horizon.png</t>
+          <t>results/direction/multi_horizon/mh_summary.md</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>up-share null added to stop false positive</t>
+          <t>direction_multi_horizon.py; Tier-1 only; dead-zone +/-0.5%*sqrt(h)</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2868,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Phase B ablation (+Tier-2)</t>
+          <t>Phase A best single horizon</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2875,29 +2883,29 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds, A vs B</t>
+          <t>80/20 chrono + h-bar purge</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Logistic</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, ablation</t>
+          <t>direct, h=22d (1 month)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from Tier-2 (pp)</t>
+          <t>Accuracy %</t>
         </is>
       </c>
       <c r="K31" s="2" t="n">
-        <v>-0.9</v>
+        <v>40.1</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>42.1</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
@@ -2906,17 +2914,17 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>RSI+MACD+volume add NOTHING. Mean -0.9pp, 0/9 beat baseline. Technical indicators exhausted.</t>
+          <t>Best model result of the sweep (1-month Logistic 40.1%) still loses to persistence 42.1%. Logistic &gt; XGBoost at every horizon -&gt; no nonlinear structure to find.</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>results/direction/phase_ablation/ablation_summary.md</t>
+          <t>mh_direction_table.csv</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_ablation.py; 9 -&gt; 16 features; value restated on the 4-phase run (macro availability trims early rows)</t>
+          <t>edge -2.0pp</t>
         </is>
       </c>
     </row>
@@ -2931,12 +2939,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Phase B feature attention check</t>
+          <t>Phase A multi-horizon return %</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2951,50 +2959,48 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>80/20 chrono + h-bar purge</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>XGBoost importance</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, 9 horizons (1d-252d)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Tier-2 share of importance %</t>
+          <t>RMSE ratio vs train-mean</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M32" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.99</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Tie</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>XGBoost spends 41% of importance on Tier-2 (macd_signal is top feature at 6/9 horizons) yet accuracy does not improve -&gt; the model USES them but they carry no signal.</t>
+          <t>Ridge beats naive-0 at 8/9 horizons BUT is only ~1% better than train-mean drift -&gt; it learned drift, NOT signal. XGBoost worse than naive everywhere (ratio 1.01-1.14).</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ablation_tier2_importance.csv</t>
+          <t>mh_return_table.csv</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>strong evidence indicators are redundant with price</t>
+          <t>train-mean is the honest null, not naive-0</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3020,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Phase B return % (+Tier-2)</t>
+          <t>Phase A return sign accuracy</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3029,48 +3035,52 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>80/20 chrono + h-bar purge</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, sign of h-day return</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>RMSE ratio vs train-mean (B)</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>Tie</t>
+          <t>Horizons beating sign null</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>2 of 9</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>always-guess-winning-side</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>Tier-2 made return RMSE slightly WORSE at 9/9 horizons (ratio gain +0.000 to +0.046). Sign edge stays negative everywhere.</t>
+          <t>TRAP CHECK: 55-57% sign accuracy @1-3mo looks like the 52-58% target but 'always guess up' matches/beats it (test window drifted up 59-95%). Both 'wins' are +0.2pp = noise.</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ablation_return_table.csv</t>
+          <t>mh_edge_vs_horizon.png</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>A ratio 0.991 -&gt; B ratio 0.991-1.034</t>
+          <t>up-share null added to stop false positive</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3100,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Phase C ablation (+macro rates)</t>
+          <t>Phase B ablation (+Tier-2)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3105,7 +3115,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds, 35d publication lag</t>
+          <t>identical rows/split/seeds, A vs B</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3120,11 +3130,11 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from macro (pp)</t>
+          <t>Mean gain from Tier-2 (pp)</t>
         </is>
       </c>
       <c r="K34" s="2" t="n">
-        <v>-2.8</v>
+        <v>-0.9</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -3136,7 +3146,7 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>Macro rates make it WORSE and unstable: gain swings -22.3 to +10.3 pp, 0/9 beat baseline. Not weak signal - overfitting.</t>
+          <t>RSI+MACD+volume add NOTHING. Mean -0.9pp, 0/9 beat baseline. Technical indicators exhausted.</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -3146,7 +3156,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_ablation.py; 16 -&gt; 29 features; inflation/FX/M2 still uncollected</t>
+          <t>direction_phase_ablation.py; 9 -&gt; 16 features; value restated on the 4-phase run (macro availability trims early rows)</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3176,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Phase C2 diagnostic (macro changes only)</t>
+          <t>Phase B feature attention check</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3186,24 +3196,26 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>XGBoost importance</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, ablation</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from macro d (pp)</t>
+          <t>Tier-2 share of importance %</t>
         </is>
       </c>
       <c r="K35" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>-2.8</v>
+        <v>41</v>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -3212,17 +3224,17 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>DROPPING RATE LEVELS FIXES THE DAMAGE (-2.8 -&gt; +3.4 pp; 1yr 4.5% -&gt; 49.7%). Non-stationary levels were being memorised. Still 0/9 beat baseline -&gt; form was wrong AND no signal.</t>
+          <t>XGBoost spends 41% of importance on Tier-2 (macd_signal is top feature at 6/9 horizons) yet accuracy does not improve -&gt; the model USES them but they carry no signal.</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ablation_gain_table.csv</t>
+          <t>ablation_tier2_importance.csv</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>key methodology lesson: feed macro as changes, never levels</t>
+          <t>strong evidence indicators are redundant with price</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3249,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Phase C feature attention check</t>
+          <t>Phase B return % (+Tier-2)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3262,7 +3274,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>XGBoost importance</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -3272,35 +3284,33 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Macro share of importance %</t>
+          <t>RMSE ratio vs train-mean (B)</t>
         </is>
       </c>
       <c r="K36" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M36" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.991</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Tie</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Macro importance rises 46% (1d) -&gt; 80% (1yr) while accuracy FALLS. Model fits rates as a trend proxy, not signal. tb_12m/spread/policy_rate are top features at 8/9 horizons.</t>
+          <t>Tier-2 made return RMSE slightly WORSE at 9/9 horizons (ratio gain +0.000 to +0.046). Sign edge stays negative everywhere.</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ablation_feature_importance.csv</t>
+          <t>ablation_return_table.csv</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>fingerprint of trending-variable overfit</t>
+          <t>A ratio 0.991 -&gt; B ratio 0.991-1.034</t>
         </is>
       </c>
     </row>
@@ -3315,12 +3325,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Phase C return % (+macro)</t>
+          <t>Phase C ablation (+macro rates)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3335,29 +3345,29 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>identical rows/split/seeds, 35d publication lag</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, 9 horizons, ablation</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>RMSE ratio vs train-mean (C)</t>
+          <t>Mean gain from macro (pp)</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1.37</v>
+        <v>-2.8</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0.995</v>
+        <v>0</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
@@ -3366,17 +3376,17 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>Macro blows out return RMSE to 1.29-1.37x the train-mean null (A/B sat at ~0.99). Clear damage, confirms the overfit reading.</t>
+          <t>Macro rates make it WORSE and unstable: gain swings -22.3 to +10.3 pp, 0/9 beat baseline. Not weak signal - overfitting.</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ablation_return_table.csv</t>
+          <t>results/direction/phase_ablation/ablation_summary.md</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>worst at 2-3 month horizons</t>
+          <t>direction_phase_ablation.py; 16 -&gt; 29 features; inflation/FX/M2 still uncollected</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3406,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Phase D ablation (+sector)</t>
+          <t>Phase C2 diagnostic (macro changes only)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3426,33 +3436,33 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from sector (pp)</t>
+          <t>Mean gain from macro d (pp)</t>
         </is>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>-2.8</v>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>FIRST consistently POSITIVE step: +2.6pp mean, positive at 6/9 horizons. Built on C2 (macro changes only). But still 0/9 beat baseline.</t>
+          <t>DROPPING RATE LEVELS FIXES THE DAMAGE (-2.8 -&gt; +3.4 pp; 1yr 4.5% -&gt; 49.7%). Non-stationary levels were being memorised. Still 0/9 beat baseline -&gt; form was wrong AND no signal.</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>results/direction/phase_ablation/ablation_summary.md</t>
+          <t>ablation_gain_table.csv</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_ablation.py; C2 16+7 -&gt; D 39 features; ASPI + COMB/SAMP + LOFC/LOLC/LFIN/CFIN</t>
+          <t>key methodology lesson: feed macro as changes, never levels</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3482,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Phase D best single horizon</t>
+          <t>Phase C feature attention check</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3492,43 +3502,45 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>XGBoost importance</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>direct, h=5d (1 week)</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Edge over baseline (pp)</t>
+          <t>Macro share of importance %</t>
         </is>
       </c>
       <c r="K39" s="2" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>64</v>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>Closest call of the whole study: 1-week Phase D 37.3% vs baseline 37.4%. Near-parity at short horizons (1d -1.7, 1wk -0.2, 2wk -1.6) but never crosses.</t>
+          <t>Macro importance rises 46% (1d) -&gt; 80% (1yr) while accuracy FALLS. Model fits rates as a trend proxy, not signal. tb_12m/spread/policy_rate are top features at 8/9 horizons.</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ablation_gain_table.csv</t>
+          <t>ablation_feature_importance.csv</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>not a win; single split, one stock</t>
+          <t>fingerprint of trending-variable overfit</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3560,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Phase D return sign edge (+sector)</t>
+          <t>Phase C return % (+macro)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3573,32 +3585,28 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>direct, sign of h-day return</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Sign edge 1wk/2wk/3wk (pp)</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>+1.7 / +1.7 / +1.1</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>always-guess-winning-side</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>Tie</t>
+          <t>RMSE ratio vs train-mean (C)</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>First POSITIVE sign edges in the study, and at 3 adjacent horizons (1-3 weeks). Tiny (~1-2pp) and one split only -&gt; flag as worth re-testing, NOT a finding.</t>
+          <t>Macro blows out return RMSE to 1.29-1.37x the train-mean null (A/B sat at ~0.99). Clear damage, confirms the overfit reading.</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3608,7 +3616,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>check on other tickers before claiming anything</t>
+          <t>worst at 2-3 month horizons</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3636,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Phase D feature attention check</t>
+          <t>Phase D ablation (+sector)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3648,45 +3656,43 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>XGBoost importance</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, 9 horizons, ablation</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Sector share of importance %</t>
+          <t>Mean gain from sector (pp)</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>2.6</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>Sector takes 34% avg (42% at 1 day, falling to 27% at 1yr) - mirror image of macro, which rises with horizon. Sector matters short, macro long, neither enough.</t>
+          <t>FIRST consistently POSITIVE step: +2.6pp mean, positive at 6/9 horizons. Built on C2 (macro changes only). But still 0/9 beat baseline.</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ablation_feature_importance.csv</t>
+          <t>results/direction/phase_ablation/ablation_summary.md</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>vol_20 is top feature at 1d/1wk; d_tb3m dominates long</t>
+          <t>direction_phase_ablation.py; C2 16+7 -&gt; D 39 features; ASPI + COMB/SAMP + LOFC/LOLC/LFIN/CFIN</t>
         </is>
       </c>
     </row>
@@ -3706,12 +3712,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Sector sweep - replication test</t>
+          <t>Phase D best single horizon</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks (3 banks, 4 finance, 4 control)</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3721,7 +3727,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge, per stock</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3731,23 +3737,19 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, h=5d (1 week)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Cells beating baseline</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>27 of 99</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>14 of 99 (Phase A)</t>
-        </is>
+          <t>Edge over baseline (pp)</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
@@ -3756,17 +3758,17 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>Sector features nearly DOUBLE the win rate vs Tier-1 (14-&gt;27 of 99) but wins sit at exactly coin-flip at short horizons and collapse at long ones. No real edge.</t>
+          <t>Closest call of the whole study: 1-week Phase D 37.3% vs baseline 37.4%. Near-parity at short horizons (1d -1.7, 1wk -0.2, 2wk -1.6) but never crosses.</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>results/direction/sector_sweep/sweep_summary.md</t>
+          <t>ablation_gain_table.csv</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>direction_sector_sweep.py; peer composites exclude the target stock</t>
+          <t>not a win; single split, one stock</t>
         </is>
       </c>
     </row>
@@ -3781,17 +3783,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Sector gain replication (HNB claim 3)</t>
+          <t>Phase D return sign edge (+sector)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3801,48 +3803,52 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>identical protocol per stock</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Phase D - Phase A</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, sign of h-day return</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Mean sector gain (pp)</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Sign edge 1wk/2wk/3wk (pp)</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>+1.7 / +1.7 / +1.1</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>always-guess-winning-side</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Tie</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>REPLICATES: +3.8pp mean, positive in 66/99 cells (67%), 9 of 11 stocks positive. HNB was not a fluke - sector context genuinely helps the model. Best: LFIN +13.2, SAMP +9.4, LOFC +8.2. Worst: CTC -11.0.</t>
+          <t>First POSITIVE sign edges in the study, and at 3 adjacent horizons (1-3 weeks). Tiny (~1-2pp) and one split only -&gt; flag as worth re-testing, NOT a finding.</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>sweep_gain_by_ticker.csv</t>
+          <t>ablation_return_table.csv</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>helping is not the same as winning</t>
+          <t>check on other tickers before claiming anything</t>
         </is>
       </c>
     </row>
@@ -3862,12 +3868,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Sector sweep significance screen</t>
+          <t>Phase D feature attention check</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3877,12 +3883,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>sign test + Wilcoxon across stocks, per horizon</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>binomial sign test (H0 p=0.5)</t>
+          <t>XGBoost importance</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -3892,33 +3898,35 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Best sign-test p</t>
+          <t>Sector share of importance %</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>34</v>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>NOTHING SIGNIFICANT AT ANY HORIZON. Best cells (1 day, 1 week) are 6/11 stocks positive = p=0.500, exactly a coin flip. Long horizons far worse (1yr 0/11).</t>
+          <t>Sector takes 34% avg (42% at 1 day, falling to 27% at 1yr) - mirror image of macro, which rises with horizon. Sector matters short, macro long, neither enough.</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>sweep_significance.csv</t>
+          <t>ablation_feature_importance.csv</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>stocks share a market factor so p-values are already optimistic</t>
+          <t>vol_20 is top feature at 1d/1wk; d_tb3m dominates long</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3946,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>HNB sign-edge claim retest (claim 2)</t>
+          <t>Sector sweep - replication test</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>11 CSE stocks (3 banks, 4 finance, 4 control)</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -3953,32 +3961,32 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>identical protocol per stock</t>
+          <t>80/20 chrono + h-bar purge, per stock</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>direct, sign of h-day return, 1-3 week horizons</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Cells with positive sign edge</t>
+          <t>Cells beating baseline</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>6 of 33</t>
+          <t>27 of 99</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>~17 of 33 (coin flip)</t>
+          <t>14 of 99 (Phase A)</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
@@ -3988,17 +3996,17 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>REFUTED. HNB's positive 1-3 week sign edge did NOT replicate - 18% vs the ~50% chance would give. It was luck. Flagged as provisional when found, now closed.</t>
+          <t>Sector features nearly DOUBLE the win rate vs Tier-1 (14-&gt;27 of 99) but wins sit at exactly coin-flip at short horizons and collapse at long ones. No real edge.</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>sweep_all_results.csv</t>
+          <t>results/direction/sector_sweep/sweep_summary.md</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>value of naming a claim before retesting it</t>
+          <t>direction_sector_sweep.py; peer composites exclude the target stock</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4026,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Phase E - daily USD/LKR</t>
+          <t>Sector gain replication (HNB claim 3)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4033,12 +4041,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge, 2015-2026 window</t>
+          <t>identical protocol per stock</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Phase D - Phase A</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -4048,33 +4056,33 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from daily FX (pp)</t>
+          <t>Mean sector gain (pp)</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>FREQUENCY WAS NOT THE PROBLEM. Daily FX gain is exactly 0.0pp (positive in 57/99 cells = coin flip). Macro fails daily exactly as it failed monthly.</t>
+          <t>REPLICATES: +3.8pp mean, positive in 66/99 cells (67%), 9 of 11 stocks positive. HNB was not a fluke - sector context genuinely helps the model. Best: LFIN +13.2, SAMP +9.4, LOFC +8.2. Worst: CTC -11.0.</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>results/direction/daily_macro/daily_macro_summary.md</t>
+          <t>sweep_gain_by_ticker.csv</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>direction_daily_macro.py; new cleaned_data/usd_lkr_daily.csv</t>
+          <t>helping is not the same as winning</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4102,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Phase E2 - daily global + CPI</t>
+          <t>Sector sweep significance screen</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4109,29 +4117,29 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>sign test + Wilcoxon across stocks, per horizon</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>binomial sign test (H0 p=0.5)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from global+CPI (pp)</t>
+          <t>Best sign-test p</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>-1.9</v>
+        <v>0.5</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
@@ -4140,17 +4148,17 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>Oil, US 10Y, DXY and inflation make it WORSE (-1.9pp), worst at long horizons (-6.0pp at 1yr). Same trending-variable overfit as Phase C.</t>
+          <t>NOTHING SIGNIFICANT AT ANY HORIZON. Best cells (1 day, 1 week) are 6/11 stocks positive = p=0.500, exactly a coin flip. Long horizons far worse (1yr 0/11).</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>daily_macro_gain.csv</t>
+          <t>sweep_significance.csv</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>CPI spliced across 4 base years; money supply excluded (ends 2024-08, inside test window)</t>
+          <t>stocks share a market factor so p-values are already optimistic</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4178,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Phase E significance screen</t>
+          <t>HNB sign-edge claim retest (claim 2)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4185,31 +4193,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>sign test across stocks, 4 phases x 9 horizons</t>
+          <t>identical protocol per stock</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>binomial sign test (H0 p=0.5)</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, sign of h-day return, 1-3 week horizons</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Combinations with p&lt;0.05</t>
+          <t>Cells with positive sign edge</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0 of 36</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0.05</v>
+          <t>6 of 33</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>~17 of 33 (coin flip)</t>
+        </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
@@ -4218,17 +4228,17 @@
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>NOTHING SIGNIFICANT ANYWHERE. Best cell is 1 day (6/11 stocks, p=0.500) - exact coin flip, same as the sector sweep. Cells beating baseline: A 17, D 27, E 24, E2 25 of 99.</t>
+          <t>REFUTED. HNB's positive 1-3 week sign edge did NOT replicate - 18% vs the ~50% chance would give. It was luck. Flagged as provisional when found, now closed.</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>daily_macro_significance.csv</t>
+          <t>sweep_all_results.csv</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>macro information source now closed at both frequencies</t>
+          <t>value of naming a claim before retesting it</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4258,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Phase E feature attention check</t>
+          <t>Phase E - daily USD/LKR</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4263,12 +4273,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>80/20 chrono + h-bar purge, 2015-2026 window</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>XGBoost importance</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -4278,35 +4288,33 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>New-data share of importance %</t>
+          <t>Mean gain from daily FX (pp)</t>
         </is>
       </c>
       <c r="K49" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M49" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>Model spends 27% of importance on the new data (FX 7%, global 11%, CPI 9%) and gains nothing - third time this fingerprint has appeared (Tier-2 41%, macro 64%, now 27%).</t>
+          <t>FREQUENCY WAS NOT THE PROBLEM. Daily FX gain is exactly 0.0pp (positive in 57/99 cells = coin flip). Macro fails daily exactly as it failed monthly.</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>daily_macro_all_results.csv</t>
+          <t>results/direction/daily_macro/daily_macro_summary.md</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>using a feature is not the same as profiting from it</t>
+          <t>direction_daily_macro.py; new cleaned_data/usd_lkr_daily.csv</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4334,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Phase F - money supply (M1/M2/M2b/M4)</t>
+          <t>Phase E2 - daily global + CPI</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4341,7 +4349,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono, sample cut at 2024-08; test 2022-03 to 2024-08</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4356,11 +4364,11 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from money supply (pp)</t>
+          <t>Mean gain from global+CPI (pp)</t>
         </is>
       </c>
       <c r="K50" s="2" t="n">
-        <v>-0.7</v>
+        <v>-1.9</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -4372,17 +4380,17 @@
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>Money supply adds NOTHING even on a crisis-era test window (positive in 50/99 cells = exact coin flip). Window moved back so M1/M2 could be tested fairly rather than excluded.</t>
+          <t>Oil, US 10Y, DXY and inflation make it WORSE (-1.9pp), worst at long horizons (-6.0pp at 1yr). Same trending-variable overfit as Phase C.</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>results/direction/money_supply/money_summary.md</t>
+          <t>daily_macro_gain.csv</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>direction_money_supply.py; 65-day publication lag per CBSL's own note; reserve money dropped (ends 2024-02)</t>
+          <t>CPI spliced across 4 base years; money supply excluded (ends 2024-08, inside test window)</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4410,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Phase F - full classic macro set</t>
+          <t>Phase E significance screen</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4417,29 +4425,31 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>sign test across stocks, 4 phases x 9 horizons</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>binomial sign test (H0 p=0.5)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Mean gain money-&gt;full macro (pp)</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>1.1</v>
+          <t>Combinations with p&lt;0.05</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>0 of 36</t>
+        </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
@@ -4448,17 +4458,17 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>Full classic set (money + rates + FX + inflation) = 4 of the 5 Naik-Padhi variables. Still 42/99 cells, below the money-only phase (51/99). Only industrial production remains uncollected.</t>
+          <t>NOTHING SIGNIFICANT ANYWHERE. Best cell is 1 day (6/11 stocks, p=0.500) - exact coin flip, same as the sector sweep. Cells beating baseline: A 17, D 27, E 24, E2 25 of 99.</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>money_gain.csv</t>
+          <t>daily_macro_significance.csv</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>closes the macro chapter apart from IIP</t>
+          <t>macro information source now closed at both frequencies</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4488,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Crisis-window effect (window sensitivity)</t>
+          <t>Phase E feature attention check</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4493,12 +4503,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2022-03 to 2024-08 vs 2024-2026</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>XGBoost importance</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -4508,17 +4518,15 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Cells beating baseline</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>43-51 of 99</t>
-        </is>
+          <t>New-data share of importance %</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>27</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>17-27 of 99 (calm window)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M52" s="6" t="inlineStr">
@@ -4528,17 +4536,17 @@
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>IMPORTANT METHOD FINDING: moving the test window into the 2022 crisis roughly DOUBLES the win rate for ALL phases including price-only. Results are window-dependent, not model-dependent.</t>
+          <t>Model spends 27% of importance on the new data (FX 7%, global 11%, CPI 9%) and gains nothing - third time this fingerprint has appeared (Tier-2 41%, macro 64%, now 27%).</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>money_by_horizon.csv</t>
+          <t>daily_macro_all_results.csv</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>argues for walk-forward / multi-window evaluation in the write-up</t>
+          <t>using a feature is not the same as profiting from it</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4566,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1-day significance - macro ruled out</t>
+          <t>Phase F - money supply (M1/M2/M2b/M4)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -4573,33 +4581,29 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>sign test across stocks, 4 phases x 9 horizons</t>
+          <t>80/20 chrono, sample cut at 2024-08; test 2022-03 to 2024-08</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>binomial sign test (H0 p=0.5)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Cells with p&lt;0.05</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>2 of 36</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>1.8 expected by chance</t>
-        </is>
+          <t>Mean gain from money supply (pp)</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
@@ -4608,17 +4612,17 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>Both hits are at 1 day, and the STRONGEST is Phase A (price only, 9/11, +3.9pp, p=0.033). Adding money supply SHRINKS it to +3.2pp. So it is the crisis window, not macro - and 2/36 is chance anyway.</t>
+          <t>Money supply adds NOTHING even on a crisis-era test window (positive in 50/99 cells = exact coin flip). Window moved back so M1/M2 could be tested fairly rather than excluded.</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>money_significance.csv</t>
+          <t>results/direction/money_supply/money_summary.md</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>checking the null model is what prevented a false claim</t>
+          <t>direction_money_supply.py; 65-day publication lag per CBSL's own note; reserve money dropped (ends 2024-02)</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4632,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4638,7 +4642,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Phase G - industrial production (IIP)</t>
+          <t>Phase F - full classic macro set</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4653,7 +4657,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono, sample 2016-2026 (IIP coverage)</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4668,11 +4672,11 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from IIP (pp)</t>
+          <t>Mean gain money-&gt;full macro (pp)</t>
         </is>
       </c>
       <c r="K54" s="2" t="n">
-        <v>-6.4</v>
+        <v>1.1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -4684,17 +4688,17 @@
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>IIP makes it WORSE (-6.4pp, positive in only 25/99 cells, 0/36 significant). It was the STRONGEST variable in the Naik-Padhi reference paper, and it still does not predict direction.</t>
+          <t>Full classic set (money + rates + FX + inflation) = 4 of the 5 Naik-Padhi variables. Still 42/99 cells, below the money-only phase (51/99). Only industrial production remains uncollected.</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>results/direction/industrial_production/iip_summary.md</t>
+          <t>money_gain.csv</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>direction_industrial_production.py; DCS index entered by hand, 2016-01 to 2026-05; 50-day publication lag</t>
+          <t>closes the macro chapter apart from IIP</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4708,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4714,7 +4718,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Phase G - full classic macro set complete</t>
+          <t>Crisis-window effect (window sensitivity)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -4729,7 +4733,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>2022-03 to 2024-08 vs 2024-2026</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4749,32 +4753,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>25 of 99</t>
+          <t>43-51 of 99</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>27 of 99 (no macro)</t>
-        </is>
-      </c>
-      <c r="M55" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>17-27 of 99 (calm window)</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>ALL FIVE Naik-Padhi macro variables now tested (IIP, money supply, T-bill rate, exchange rate, inflation). NONE beats plain price history. Macro chapter complete.</t>
+          <t>IMPORTANT METHOD FINDING: moving the test window into the 2022 crisis roughly DOUBLES the win rate for ALL phases including price-only. Results are window-dependent, not model-dependent.</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>iip_gain.csv</t>
+          <t>money_by_horizon.csv</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>adding all macro is WORSE than sector-only (27/99)</t>
+          <t>argues for walk-forward / multi-window evaluation in the write-up</t>
         </is>
       </c>
     </row>
@@ -4784,77 +4788,77 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>IIP seasonality guard</t>
+          <t>1-day significance - macro ruled out</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Sri Lanka DCS IIP</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>monthly (125)</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>2016-01 to 2026-05</t>
+          <t>sign test across stocks, 4 phases x 9 horizons</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>seasonal inspection</t>
+          <t>binomial sign test (H0 p=0.5)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>April vs March gap (pts)</t>
+          <t>Cells with p&lt;0.05</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-10 to -34</t>
+          <t>2 of 36</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M56" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>1.8 expected by chance</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>IIP is NOT seasonally adjusted - April falls 10-34 pts EVERY year (Sinhala/Tamil New Year), March always peaks. Month-on-month would be a calendar signal, so YoY-only features were used.</t>
+          <t>Both hits are at 1 day, and the STRONGEST is Phase A (price only, 9/11, +3.9pp, p=0.033). Adding money supply SHRINKS it to +3.2pp. So it is the crisis window, not macro - and 2/36 is chance anyway.</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>cleaned_data/industrial_production_monthly.csv</t>
+          <t>money_significance.csv</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>clean_macro_sources.py; mom column deliberately named _DO_NOT_USE</t>
+          <t>checking the null model is what prevented a false claim</t>
         </is>
       </c>
     </row>
@@ -4869,17 +4873,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Correlation</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Co-movement lift table (no model)</t>
+          <t>Phase G - industrial production (IIP)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks (22,677 stock-days)</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -4889,48 +4893,48 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>full panel, 15 indicators x 9 horizons</t>
+          <t>80/20 chrono, sample 2016-2026 (IIP coverage)</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>conditional probability + 2-proportion z</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Median |lift| short horizons (pp)</t>
+          <t>Mean gain from IIP (pp)</t>
         </is>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2.5</v>
+        <v>-6.4</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M57" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>'If indicator up, does stock go up?' answered by pure counting. Market/peer indicators give a real +6 to +10pp lift at 1d-1mo on huge samples. Macro lifts are near zero at short horizons.</t>
+          <t>IIP makes it WORSE (-6.4pp, positive in only 25/99 cells, 0/36 significant). It was the STRONGEST variable in the Naik-Padhi reference paper, and it still does not predict direction.</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>results/direction/pooled_rules/comovement_table.csv</t>
+          <t>results/direction/industrial_production/iip_summary.md</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>direction_pooled_and_rules.py; lift = P(up|ind up) - P(up|ind down)</t>
+          <t>direction_industrial_production.py; DCS index entered by hand, 2016-01 to 2026-05; 50-day publication lag</t>
         </is>
       </c>
     </row>
@@ -4945,17 +4949,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Correlation</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Co-movement - long-horizon lifts are artifacts</t>
+          <t>Phase G - full classic macro set complete</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -4965,32 +4969,32 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>panel, |lift|&gt;=10pp cells</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>independent-window audit</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Independent windows behind biggest lifts</t>
+          <t>Cells beating baseline</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>7-24</t>
+          <t>25 of 99</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>hundreds needed</t>
+          <t>27 of 99 (no macro)</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
@@ -5000,17 +5004,17 @@
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>All 19 large lifts (T-bill -19.3, M2 +17.0, USD/LKR -15.3) sit at 3mo-1yr where only 7-24 INDEPENDENT windows exist. Overlapping windows inflate the z-test. Discard them.</t>
+          <t>ALL FIVE Naik-Padhi macro variables now tested (IIP, money supply, T-bill rate, exchange rate, inflation). NONE beats plain price history. Macro chapter complete.</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>comovement_table.csv</t>
+          <t>iip_gain.csv</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>median |lift| long 4.2pp vs short 2.5pp is a sample-size illusion</t>
+          <t>adding all macro is WORSE than sector-only (27/99)</t>
         </is>
       </c>
     </row>
@@ -5025,72 +5029,72 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Pooled panel model (sector-wide)</t>
+          <t>IIP seasonality guard</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks pooled</t>
+          <t>Sri Lanka DCS IIP</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly (125)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>split by DATE not row, 17,770 train rows</t>
+          <t>2016-01 to 2026-05</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>seasonal inspection</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, one model for whole sector</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Horizons beating pooled baseline</t>
+          <t>April vs March gap (pts)</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>2 of 9</t>
+          <t>-10 to -34</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>majority / persistence</t>
-        </is>
-      </c>
-      <c r="M59" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M59" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>7x more training data (17,770 vs ~2,700 per stock). Beats the POOLED baseline at 1 day (+3.3pp) and 1 week (+2.7pp) only.</t>
+          <t>IIP is NOT seasonally adjusted - April falls 10-34 pts EVERY year (Sinhala/Tamil New Year), March always peaks. Month-on-month would be a calendar signal, so YoY-only features were used.</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>results/direction/pooled_rules/pooled_model_results.csv</t>
+          <t>cleaned_data/industrial_production_monthly.csv</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>direction_pooled_and_rules.py</t>
+          <t>clean_macro_sources.py; mom column deliberately named _DO_NOT_USE</t>
         </is>
       </c>
     </row>
@@ -5105,17 +5109,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Correlation</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Pooled model fairness check</t>
+          <t>Co-movement lift table (no model)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>7 bank/finance stocks (22,677 stock-days)</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -5125,52 +5129,48 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>pooled model scored vs each stock's OWN baseline</t>
+          <t>full panel, 15 indicators x 9 horizons</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>binomial sign test (H0 p=0.5)</t>
+          <t>conditional probability + 2-proportion z</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>1-day: stocks positive</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>6 of 7</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>p=0.062</t>
-        </is>
-      </c>
-      <c r="M60" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Median |lift| short horizons (pp)</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>STRONGEST RESULT OF THE PROJECT but still not significant. The 1-week +2.7pp was a POOLING ARTIFACT (-0.5pp vs own baselines). Only 1 day survives: median +2.5pp, p=0.062, 1 of 9 horizons, single window.</t>
+          <t>'If indicator up, does stock go up?' answered by pure counting. Market/peer indicators give a real +6 to +10pp lift at 1d-1mo on huge samples. Macro lifts are near zero at short horizons.</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>pooled_vs_own_baseline.csv</t>
+          <t>results/direction/pooled_rules/comovement_table.csv</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>pooling stocks with different class balance weakens the majority baseline and fakes an edge</t>
+          <t>direction_pooled_and_rules.py; lift = P(up|ind up) - P(up|ind down)</t>
         </is>
       </c>
     </row>
@@ -5185,17 +5185,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Correlation</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Readable rules extracted</t>
+          <t>Co-movement - long-horizon lifts are artifacts</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks pooled</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -5205,48 +5205,52 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>depth-3 tree, scored on unseen test set</t>
+          <t>panel, |lift|&gt;=10pp cells</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Decision tree (depth 3)</t>
+          <t>independent-window audit</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/22</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Best 1-day rule accuracy %</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="M61" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Independent windows behind biggest lifts</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>7-24</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>hundreds needed</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>17 plain-English rules with out-of-sample hit rates. Best 1-day rule: calm market + flat ASPI + no big drop -&gt; Hold, 49.3% (+11.3pp). Shows WHAT the model believes, not just that it fails.</t>
+          <t>All 19 large lifts (T-bill -19.3, M2 +17.0, USD/LKR -15.3) sit at 3mo-1yr where only 7-24 INDEPENDENT windows exist. Overlapping windows inflate the z-test. Discard them.</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>readable_rules.csv</t>
+          <t>comovement_table.csv</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1-month rule at 68.5% fires only 317 times - treat as noise</t>
+          <t>median |lift| long 4.2pp vs short 2.5pp is a sample-size illusion</t>
         </is>
       </c>
     </row>
@@ -5266,12 +5270,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1-day claim re-test (walk-forward)</t>
+          <t>Pooled panel model (sector-wide)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>7 bank/finance stocks pooled</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -5281,32 +5285,32 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>21 non-overlapping 6-month windows, expanding train</t>
+          <t>split by DATE not row, 17,770 train rows</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost (reported separately)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>direct, walk-forward, h=1</t>
+          <t>direct, 9 horizons, one model for whole sector</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Folds with positive median edge</t>
+          <t>Horizons beating pooled baseline</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>6-7 of 21</t>
+          <t>2 of 9</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>10.5 expected by chance</t>
+          <t>majority / persistence</t>
         </is>
       </c>
       <c r="M62" s="5" t="inlineStr">
@@ -5316,17 +5320,17 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>CLAIM REFUTED. Median of fold medians -1.8pp (Logistic) / -1.9pp (XGBoost), sign-test p=0.96 and 0.99. The single-split +2.5pp did not survive 21 independent windows.</t>
+          <t>7x more training data (17,770 vs ~2,700 per stock). Beats the POOLED baseline at 1 day (+3.3pp) and 1 week (+2.7pp) only.</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>results/direction/retest_1day/retest_summary.md</t>
+          <t>results/direction/pooled_rules/pooled_model_results.csv</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>direction_1day_retest.py; verdict rule fixed IN ADVANCE; 1-week carried as control, also negative</t>
+          <t>direction_pooled_and_rules.py</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5350,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>1-day re-test - window regime effect</t>
+          <t>Pooled model fairness check</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -5361,52 +5365,52 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>21 walk-forward folds</t>
+          <t>pooled model scored vs each stock's OWN baseline</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>binomial sign test (H0 p=0.5)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Positive folds 2016-2020 vs 2021-2024</t>
+          <t>1-day: stocks positive</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>1 of 10 vs 6 of 8</t>
+          <t>6 of 7</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M63" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>p=0.062</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>Confirms the crisis-window finding a second time: folds in 2021-2024 are mostly POSITIVE, 2016-2020 mostly negative. Apparent skill is a property of the period, not the model.</t>
+          <t>STRONGEST RESULT OF THE PROJECT but still not significant. The 1-week +2.7pp was a POOLING ARTIFACT (-0.5pp vs own baselines). Only 1 day survives: median +2.5pp, p=0.062, 1 of 9 horizons, single window.</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>retest_by_fold.csv</t>
+          <t>pooled_vs_own_baseline.csv</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>strong argument for walk-forward reporting in the dissertation</t>
+          <t>pooling stocks with different class balance weakens the majority baseline and fakes an edge</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5430,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1-day re-test - per stock consistency</t>
+          <t>Readable rules extracted</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>7 bank/finance stocks pooled</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -5441,52 +5445,48 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>21 walk-forward folds each</t>
+          <t>depth-3 tree, scored on unseen test set</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Decision tree (depth 3)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1</t>
+          <t>direct, h=1/5/22</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Stocks positive in &gt;50% of folds</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>2 of 7</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M64" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Best 1-day rule accuracy %</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="M64" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>No consistency: LOFC and CFIN positive in 62% of folds, HNB in only 19%. A real edge would show across the sector, not in two names.</t>
+          <t>17 plain-English rules with out-of-sample hit rates. Best 1-day rule: calm market + flat ASPI + no big drop -&gt; Hold, 49.3% (+11.3pp). Shows WHAT the model believes, not just that it fails.</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>retest_by_stock.csv</t>
+          <t>readable_rules.csv</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>median edge per stock ranges +4.9 (LOFC) to -4.9 (SAMP)</t>
+          <t>1-month rule at 68.5% fires only 317 times - treat as noise</t>
         </is>
       </c>
     </row>
@@ -5506,47 +5506,47 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>LSTM/GRU for direction</t>
+          <t>1-day claim re-test (walk-forward)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks pooled</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>daily (30-day sequences)</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>7 walk-forward 12-month folds, 3 seeds</t>
+          <t>21 non-overlapping 6-month windows, expanding train</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>LSTM + GRU (PyTorch)</t>
+          <t>Logistic + XGBoost (reported separately)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>direct, sequence input, h=1/5/22</t>
+          <t>direct, walk-forward, h=1</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Folds positive (LSTM, h=1)</t>
+          <t>Folds with positive median edge</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>5 of 7</t>
+          <t>6-7 of 21</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>p=0.227</t>
+          <t>10.5 expected by chance</t>
         </is>
       </c>
       <c r="M65" s="5" t="inlineStr">
@@ -5556,17 +5556,17 @@
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>Recurrent nets do NOT beat the naive baseline at any horizon. Closes the 'did you try deep learning on direction?' question. LSTM finally applied to the direction target (project is named after it).</t>
+          <t>CLAIM REFUTED. Median of fold medians -1.8pp (Logistic) / -1.9pp (XGBoost), sign-test p=0.96 and 0.99. The single-split +2.5pp did not survive 21 independent windows.</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>results/direction/lstm_gru/lstm_gru_summary.md</t>
+          <t>results/direction/retest_1day/retest_summary.md</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>direction_lstm_gru.py; monthly macro excluded (flat inside a 30-day window)</t>
+          <t>direction_1day_retest.py; verdict rule fixed IN ADVANCE; 1-week carried as control, also negative</t>
         </is>
       </c>
     </row>
@@ -5586,12 +5586,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Sequence vs flat control (LSTM value)</t>
+          <t>1-day re-test - window regime effect</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks pooled</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -5601,32 +5601,32 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>identical sequences, flattened for the control</t>
+          <t>21 walk-forward folds</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>LSTM vs Logistic on flattened sequences</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/22</t>
+          <t>direct, h=1</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Median edge LSTM vs flat (pp)</t>
+          <t>Positive folds 2016-2020 vs 2021-2024</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>+2.9 vs -1.7</t>
+          <t>1 of 10 vs 6 of 8</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Logistic(flat)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M66" s="6" t="inlineStr">
@@ -5636,17 +5636,17 @@
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>REAL NUANCE: LSTM beats the FLATTENED same data at ALL 3 horizons (1d +2.9 vs -1.7, 1wk -0.4 vs -2.1, 1mo -5.4 vs -9.9). Order of recent days carries a little signal that summary features discard - first time added complexity helped. Still not enough to reach the baseline.</t>
+          <t>Confirms the crisis-window finding a second time: folds in 2021-2024 are mostly POSITIVE, 2016-2020 mostly negative. Apparent skill is a property of the period, not the model.</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>lstm_gru_by_fold.csv</t>
+          <t>retest_by_fold.csv</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>the flat control is what makes this interpretable</t>
+          <t>strong argument for walk-forward reporting in the dissertation</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Regime effect - THIRD confirmation</t>
+          <t>1-day re-test - per stock consistency</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -5681,27 +5681,27 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>7 walk-forward folds, LSTM h=1</t>
+          <t>21 walk-forward folds each</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, h=1</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Positive folds 2019-2020 vs 2021-2025</t>
+          <t>Stocks positive in &gt;50% of folds</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0 of 2 vs 5 of 5</t>
+          <t>2 of 7</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -5709,24 +5709,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M67" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>Same window/regime pattern found for a THIRD time (after money supply and the 1-day retest). Every model looks skilled post-2021 and useless before, with identical code and features. Explains why 5/7 folds here is not convincing.</t>
+          <t>No consistency: LOFC and CFIN positive in 62% of folds, HNB in only 19%. A real edge would show across the sector, not in two names.</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>lstm_gru_by_fold.csv</t>
+          <t>retest_by_stock.csv</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>strongest methodological finding of the project</t>
+          <t>median edge per stock ranges +4.9 (LOFC) to -4.9 (SAMP)</t>
         </is>
       </c>
     </row>
@@ -5746,44 +5746,48 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Phase H - news sentiment</t>
+          <t>LSTM/GRU for direction</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>7 bank/finance stocks pooled</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>daily (30-day sequences)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>7 walk-forward 6-month folds, 2016-2022</t>
+          <t>7 walk-forward 12-month folds, 3 seeds</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>LSTM + GRU (PyTorch)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/10/22</t>
+          <t>direct, sequence input, h=1/5/22</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from sentiment (pp)</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>Folds positive (LSTM, h=1)</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>5 of 7</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>p=0.227</t>
+        </is>
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
@@ -5792,17 +5796,17 @@
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>News sentiment does NOT improve direction. Gain positive at 2 of 4 horizons (-0.8, -0.7, +2.4, +1.6), nothing near significance (all p&gt;=0.50). No phase beats the naive baseline.</t>
+          <t>Recurrent nets do NOT beat the naive baseline at any horizon. Closes the 'did you try deep learning on direction?' question. LSTM finally applied to the direction target (project is named after it).</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>results/direction/sentiment/sentiment_summary.md</t>
+          <t>results/direction/lstm_gru/lstm_gru_summary.md</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_h_sentiment.py; 149k Dailymirror/Newsfirst articles, 9,785 market-relevant</t>
+          <t>direction_lstm_gru.py; monthly macro excluded (flat inside a 30-day window)</t>
         </is>
       </c>
     </row>
@@ -5822,12 +5826,12 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Phase H - lexicon disagreement</t>
+          <t>Sequence vs flat control (LSTM value)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Dailymirror + Newsfirst news</t>
+          <t>7 bank/finance stocks pooled</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -5837,50 +5841,52 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>9,785 market-relevant articles 2016-2022</t>
+          <t>identical sequences, flattened for the control</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>VADER vs Loughran-McDonald style</t>
+          <t>LSTM vs Logistic on flattened sequences</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>sentiment scoring</t>
+          <t>direct, h=1/5/22</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Correlation between lexicons</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="n">
-        <v>0.416</v>
+          <t>Median edge LSTM vs flat (pp)</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>+2.9 vs -1.7</t>
+        </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
+          <t>Logistic(flat)</t>
+        </is>
+      </c>
+      <c r="M69" s="6" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M69" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>Two reasonable sentiment measures on the SAME articles correlate only 0.42. Direct evidence the sentiment signal is fragile, not merely weak. Running one lexicon alone would have hidden this.</t>
+          <t>REAL NUANCE: LSTM beats the FLATTENED same data at ALL 3 horizons (1d +2.9 vs -1.7, 1wk -0.4 vs -2.1, 1mo -5.4 vs -9.9). Order of recent days carries a little signal that summary features discard - first time added complexity helped. Still not enough to reach the baseline.</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>sentiment_verdict.csv</t>
+          <t>lstm_gru_by_fold.csv</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>finance_lexicon.py; full LM dictionary can be dropped in without code change</t>
+          <t>the flat control is what makes this interpretable</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5906,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Phase H - regime confound ruled out</t>
+          <t>Regime effect - THIRD confirmation</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5915,12 +5921,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>folds split calm vs crisis</t>
+          <t>7 walk-forward folds, LSTM h=1</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>LSTM</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -5930,12 +5936,12 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Sentiment gain calm vs crisis (pp)</t>
+          <t>Positive folds 2019-2020 vs 2021-2025</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>+0.85 vs -0.45</t>
+          <t>0 of 2 vs 5 of 5</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -5950,17 +5956,17 @@
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>Expected sentiment to 'work' only in the 2022 crisis; the OPPOSITE happened (calm 9/16 folds positive, crisis 3/12). So this null is NOT a regime artifact - cleaner than the other phases.</t>
+          <t>Same window/regime pattern found for a THIRD time (after money supply and the 1-day retest). Every model looks skilled post-2021 and useless before, with identical code and features. Explains why 5/7 folds here is not convincing.</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>sentiment_regime_split.csv</t>
+          <t>lstm_gru_by_fold.csv</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>first phase where the regime effect did not appear</t>
+          <t>strongest methodological finding of the project</t>
         </is>
       </c>
     </row>
@@ -5975,17 +5981,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>News look-ahead guard</t>
+          <t>Phase H - news sentiment</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Dailymirror + Newsfirst news</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -5995,50 +6001,48 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>publication timestamps vs 14:30 CSE close</t>
+          <t>7 walk-forward 6-month folds, 2016-2022</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>time-of-day assignment</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>direct, h=1/5/10/22</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Articles pushed to next trading day %</t>
+          <t>Mean gain from sentiment (pp)</t>
         </is>
       </c>
       <c r="K71" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.6</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>36% of articles were published AFTER the 14:30 close and were reassigned to the next trading day. Without this rule those articles report the very move being predicted and sentiment would look excellent and be worthless.</t>
+          <t>News sentiment does NOT improve direction. Gain positive at 2 of 4 horizons (-0.8, -0.7, +2.4, +1.6), nothing near significance (all p&gt;=0.50). No phase beats the naive baseline.</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>cleaned_data/news_sentiment_daily.csv</t>
+          <t>results/direction/sentiment/sentiment_summary.md</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>only 75 of 149,240 rows lacked a timestamp</t>
+          <t>direction_phase_h_sentiment.py; 149k Dailymirror/Newsfirst articles, 9,785 market-relevant</t>
         </is>
       </c>
     </row>
@@ -6058,12 +6062,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>POSITIVE CONTROL - pipeline validation</t>
+          <t>Phase H - lexicon disagreement</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>Dailymirror + Newsfirst news</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -6073,48 +6077,50 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, same-day vs lagged info</t>
+          <t>9,785 market-relevant articles 2016-2022</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>VADER vs Loughran-McDonald style</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>contemporaneous vs predictive</t>
+          <t>sentiment scoring</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Edge over baseline (pp)</t>
+          <t>Correlation between lexicons</t>
         </is>
       </c>
       <c r="K72" s="2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="M72" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>0.416</v>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>DECISIVE: same code finds +8.2pp (17/19 folds, p=0.0004) using TODAY's market/macro/news, and -4.1pp using the SAME info one day earlier. Gap 13.7pp. The pipeline is NOT blind - this information EXPLAINS returns but does not PREDICT them.</t>
+          <t>Two reasonable sentiment measures on the SAME articles correlate only 0.42. Direct evidence the sentiment signal is fragile, not merely weak. Running one lexicon alone would have hidden this.</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>results/direction/diagnostics/diagnostics_summary.md</t>
+          <t>sentiment_verdict.csv</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>direction_diagnostics.py; own-stock return excluded from contemporaneous features</t>
+          <t>finance_lexicon.py; full LM dictionary can be dropped in without code change</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6140,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Binary up/down reformulation</t>
+          <t>Phase H - regime confound ruled out</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -6149,7 +6155,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds</t>
+          <t>folds split calm vs crisis</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -6159,38 +6165,42 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>binary, h=1/5/22</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Edge over baseline (pp)</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Sentiment gain calm vs crisis (pp)</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>+0.85 vs -0.45</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>3-class dead-zone was NOT hiding a signal. Binary edge -4.8/-1.1/-2.1pp at 1d/1wk/1mo, positive in only 1/19, 7/19, 4/19 folds.</t>
+          <t>Expected sentiment to 'work' only in the 2022 crisis; the OPPOSITE happened (calm 9/16 folds positive, crisis 3/12). So this null is NOT a regime artifact - cleaner than the other phases.</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>diagnostics_verdict.csv</t>
+          <t>sentiment_regime_split.csv</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>rules out the Hold-majority explanation</t>
+          <t>first phase where the regime effect did not appear</t>
         </is>
       </c>
     </row>
@@ -6205,17 +6215,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>MAGNITUDE-WEIGHTED edge (survives)</t>
+          <t>News look-ahead guard</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>Dailymirror + Newsfirst news</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -6225,50 +6235,50 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds</t>
+          <t>publication timestamps vs 14:30 CSE close</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>time-of-day assignment</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>binary, |return|-weighted</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Weighted edge 1d / 1wk (pp)</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>+7.9 / +13.2</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Articles pushed to next trading day %</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>FIRST RESULT TO SURVIVE. Model is WRONG more often than baseline on plain accuracy (-4.3pp) but RIGHT on the big moves: weighted edge +7.9pp (15/19 folds, p=0.0096) at 1 day and +13.2pp (15/19, p=0.0096) at 1 week. Accuracy was the wrong metric.</t>
+          <t>36% of articles were published AFTER the 14:30 close and were reassigned to the next trading day. Without this rule those articles report the very move being predicted and sentiment would look excellent and be worthless.</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>diagnostics_magnitude.csv</t>
+          <t>cleaned_data/news_sentiment_daily.csv</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>1-month +9.5pp but p=0.18</t>
+          <t>only 75 of 149,240 rows lacked a timestamp</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6298,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Trading backtest with costs</t>
+          <t>POSITIVE CONTROL - pipeline validation</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -6303,48 +6313,48 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, h=1 only (non-overlapping)</t>
+          <t>19 walk-forward folds, same-day vs lagged info</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>long/short on model signal</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>economic evaluation</t>
+          <t>contemporaneous vs predictive</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Net return @50bps (%)</t>
+          <t>Edge over baseline (pp)</t>
         </is>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.05</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="M75" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>-4.1</v>
+      </c>
+      <c r="M75" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>THE EDGE IS REAL BUT NOT EXPLOITABLE. Gross +22.19% vs buy-and-hold +6.49%, but median 40 position flips per 6-month fold: net +17.35% @10bps, +11.24% @25bps, +0.05% @50bps. At realistic CSE costs the edge is exactly zero (8/19 folds, p=0.82).</t>
+          <t>DECISIVE: same code finds +8.2pp (17/19 folds, p=0.0004) using TODAY's market/macro/news, and -4.1pp using the SAME info one day earlier. Gap 13.7pp. The pipeline is NOT blind - this information EXPLAINS returns but does not PREDICT them.</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>diagnostics_backtest_h1.csv</t>
+          <t>results/direction/diagnostics/diagnostics_summary.md</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>h=5 and h=22 backtests omitted - overlapping returns cannot be summed</t>
+          <t>direction_diagnostics.py; own-stock return excluded from contemporaneous features</t>
         </is>
       </c>
     </row>
@@ -6359,12 +6369,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Price + macro + news vs naive</t>
+          <t>Binary up/down reformulation</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6379,33 +6389,29 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>walk-forward 6-month folds, per stock</t>
+          <t>19 walk-forward folds</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>naive / ARIMA(1,1,1) / Ridge / XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>1-day and 5-day, return-then-reconstruct</t>
+          <t>binary, h=1/5/22</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Cases beating naive (MAPE)</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>0 of 133</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>naive</t>
-        </is>
+          <t>Edge over baseline (pp)</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
@@ -6414,17 +6420,17 @@
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>NAIVE UNBEATEN. Best model ARIMA(1,1,1) at 1.004x naive MAPE. Stage 1's univariate conclusion survives the multivariate test - adding macro and news does not rescue price forecasting.</t>
+          <t>3-class dead-zone was NOT hiding a signal. Binary edge -4.8/-1.1/-2.1pp at 1d/1wk/1mo, positive in only 1/19, 7/19, 4/19 folds.</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>results/price_macro_news/price_summary.md</t>
+          <t>diagnostics_verdict.csv</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>price_with_macro_news.py; models predict RETURN then reconstruct price to stop them echoing today's price</t>
+          <t>rules out the Hold-majority explanation</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6445,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Does macro/news improve price forecasting?</t>
+          <t>MAGNITUDE-WEIGHTED edge (survives)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -6459,48 +6465,50 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>nested feature sets P / P+M / P+M+N</t>
+          <t>19 walk-forward folds</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>ablation on MAPE</t>
+          <t>binary, |return|-weighted</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Median MAPE improvement (pp)</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="n">
-        <v>-0.019</v>
+          <t>Weighted edge 1d / 1wk (pp)</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>+7.9 / +13.2</t>
+        </is>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M77" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M77" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>ALL EIGHT combinations NEGATIVE (-0.008 to -0.078pp). Adding macro and news makes price forecasting WORSE, consistently across both algorithms and both horizons.</t>
+          <t>FIRST RESULT TO SURVIVE. Model is WRONG more often than baseline on plain accuracy (-4.3pp) but RIGHT on the big moves: weighted edge +7.9pp (15/19 folds, p=0.0096) at 1 day and +13.2pp (15/19, p=0.0096) at 1 week. Accuracy was the wrong metric.</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>price_ablation_gain.csv</t>
+          <t>diagnostics_magnitude.csv</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>mirrors the direction chapter exactly</t>
+          <t>1-month +9.5pp but p=0.18</t>
         </is>
       </c>
     </row>
@@ -6515,12 +6523,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>CSE flat-day share (illiquidity)</t>
+          <t>Trading backtest with costs</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -6535,50 +6543,48 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>2017-2026</t>
+          <t>19 walk-forward folds, h=1 only (non-overlapping)</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>share of zero-return days</t>
+          <t>long/short on model signal</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>economic evaluation</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Flat days at 1 day (%)</t>
+          <t>Net return @50bps (%)</t>
         </is>
       </c>
       <c r="K78" s="2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.05</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>~10% of bank/finance trading days close EXACTLY unchanged; LOFC 36.0%, HNB 12.9%, LOLC 7.2%. Illiquidity is part of why the naive baseline is so hard to beat and why the Hold class dominates.</t>
+          <t>THE EDGE IS REAL BUT NOT EXPLOITABLE. Gross +22.19% vs buy-and-hold +6.49%, but median 40 position flips per 6-month fold: net +17.35% @10bps, +11.24% @25bps, +0.05% @50bps. At realistic CSE costs the edge is exactly zero (8/19 folds, p=0.82).</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>price_all_results.csv</t>
+          <t>diagnostics_backtest_h1.csv</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>surfaced as an artefact of the naive model's directional-accuracy column</t>
+          <t>h=5 and h=22 backtests omitted - overlapping returns cannot be summed</t>
         </is>
       </c>
     </row>
@@ -6593,17 +6599,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>LEAK CAUGHT - ASPI forward-fill</t>
+          <t>Price + macro + news vs naive</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 index</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -6613,48 +6619,52 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>feature vs same-day and next-day return</t>
+          <t>walk-forward 6-month folds, per stock</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>correlation audit</t>
+          <t>naive / ARIMA(1,1,1) / Ridge / XGBoost</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>leak detection</t>
+          <t>1-day and 5-day, return-then-reconstruct</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>corr with next-day vs same-day</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="M79" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Cases beating naive (MAPE)</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0 of 133</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>SPSL20 and ASPI do not share a trading calendar (207 / 962 mismatched dates). Forward-filling ASPI across the gaps let it carry a move SPSL20 only recorded on its NEXT row. Halved MAPE for free: ratio 0.496 vs a true 0.970.</t>
+          <t>NAIVE UNBEATEN. Best model ARIMA(1,1,1) at 1.004x naive MAPE. Stage 1's univariate conclusion survives the multivariate test - adding macro and news does not rescue price forecasting.</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>results/price_macro_news/leak_scan.csv</t>
+          <t>results/price_macro_news/price_summary.md</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>fix: no ffill across calendars + no ASPI features for index targets</t>
+          <t>price_with_macro_news.py; models predict RETURN then reconstruct price to stop them echoing today's price</t>
         </is>
       </c>
     </row>
@@ -6669,17 +6679,17 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Automated leak scan added</t>
+          <t>Does macro/news improve price forecasting?</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>all 9 targets</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -6689,50 +6699,48 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>every feature, every run</t>
+          <t>nested feature sets P / P+M / P+M+N</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>corr(feature, future) vs corr(feature, present)</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>guard</t>
+          <t>ablation on MAPE</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Features flagged after fix</t>
+          <t>Median MAPE improvement (pp)</t>
         </is>
       </c>
       <c r="K80" s="2" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="L80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M80" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>Permanent guard: any feature correlating MORE with the future than the present is flagged. Would have caught the ASPI bug instantly. Runs on every target automatically. THIRD leak-class bug in this project - all three flattered the model.</t>
+          <t>ALL EIGHT combinations NEGATIVE (-0.008 to -0.078pp). Adding macro and news makes price forecasting WORSE, consistently across both algorithms and both horizons.</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>price_with_macro_news.py</t>
+          <t>price_ablation_gain.csv</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>previous two: persistence baseline lookback, pooled baseline</t>
+          <t>mirrors the direction chapter exactly</t>
         </is>
       </c>
     </row>
@@ -6747,17 +6755,17 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 with macro + news (corrected)</t>
+          <t>CSE flat-day share (illiquidity)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 index</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -6767,48 +6775,50 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>17 walk-forward 6-month folds</t>
+          <t>2017-2026</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>naive / ARIMA / Ridge / XGBoost</t>
+          <t>share of zero-return days</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>direct 1-day and 5-day</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>MAPE ratio vs naive (best)</t>
+          <t>Flat days at 1 day (%)</t>
         </is>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>10.5</v>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>After the leak fix: best is Ridge price-only at 0.970 (1d) and 0.959 (5d), beating naive in only 10/17 and 9/17 folds. Macro and news make it WORSE (ratios 1.00-1.10).</t>
+          <t>~10% of bank/finance trading days close EXACTLY unchanged; LOFC 36.0%, HNB 12.9%, LOLC 7.2%. Illiquidity is part of why the naive baseline is so hard to beat and why the Hold class dominates.</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>results/price_macro_news/price_summary.md</t>
+          <t>price_all_results.csv</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>pre-fix figure was 0.496 - entirely the ASPI leak</t>
+          <t>surfaced as an artefact of the naive model's directional-accuracy column</t>
         </is>
       </c>
     </row>
@@ -6823,17 +6833,17 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Index vs stock autocorrelation</t>
+          <t>LEAK CAUGHT - ASPI forward-fill</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>SPSL20, ASPI vs 7 stocks</t>
+          <t>S&amp;P SL 20 index</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -6843,52 +6853,48 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>full sample</t>
+          <t>feature vs same-day and next-day return</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>lag-1 return autocorrelation</t>
+          <t>correlation audit</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>leak detection</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Lag-1 autocorr (index vs stock)</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>+0.24 vs +0.04</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
+          <t>corr with next-day vs same-day</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="M82" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M82" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>REAL EFFECT: indices show +0.237 (SPSL20) and +0.233 (ASPI) lag-1 return autocorrelation vs +0.038 for HNB. Non-synchronous trading - illiquid constituents (LOFC 37.8% flat days) reprice a day late, smearing shocks. A 1-parameter AR(1) captures the entire index 'edge'.</t>
+          <t>SPSL20 and ASPI do not share a trading calendar (207 / 962 mismatched dates). Forward-filling ASPI across the gaps let it carry a move SPSL20 only recorded on its NEXT row. Halved MAPE for free: ratio 0.496 vs a true 0.970.</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>price_all_results.csv</t>
+          <t>results/price_macro_news/leak_scan.csv</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>statistically real, economically useless - capturing it means trading the illiquid names that cause it</t>
+          <t>fix: no ffill across calendars + no ASPI features for index targets</t>
         </is>
       </c>
     </row>
@@ -6903,17 +6909,17 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Method study</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Hybrid ARIMA+LSTM (Zhang 2003)</t>
+          <t>Automated leak scan added</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + HNB</t>
+          <t>all 9 targets</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -6923,48 +6929,50 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20 + 7 walk-forward folds</t>
+          <t>every feature, every run</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>ARIMA(2,1,0) + LSTM on residuals</t>
+          <t>corr(feature, future) vs corr(feature, present)</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead, rolling ARIMA state</t>
+          <t>guard</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Theil U2 (fixed split)</t>
+          <t>Features flagged after fix</t>
         </is>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1.012</v>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M83" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>0</v>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M83" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>Hybrid built properly (Y=L+N, LSTM on ARIMA residuals, 3 seeds averaged) and it does NOT beat the naive random walk. SPSL20 U2=1.012, HNB U2=1.005. Marginally WORSE than plain ARIMA on both targets.</t>
+          <t>Permanent guard: any feature correlating MORE with the future than the present is flagged. Would have caught the ASPI bug instantly. Runs on every target automatically. THIRD leak-class bug in this project - all three flattered the model.</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>results/hybrid_comparable/hybrid_summary.md</t>
+          <t>price_with_macro_news.py</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>hybrid_arima_lstm_macro_news.py; supervisor-committed architecture, now tested</t>
+          <t>previous two: persistence baseline lookback, pooled baseline</t>
         </is>
       </c>
     </row>
@@ -6984,12 +6992,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Hybrid + macro + news (extension)</t>
+          <t>S&amp;P SL 20 with macro + news (corrected)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + HNB</t>
+          <t>S&amp;P SL 20 index</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -6999,33 +7007,29 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20 + 7 walk-forward folds</t>
+          <t>17 walk-forward 6-month folds</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>ARIMA + LSTM on residuals WITH exogenous macro/news</t>
+          <t>naive / ARIMA / Ridge / XGBoost</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead</t>
+          <t>direct 1-day and 5-day</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Folds better than naive (HNB)</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>0 of 7</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>naive</t>
-        </is>
+          <t>MAPE ratio vs naive (best)</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M84" s="5" t="inlineStr">
         <is>
@@ -7034,17 +7038,17 @@
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>THE PROJECT'S EXTENSION: macro+news fed into the residual model - the part ARIMA provably cannot explain. It makes things WORSE. SPSL20 U2 1.032, HNB U2 1.011, HNB walk-forward 0/7 folds.</t>
+          <t>After the leak fix: best is Ridge price-only at 0.970 (1d) and 0.959 (5d), beating naive in only 10/17 and 9/17 folds. Macro and news make it WORSE (ratios 1.00-1.10).</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>hybrid_walkforward_table.csv</t>
+          <t>results/price_macro_news/price_summary.md</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>best place to put macro if it carried information; it does not</t>
+          <t>pre-fix figure was 0.496 - entirely the ASPI leak</t>
         </is>
       </c>
     </row>
@@ -7059,17 +7063,17 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Diebold-Mariano + Theil U added</t>
+          <t>Index vs stock autocorrelation</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + HNB</t>
+          <t>SPSL20, ASPI vs 7 stocks</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -7079,50 +7083,52 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20</t>
+          <t>full sample</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>DM test (Newey-West HAC) + Theil U2</t>
+          <t>lag-1 return autocorrelation</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>forecast comparison</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Models significantly better than naive</t>
+          <t>Lag-1 autocorr (index vs stock)</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0 of 8</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>+0.24 vs +0.04</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M85" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>COMPARABILITY GAP CLOSED. Papers claim superiority with the DM test; this project had only baseline-relative edge. DM run vs naive AND vs ARIMA: ZERO models significant at p&lt;0.05. Only 1 of 8 has Theil U2&lt;1.</t>
+          <t>REAL EFFECT: indices show +0.237 (SPSL20) and +0.233 (ASPI) lag-1 return autocorrelation vs +0.038 for HNB. Non-synchronous trading - illiquid constituents (LOFC 37.8% flat days) reprice a day late, smearing shocks. A 1-parameter AR(1) captures the entire index 'edge'.</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>hybrid_fixed_split_table.csv</t>
+          <t>price_all_results.csv</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>the standard test reviewers expect; previously missing</t>
+          <t>statistically real, economically useless - capturing it means trading the illiquid names that cause it</t>
         </is>
       </c>
     </row>
@@ -7137,12 +7143,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>R-squared on price levels is meaningless</t>
+          <t>Hybrid ARIMA+LSTM (Zhang 2003)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -7157,50 +7163,48 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20</t>
+          <t>fixed 80/20 + 7 walk-forward folds</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>all models incl. naive</t>
+          <t>ARIMA(2,1,0) + LSTM on residuals</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>one-step-ahead, rolling ARIMA state</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>R2 of the NAIVE model</t>
+          <t>Theil U2 (fixed split)</t>
         </is>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.9979</v>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M86" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1.012</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>IMPORTANT FOR THE WRITE-UP: every model scores R2 0.9977-0.9980 - INCLUDING the naive random walk. Papers reporting R2~0.99 on price levels are reporting nothing. R2 on a level only measures being in the right magnitude.</t>
+          <t>Hybrid built properly (Y=L+N, LSTM on ARIMA residuals, 3 seeds averaged) and it does NOT beat the naive random walk. SPSL20 U2=1.012, HNB U2=1.005. Marginally WORSE than plain ARIMA on both targets.</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>hybrid_fixed_split_table.csv</t>
+          <t>results/hybrid_comparable/hybrid_summary.md</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>direct rebuttal to a common claim in this literature</t>
+          <t>hybrid_arima_lstm_macro_news.py; supervisor-committed architecture, now tested</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7219,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Fixed split vs walk-forward disagreement</t>
+          <t>Hybrid + macro + news (extension)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -7235,12 +7239,12 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>both protocols, same models</t>
+          <t>fixed 80/20 + 7 walk-forward folds</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>ARIMA / LSTM / Hybrid</t>
+          <t>ARIMA + LSTM on residuals WITH exogenous macro/news</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -7250,37 +7254,37 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>ARIMA SPSL20 U2 (fixed vs WF)</t>
+          <t>Folds better than naive (HNB)</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>1.005 vs 0.985</t>
+          <t>0 of 7</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M87" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>The two protocols DISAGREE: ARIMA is worse than naive on the SPSL20 fixed split (6/7 folds better in walk-forward), and the reverse pattern on HNB. Reporting only one protocol would mislead - hence both are published.</t>
+          <t>THE PROJECT'S EXTENSION: macro+news fed into the residual model - the part ARIMA provably cannot explain. It makes things WORSE. SPSL20 U2 1.032, HNB U2 1.011, HNB walk-forward 0/7 folds.</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>hybrid_all_results.csv</t>
+          <t>hybrid_walkforward_table.csv</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>4th demonstration that the test window drives the result</t>
+          <t>best place to put macro if it carried information; it does not</t>
         </is>
       </c>
     </row>
@@ -7295,17 +7299,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Method study</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Sector composite autocorrelation</t>
+          <t>Diebold-Mariano + Theil U added</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>BANKS/FINANCE/SECTOR composites</t>
+          <t>S&amp;P SL 20 + HNB</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -7315,52 +7319,50 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>full sample</t>
+          <t>fixed 80/20</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>lag-1 autocorrelation</t>
+          <t>DM test (Newey-West HAC) + Theil U2</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>forecast comparison</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Composite vs constituent autocorr</t>
+          <t>Models significantly better than naive</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>BANKS +0.178 vs ~0.07</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M88" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>0 of 8</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>Averaging HELPS for banks (composite 0.178 &gt; every constituent) but FAILS for finance (0.017 - constituents have negative autocorrs that cancel). Mixing them is worse (0.078). SYSTEM DESIGN: build a BANKS index, not a banks+finance index.</t>
+          <t>COMPARABILITY GAP CLOSED. Papers claim superiority with the DM test; this project had only baseline-relative edge. DM run vs naive AND vs ARIMA: ZERO models significant at p&lt;0.05. Only 1 of 8 has Theil U2&lt;1.</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>results/sector_direction/autocorrelation.csv</t>
+          <t>hybrid_fixed_split_table.csv</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>sector_direction.py; the '6x more predictable' estimate was too strong - 1.2x on average</t>
+          <t>the standard test reviewers expect; previously missing</t>
         </is>
       </c>
     </row>
@@ -7375,17 +7377,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Method study</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Sector direction (the product target)</t>
+          <t>R-squared on price levels is meaningless</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>BANKS/FINANCE/SECTOR composites</t>
+          <t>S&amp;P SL 20 + HNB</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -7395,52 +7397,50 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward 6-month folds</t>
+          <t>fixed 80/20</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>all models incl. naive</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/10/22, binary + 3-class</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Configurations beating baseline</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>0 of 24</t>
-        </is>
+          <t>R2 of the NAIVE model</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>0.9979</v>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>majority / persistence</t>
-        </is>
-      </c>
-      <c r="M89" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>The target the SYSTEM actually predicts, never tested before. Sector-level direction is NOT predictable on plain accuracy at any horizon or grouping. Leak scan clean.</t>
+          <t>IMPORTANT FOR THE WRITE-UP: every model scores R2 0.9977-0.9980 - INCLUDING the naive random walk. Papers reporting R2~0.99 on price levels are reporting nothing. R2 on a level only measures being in the right magnitude.</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>results/sector_direction/sector_direction_summary.md</t>
+          <t>hybrid_fixed_split_table.csv</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>sector_direction.py</t>
+          <t>direct rebuttal to a common claim in this literature</t>
         </is>
       </c>
     </row>
@@ -7455,17 +7455,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Method study</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Magnitude edge on BANKS composite</t>
+          <t>Fixed split vs walk-forward disagreement</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite</t>
+          <t>S&amp;P SL 20 + HNB</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -7475,50 +7475,52 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, binary</t>
+          <t>both protocols, same models</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>ARIMA / LSTM / Hybrid</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>|return|-weighted accuracy</t>
+          <t>one-step-ahead</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Weighted edge 1d/1wk/2wk (pp)</t>
+          <t>ARIMA SPSL20 U2 (fixed vs WF)</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>+10.2 / +8.1 / +11.5</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>1.005 vs 0.985</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>THIRD independent replication of the magnitude edge (after single stocks and pooled panel). Consistent across 4 horizons, 14-15 of 19 folds each, while plain accuracy edge is NEGATIVE. Product: flag big-move periods, do not emit daily direction calls.</t>
+          <t>The two protocols DISAGREE: ARIMA is worse than naive on the SPSL20 fixed split (6/7 folds better in walk-forward), and the reverse pattern on HNB. Reporting only one protocol would mislead - hence both are published.</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>sector_direction_all.csv</t>
+          <t>hybrid_all_results.csv</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>3-class magnitude figures (+34/+39pp) are INFLATED by a degenerate weighted-majority baseline - use the binary ones</t>
+          <t>4th demonstration that the test window drives the result</t>
         </is>
       </c>
     </row>
@@ -7538,12 +7540,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>PROBABILITY CALIBRATION (product-critical)</t>
+          <t>Sector composite autocorrelation</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>BANKS + SECTOR composites</t>
+          <t>BANKS/FINANCE/SECTOR composites</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -7553,52 +7555,52 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, calibrator fitted inside training window only</t>
+          <t>full sample</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Logistic/XGBoost x raw/Platt/isotonic</t>
+          <t>lag-1 autocorrelation</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>binary, h=5/10/22</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Configurations usable (skill&gt;0 &amp; ECE&lt;0.10)</t>
+          <t>Composite vs constituent autocorr</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0 of 36</t>
+          <t>BANKS +0.178 vs ~0.07</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>climatology (base rate)</t>
-        </is>
-      </c>
-      <c r="M91" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M91" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>THE DASHBOARD CANNOT SHOW A MODEL CONFIDENCE NUMBER. Every Brier skill score is NEGATIVE; AUC 0.41-0.56 = coin flip. Calibration cannot fix a model that cannot rank.</t>
+          <t>Averaging HELPS for banks (composite 0.178 &gt; every constituent) but FAILS for finance (0.017 - constituents have negative autocorrs that cancel). Mixing them is worse (0.078). SYSTEM DESIGN: build a BANKS index, not a banks+finance index.</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>results/sector_calibration/calibration_summary.md</t>
+          <t>results/sector_direction/autocorrelation.csv</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>sector_calibration.py; sklearn 1.9 removed cv='prefit', FrozenEstimator required</t>
+          <t>sector_direction.py; the '6x more predictable' estimate was too strong - 1.2x on average</t>
         </is>
       </c>
     </row>
@@ -7618,12 +7620,12 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Calibration removes error by removing information</t>
+          <t>Sector direction (the product target)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>BANKS + SECTOR composites</t>
+          <t>BANKS/FINANCE/SECTOR composites</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -7633,52 +7635,52 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds</t>
+          <t>19 walk-forward 6-month folds</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Platt vs raw probabilities</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>direct, h=1/5/10/22, binary + 3-class</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>prob_std Platt vs raw</t>
+          <t>Configurations beating baseline</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0.012-0.054 vs 0.164-0.232</t>
+          <t>0 of 24</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M92" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>majority / persistence</t>
+        </is>
+      </c>
+      <c r="M92" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>Platt roughly HALVES calibration error by collapsing the forecast to near-constant. A model that says '54%' every day is perfectly calibrated and useless - no resolution. Calibration alone is not evidence of a usable forecast.</t>
+          <t>The target the SYSTEM actually predicts, never tested before. Sector-level direction is NOT predictable on plain accuracy at any horizon or grouping. Leak scan clean.</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>calibration_all_folds.csv</t>
+          <t>results/sector_direction/sector_direction_summary.md</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>product answer: replace model confidence with a realised track record</t>
+          <t>sector_direction.py</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7700,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>News isolated - macro removed</t>
+          <t>Magnitude edge on BANKS composite</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + S&amp;P SL 20</t>
+          <t>BANKS composite</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -7713,7 +7715,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds, 2016-2022 (news window)</t>
+          <t>19 walk-forward folds, binary</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7723,40 +7725,40 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/10, P vs P+N</t>
+          <t>|return|-weighted accuracy</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Horizons where news helps</t>
+          <t>Weighted edge 1d/1wk/2wk (pp)</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0 of 6</t>
+          <t>+10.2 / +8.1 / +11.5</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M93" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>0</v>
+      </c>
+      <c r="M93" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>CLEAN ISOLATION TEST. In Phase H news competed with ~30 other columns incl. macro, which Phase C showed can actively hurt. Stripped back to price+news only: news gain -1.25 to +2.60pp, nothing significant. Macro was NOT masking news.</t>
+          <t>THIRD independent replication of the magnitude edge (after single stocks and pooled panel). Consistent across 4 horizons, 14-15 of 19 folds each, while plain accuracy edge is NEGATIVE. Product: flag big-move periods, do not emit daily direction calls.</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>results/price_news_hybrid/news_gain.csv</t>
+          <t>sector_direction_all.csv</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>price_news_hybrid.py; window 2016-2022 not comparable to other phases</t>
+          <t>3-class magnitude figures (+34/+39pp) are INFLATED by a degenerate weighted-majority baseline - use the binary ones</t>
         </is>
       </c>
     </row>
@@ -7771,17 +7773,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Hybrid + news, no macro</t>
+          <t>PROBABILITY CALIBRATION (product-critical)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + S&amp;P SL 20</t>
+          <t>BANKS + SECTOR composites</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -7791,29 +7793,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds</t>
+          <t>19 walk-forward folds, calibrator fitted inside training window only</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>naive / ARIMA(2,1,0) / Hybrid / Hybrid+News</t>
+          <t>Logistic/XGBoost x raw/Platt/isotonic</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead</t>
+          <t>binary, h=5/10/22</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Theil U2 (Hybrid+News, BANKS)</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="n">
-        <v>1.0003</v>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>1</v>
+          <t>Configurations usable (skill&gt;0 &amp; ECE&lt;0.10)</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>0 of 36</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>climatology (base rate)</t>
+        </is>
       </c>
       <c r="M94" s="5" t="inlineStr">
         <is>
@@ -7822,17 +7828,17 @@
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>Adding news to the hybrid makes it WORSE on both targets (BANKS 0.989-&gt;1.000, SPSL20 0.987-&gt;1.017). Plain ARIMA is the best model in the table and even it is not significant (DM p=0.30/0.46). Simplest wins again.</t>
+          <t>THE DASHBOARD CANNOT SHOW A MODEL CONFIDENCE NUMBER. Every Brier skill score is NEGATIVE; AUC 0.41-0.56 = coin flip. Calibration cannot fix a model that cannot rank.</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>results/price_news_hybrid/price_summary.csv</t>
+          <t>results/sector_calibration/calibration_summary.md</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>supports cutting BOTH the news and hybrid stages from the production system</t>
+          <t>sector_calibration.py; sklearn 1.9 removed cv='prefit', FrozenEstimator required</t>
         </is>
       </c>
     </row>
@@ -7847,17 +7853,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>LEAK #4 - SPSL20 calendar vs ASPI (again)</t>
+          <t>Calibration removes error by removing information</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20</t>
+          <t>BANKS + SECTOR composites</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -7867,29 +7873,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>feature vs same-day and next-day return</t>
+          <t>19 walk-forward folds</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>correlation audit</t>
+          <t>Platt vs raw probabilities</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>leak detection</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>corr with next-day vs same-day</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="n">
-        <v>0.871</v>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0.227</v>
+          <t>prob_std Platt vs raw</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>0.012-0.054 vs 0.164-0.232</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
@@ -7898,17 +7908,17 @@
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>The 'clean' SPSL20 file DELETED every flat day, misaligning it against ASPI (352 of 1505 rows drop). Removing .ffill() was NOT enough. Faked 82.8% accuracy / +20.7pp edge; a trivial 'copy sign of ASPI' rule scored 84.3%. Fixed by using the ASPI-calendar SPSL20 file AND dropping ASPI features for index targets.</t>
+          <t>Platt roughly HALVES calibration error by collapsing the forecast to near-constant. A model that says '54%' every day is perfectly calibrated and useless - no resolution. Calibration alone is not evidence of a usable forecast.</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>results/price_news_hybrid/leak_scan.csv</t>
+          <t>calibration_all_folds.csv</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>corrected result: 56.8% accuracy, -5.5pp edge</t>
+          <t>product answer: replace model confidence with a realised track record</t>
         </is>
       </c>
     </row>
@@ -7923,17 +7933,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Leak guard now HALTS the run</t>
+          <t>News isolated - macro removed</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>all targets</t>
+          <t>BANKS composite + S&amp;P SL 20</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -7943,52 +7953,50 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>every feature set</t>
+          <t>6 walk-forward folds, 2016-2022 (news window)</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>automated leak scan</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>guard</t>
+          <t>direct, h=1/5/10, P vs P+N</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Runs aborted on leak detection</t>
+          <t>Horizons where news helps</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>1 of 1</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M96" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>0 of 6</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M96" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N96" s="4" t="inlineStr">
         <is>
-          <t>The guard previously only wrote a CSV and the run continued, reporting a fake +20.7pp edge while the summary line claimed 'clean'. A guard that does not stop the run is not a guard. Now raises SystemExit.</t>
+          <t>CLEAN ISOLATION TEST. In Phase H news competed with ~30 other columns incl. macro, which Phase C showed can actively hurt. Stripped back to price+news only: news gain -1.25 to +2.60pp, nothing significant. Macro was NOT masking news.</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>price_news_hybrid.py</t>
+          <t>results/price_news_hybrid/news_gain.csv</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>4th leak caught in this project; all four flattered the model</t>
+          <t>price_news_hybrid.py; window 2016-2022 not comparable to other phases</t>
         </is>
       </c>
     </row>
@@ -8003,17 +8011,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Late fusion (one model per source)</t>
+          <t>Hybrid + news, no macro</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + HNB</t>
+          <t>BANKS composite + S&amp;P SL 20</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -8023,33 +8031,29 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds, chronological base/meta split</t>
+          <t>6 walk-forward folds</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>XGBoost bases + Logistic meta-learner</t>
+          <t>naive / ARIMA(2,1,0) / Hybrid / Hybrid+News</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>stacking, h=1/5/10</t>
+          <t>one-step-ahead</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Configurations beating baseline</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>0 of 6</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>majority / persistence</t>
-        </is>
+          <t>Theil U2 (Hybrid+News, BANKS)</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>1.0003</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
@@ -8058,17 +8062,17 @@
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>ARCHITECTURE WAS NOT THE CONSTRAINT. Separate models for price/news/macro combined by a meta-learner: 0/6 beat the baseline. Late fusion IS less bad than early fusion (better in 5/6) but beats it significantly in only 1/6 = chance.</t>
+          <t>Adding news to the hybrid makes it WORSE on both targets (BANKS 0.989-&gt;1.000, SPSL20 0.987-&gt;1.017). Plain ARIMA is the best model in the table and even it is not significant (DM p=0.30/0.46). Simplest wins again.</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>results/late_fusion/late_fusion_summary.md</t>
+          <t>results/price_news_hybrid/price_summary.csv</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>late_fusion_stacking.py; meta-learner trained on OUT-OF-FOLD base predictions</t>
+          <t>supports cutting BOTH the news and hybrid stages from the production system</t>
         </is>
       </c>
     </row>
@@ -8083,17 +8087,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Meta-learner weight allocation</t>
+          <t>LEAK #4 - SPSL20 calendar vs ASPI (again)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + HNB</t>
+          <t>S&amp;P SL 20</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -8103,52 +8107,48 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds</t>
+          <t>feature vs same-day and next-day return</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Logistic meta-learner on 3 base models</t>
+          <t>correlation audit</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>stacking</t>
+          <t>leak detection</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Median weight share price/news/macro</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>29% / 38% / 33%</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr">
+          <t>corr with next-day vs same-day</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="M98" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M98" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N98" s="4" t="inlineStr">
         <is>
-          <t>CLEANEST VERSION OF THE CENTRAL FINDING. A model free to weight the three sources however it likes splits ~1/3 each and leans MOST on news. If price carried signal and news did not, it would load onto price. Even allocation = nothing to prefer.</t>
+          <t>The 'clean' SPSL20 file DELETED every flat day, misaligning it against ASPI (352 of 1505 rows drop). Removing .ffill() was NOT enough. Faked 82.8% accuracy / +20.7pp edge; a trivial 'copy sign of ASPI' rule scored 84.3%. Fixed by using the ASPI-calendar SPSL20 file AND dropping ASPI features for index targets.</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>results/late_fusion/meta_weights_summary.csv</t>
+          <t>results/price_news_hybrid/leak_scan.csv</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>resolves the ambiguous early-fusion result (high importance, zero gain)</t>
+          <t>corrected result: 56.8% accuracy, -5.5pp edge</t>
         </is>
       </c>
     </row>
@@ -8168,12 +8168,12 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Early vs late fusion ruled out as explanation</t>
+          <t>Leak guard now HALTS the run</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + HNB</t>
+          <t>all targets</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -8183,50 +8183,52 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>identical folds, both architectures</t>
+          <t>every feature set</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>early (concatenated) vs late (stacked)</t>
+          <t>automated leak scan</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>guard</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>Late beats early significantly</t>
+          <t>Runs aborted on leak detection</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>1 of 6</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M99" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>1 of 1</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>Rules out one candidate explanation for why published papers report gains: 'early fusion drowned the weak signals'. Giving news and macro dedicated models surfaces nothing. Still open: missing naive baselines, no publication lag, single favourable split, decomposition hybrids.</t>
+          <t>The guard previously only wrote a CSV and the run continued, reporting a fake +20.7pp edge while the summary line claimed 'clean'. A guard that does not stop the run is not a guard. Now raises SystemExit.</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>late_fusion_folds.csv</t>
+          <t>price_news_hybrid.py</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>late_fusion_stacking.py</t>
+          <t>4th leak caught in this project; all four flattered the model</t>
         </is>
       </c>
     </row>
@@ -8241,17 +8243,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Reproduce-then-break ladder</t>
+          <t>Late fusion (one model per source)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + BANKS composite</t>
+          <t>BANKS composite + HNB</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -8261,50 +8263,52 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>L0 paper-style -&gt; L3 walk-forward, one guard at a time</t>
+          <t>6 walk-forward folds, chronological base/meta split</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost (best reported)</t>
+          <t>XGBoost bases + Logistic meta-learner</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>next-day price</t>
+          <t>stacking, h=1/5/10</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>L0 'macro improvement' %</t>
+          <t>Configurations beating baseline</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>+0.17 / -0.04</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>0 of 6</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>majority / persistence</t>
+        </is>
+      </c>
+      <c r="M100" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N100" s="4" t="inlineStr">
         <is>
-          <t>REPRODUCTION FAILED - and that is the finding. Removing the publication lag, leaking the scaler and using a single split move the number by FRACTIONS OF A PERCENT. These three shortcuts are NOT the mechanism behind published macro gains.</t>
+          <t>ARCHITECTURE WAS NOT THE CONSTRAINT. Separate models for price/news/macro combined by a meta-learner: 0/6 beat the baseline. Late fusion IS less bad than early fusion (better in 5/6) but beats it significantly in only 1/6 = chance.</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>results/reproduce_then_break/ladder_summary.md</t>
+          <t>results/late_fusion/late_fusion_summary.md</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>reproduce_then_break.py; hypothesis was wrong, reported as such</t>
+          <t>late_fusion_stacking.py; meta-learner trained on OUT-OF-FOLD base predictions</t>
         </is>
       </c>
     </row>
@@ -8319,17 +8323,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>The likely real mechanism: no naive baseline</t>
+          <t>Meta-learner weight allocation</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + BANKS composite</t>
+          <t>BANKS composite + HNB</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -8339,29 +8343,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>all ladder levels</t>
+          <t>6 walk-forward folds</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>all configs incl. naive</t>
+          <t>Logistic meta-learner on 3 base models</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>next-day price</t>
+          <t>stacking</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>R2 across every level</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="n">
-        <v>0.998</v>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0.9979</v>
+          <t>Median weight share price/news/macro</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>29% / 38% / 33%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
@@ -8370,17 +8378,17 @@
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>R2 is 0.9978-0.9984 at EVERY level for EVERY config - and naive scores 0.9979. A paper running this exact setup would truthfully report 'R2=0.998, MAPE=0.83%, outperforms benchmark'. The gain is model-vs-weaker-model, reported with metrics that cannot distinguish either from a random walk.</t>
+          <t>CLEANEST VERSION OF THE CENTRAL FINDING. A model free to weight the three sources however it likes splits ~1/3 each and leans MOST on news. If price carried signal and news did not, it would load onto price. Even allocation = nothing to prefer.</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ladder_summary.csv</t>
+          <t>results/late_fusion/meta_weights_summary.csv</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>DM p = 0.48-0.86 throughout; nothing significant</t>
+          <t>resolves the ambiguous early-fusion result (high importance, zero gain)</t>
         </is>
       </c>
     </row>
@@ -8400,12 +8408,12 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Single split is the shortcut that matters most</t>
+          <t>Early vs late fusion ruled out as explanation</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + BANKS composite</t>
+          <t>BANKS composite + HNB</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -8415,33 +8423,31 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>L0-L2 single split vs L3 walk-forward</t>
+          <t>identical folds, both architectures</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>early (concatenated) vs late (stacked)</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>next-day price</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>MAPE(macro)/MAPE(naive)</t>
+          <t>Late beats early significantly</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0.96-0.98 -&gt; 1.027</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>1 of 6</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0.05</v>
       </c>
       <c r="M102" s="5" t="inlineStr">
         <is>
@@ -8450,17 +8456,17 @@
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
-          <t>Under single-split levels price+macro sits BELOW naive (0.964-0.980); under walk-forward it crosses ABOVE 1.0 on both targets. Of the three shortcuts tested, the single split changes the conclusion; the other two do not. 4th confirmation of the window effect.</t>
+          <t>Rules out one candidate explanation for why published papers report gains: 'early fusion drowned the weak signals'. Giving news and macro dedicated models surfaces nothing. Still open: missing naive baselines, no publication lag, single favourable split, decomposition hybrids.</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ladder_all.csv</t>
+          <t>late_fusion_folds.csv</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>argues for walk-forward as the default reporting protocol</t>
+          <t>late_fusion_stacking.py</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8486,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>DECOMPOSITION LEAK - the mechanism found</t>
+          <t>Reproduce-then-break ladder</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -8495,33 +8501,31 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20, identical model/data, only pipeline ORDER differs</t>
+          <t>L0 paper-style -&gt; L3 walk-forward, one guard at a time</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>wavelet(db4,3) + CEEMDAN -&gt; Ridge/XGBoost</t>
+          <t>Ridge + XGBoost (best reported)</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead price</t>
+          <t>next-day price</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>Improvement over naive: leaky vs honest</t>
+          <t>L0 'macro improvement' %</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>+19.2% vs -6.9%</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>naive</t>
-        </is>
+          <t>+0.17 / -0.04</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -8530,17 +8534,17 @@
       </c>
       <c r="N103" s="4" t="inlineStr">
         <is>
-          <t>★ THE MECHANISM. Decomposing the FULL series BEFORE splitting creates a 13-26pp improvement out of nothing. Wavelet/CEEMDAN are GLOBAL transforms: component values at time t are computed from the whole series, so training components carry test-period information and test components were built from their own future.</t>
+          <t>REPRODUCTION FAILED - and that is the finding. Removing the publication lag, leaking the scaler and using a single split move the number by FRACTIONS OF A PERCENT. These three shortcuts are NOT the mechanism behind published macro gains.</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>results/decomposition_leak/decomposition_summary.md</t>
+          <t>results/reproduce_then_break/ladder_summary.md</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>decomposition_leak_test.py; explains the gap between published hybrid results and this project</t>
+          <t>reproduce_then_break.py; hypothesis was wrong, reported as such</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8564,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Leaky decomposition is highly significant</t>
+          <t>The likely real mechanism: no naive baseline</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -8575,50 +8579,48 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20</t>
+          <t>all ladder levels</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>wavelet + CEEMDAN, leaky pipeline</t>
+          <t>all configs incl. naive</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead price</t>
+          <t>next-day price</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>DM p vs naive (4 configs)</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>0.0000-0.0199</t>
-        </is>
+          <t>R2 across every level</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0.998</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M104" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>0.9979</v>
+      </c>
+      <c r="M104" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N104" s="4" t="inlineStr">
         <is>
-          <t>ALL FOUR leaky configurations beat naive significantly (Theil U2 0.794-0.871, DM p&lt;0.02, two at p&lt;0.0001). These are exactly the numbers decomposition-hybrid papers report.</t>
+          <t>R2 is 0.9978-0.9984 at EVERY level for EVERY config - and naive scores 0.9979. A paper running this exact setup would truthfully report 'R2=0.998, MAPE=0.83%, outperforms benchmark'. The gain is model-vs-weaker-model, reported with metrics that cannot distinguish either from a random walk.</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>decomposition_results.csv</t>
+          <t>ladder_summary.csv</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>the result is real as computed - it is the pipeline that is wrong</t>
+          <t>DM p = 0.48-0.86 throughout; nothing significant</t>
         </is>
       </c>
     </row>
@@ -8638,70 +8640,308 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
+          <t>Single split is the shortcut that matters most</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>L0-L2 single split vs L3 walk-forward</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Ridge + XGBoost</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>next-day price</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>MAPE(macro)/MAPE(naive)</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>0.96-0.98 -&gt; 1.027</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="M105" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>Under single-split levels price+macro sits BELOW naive (0.964-0.980); under walk-forward it crosses ABOVE 1.0 on both targets. Of the three shortcuts tested, the single split changes the conclusion; the other two do not. 4th confirmation of the window effect.</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>ladder_all.csv</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>argues for walk-forward as the default reporting protocol</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>DECOMPOSITION LEAK - the mechanism found</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>fixed 80/20, identical model/data, only pipeline ORDER differs</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>wavelet(db4,3) + CEEMDAN -&gt; Ridge/XGBoost</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>one-step-ahead price</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Improvement over naive: leaky vs honest</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>+19.2% vs -6.9%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M106" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t>★ THE MECHANISM. Decomposing the FULL series BEFORE splitting creates a 13-26pp improvement out of nothing. Wavelet/CEEMDAN are GLOBAL transforms: component values at time t are computed from the whole series, so training components carry test-period information and test components were built from their own future.</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>results/decomposition_leak/decomposition_summary.md</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>decomposition_leak_test.py; explains the gap between published hybrid results and this project</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Leaky decomposition is highly significant</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>fixed 80/20</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>wavelet + CEEMDAN, leaky pipeline</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>one-step-ahead price</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>DM p vs naive (4 configs)</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0.0000-0.0199</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M107" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N107" s="4" t="inlineStr">
+        <is>
+          <t>ALL FOUR leaky configurations beat naive significantly (Theil U2 0.794-0.871, DM p&lt;0.02, two at p&lt;0.0001). These are exactly the numbers decomposition-hybrid papers report.</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>decomposition_results.csv</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>the result is real as computed - it is the pipeline that is wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
           <t>Honest decomposition loses to naive</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>S&amp;P SL 20 + BANKS composite</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>fixed 80/20, decompose only series[:t] at each t</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>wavelet + CEEMDAN, honest pipeline</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr">
         <is>
           <t>one-step-ahead price</t>
         </is>
       </c>
-      <c r="J105" s="2" t="inlineStr">
+      <c r="J108" s="2" t="inlineStr">
         <is>
           <t>Theil U2 (4 configs)</t>
         </is>
       </c>
-      <c r="K105" s="2" t="inlineStr">
+      <c r="K108" s="2" t="inlineStr">
         <is>
           <t>1.008-1.028</t>
         </is>
       </c>
-      <c r="L105" s="2" t="n">
+      <c r="L108" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M105" s="5" t="inlineStr">
+      <c r="M108" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N105" s="4" t="inlineStr">
+      <c r="N108" s="4" t="inlineStr">
         <is>
           <t>Same models, same data, decomposition restricted to past data only: ALL FOUR configs are WORSE than a random walk and none significant (DM p 0.35-0.84). The decomposition advantage does not survive an honest pipeline.</t>
         </is>
       </c>
-      <c r="O105" s="2" t="inlineStr">
+      <c r="O108" s="2" t="inlineStr">
         <is>
           <t>decomposition_results.csv</t>
         </is>
       </c>
-      <c r="P105" s="2" t="inlineStr">
+      <c r="P108" s="2" t="inlineStr">
         <is>
           <t>honest CEEMDAN re-decomposes every 3rd point for runtime; wavelet every point</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P105"/>
+  <autoFilter ref="A1:P108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P108"/>
+  <dimension ref="A1:P113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2778,22 +2778,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Multi-horizon</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Phase A multi-horizon direction</t>
+          <t>MH ARIMAX/RF/CNN-LSTM</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>HNB</t>
+          <t>ASPI</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2803,52 +2803,52 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge</t>
+          <t>80/20 direct, 11 horizons</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>ARIMAX / RandomForest / CNN-LSTM</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons (1d-252d)</t>
+          <t>direction + price %</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Horizons beating baseline</t>
+          <t>dir acc / price MAPE</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0 of 9</t>
+          <t>see CSV</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>majority / persistence</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>NO EDGE AT ANY HORIZON. Best model always below best baseline; gap widens with horizon (-3.5pp @1d -&gt; -47.1pp @1yr) because long-horizon drift makes the dumb baseline huge (maj 78% @6mo, pers 77% @1yr).</t>
+          <t>All-Share index (no volume, 28 feat). PRICE: ARIMAX+RF good at long — AVG2 beats naive 5/11 (long 5/5): 6mo 9.2vs11.2, 1yr 17.0vs22.2. Short=tie. DIRECTION naive huge at long (94-96% = uptrend). Combo edge holds for broad index.</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>results/direction/multi_horizon/mh_summary.md</t>
+          <t>results/mh_models/ASPI_results.csv + ASPI_ensemble.csv + ASPI_decay_chart.png</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>direction_multi_horizon.py; Tier-1 only; dead-zone +/-0.5%*sqrt(h)</t>
+          <t>mh_multimodel/ensemble/decay.py ASPI</t>
         </is>
       </c>
     </row>
@@ -2858,22 +2858,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Multi-horizon</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Phase A best single horizon</t>
+          <t>MH ARIMAX/RF/CNN-LSTM</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>HNB</t>
+          <t>SPSL20</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2883,48 +2883,52 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge</t>
+          <t>80/20 direct, 11 horizons</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Logistic</t>
+          <t>ARIMAX / RandomForest / CNN-LSTM</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>direct, h=22d (1 month)</t>
+          <t>direction + price %</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Accuracy %</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="M31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>dir acc / price MAPE</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>see CSV</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>No (combo fails)</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>Best model result of the sweep (1-month Logistic 40.1%) still loses to persistence 42.1%. Logistic &gt; XGBoost at every horizon -&gt; no nonlinear structure to find.</t>
+          <t>S&amp;P SL20 index (2295 rows). BREAKS the pattern: AVG2 beats naive 0/11 — RF is WORSE than naive here (1yr RF 24.2 vs naive 23.6) and drags the combo down. Short=tie. Naive near-unbeatable on this index. Honest counter-example: the AVG2 long-horizon edge does NOT generalise to S&amp;P SL20.</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>mh_direction_table.csv</t>
+          <t>results/mh_models/SPSL20_results.csv + SPSL20_ensemble.csv + SPSL20_decay_chart.png</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>edge -2.0pp</t>
+          <t>mh_multimodel/ensemble/decay.py SPSL20</t>
         </is>
       </c>
     </row>
@@ -2934,73 +2938,77 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Ensemble</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Phase A multi-horizon return %</t>
+          <t>AVG2 combo out-of-market test</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>HNB</t>
+          <t>AAPL (Apple)</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>daily 2000-2025</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge</t>
+          <t>80/20 blind, no macro</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>ARIMA / RandomForest / AVG2</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons (1d-252d)</t>
+          <t>direct, 11 horizons, price MAPE</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>RMSE ratio vs train-mean</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>Tie</t>
+          <t>long-horizon beats naive?</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>AVG2: 3mo/6mo/1yr all beat</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>Yes — generalises</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Ridge beats naive-0 at 8/9 horizons BUT is only ~1% better than train-mean drift -&gt; it learned drift, NOT signal. XGBoost worse than naive everywhere (ratio 1.01-1.14).</t>
+          <t>GENERALISATION CHECK on US large-cap, 25yr, NO macro (ARIMAX-&gt;plain ARIMA). Same pattern: short=tie (naive wins 1d-1mo), long AVG2 beats naive: 3mo 9.9vs10.1, 6mo 11.6vs12.6, 1yr 12.9vs16.6. RF alone blows up long (25.4@1yr), ARIMA~naive, but their AVERAGE beats both (error-cancelling). Finding is market-independent, not a Colombo quirk. Crossover at 3mo (vs 1mo for CSE stocks).</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>mh_return_table.csv</t>
+          <t>results/mh_models/AAPL_ensemble.csv + AAPL_ensemble_chart.png + AAPL_price_overlay.png</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>train-mean is the honest null, not naive-0</t>
+          <t>mh_apple.py</t>
         </is>
       </c>
     </row>
@@ -3010,17 +3018,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>PURE forecast</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Phase A return sign accuracy</t>
+          <t>Blind whole-test forecast (no test data fed)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3035,32 +3043,32 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge</t>
+          <t>80/20, one-shot blind</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>ARIMA / RF-recursive / Combo</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>direct, sign of h-day return</t>
+          <t>predict ENTIRE 20% test in one shot</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Horizons beating sign null</t>
+          <t>MAPE over whole test %</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2 of 9</t>
+          <t>all ~38</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>always-guess-winning-side</t>
+          <t>naive 38.36</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
@@ -3070,17 +3078,17 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>TRAP CHECK: 55-57% sign accuracy @1-3mo looks like the 52-58% target but 'always guess up' matches/beats it (test window drifted up 59-95%). Both 'wins' are +0.2pp = noise.</t>
+          <t>CORRECTS earlier finding. Under the ONLY-allowed protocol (train 80%, predict whole 20% blind, ZERO test data fed): ARIMA/RF/Combo all collapse to a ~flat line at last train price = SAME as naive (all ~38% MAPE). Nobody beats naive. The prior 'combo beats naive at long horizon' was an ARTIFACT of rolling origins re-feeding the real daily price; removing that crutch, the edge vanishes.</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>mh_edge_vs_horizon.png</t>
+          <t>results/mh_models/HNB_pure_forecast.png</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>up-share null added to stop false positive</t>
+          <t>pure_forecast.py HNB</t>
         </is>
       </c>
     </row>
@@ -3090,54 +3098,58 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>PURE forecast</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Phase B ablation (+Tier-2)</t>
+          <t>Blind whole-test forecast (no test data fed)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>HNB</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>daily 2000+</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds, A vs B</t>
+          <t>80/20, one-shot blind</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>ARIMA / RF-recursive / Combo</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, ablation</t>
+          <t>predict ENTIRE 20% test in one shot</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from Tier-2 (pp)</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
+          <t>MAPE over whole test %</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>naive best 30.8</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>naive 30.76</t>
+        </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
@@ -3146,17 +3158,17 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>RSI+MACD+volume add NOTHING. Mean -0.9pp, 0/9 beat baseline. Technical indicators exhausted.</t>
+          <t>Same verdict, starker: naive(flat) 30.8 BEST. ARIMA=flat 30.8. RF-recursive EXPLODES to 116% (compounding drift). Combo 45% (RF drags it up, WORSE than naive). Pure blind long-horizon forecasting fails everywhere — random walk confirmed. Rolling-protocol combo edge does NOT survive.</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>results/direction/phase_ablation/ablation_summary.md</t>
+          <t>results/mh_models/AAPL_pure_forecast.png</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_ablation.py; 9 -&gt; 16 features; value restated on the 4-phase run (macro availability trims early rows)</t>
+          <t>pure_forecast.py AAPL</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3188,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Phase B feature attention check</t>
+          <t>Phase A multi-horizon direction</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3191,50 +3203,52 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>80/20 chrono + h-bar purge</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>XGBoost importance</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, 9 horizons (1d-252d)</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Tier-2 share of importance %</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>41</v>
+          <t>Horizons beating baseline</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0 of 9</t>
+        </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M35" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>majority / persistence</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>XGBoost spends 41% of importance on Tier-2 (macd_signal is top feature at 6/9 horizons) yet accuracy does not improve -&gt; the model USES them but they carry no signal.</t>
+          <t>NO EDGE AT ANY HORIZON. Best model always below best baseline; gap widens with horizon (-3.5pp @1d -&gt; -47.1pp @1yr) because long-horizon drift makes the dumb baseline huge (maj 78% @6mo, pers 77% @1yr).</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ablation_tier2_importance.csv</t>
+          <t>results/direction/multi_horizon/mh_summary.md</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>strong evidence indicators are redundant with price</t>
+          <t>direction_multi_horizon.py; Tier-1 only; dead-zone +/-0.5%*sqrt(h)</t>
         </is>
       </c>
     </row>
@@ -3249,12 +3263,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Phase B return % (+Tier-2)</t>
+          <t>Phase A best single horizon</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3269,48 +3283,48 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>80/20 chrono + h-bar purge</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Logistic</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, h=22d (1 month)</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>RMSE ratio vs train-mean (B)</t>
+          <t>Accuracy %</t>
         </is>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.991</v>
+        <v>40.1</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>Tie</t>
+        <v>42.1</v>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Tier-2 made return RMSE slightly WORSE at 9/9 horizons (ratio gain +0.000 to +0.046). Sign edge stays negative everywhere.</t>
+          <t>Best model result of the sweep (1-month Logistic 40.1%) still loses to persistence 42.1%. Logistic &gt; XGBoost at every horizon -&gt; no nonlinear structure to find.</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ablation_return_table.csv</t>
+          <t>mh_direction_table.csv</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>A ratio 0.991 -&gt; B ratio 0.991-1.034</t>
+          <t>edge -2.0pp</t>
         </is>
       </c>
     </row>
@@ -3325,12 +3339,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Phase C ablation (+macro rates)</t>
+          <t>Phase A multi-horizon return %</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3345,48 +3359,48 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds, 35d publication lag</t>
+          <t>80/20 chrono + h-bar purge</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, ablation</t>
+          <t>direct, 9 horizons (1d-252d)</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from macro (pp)</t>
+          <t>RMSE ratio vs train-mean</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
-        <v>-2.8</v>
+        <v>0.99</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>1</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Tie</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>Macro rates make it WORSE and unstable: gain swings -22.3 to +10.3 pp, 0/9 beat baseline. Not weak signal - overfitting.</t>
+          <t>Ridge beats naive-0 at 8/9 horizons BUT is only ~1% better than train-mean drift -&gt; it learned drift, NOT signal. XGBoost worse than naive everywhere (ratio 1.01-1.14).</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>results/direction/phase_ablation/ablation_summary.md</t>
+          <t>mh_return_table.csv</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_ablation.py; 16 -&gt; 29 features; inflation/FX/M2 still uncollected</t>
+          <t>train-mean is the honest null, not naive-0</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3415,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Phase C2 diagnostic (macro changes only)</t>
+          <t>Phase A return sign accuracy</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3421,48 +3435,52 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>80/20 chrono + h-bar purge</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, ablation</t>
+          <t>direct, sign of h-day return</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from macro d (pp)</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="M38" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Horizons beating sign null</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>2 of 9</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>always-guess-winning-side</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>DROPPING RATE LEVELS FIXES THE DAMAGE (-2.8 -&gt; +3.4 pp; 1yr 4.5% -&gt; 49.7%). Non-stationary levels were being memorised. Still 0/9 beat baseline -&gt; form was wrong AND no signal.</t>
+          <t>TRAP CHECK: 55-57% sign accuracy @1-3mo looks like the 52-58% target but 'always guess up' matches/beats it (test window drifted up 59-95%). Both 'wins' are +0.2pp = noise.</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ablation_gain_table.csv</t>
+          <t>mh_edge_vs_horizon.png</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>key methodology lesson: feed macro as changes, never levels</t>
+          <t>up-share null added to stop false positive</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3500,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Phase C feature attention check</t>
+          <t>Phase B ablation (+Tier-2)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3497,50 +3515,48 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>identical rows/split/seeds, A vs B</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>XGBoost importance</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, 9 horizons, ablation</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Macro share of importance %</t>
+          <t>Mean gain from Tier-2 (pp)</t>
         </is>
       </c>
       <c r="K39" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M39" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>-0.9</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>Macro importance rises 46% (1d) -&gt; 80% (1yr) while accuracy FALLS. Model fits rates as a trend proxy, not signal. tb_12m/spread/policy_rate are top features at 8/9 horizons.</t>
+          <t>RSI+MACD+volume add NOTHING. Mean -0.9pp, 0/9 beat baseline. Technical indicators exhausted.</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ablation_feature_importance.csv</t>
+          <t>results/direction/phase_ablation/ablation_summary.md</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>fingerprint of trending-variable overfit</t>
+          <t>direction_phase_ablation.py; 9 -&gt; 16 features; value restated on the 4-phase run (macro availability trims early rows)</t>
         </is>
       </c>
     </row>
@@ -3555,12 +3571,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Phase C return % (+macro)</t>
+          <t>Phase B feature attention check</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3580,7 +3596,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>XGBoost importance</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -3590,33 +3606,35 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>RMSE ratio vs train-mean (C)</t>
+          <t>Tier-2 share of importance %</t>
         </is>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>41</v>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>Macro blows out return RMSE to 1.29-1.37x the train-mean null (A/B sat at ~0.99). Clear damage, confirms the overfit reading.</t>
+          <t>XGBoost spends 41% of importance on Tier-2 (macd_signal is top feature at 6/9 horizons) yet accuracy does not improve -&gt; the model USES them but they carry no signal.</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ablation_return_table.csv</t>
+          <t>ablation_tier2_importance.csv</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>worst at 2-3 month horizons</t>
+          <t>strong evidence indicators are redundant with price</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3649,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Phase D ablation (+sector)</t>
+          <t>Phase B return % (+Tier-2)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3656,43 +3674,43 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, ablation</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from sector (pp)</t>
+          <t>RMSE ratio vs train-mean (B)</t>
         </is>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2.6</v>
+        <v>0.991</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>0.991</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Tie</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>FIRST consistently POSITIVE step: +2.6pp mean, positive at 6/9 horizons. Built on C2 (macro changes only). But still 0/9 beat baseline.</t>
+          <t>Tier-2 made return RMSE slightly WORSE at 9/9 horizons (ratio gain +0.000 to +0.046). Sign edge stays negative everywhere.</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>results/direction/phase_ablation/ablation_summary.md</t>
+          <t>ablation_return_table.csv</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_ablation.py; C2 16+7 -&gt; D 39 features; ASPI + COMB/SAMP + LOFC/LOLC/LFIN/CFIN</t>
+          <t>A ratio 0.991 -&gt; B ratio 0.991-1.034</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3730,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Phase D best single horizon</t>
+          <t>Phase C ablation (+macro rates)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3727,7 +3745,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>identical rows/split/seeds, 35d publication lag</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3737,16 +3755,16 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>direct, h=5d (1 week)</t>
+          <t>direct, 9 horizons, ablation</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Edge over baseline (pp)</t>
+          <t>Mean gain from macro (pp)</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>-0.2</v>
+        <v>-2.8</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -3758,17 +3776,17 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>Closest call of the whole study: 1-week Phase D 37.3% vs baseline 37.4%. Near-parity at short horizons (1d -1.7, 1wk -0.2, 2wk -1.6) but never crosses.</t>
+          <t>Macro rates make it WORSE and unstable: gain swings -22.3 to +10.3 pp, 0/9 beat baseline. Not weak signal - overfitting.</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ablation_gain_table.csv</t>
+          <t>results/direction/phase_ablation/ablation_summary.md</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>not a win; single split, one stock</t>
+          <t>direction_phase_ablation.py; 16 -&gt; 29 features; inflation/FX/M2 still uncollected</t>
         </is>
       </c>
     </row>
@@ -3783,12 +3801,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Phase D return sign edge (+sector)</t>
+          <t>Phase C2 diagnostic (macro changes only)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3808,47 +3826,43 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>direct, sign of h-day return</t>
+          <t>direct, 9 horizons, ablation</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Sign edge 1wk/2wk/3wk (pp)</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>+1.7 / +1.7 / +1.1</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>always-guess-winning-side</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>Tie</t>
+          <t>Mean gain from macro d (pp)</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>First POSITIVE sign edges in the study, and at 3 adjacent horizons (1-3 weeks). Tiny (~1-2pp) and one split only -&gt; flag as worth re-testing, NOT a finding.</t>
+          <t>DROPPING RATE LEVELS FIXES THE DAMAGE (-2.8 -&gt; +3.4 pp; 1yr 4.5% -&gt; 49.7%). Non-stationary levels were being memorised. Still 0/9 beat baseline -&gt; form was wrong AND no signal.</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ablation_return_table.csv</t>
+          <t>ablation_gain_table.csv</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>check on other tickers before claiming anything</t>
+          <t>key methodology lesson: feed macro as changes, never levels</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3882,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Phase D feature attention check</t>
+          <t>Phase C feature attention check</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3898,11 +3912,11 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Sector share of importance %</t>
+          <t>Macro share of importance %</t>
         </is>
       </c>
       <c r="K44" s="2" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
@@ -3916,7 +3930,7 @@
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>Sector takes 34% avg (42% at 1 day, falling to 27% at 1yr) - mirror image of macro, which rises with horizon. Sector matters short, macro long, neither enough.</t>
+          <t>Macro importance rises 46% (1d) -&gt; 80% (1yr) while accuracy FALLS. Model fits rates as a trend proxy, not signal. tb_12m/spread/policy_rate are top features at 8/9 horizons.</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3926,7 +3940,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>vol_20 is top feature at 1d/1wk; d_tb3m dominates long</t>
+          <t>fingerprint of trending-variable overfit</t>
         </is>
       </c>
     </row>
@@ -3941,17 +3955,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Sector sweep - replication test</t>
+          <t>Phase C return % (+macro)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks (3 banks, 4 finance, 4 control)</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -3961,33 +3975,29 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge, per stock</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Cells beating baseline</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>27 of 99</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>14 of 99 (Phase A)</t>
-        </is>
+          <t>RMSE ratio vs train-mean (C)</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0.995</v>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
@@ -3996,17 +4006,17 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>Sector features nearly DOUBLE the win rate vs Tier-1 (14-&gt;27 of 99) but wins sit at exactly coin-flip at short horizons and collapse at long ones. No real edge.</t>
+          <t>Macro blows out return RMSE to 1.29-1.37x the train-mean null (A/B sat at ~0.99). Clear damage, confirms the overfit reading.</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>results/direction/sector_sweep/sweep_summary.md</t>
+          <t>ablation_return_table.csv</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>direction_sector_sweep.py; peer composites exclude the target stock</t>
+          <t>worst at 2-3 month horizons</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4036,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Sector gain replication (HNB claim 3)</t>
+          <t>Phase D ablation (+sector)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -4041,48 +4051,48 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>identical protocol per stock</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Phase D - Phase A</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, 9 horizons, ablation</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Mean sector gain (pp)</t>
+          <t>Mean gain from sector (pp)</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M46" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>REPLICATES: +3.8pp mean, positive in 66/99 cells (67%), 9 of 11 stocks positive. HNB was not a fluke - sector context genuinely helps the model. Best: LFIN +13.2, SAMP +9.4, LOFC +8.2. Worst: CTC -11.0.</t>
+          <t>FIRST consistently POSITIVE step: +2.6pp mean, positive at 6/9 horizons. Built on C2 (macro changes only). But still 0/9 beat baseline.</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>sweep_gain_by_ticker.csv</t>
+          <t>results/direction/phase_ablation/ablation_summary.md</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>helping is not the same as winning</t>
+          <t>direction_phase_ablation.py; C2 16+7 -&gt; D 39 features; ASPI + COMB/SAMP + LOFC/LOLC/LFIN/CFIN</t>
         </is>
       </c>
     </row>
@@ -4102,12 +4112,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Sector sweep significance screen</t>
+          <t>Phase D best single horizon</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -4117,29 +4127,29 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>sign test + Wilcoxon across stocks, per horizon</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>binomial sign test (H0 p=0.5)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, h=5d (1 week)</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Best sign-test p</t>
+          <t>Edge over baseline (pp)</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
@@ -4148,17 +4158,17 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>NOTHING SIGNIFICANT AT ANY HORIZON. Best cells (1 day, 1 week) are 6/11 stocks positive = p=0.500, exactly a coin flip. Long horizons far worse (1yr 0/11).</t>
+          <t>Closest call of the whole study: 1-week Phase D 37.3% vs baseline 37.4%. Near-parity at short horizons (1d -1.7, 1wk -0.2, 2wk -1.6) but never crosses.</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>sweep_significance.csv</t>
+          <t>ablation_gain_table.csv</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>stocks share a market factor so p-values are already optimistic</t>
+          <t>not a win; single split, one stock</t>
         </is>
       </c>
     </row>
@@ -4173,17 +4183,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>HNB sign-edge claim retest (claim 2)</t>
+          <t>Phase D return sign edge (+sector)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -4193,7 +4203,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>identical protocol per stock</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4203,42 +4213,42 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>direct, sign of h-day return, 1-3 week horizons</t>
+          <t>direct, sign of h-day return</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Cells with positive sign edge</t>
+          <t>Sign edge 1wk/2wk/3wk (pp)</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>6 of 33</t>
+          <t>+1.7 / +1.7 / +1.1</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>~17 of 33 (coin flip)</t>
-        </is>
-      </c>
-      <c r="M48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>always-guess-winning-side</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Tie</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>REFUTED. HNB's positive 1-3 week sign edge did NOT replicate - 18% vs the ~50% chance would give. It was luck. Flagged as provisional when found, now closed.</t>
+          <t>First POSITIVE sign edges in the study, and at 3 adjacent horizons (1-3 weeks). Tiny (~1-2pp) and one split only -&gt; flag as worth re-testing, NOT a finding.</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>sweep_all_results.csv</t>
+          <t>ablation_return_table.csv</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>value of naming a claim before retesting it</t>
+          <t>check on other tickers before claiming anything</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4268,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Phase E - daily USD/LKR</t>
+          <t>Phase D feature attention check</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -4273,48 +4283,50 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge, 2015-2026 window</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>XGBoost importance</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from daily FX (pp)</t>
+          <t>Sector share of importance %</t>
         </is>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>34</v>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>FREQUENCY WAS NOT THE PROBLEM. Daily FX gain is exactly 0.0pp (positive in 57/99 cells = coin flip). Macro fails daily exactly as it failed monthly.</t>
+          <t>Sector takes 34% avg (42% at 1 day, falling to 27% at 1yr) - mirror image of macro, which rises with horizon. Sector matters short, macro long, neither enough.</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>results/direction/daily_macro/daily_macro_summary.md</t>
+          <t>ablation_feature_importance.csv</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>direction_daily_macro.py; new cleaned_data/usd_lkr_daily.csv</t>
+          <t>vol_20 is top feature at 1d/1wk; d_tb3m dominates long</t>
         </is>
       </c>
     </row>
@@ -4334,12 +4346,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Phase E2 - daily global + CPI</t>
+          <t>Sector sweep - replication test</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>11 CSE stocks (3 banks, 4 finance, 4 control)</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -4349,7 +4361,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>80/20 chrono + h-bar purge, per stock</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4364,14 +4376,18 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from global+CPI (pp)</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>Cells beating baseline</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>27 of 99</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>14 of 99 (Phase A)</t>
+        </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
@@ -4380,17 +4396,17 @@
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>Oil, US 10Y, DXY and inflation make it WORSE (-1.9pp), worst at long horizons (-6.0pp at 1yr). Same trending-variable overfit as Phase C.</t>
+          <t>Sector features nearly DOUBLE the win rate vs Tier-1 (14-&gt;27 of 99) but wins sit at exactly coin-flip at short horizons and collapse at long ones. No real edge.</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>daily_macro_gain.csv</t>
+          <t>results/direction/sector_sweep/sweep_summary.md</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>CPI spliced across 4 base years; money supply excluded (ends 2024-08, inside test window)</t>
+          <t>direction_sector_sweep.py; peer composites exclude the target stock</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4426,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Phase E significance screen</t>
+          <t>Sector gain replication (HNB claim 3)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4425,50 +4441,48 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>sign test across stocks, 4 phases x 9 horizons</t>
+          <t>identical protocol per stock</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>binomial sign test (H0 p=0.5)</t>
+          <t>Phase D - Phase A</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Combinations with p&lt;0.05</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>0 of 36</t>
-        </is>
+          <t>Mean sector gain (pp)</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>3.8</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>0</v>
+      </c>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>NOTHING SIGNIFICANT ANYWHERE. Best cell is 1 day (6/11 stocks, p=0.500) - exact coin flip, same as the sector sweep. Cells beating baseline: A 17, D 27, E 24, E2 25 of 99.</t>
+          <t>REPLICATES: +3.8pp mean, positive in 66/99 cells (67%), 9 of 11 stocks positive. HNB was not a fluke - sector context genuinely helps the model. Best: LFIN +13.2, SAMP +9.4, LOFC +8.2. Worst: CTC -11.0.</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>daily_macro_significance.csv</t>
+          <t>sweep_gain_by_ticker.csv</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>macro information source now closed at both frequencies</t>
+          <t>helping is not the same as winning</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4502,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Phase E feature attention check</t>
+          <t>Sector sweep significance screen</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4503,50 +4517,48 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>sign test + Wilcoxon across stocks, per horizon</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>XGBoost importance</t>
+          <t>binomial sign test (H0 p=0.5)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>New-data share of importance %</t>
+          <t>Best sign-test p</t>
         </is>
       </c>
       <c r="K52" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M52" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.5</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>Model spends 27% of importance on the new data (FX 7%, global 11%, CPI 9%) and gains nothing - third time this fingerprint has appeared (Tier-2 41%, macro 64%, now 27%).</t>
+          <t>NOTHING SIGNIFICANT AT ANY HORIZON. Best cells (1 day, 1 week) are 6/11 stocks positive = p=0.500, exactly a coin flip. Long horizons far worse (1yr 0/11).</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>daily_macro_all_results.csv</t>
+          <t>sweep_significance.csv</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>using a feature is not the same as profiting from it</t>
+          <t>stocks share a market factor so p-values are already optimistic</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4578,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Phase F - money supply (M1/M2/M2b/M4)</t>
+          <t>HNB sign-edge claim retest (claim 2)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -4581,29 +4593,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono, sample cut at 2024-08; test 2022-03 to 2024-08</t>
+          <t>identical protocol per stock</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, sign of h-day return, 1-3 week horizons</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from money supply (pp)</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>Cells with positive sign edge</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>6 of 33</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>~17 of 33 (coin flip)</t>
+        </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
@@ -4612,17 +4628,17 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>Money supply adds NOTHING even on a crisis-era test window (positive in 50/99 cells = exact coin flip). Window moved back so M1/M2 could be tested fairly rather than excluded.</t>
+          <t>REFUTED. HNB's positive 1-3 week sign edge did NOT replicate - 18% vs the ~50% chance would give. It was luck. Flagged as provisional when found, now closed.</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>results/direction/money_supply/money_summary.md</t>
+          <t>sweep_all_results.csv</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>direction_money_supply.py; 65-day publication lag per CBSL's own note; reserve money dropped (ends 2024-02)</t>
+          <t>value of naming a claim before retesting it</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4658,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Phase F - full classic macro set</t>
+          <t>Phase E - daily USD/LKR</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4657,7 +4673,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>80/20 chrono + h-bar purge, 2015-2026 window</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4672,11 +4688,11 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Mean gain money-&gt;full macro (pp)</t>
+          <t>Mean gain from daily FX (pp)</t>
         </is>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -4688,17 +4704,17 @@
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>Full classic set (money + rates + FX + inflation) = 4 of the 5 Naik-Padhi variables. Still 42/99 cells, below the money-only phase (51/99). Only industrial production remains uncollected.</t>
+          <t>FREQUENCY WAS NOT THE PROBLEM. Daily FX gain is exactly 0.0pp (positive in 57/99 cells = coin flip). Macro fails daily exactly as it failed monthly.</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>money_gain.csv</t>
+          <t>results/direction/daily_macro/daily_macro_summary.md</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>closes the macro chapter apart from IIP</t>
+          <t>direction_daily_macro.py; new cleaned_data/usd_lkr_daily.csv</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4734,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Crisis-window effect (window sensitivity)</t>
+          <t>Phase E2 - daily global + CPI</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -4733,7 +4749,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>2022-03 to 2024-08 vs 2024-2026</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4748,37 +4764,33 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Cells beating baseline</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>43-51 of 99</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>17-27 of 99 (calm window)</t>
-        </is>
-      </c>
-      <c r="M55" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Mean gain from global+CPI (pp)</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>IMPORTANT METHOD FINDING: moving the test window into the 2022 crisis roughly DOUBLES the win rate for ALL phases including price-only. Results are window-dependent, not model-dependent.</t>
+          <t>Oil, US 10Y, DXY and inflation make it WORSE (-1.9pp), worst at long horizons (-6.0pp at 1yr). Same trending-variable overfit as Phase C.</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>money_by_horizon.csv</t>
+          <t>daily_macro_gain.csv</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>argues for walk-forward / multi-window evaluation in the write-up</t>
+          <t>CPI spliced across 4 base years; money supply excluded (ends 2024-08, inside test window)</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4810,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1-day significance - macro ruled out</t>
+          <t>Phase E significance screen</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4828,18 +4840,16 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Cells with p&lt;0.05</t>
+          <t>Combinations with p&lt;0.05</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2 of 36</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>1.8 expected by chance</t>
-        </is>
+          <t>0 of 36</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0.05</v>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
@@ -4848,17 +4858,17 @@
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>Both hits are at 1 day, and the STRONGEST is Phase A (price only, 9/11, +3.9pp, p=0.033). Adding money supply SHRINKS it to +3.2pp. So it is the crisis window, not macro - and 2/36 is chance anyway.</t>
+          <t>NOTHING SIGNIFICANT ANYWHERE. Best cell is 1 day (6/11 stocks, p=0.500) - exact coin flip, same as the sector sweep. Cells beating baseline: A 17, D 27, E 24, E2 25 of 99.</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>money_significance.csv</t>
+          <t>daily_macro_significance.csv</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>checking the null model is what prevented a false claim</t>
+          <t>macro information source now closed at both frequencies</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4878,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4878,7 +4888,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Phase G - industrial production (IIP)</t>
+          <t>Phase E feature attention check</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -4893,12 +4903,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono, sample 2016-2026 (IIP coverage)</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>XGBoost importance</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -4908,33 +4918,35 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from IIP (pp)</t>
+          <t>New-data share of importance %</t>
         </is>
       </c>
       <c r="K57" s="2" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>27</v>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M57" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>IIP makes it WORSE (-6.4pp, positive in only 25/99 cells, 0/36 significant). It was the STRONGEST variable in the Naik-Padhi reference paper, and it still does not predict direction.</t>
+          <t>Model spends 27% of importance on the new data (FX 7%, global 11%, CPI 9%) and gains nothing - third time this fingerprint has appeared (Tier-2 41%, macro 64%, now 27%).</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>results/direction/industrial_production/iip_summary.md</t>
+          <t>daily_macro_all_results.csv</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>direction_industrial_production.py; DCS index entered by hand, 2016-01 to 2026-05; 50-day publication lag</t>
+          <t>using a feature is not the same as profiting from it</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4956,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4954,7 +4966,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Phase G - full classic macro set complete</t>
+          <t>Phase F - money supply (M1/M2/M2b/M4)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -4969,7 +4981,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>80/20 chrono, sample cut at 2024-08; test 2022-03 to 2024-08</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4984,18 +4996,14 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Cells beating baseline</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>25 of 99</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>27 of 99 (no macro)</t>
-        </is>
+          <t>Mean gain from money supply (pp)</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
@@ -5004,17 +5012,17 @@
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>ALL FIVE Naik-Padhi macro variables now tested (IIP, money supply, T-bill rate, exchange rate, inflation). NONE beats plain price history. Macro chapter complete.</t>
+          <t>Money supply adds NOTHING even on a crisis-era test window (positive in 50/99 cells = exact coin flip). Window moved back so M1/M2 could be tested fairly rather than excluded.</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>iip_gain.csv</t>
+          <t>results/direction/money_supply/money_summary.md</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>adding all macro is WORSE than sector-only (27/99)</t>
+          <t>direction_money_supply.py; 65-day publication lag per CBSL's own note; reserve money dropped (ends 2024-02)</t>
         </is>
       </c>
     </row>
@@ -5024,77 +5032,73 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>IIP seasonality guard</t>
+          <t>Phase F - full classic macro set</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Sri Lanka DCS IIP</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>monthly (125)</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>2016-01 to 2026-05</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>seasonal inspection</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>April vs March gap (pts)</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>-10 to -34</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M59" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Mean gain money-&gt;full macro (pp)</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>IIP is NOT seasonally adjusted - April falls 10-34 pts EVERY year (Sinhala/Tamil New Year), March always peaks. Month-on-month would be a calendar signal, so YoY-only features were used.</t>
+          <t>Full classic set (money + rates + FX + inflation) = 4 of the 5 Naik-Padhi variables. Still 42/99 cells, below the money-only phase (51/99). Only industrial production remains uncollected.</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>cleaned_data/industrial_production_monthly.csv</t>
+          <t>money_gain.csv</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>clean_macro_sources.py; mom column deliberately named _DO_NOT_USE</t>
+          <t>closes the macro chapter apart from IIP</t>
         </is>
       </c>
     </row>
@@ -5104,22 +5108,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Correlation</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Co-movement lift table (no model)</t>
+          <t>Crisis-window effect (window sensitivity)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks (22,677 stock-days)</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -5129,29 +5133,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>full panel, 15 indicators x 9 horizons</t>
+          <t>2022-03 to 2024-08 vs 2024-2026</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>conditional probability + 2-proportion z</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Median |lift| short horizons (pp)</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>Cells beating baseline</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>43-51 of 99</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>17-27 of 99 (calm window)</t>
+        </is>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -5160,17 +5168,17 @@
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>'If indicator up, does stock go up?' answered by pure counting. Market/peer indicators give a real +6 to +10pp lift at 1d-1mo on huge samples. Macro lifts are near zero at short horizons.</t>
+          <t>IMPORTANT METHOD FINDING: moving the test window into the 2022 crisis roughly DOUBLES the win rate for ALL phases including price-only. Results are window-dependent, not model-dependent.</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>results/direction/pooled_rules/comovement_table.csv</t>
+          <t>money_by_horizon.csv</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>direction_pooled_and_rules.py; lift = P(up|ind up) - P(up|ind down)</t>
+          <t>argues for walk-forward / multi-window evaluation in the write-up</t>
         </is>
       </c>
     </row>
@@ -5180,22 +5188,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Correlation</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Co-movement - long-horizon lifts are artifacts</t>
+          <t>1-day significance - macro ruled out</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -5205,12 +5213,12 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>panel, |lift|&gt;=10pp cells</t>
+          <t>sign test across stocks, 4 phases x 9 horizons</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>independent-window audit</t>
+          <t>binomial sign test (H0 p=0.5)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -5220,17 +5228,17 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Independent windows behind biggest lifts</t>
+          <t>Cells with p&lt;0.05</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>7-24</t>
+          <t>2 of 36</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>hundreds needed</t>
+          <t>1.8 expected by chance</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
@@ -5240,17 +5248,17 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>All 19 large lifts (T-bill -19.3, M2 +17.0, USD/LKR -15.3) sit at 3mo-1yr where only 7-24 INDEPENDENT windows exist. Overlapping windows inflate the z-test. Discard them.</t>
+          <t>Both hits are at 1 day, and the STRONGEST is Phase A (price only, 9/11, +3.9pp, p=0.033). Adding money supply SHRINKS it to +3.2pp. So it is the crisis window, not macro - and 2/36 is chance anyway.</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>comovement_table.csv</t>
+          <t>money_significance.csv</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>median |lift| long 4.2pp vs short 2.5pp is a sample-size illusion</t>
+          <t>checking the null model is what prevented a false claim</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5278,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Pooled panel model (sector-wide)</t>
+          <t>Phase G - industrial production (IIP)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks pooled</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -5285,7 +5293,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>split by DATE not row, 17,770 train rows</t>
+          <t>80/20 chrono, sample 2016-2026 (IIP coverage)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5295,23 +5303,19 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, one model for whole sector</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Horizons beating pooled baseline</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>2 of 9</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>majority / persistence</t>
-        </is>
+          <t>Mean gain from IIP (pp)</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
@@ -5320,17 +5324,17 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>7x more training data (17,770 vs ~2,700 per stock). Beats the POOLED baseline at 1 day (+3.3pp) and 1 week (+2.7pp) only.</t>
+          <t>IIP makes it WORSE (-6.4pp, positive in only 25/99 cells, 0/36 significant). It was the STRONGEST variable in the Naik-Padhi reference paper, and it still does not predict direction.</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>results/direction/pooled_rules/pooled_model_results.csv</t>
+          <t>results/direction/industrial_production/iip_summary.md</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>direction_pooled_and_rules.py</t>
+          <t>direction_industrial_production.py; DCS index entered by hand, 2016-01 to 2026-05; 50-day publication lag</t>
         </is>
       </c>
     </row>
@@ -5350,12 +5354,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Pooled model fairness check</t>
+          <t>Phase G - full classic macro set complete</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -5365,32 +5369,32 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>pooled model scored vs each stock's OWN baseline</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>binomial sign test (H0 p=0.5)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>1-day: stocks positive</t>
+          <t>Cells beating baseline</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>6 of 7</t>
+          <t>25 of 99</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>p=0.062</t>
+          <t>27 of 99 (no macro)</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
@@ -5400,17 +5404,17 @@
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>STRONGEST RESULT OF THE PROJECT but still not significant. The 1-week +2.7pp was a POOLING ARTIFACT (-0.5pp vs own baselines). Only 1 day survives: median +2.5pp, p=0.062, 1 of 9 horizons, single window.</t>
+          <t>ALL FIVE Naik-Padhi macro variables now tested (IIP, money supply, T-bill rate, exchange rate, inflation). NONE beats plain price history. Macro chapter complete.</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>pooled_vs_own_baseline.csv</t>
+          <t>iip_gain.csv</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>pooling stocks with different class balance weakens the majority baseline and fakes an edge</t>
+          <t>adding all macro is WORSE than sector-only (27/99)</t>
         </is>
       </c>
     </row>
@@ -5425,68 +5429,72 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Readable rules extracted</t>
+          <t>IIP seasonality guard</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks pooled</t>
+          <t>Sri Lanka DCS IIP</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly (125)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>depth-3 tree, scored on unseen test set</t>
+          <t>2016-01 to 2026-05</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Decision tree (depth 3)</t>
+          <t>seasonal inspection</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/22</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Best 1-day rule accuracy %</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="M64" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>April vs March gap (pts)</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>-10 to -34</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>17 plain-English rules with out-of-sample hit rates. Best 1-day rule: calm market + flat ASPI + no big drop -&gt; Hold, 49.3% (+11.3pp). Shows WHAT the model believes, not just that it fails.</t>
+          <t>IIP is NOT seasonally adjusted - April falls 10-34 pts EVERY year (Sinhala/Tamil New Year), March always peaks. Month-on-month would be a calendar signal, so YoY-only features were used.</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>readable_rules.csv</t>
+          <t>cleaned_data/industrial_production_monthly.csv</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>1-month rule at 68.5% fires only 317 times - treat as noise</t>
+          <t>clean_macro_sources.py; mom column deliberately named _DO_NOT_USE</t>
         </is>
       </c>
     </row>
@@ -5501,17 +5509,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Correlation</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>1-day claim re-test (walk-forward)</t>
+          <t>Co-movement lift table (no model)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>7 bank/finance stocks (22,677 stock-days)</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -5521,52 +5529,48 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>21 non-overlapping 6-month windows, expanding train</t>
+          <t>full panel, 15 indicators x 9 horizons</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost (reported separately)</t>
+          <t>conditional probability + 2-proportion z</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>direct, walk-forward, h=1</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Folds with positive median edge</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>6-7 of 21</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>10.5 expected by chance</t>
-        </is>
-      </c>
-      <c r="M65" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Median |lift| short horizons (pp)</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>CLAIM REFUTED. Median of fold medians -1.8pp (Logistic) / -1.9pp (XGBoost), sign-test p=0.96 and 0.99. The single-split +2.5pp did not survive 21 independent windows.</t>
+          <t>'If indicator up, does stock go up?' answered by pure counting. Market/peer indicators give a real +6 to +10pp lift at 1d-1mo on huge samples. Macro lifts are near zero at short horizons.</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>results/direction/retest_1day/retest_summary.md</t>
+          <t>results/direction/pooled_rules/comovement_table.csv</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>direction_1day_retest.py; verdict rule fixed IN ADVANCE; 1-week carried as control, also negative</t>
+          <t>direction_pooled_and_rules.py; lift = P(up|ind up) - P(up|ind down)</t>
         </is>
       </c>
     </row>
@@ -5581,12 +5585,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Correlation</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1-day re-test - window regime effect</t>
+          <t>Co-movement - long-horizon lifts are artifacts</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -5601,52 +5605,52 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>21 walk-forward folds</t>
+          <t>panel, |lift|&gt;=10pp cells</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>independent-window audit</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Positive folds 2016-2020 vs 2021-2024</t>
+          <t>Independent windows behind biggest lifts</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>1 of 10 vs 6 of 8</t>
+          <t>7-24</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M66" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>hundreds needed</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>Confirms the crisis-window finding a second time: folds in 2021-2024 are mostly POSITIVE, 2016-2020 mostly negative. Apparent skill is a property of the period, not the model.</t>
+          <t>All 19 large lifts (T-bill -19.3, M2 +17.0, USD/LKR -15.3) sit at 3mo-1yr where only 7-24 INDEPENDENT windows exist. Overlapping windows inflate the z-test. Discard them.</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>retest_by_fold.csv</t>
+          <t>comovement_table.csv</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>strong argument for walk-forward reporting in the dissertation</t>
+          <t>median |lift| long 4.2pp vs short 2.5pp is a sample-size illusion</t>
         </is>
       </c>
     </row>
@@ -5666,12 +5670,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>1-day re-test - per stock consistency</t>
+          <t>Pooled panel model (sector-wide)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>7 bank/finance stocks pooled</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -5681,32 +5685,32 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>21 walk-forward folds each</t>
+          <t>split by DATE not row, 17,770 train rows</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1</t>
+          <t>direct, 9 horizons, one model for whole sector</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Stocks positive in &gt;50% of folds</t>
+          <t>Horizons beating pooled baseline</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>2 of 7</t>
+          <t>2 of 9</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>majority / persistence</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
@@ -5716,17 +5720,17 @@
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>No consistency: LOFC and CFIN positive in 62% of folds, HNB in only 19%. A real edge would show across the sector, not in two names.</t>
+          <t>7x more training data (17,770 vs ~2,700 per stock). Beats the POOLED baseline at 1 day (+3.3pp) and 1 week (+2.7pp) only.</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>retest_by_stock.csv</t>
+          <t>results/direction/pooled_rules/pooled_model_results.csv</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>median edge per stock ranges +4.9 (LOFC) to -4.9 (SAMP)</t>
+          <t>direction_pooled_and_rules.py</t>
         </is>
       </c>
     </row>
@@ -5746,47 +5750,47 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>LSTM/GRU for direction</t>
+          <t>Pooled model fairness check</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks pooled</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>daily (30-day sequences)</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>7 walk-forward 12-month folds, 3 seeds</t>
+          <t>pooled model scored vs each stock's OWN baseline</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>LSTM + GRU (PyTorch)</t>
+          <t>binomial sign test (H0 p=0.5)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>direct, sequence input, h=1/5/22</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Folds positive (LSTM, h=1)</t>
+          <t>1-day: stocks positive</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>5 of 7</t>
+          <t>6 of 7</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>p=0.227</t>
+          <t>p=0.062</t>
         </is>
       </c>
       <c r="M68" s="5" t="inlineStr">
@@ -5796,17 +5800,17 @@
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>Recurrent nets do NOT beat the naive baseline at any horizon. Closes the 'did you try deep learning on direction?' question. LSTM finally applied to the direction target (project is named after it).</t>
+          <t>STRONGEST RESULT OF THE PROJECT but still not significant. The 1-week +2.7pp was a POOLING ARTIFACT (-0.5pp vs own baselines). Only 1 day survives: median +2.5pp, p=0.062, 1 of 9 horizons, single window.</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>results/direction/lstm_gru/lstm_gru_summary.md</t>
+          <t>pooled_vs_own_baseline.csv</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>direction_lstm_gru.py; monthly macro excluded (flat inside a 30-day window)</t>
+          <t>pooling stocks with different class balance weakens the majority baseline and fakes an edge</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5830,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Sequence vs flat control (LSTM value)</t>
+          <t>Readable rules extracted</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -5841,12 +5845,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>identical sequences, flattened for the control</t>
+          <t>depth-3 tree, scored on unseen test set</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>LSTM vs Logistic on flattened sequences</t>
+          <t>Decision tree (depth 3)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -5856,37 +5860,33 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Median edge LSTM vs flat (pp)</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>+2.9 vs -1.7</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>Logistic(flat)</t>
-        </is>
-      </c>
-      <c r="M69" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Best 1-day rule accuracy %</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="M69" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>REAL NUANCE: LSTM beats the FLATTENED same data at ALL 3 horizons (1d +2.9 vs -1.7, 1wk -0.4 vs -2.1, 1mo -5.4 vs -9.9). Order of recent days carries a little signal that summary features discard - first time added complexity helped. Still not enough to reach the baseline.</t>
+          <t>17 plain-English rules with out-of-sample hit rates. Best 1-day rule: calm market + flat ASPI + no big drop -&gt; Hold, 49.3% (+11.3pp). Shows WHAT the model believes, not just that it fails.</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>lstm_gru_by_fold.csv</t>
+          <t>readable_rules.csv</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>the flat control is what makes this interpretable</t>
+          <t>1-month rule at 68.5% fires only 317 times - treat as noise</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Regime effect - THIRD confirmation</t>
+          <t>1-day claim re-test (walk-forward)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5921,52 +5921,52 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>7 walk-forward folds, LSTM h=1</t>
+          <t>21 non-overlapping 6-month windows, expanding train</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>Logistic + XGBoost (reported separately)</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, walk-forward, h=1</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Positive folds 2019-2020 vs 2021-2025</t>
+          <t>Folds with positive median edge</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0 of 2 vs 5 of 5</t>
+          <t>6-7 of 21</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>10.5 expected by chance</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>Same window/regime pattern found for a THIRD time (after money supply and the 1-day retest). Every model looks skilled post-2021 and useless before, with identical code and features. Explains why 5/7 folds here is not convincing.</t>
+          <t>CLAIM REFUTED. Median of fold medians -1.8pp (Logistic) / -1.9pp (XGBoost), sign-test p=0.96 and 0.99. The single-split +2.5pp did not survive 21 independent windows.</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>lstm_gru_by_fold.csv</t>
+          <t>results/direction/retest_1day/retest_summary.md</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>strongest methodological finding of the project</t>
+          <t>direction_1day_retest.py; verdict rule fixed IN ADVANCE; 1-week carried as control, also negative</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Phase H - news sentiment</t>
+          <t>1-day re-test - window regime effect</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>7 walk-forward 6-month folds, 2016-2022</t>
+          <t>21 walk-forward folds</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -6011,38 +6011,42 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/10/22</t>
+          <t>direct, h=1</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from sentiment (pp)</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Positive folds 2016-2020 vs 2021-2024</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>1 of 10 vs 6 of 8</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>News sentiment does NOT improve direction. Gain positive at 2 of 4 horizons (-0.8, -0.7, +2.4, +1.6), nothing near significance (all p&gt;=0.50). No phase beats the naive baseline.</t>
+          <t>Confirms the crisis-window finding a second time: folds in 2021-2024 are mostly POSITIVE, 2016-2020 mostly negative. Apparent skill is a property of the period, not the model.</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>results/direction/sentiment/sentiment_summary.md</t>
+          <t>retest_by_fold.csv</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_h_sentiment.py; 149k Dailymirror/Newsfirst articles, 9,785 market-relevant</t>
+          <t>strong argument for walk-forward reporting in the dissertation</t>
         </is>
       </c>
     </row>
@@ -6062,12 +6066,12 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Phase H - lexicon disagreement</t>
+          <t>1-day re-test - per stock consistency</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Dailymirror + Newsfirst news</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -6077,50 +6081,52 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>9,785 market-relevant articles 2016-2022</t>
+          <t>21 walk-forward folds each</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>VADER vs Loughran-McDonald style</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>sentiment scoring</t>
+          <t>direct, h=1</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Correlation between lexicons</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="n">
-        <v>0.416</v>
+          <t>Stocks positive in &gt;50% of folds</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>2 of 7</t>
+        </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M72" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>Two reasonable sentiment measures on the SAME articles correlate only 0.42. Direct evidence the sentiment signal is fragile, not merely weak. Running one lexicon alone would have hidden this.</t>
+          <t>No consistency: LOFC and CFIN positive in 62% of folds, HNB in only 19%. A real edge would show across the sector, not in two names.</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>sentiment_verdict.csv</t>
+          <t>retest_by_stock.csv</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>finance_lexicon.py; full LM dictionary can be dropped in without code change</t>
+          <t>median edge per stock ranges +4.9 (LOFC) to -4.9 (SAMP)</t>
         </is>
       </c>
     </row>
@@ -6140,67 +6146,67 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Phase H - regime confound ruled out</t>
+          <t>LSTM/GRU for direction</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>7 bank/finance stocks pooled</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>daily (30-day sequences)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>folds split calm vs crisis</t>
+          <t>7 walk-forward 12-month folds, 3 seeds</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>LSTM + GRU (PyTorch)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, sequence input, h=1/5/22</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Sentiment gain calm vs crisis (pp)</t>
+          <t>Folds positive (LSTM, h=1)</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>+0.85 vs -0.45</t>
+          <t>5 of 7</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>p=0.227</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>Expected sentiment to 'work' only in the 2022 crisis; the OPPOSITE happened (calm 9/16 folds positive, crisis 3/12). So this null is NOT a regime artifact - cleaner than the other phases.</t>
+          <t>Recurrent nets do NOT beat the naive baseline at any horizon. Closes the 'did you try deep learning on direction?' question. LSTM finally applied to the direction target (project is named after it).</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>sentiment_regime_split.csv</t>
+          <t>results/direction/lstm_gru/lstm_gru_summary.md</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>first phase where the regime effect did not appear</t>
+          <t>direction_lstm_gru.py; monthly macro excluded (flat inside a 30-day window)</t>
         </is>
       </c>
     </row>
@@ -6215,17 +6221,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>News look-ahead guard</t>
+          <t>Sequence vs flat control (LSTM value)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Dailymirror + Newsfirst news</t>
+          <t>7 bank/finance stocks pooled</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -6235,50 +6241,52 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>publication timestamps vs 14:30 CSE close</t>
+          <t>identical sequences, flattened for the control</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>time-of-day assignment</t>
+          <t>LSTM vs Logistic on flattened sequences</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>direct, h=1/5/22</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Articles pushed to next trading day %</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="n">
-        <v>36</v>
+          <t>Median edge LSTM vs flat (pp)</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>+2.9 vs -1.7</t>
+        </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
+          <t>Logistic(flat)</t>
+        </is>
+      </c>
+      <c r="M74" s="6" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M74" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>36% of articles were published AFTER the 14:30 close and were reassigned to the next trading day. Without this rule those articles report the very move being predicted and sentiment would look excellent and be worthless.</t>
+          <t>REAL NUANCE: LSTM beats the FLATTENED same data at ALL 3 horizons (1d +2.9 vs -1.7, 1wk -0.4 vs -2.1, 1mo -5.4 vs -9.9). Order of recent days carries a little signal that summary features discard - first time added complexity helped. Still not enough to reach the baseline.</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>cleaned_data/news_sentiment_daily.csv</t>
+          <t>lstm_gru_by_fold.csv</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>only 75 of 149,240 rows lacked a timestamp</t>
+          <t>the flat control is what makes this interpretable</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6306,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>POSITIVE CONTROL - pipeline validation</t>
+          <t>Regime effect - THIRD confirmation</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -6313,48 +6321,52 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, same-day vs lagged info</t>
+          <t>7 walk-forward folds, LSTM h=1</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>LSTM</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>contemporaneous vs predictive</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Edge over baseline (pp)</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="M75" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Positive folds 2019-2020 vs 2021-2025</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>0 of 2 vs 5 of 5</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>DECISIVE: same code finds +8.2pp (17/19 folds, p=0.0004) using TODAY's market/macro/news, and -4.1pp using the SAME info one day earlier. Gap 13.7pp. The pipeline is NOT blind - this information EXPLAINS returns but does not PREDICT them.</t>
+          <t>Same window/regime pattern found for a THIRD time (after money supply and the 1-day retest). Every model looks skilled post-2021 and useless before, with identical code and features. Explains why 5/7 folds here is not convincing.</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>results/direction/diagnostics/diagnostics_summary.md</t>
+          <t>lstm_gru_by_fold.csv</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>direction_diagnostics.py; own-stock return excluded from contemporaneous features</t>
+          <t>strongest methodological finding of the project</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6386,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Binary up/down reformulation</t>
+          <t>Phase H - news sentiment</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6389,7 +6401,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds</t>
+          <t>7 walk-forward 6-month folds, 2016-2022</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6399,16 +6411,16 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>binary, h=1/5/22</t>
+          <t>direct, h=1/5/10/22</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Edge over baseline (pp)</t>
+          <t>Mean gain from sentiment (pp)</t>
         </is>
       </c>
       <c r="K76" s="2" t="n">
-        <v>-4.8</v>
+        <v>0.6</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -6420,17 +6432,17 @@
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>3-class dead-zone was NOT hiding a signal. Binary edge -4.8/-1.1/-2.1pp at 1d/1wk/1mo, positive in only 1/19, 7/19, 4/19 folds.</t>
+          <t>News sentiment does NOT improve direction. Gain positive at 2 of 4 horizons (-0.8, -0.7, +2.4, +1.6), nothing near significance (all p&gt;=0.50). No phase beats the naive baseline.</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>diagnostics_verdict.csv</t>
+          <t>results/direction/sentiment/sentiment_summary.md</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>rules out the Hold-majority explanation</t>
+          <t>direction_phase_h_sentiment.py; 149k Dailymirror/Newsfirst articles, 9,785 market-relevant</t>
         </is>
       </c>
     </row>
@@ -6450,12 +6462,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>MAGNITUDE-WEIGHTED edge (survives)</t>
+          <t>Phase H - lexicon disagreement</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>Dailymirror + Newsfirst news</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -6465,50 +6477,50 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds</t>
+          <t>9,785 market-relevant articles 2016-2022</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>VADER vs Loughran-McDonald style</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>binary, |return|-weighted</t>
+          <t>sentiment scoring</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Weighted edge 1d / 1wk (pp)</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>+7.9 / +13.2</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Correlation between lexicons</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>FIRST RESULT TO SURVIVE. Model is WRONG more often than baseline on plain accuracy (-4.3pp) but RIGHT on the big moves: weighted edge +7.9pp (15/19 folds, p=0.0096) at 1 day and +13.2pp (15/19, p=0.0096) at 1 week. Accuracy was the wrong metric.</t>
+          <t>Two reasonable sentiment measures on the SAME articles correlate only 0.42. Direct evidence the sentiment signal is fragile, not merely weak. Running one lexicon alone would have hidden this.</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>diagnostics_magnitude.csv</t>
+          <t>sentiment_verdict.csv</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>1-month +9.5pp but p=0.18</t>
+          <t>finance_lexicon.py; full LM dictionary can be dropped in without code change</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6540,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Trading backtest with costs</t>
+          <t>Phase H - regime confound ruled out</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -6543,48 +6555,52 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, h=1 only (non-overlapping)</t>
+          <t>folds split calm vs crisis</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>long/short on model signal</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>economic evaluation</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Net return @50bps (%)</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="M78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Sentiment gain calm vs crisis (pp)</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>+0.85 vs -0.45</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>THE EDGE IS REAL BUT NOT EXPLOITABLE. Gross +22.19% vs buy-and-hold +6.49%, but median 40 position flips per 6-month fold: net +17.35% @10bps, +11.24% @25bps, +0.05% @50bps. At realistic CSE costs the edge is exactly zero (8/19 folds, p=0.82).</t>
+          <t>Expected sentiment to 'work' only in the 2022 crisis; the OPPOSITE happened (calm 9/16 folds positive, crisis 3/12). So this null is NOT a regime artifact - cleaner than the other phases.</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>diagnostics_backtest_h1.csv</t>
+          <t>sentiment_regime_split.csv</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>h=5 and h=22 backtests omitted - overlapping returns cannot be summed</t>
+          <t>first phase where the regime effect did not appear</t>
         </is>
       </c>
     </row>
@@ -6599,17 +6615,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Price + macro + news vs naive</t>
+          <t>News look-ahead guard</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>Dailymirror + Newsfirst news</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -6619,52 +6635,50 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>walk-forward 6-month folds, per stock</t>
+          <t>publication timestamps vs 14:30 CSE close</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>naive / ARIMA(1,1,1) / Ridge / XGBoost</t>
+          <t>time-of-day assignment</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>1-day and 5-day, return-then-reconstruct</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Cases beating naive (MAPE)</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>0 of 133</t>
-        </is>
+          <t>Articles pushed to next trading day %</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>36</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>naive</t>
-        </is>
-      </c>
-      <c r="M79" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>NAIVE UNBEATEN. Best model ARIMA(1,1,1) at 1.004x naive MAPE. Stage 1's univariate conclusion survives the multivariate test - adding macro and news does not rescue price forecasting.</t>
+          <t>36% of articles were published AFTER the 14:30 close and were reassigned to the next trading day. Without this rule those articles report the very move being predicted and sentiment would look excellent and be worthless.</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>results/price_macro_news/price_summary.md</t>
+          <t>cleaned_data/news_sentiment_daily.csv</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>price_with_macro_news.py; models predict RETURN then reconstruct price to stop them echoing today's price</t>
+          <t>only 75 of 149,240 rows lacked a timestamp</t>
         </is>
       </c>
     </row>
@@ -6679,12 +6693,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Does macro/news improve price forecasting?</t>
+          <t>POSITIVE CONTROL - pipeline validation</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -6699,48 +6713,48 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>nested feature sets P / P+M / P+M+N</t>
+          <t>19 walk-forward folds, same-day vs lagged info</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>ablation on MAPE</t>
+          <t>contemporaneous vs predictive</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Median MAPE improvement (pp)</t>
+          <t>Edge over baseline (pp)</t>
         </is>
       </c>
       <c r="K80" s="2" t="n">
-        <v>-0.019</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>-4.1</v>
+      </c>
+      <c r="M80" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>ALL EIGHT combinations NEGATIVE (-0.008 to -0.078pp). Adding macro and news makes price forecasting WORSE, consistently across both algorithms and both horizons.</t>
+          <t>DECISIVE: same code finds +8.2pp (17/19 folds, p=0.0004) using TODAY's market/macro/news, and -4.1pp using the SAME info one day earlier. Gap 13.7pp. The pipeline is NOT blind - this information EXPLAINS returns but does not PREDICT them.</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>price_ablation_gain.csv</t>
+          <t>results/direction/diagnostics/diagnostics_summary.md</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>mirrors the direction chapter exactly</t>
+          <t>direction_diagnostics.py; own-stock return excluded from contemporaneous features</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6769,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>CSE flat-day share (illiquidity)</t>
+          <t>Binary up/down reformulation</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -6775,50 +6789,48 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>2017-2026</t>
+          <t>19 walk-forward folds</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>share of zero-return days</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>binary, h=1/5/22</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Flat days at 1 day (%)</t>
+          <t>Edge over baseline (pp)</t>
         </is>
       </c>
       <c r="K81" s="2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>-4.8</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>~10% of bank/finance trading days close EXACTLY unchanged; LOFC 36.0%, HNB 12.9%, LOLC 7.2%. Illiquidity is part of why the naive baseline is so hard to beat and why the Hold class dominates.</t>
+          <t>3-class dead-zone was NOT hiding a signal. Binary edge -4.8/-1.1/-2.1pp at 1d/1wk/1mo, positive in only 1/19, 7/19, 4/19 folds.</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>price_all_results.csv</t>
+          <t>diagnostics_verdict.csv</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>surfaced as an artefact of the naive model's directional-accuracy column</t>
+          <t>rules out the Hold-majority explanation</t>
         </is>
       </c>
     </row>
@@ -6833,17 +6845,17 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>LEAK CAUGHT - ASPI forward-fill</t>
+          <t>MAGNITUDE-WEIGHTED edge (survives)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 index</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -6853,48 +6865,50 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>feature vs same-day and next-day return</t>
+          <t>19 walk-forward folds</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>correlation audit</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>leak detection</t>
+          <t>binary, |return|-weighted</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>corr with next-day vs same-day</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="n">
-        <v>0.742</v>
+          <t>Weighted edge 1d / 1wk (pp)</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>+7.9 / +13.2</t>
+        </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="M82" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0</v>
+      </c>
+      <c r="M82" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>SPSL20 and ASPI do not share a trading calendar (207 / 962 mismatched dates). Forward-filling ASPI across the gaps let it carry a move SPSL20 only recorded on its NEXT row. Halved MAPE for free: ratio 0.496 vs a true 0.970.</t>
+          <t>FIRST RESULT TO SURVIVE. Model is WRONG more often than baseline on plain accuracy (-4.3pp) but RIGHT on the big moves: weighted edge +7.9pp (15/19 folds, p=0.0096) at 1 day and +13.2pp (15/19, p=0.0096) at 1 week. Accuracy was the wrong metric.</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>results/price_macro_news/leak_scan.csv</t>
+          <t>diagnostics_magnitude.csv</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>fix: no ffill across calendars + no ASPI features for index targets</t>
+          <t>1-month +9.5pp but p=0.18</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6923,17 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Automated leak scan added</t>
+          <t>Trading backtest with costs</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>all 9 targets</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -6929,50 +6943,48 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>every feature, every run</t>
+          <t>19 walk-forward folds, h=1 only (non-overlapping)</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>corr(feature, future) vs corr(feature, present)</t>
+          <t>long/short on model signal</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>guard</t>
+          <t>economic evaluation</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Features flagged after fix</t>
+          <t>Net return @50bps (%)</t>
         </is>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M83" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.05</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>Permanent guard: any feature correlating MORE with the future than the present is flagged. Would have caught the ASPI bug instantly. Runs on every target automatically. THIRD leak-class bug in this project - all three flattered the model.</t>
+          <t>THE EDGE IS REAL BUT NOT EXPLOITABLE. Gross +22.19% vs buy-and-hold +6.49%, but median 40 position flips per 6-month fold: net +17.35% @10bps, +11.24% @25bps, +0.05% @50bps. At realistic CSE costs the edge is exactly zero (8/19 folds, p=0.82).</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>price_with_macro_news.py</t>
+          <t>diagnostics_backtest_h1.csv</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>previous two: persistence baseline lookback, pooled baseline</t>
+          <t>h=5 and h=22 backtests omitted - overlapping returns cannot be summed</t>
         </is>
       </c>
     </row>
@@ -6992,12 +7004,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 with macro + news (corrected)</t>
+          <t>Price + macro + news vs naive</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 index</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -7007,29 +7019,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>17 walk-forward 6-month folds</t>
+          <t>walk-forward 6-month folds, per stock</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>naive / ARIMA / Ridge / XGBoost</t>
+          <t>naive / ARIMA(1,1,1) / Ridge / XGBoost</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>direct 1-day and 5-day</t>
+          <t>1-day and 5-day, return-then-reconstruct</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>MAPE ratio vs naive (best)</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>1</v>
+          <t>Cases beating naive (MAPE)</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>0 of 133</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
       </c>
       <c r="M84" s="5" t="inlineStr">
         <is>
@@ -7038,7 +7054,7 @@
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>After the leak fix: best is Ridge price-only at 0.970 (1d) and 0.959 (5d), beating naive in only 10/17 and 9/17 folds. Macro and news make it WORSE (ratios 1.00-1.10).</t>
+          <t>NAIVE UNBEATEN. Best model ARIMA(1,1,1) at 1.004x naive MAPE. Stage 1's univariate conclusion survives the multivariate test - adding macro and news does not rescue price forecasting.</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -7048,7 +7064,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>pre-fix figure was 0.496 - entirely the ASPI leak</t>
+          <t>price_with_macro_news.py; models predict RETURN then reconstruct price to stop them echoing today's price</t>
         </is>
       </c>
     </row>
@@ -7068,12 +7084,12 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Index vs stock autocorrelation</t>
+          <t>Does macro/news improve price forecasting?</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>SPSL20, ASPI vs 7 stocks</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -7083,52 +7099,48 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>full sample</t>
+          <t>nested feature sets P / P+M / P+M+N</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>lag-1 return autocorrelation</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>ablation on MAPE</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Lag-1 autocorr (index vs stock)</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>+0.24 vs +0.04</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M85" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Median MAPE improvement (pp)</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>REAL EFFECT: indices show +0.237 (SPSL20) and +0.233 (ASPI) lag-1 return autocorrelation vs +0.038 for HNB. Non-synchronous trading - illiquid constituents (LOFC 37.8% flat days) reprice a day late, smearing shocks. A 1-parameter AR(1) captures the entire index 'edge'.</t>
+          <t>ALL EIGHT combinations NEGATIVE (-0.008 to -0.078pp). Adding macro and news makes price forecasting WORSE, consistently across both algorithms and both horizons.</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>price_all_results.csv</t>
+          <t>price_ablation_gain.csv</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>statistically real, economically useless - capturing it means trading the illiquid names that cause it</t>
+          <t>mirrors the direction chapter exactly</t>
         </is>
       </c>
     </row>
@@ -7143,17 +7155,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Hybrid ARIMA+LSTM (Zhang 2003)</t>
+          <t>CSE flat-day share (illiquidity)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + HNB</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -7163,48 +7175,50 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20 + 7 walk-forward folds</t>
+          <t>2017-2026</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>ARIMA(2,1,0) + LSTM on residuals</t>
+          <t>share of zero-return days</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead, rolling ARIMA state</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Theil U2 (fixed split)</t>
+          <t>Flat days at 1 day (%)</t>
         </is>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1.012</v>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M86" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>10.5</v>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M86" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>Hybrid built properly (Y=L+N, LSTM on ARIMA residuals, 3 seeds averaged) and it does NOT beat the naive random walk. SPSL20 U2=1.012, HNB U2=1.005. Marginally WORSE than plain ARIMA on both targets.</t>
+          <t>~10% of bank/finance trading days close EXACTLY unchanged; LOFC 36.0%, HNB 12.9%, LOLC 7.2%. Illiquidity is part of why the naive baseline is so hard to beat and why the Hold class dominates.</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>results/hybrid_comparable/hybrid_summary.md</t>
+          <t>price_all_results.csv</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>hybrid_arima_lstm_macro_news.py; supervisor-committed architecture, now tested</t>
+          <t>surfaced as an artefact of the naive model's directional-accuracy column</t>
         </is>
       </c>
     </row>
@@ -7219,17 +7233,17 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Hybrid + macro + news (extension)</t>
+          <t>LEAK CAUGHT - ASPI forward-fill</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + HNB</t>
+          <t>S&amp;P SL 20 index</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -7239,52 +7253,48 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20 + 7 walk-forward folds</t>
+          <t>feature vs same-day and next-day return</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>ARIMA + LSTM on residuals WITH exogenous macro/news</t>
+          <t>correlation audit</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead</t>
+          <t>leak detection</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Folds better than naive (HNB)</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>0 of 7</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>naive</t>
-        </is>
-      </c>
-      <c r="M87" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>corr with next-day vs same-day</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>THE PROJECT'S EXTENSION: macro+news fed into the residual model - the part ARIMA provably cannot explain. It makes things WORSE. SPSL20 U2 1.032, HNB U2 1.011, HNB walk-forward 0/7 folds.</t>
+          <t>SPSL20 and ASPI do not share a trading calendar (207 / 962 mismatched dates). Forward-filling ASPI across the gaps let it carry a move SPSL20 only recorded on its NEXT row. Halved MAPE for free: ratio 0.496 vs a true 0.970.</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>hybrid_walkforward_table.csv</t>
+          <t>results/price_macro_news/leak_scan.csv</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>best place to put macro if it carried information; it does not</t>
+          <t>fix: no ffill across calendars + no ASPI features for index targets</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7314,12 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Diebold-Mariano + Theil U added</t>
+          <t>Automated leak scan added</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + HNB</t>
+          <t>all 9 targets</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -7319,50 +7329,50 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20</t>
+          <t>every feature, every run</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>DM test (Newey-West HAC) + Theil U2</t>
+          <t>corr(feature, future) vs corr(feature, present)</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>forecast comparison</t>
+          <t>guard</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Models significantly better than naive</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>0 of 8</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M88" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Features flagged after fix</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M88" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>COMPARABILITY GAP CLOSED. Papers claim superiority with the DM test; this project had only baseline-relative edge. DM run vs naive AND vs ARIMA: ZERO models significant at p&lt;0.05. Only 1 of 8 has Theil U2&lt;1.</t>
+          <t>Permanent guard: any feature correlating MORE with the future than the present is flagged. Would have caught the ASPI bug instantly. Runs on every target automatically. THIRD leak-class bug in this project - all three flattered the model.</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>hybrid_fixed_split_table.csv</t>
+          <t>price_with_macro_news.py</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>the standard test reviewers expect; previously missing</t>
+          <t>previous two: persistence baseline lookback, pooled baseline</t>
         </is>
       </c>
     </row>
@@ -7377,17 +7387,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>R-squared on price levels is meaningless</t>
+          <t>S&amp;P SL 20 with macro + news (corrected)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + HNB</t>
+          <t>S&amp;P SL 20 index</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -7397,50 +7407,48 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20</t>
+          <t>17 walk-forward 6-month folds</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>all models incl. naive</t>
+          <t>naive / ARIMA / Ridge / XGBoost</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>direct 1-day and 5-day</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>R2 of the NAIVE model</t>
+          <t>MAPE ratio vs naive (best)</t>
         </is>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.9979</v>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M89" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.97</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>IMPORTANT FOR THE WRITE-UP: every model scores R2 0.9977-0.9980 - INCLUDING the naive random walk. Papers reporting R2~0.99 on price levels are reporting nothing. R2 on a level only measures being in the right magnitude.</t>
+          <t>After the leak fix: best is Ridge price-only at 0.970 (1d) and 0.959 (5d), beating naive in only 10/17 and 9/17 folds. Macro and news make it WORSE (ratios 1.00-1.10).</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>hybrid_fixed_split_table.csv</t>
+          <t>results/price_macro_news/price_summary.md</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>direct rebuttal to a common claim in this literature</t>
+          <t>pre-fix figure was 0.496 - entirely the ASPI leak</t>
         </is>
       </c>
     </row>
@@ -7455,17 +7463,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Fixed split vs walk-forward disagreement</t>
+          <t>Index vs stock autocorrelation</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + HNB</t>
+          <t>SPSL20, ASPI vs 7 stocks</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -7475,27 +7483,27 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>both protocols, same models</t>
+          <t>full sample</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>ARIMA / LSTM / Hybrid</t>
+          <t>lag-1 return autocorrelation</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>ARIMA SPSL20 U2 (fixed vs WF)</t>
+          <t>Lag-1 autocorr (index vs stock)</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>1.005 vs 0.985</t>
+          <t>+0.24 vs +0.04</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -7510,17 +7518,17 @@
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>The two protocols DISAGREE: ARIMA is worse than naive on the SPSL20 fixed split (6/7 folds better in walk-forward), and the reverse pattern on HNB. Reporting only one protocol would mislead - hence both are published.</t>
+          <t>REAL EFFECT: indices show +0.237 (SPSL20) and +0.233 (ASPI) lag-1 return autocorrelation vs +0.038 for HNB. Non-synchronous trading - illiquid constituents (LOFC 37.8% flat days) reprice a day late, smearing shocks. A 1-parameter AR(1) captures the entire index 'edge'.</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>hybrid_all_results.csv</t>
+          <t>price_all_results.csv</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>4th demonstration that the test window drives the result</t>
+          <t>statistically real, economically useless - capturing it means trading the illiquid names that cause it</t>
         </is>
       </c>
     </row>
@@ -7535,17 +7543,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Sector composite autocorrelation</t>
+          <t>Hybrid ARIMA+LSTM (Zhang 2003)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>BANKS/FINANCE/SECTOR composites</t>
+          <t>S&amp;P SL 20 + HNB</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -7555,52 +7563,48 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>full sample</t>
+          <t>fixed 80/20 + 7 walk-forward folds</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>lag-1 autocorrelation</t>
+          <t>ARIMA(2,1,0) + LSTM on residuals</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>one-step-ahead, rolling ARIMA state</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Composite vs constituent autocorr</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>BANKS +0.178 vs ~0.07</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M91" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Theil U2 (fixed split)</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>Averaging HELPS for banks (composite 0.178 &gt; every constituent) but FAILS for finance (0.017 - constituents have negative autocorrs that cancel). Mixing them is worse (0.078). SYSTEM DESIGN: build a BANKS index, not a banks+finance index.</t>
+          <t>Hybrid built properly (Y=L+N, LSTM on ARIMA residuals, 3 seeds averaged) and it does NOT beat the naive random walk. SPSL20 U2=1.012, HNB U2=1.005. Marginally WORSE than plain ARIMA on both targets.</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>results/sector_direction/autocorrelation.csv</t>
+          <t>results/hybrid_comparable/hybrid_summary.md</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>sector_direction.py; the '6x more predictable' estimate was too strong - 1.2x on average</t>
+          <t>hybrid_arima_lstm_macro_news.py; supervisor-committed architecture, now tested</t>
         </is>
       </c>
     </row>
@@ -7615,17 +7619,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Sector direction (the product target)</t>
+          <t>Hybrid + macro + news (extension)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>BANKS/FINANCE/SECTOR composites</t>
+          <t>S&amp;P SL 20 + HNB</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -7635,32 +7639,32 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward 6-month folds</t>
+          <t>fixed 80/20 + 7 walk-forward folds</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>ARIMA + LSTM on residuals WITH exogenous macro/news</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/10/22, binary + 3-class</t>
+          <t>one-step-ahead</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Configurations beating baseline</t>
+          <t>Folds better than naive (HNB)</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0 of 24</t>
+          <t>0 of 7</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>majority / persistence</t>
+          <t>naive</t>
         </is>
       </c>
       <c r="M92" s="5" t="inlineStr">
@@ -7670,17 +7674,17 @@
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>The target the SYSTEM actually predicts, never tested before. Sector-level direction is NOT predictable on plain accuracy at any horizon or grouping. Leak scan clean.</t>
+          <t>THE PROJECT'S EXTENSION: macro+news fed into the residual model - the part ARIMA provably cannot explain. It makes things WORSE. SPSL20 U2 1.032, HNB U2 1.011, HNB walk-forward 0/7 folds.</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>results/sector_direction/sector_direction_summary.md</t>
+          <t>hybrid_walkforward_table.csv</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>sector_direction.py</t>
+          <t>best place to put macro if it carried information; it does not</t>
         </is>
       </c>
     </row>
@@ -7695,17 +7699,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Method study</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Magnitude edge on BANKS composite</t>
+          <t>Diebold-Mariano + Theil U added</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite</t>
+          <t>S&amp;P SL 20 + HNB</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -7715,50 +7719,50 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, binary</t>
+          <t>fixed 80/20</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>DM test (Newey-West HAC) + Theil U2</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>|return|-weighted accuracy</t>
+          <t>forecast comparison</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Weighted edge 1d/1wk/2wk (pp)</t>
+          <t>Models significantly better than naive</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>+10.2 / +8.1 / +11.5</t>
+          <t>0 of 8</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>0.05</v>
+      </c>
+      <c r="M93" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>THIRD independent replication of the magnitude edge (after single stocks and pooled panel). Consistent across 4 horizons, 14-15 of 19 folds each, while plain accuracy edge is NEGATIVE. Product: flag big-move periods, do not emit daily direction calls.</t>
+          <t>COMPARABILITY GAP CLOSED. Papers claim superiority with the DM test; this project had only baseline-relative edge. DM run vs naive AND vs ARIMA: ZERO models significant at p&lt;0.05. Only 1 of 8 has Theil U2&lt;1.</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>sector_direction_all.csv</t>
+          <t>hybrid_fixed_split_table.csv</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>3-class magnitude figures (+34/+39pp) are INFLATED by a degenerate weighted-majority baseline - use the binary ones</t>
+          <t>the standard test reviewers expect; previously missing</t>
         </is>
       </c>
     </row>
@@ -7773,17 +7777,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Method study</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>PROBABILITY CALIBRATION (product-critical)</t>
+          <t>R-squared on price levels is meaningless</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>BANKS + SECTOR composites</t>
+          <t>S&amp;P SL 20 + HNB</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -7793,52 +7797,50 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, calibrator fitted inside training window only</t>
+          <t>fixed 80/20</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Logistic/XGBoost x raw/Platt/isotonic</t>
+          <t>all models incl. naive</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>binary, h=5/10/22</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Configurations usable (skill&gt;0 &amp; ECE&lt;0.10)</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>0 of 36</t>
-        </is>
+          <t>R2 of the NAIVE model</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0.9979</v>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>climatology (base rate)</t>
-        </is>
-      </c>
-      <c r="M94" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>THE DASHBOARD CANNOT SHOW A MODEL CONFIDENCE NUMBER. Every Brier skill score is NEGATIVE; AUC 0.41-0.56 = coin flip. Calibration cannot fix a model that cannot rank.</t>
+          <t>IMPORTANT FOR THE WRITE-UP: every model scores R2 0.9977-0.9980 - INCLUDING the naive random walk. Papers reporting R2~0.99 on price levels are reporting nothing. R2 on a level only measures being in the right magnitude.</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>results/sector_calibration/calibration_summary.md</t>
+          <t>hybrid_fixed_split_table.csv</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>sector_calibration.py; sklearn 1.9 removed cv='prefit', FrozenEstimator required</t>
+          <t>direct rebuttal to a common claim in this literature</t>
         </is>
       </c>
     </row>
@@ -7853,17 +7855,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Method study</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Calibration removes error by removing information</t>
+          <t>Fixed split vs walk-forward disagreement</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>BANKS + SECTOR composites</t>
+          <t>S&amp;P SL 20 + HNB</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -7873,27 +7875,27 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds</t>
+          <t>both protocols, same models</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Platt vs raw probabilities</t>
+          <t>ARIMA / LSTM / Hybrid</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>one-step-ahead</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>prob_std Platt vs raw</t>
+          <t>ARIMA SPSL20 U2 (fixed vs WF)</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0.012-0.054 vs 0.164-0.232</t>
+          <t>1.005 vs 0.985</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -7908,17 +7910,17 @@
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>Platt roughly HALVES calibration error by collapsing the forecast to near-constant. A model that says '54%' every day is perfectly calibrated and useless - no resolution. Calibration alone is not evidence of a usable forecast.</t>
+          <t>The two protocols DISAGREE: ARIMA is worse than naive on the SPSL20 fixed split (6/7 folds better in walk-forward), and the reverse pattern on HNB. Reporting only one protocol would mislead - hence both are published.</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>calibration_all_folds.csv</t>
+          <t>hybrid_all_results.csv</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>product answer: replace model confidence with a realised track record</t>
+          <t>4th demonstration that the test window drives the result</t>
         </is>
       </c>
     </row>
@@ -7938,12 +7940,12 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>News isolated - macro removed</t>
+          <t>Sector composite autocorrelation</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + S&amp;P SL 20</t>
+          <t>BANKS/FINANCE/SECTOR composites</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -7953,50 +7955,52 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds, 2016-2022 (news window)</t>
+          <t>full sample</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>lag-1 autocorrelation</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/10, P vs P+N</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Horizons where news helps</t>
+          <t>Composite vs constituent autocorr</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0 of 6</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M96" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>BANKS +0.178 vs ~0.07</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N96" s="4" t="inlineStr">
         <is>
-          <t>CLEAN ISOLATION TEST. In Phase H news competed with ~30 other columns incl. macro, which Phase C showed can actively hurt. Stripped back to price+news only: news gain -1.25 to +2.60pp, nothing significant. Macro was NOT masking news.</t>
+          <t>Averaging HELPS for banks (composite 0.178 &gt; every constituent) but FAILS for finance (0.017 - constituents have negative autocorrs that cancel). Mixing them is worse (0.078). SYSTEM DESIGN: build a BANKS index, not a banks+finance index.</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>results/price_news_hybrid/news_gain.csv</t>
+          <t>results/sector_direction/autocorrelation.csv</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>price_news_hybrid.py; window 2016-2022 not comparable to other phases</t>
+          <t>sector_direction.py; the '6x more predictable' estimate was too strong - 1.2x on average</t>
         </is>
       </c>
     </row>
@@ -8011,17 +8015,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Hybrid + news, no macro</t>
+          <t>Sector direction (the product target)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + S&amp;P SL 20</t>
+          <t>BANKS/FINANCE/SECTOR composites</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -8031,29 +8035,33 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds</t>
+          <t>19 walk-forward 6-month folds</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>naive / ARIMA(2,1,0) / Hybrid / Hybrid+News</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead</t>
+          <t>direct, h=1/5/10/22, binary + 3-class</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Theil U2 (Hybrid+News, BANKS)</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>1.0003</v>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>1</v>
+          <t>Configurations beating baseline</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>0 of 24</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>majority / persistence</t>
+        </is>
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
@@ -8062,17 +8070,17 @@
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>Adding news to the hybrid makes it WORSE on both targets (BANKS 0.989-&gt;1.000, SPSL20 0.987-&gt;1.017). Plain ARIMA is the best model in the table and even it is not significant (DM p=0.30/0.46). Simplest wins again.</t>
+          <t>The target the SYSTEM actually predicts, never tested before. Sector-level direction is NOT predictable on plain accuracy at any horizon or grouping. Leak scan clean.</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>results/price_news_hybrid/price_summary.csv</t>
+          <t>results/sector_direction/sector_direction_summary.md</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>supports cutting BOTH the news and hybrid stages from the production system</t>
+          <t>sector_direction.py</t>
         </is>
       </c>
     </row>
@@ -8087,17 +8095,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>LEAK #4 - SPSL20 calendar vs ASPI (again)</t>
+          <t>Magnitude edge on BANKS composite</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20</t>
+          <t>BANKS composite</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -8107,48 +8115,50 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>feature vs same-day and next-day return</t>
+          <t>19 walk-forward folds, binary</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>correlation audit</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>leak detection</t>
+          <t>|return|-weighted accuracy</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>corr with next-day vs same-day</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>0.871</v>
+          <t>Weighted edge 1d/1wk/2wk (pp)</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>+10.2 / +8.1 / +11.5</t>
+        </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="M98" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0</v>
+      </c>
+      <c r="M98" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N98" s="4" t="inlineStr">
         <is>
-          <t>The 'clean' SPSL20 file DELETED every flat day, misaligning it against ASPI (352 of 1505 rows drop). Removing .ffill() was NOT enough. Faked 82.8% accuracy / +20.7pp edge; a trivial 'copy sign of ASPI' rule scored 84.3%. Fixed by using the ASPI-calendar SPSL20 file AND dropping ASPI features for index targets.</t>
+          <t>THIRD independent replication of the magnitude edge (after single stocks and pooled panel). Consistent across 4 horizons, 14-15 of 19 folds each, while plain accuracy edge is NEGATIVE. Product: flag big-move periods, do not emit daily direction calls.</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>results/price_news_hybrid/leak_scan.csv</t>
+          <t>sector_direction_all.csv</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>corrected result: 56.8% accuracy, -5.5pp edge</t>
+          <t>3-class magnitude figures (+34/+39pp) are INFLATED by a degenerate weighted-majority baseline - use the binary ones</t>
         </is>
       </c>
     </row>
@@ -8163,17 +8173,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Leak guard now HALTS the run</t>
+          <t>PROBABILITY CALIBRATION (product-critical)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>all targets</t>
+          <t>BANKS + SECTOR composites</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -8183,52 +8193,52 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>every feature set</t>
+          <t>19 walk-forward folds, calibrator fitted inside training window only</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>automated leak scan</t>
+          <t>Logistic/XGBoost x raw/Platt/isotonic</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>guard</t>
+          <t>binary, h=5/10/22</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>Runs aborted on leak detection</t>
+          <t>Configurations usable (skill&gt;0 &amp; ECE&lt;0.10)</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>1 of 1</t>
+          <t>0 of 36</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M99" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>climatology (base rate)</t>
+        </is>
+      </c>
+      <c r="M99" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>The guard previously only wrote a CSV and the run continued, reporting a fake +20.7pp edge while the summary line claimed 'clean'. A guard that does not stop the run is not a guard. Now raises SystemExit.</t>
+          <t>THE DASHBOARD CANNOT SHOW A MODEL CONFIDENCE NUMBER. Every Brier skill score is NEGATIVE; AUC 0.41-0.56 = coin flip. Calibration cannot fix a model that cannot rank.</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>price_news_hybrid.py</t>
+          <t>results/sector_calibration/calibration_summary.md</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>4th leak caught in this project; all four flattered the model</t>
+          <t>sector_calibration.py; sklearn 1.9 removed cv='prefit', FrozenEstimator required</t>
         </is>
       </c>
     </row>
@@ -8248,12 +8258,12 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Late fusion (one model per source)</t>
+          <t>Calibration removes error by removing information</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + HNB</t>
+          <t>BANKS + SECTOR composites</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -8263,52 +8273,52 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds, chronological base/meta split</t>
+          <t>19 walk-forward folds</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>XGBoost bases + Logistic meta-learner</t>
+          <t>Platt vs raw probabilities</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>stacking, h=1/5/10</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>Configurations beating baseline</t>
+          <t>prob_std Platt vs raw</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0 of 6</t>
+          <t>0.012-0.054 vs 0.164-0.232</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>majority / persistence</t>
-        </is>
-      </c>
-      <c r="M100" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M100" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N100" s="4" t="inlineStr">
         <is>
-          <t>ARCHITECTURE WAS NOT THE CONSTRAINT. Separate models for price/news/macro combined by a meta-learner: 0/6 beat the baseline. Late fusion IS less bad than early fusion (better in 5/6) but beats it significantly in only 1/6 = chance.</t>
+          <t>Platt roughly HALVES calibration error by collapsing the forecast to near-constant. A model that says '54%' every day is perfectly calibrated and useless - no resolution. Calibration alone is not evidence of a usable forecast.</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>results/late_fusion/late_fusion_summary.md</t>
+          <t>calibration_all_folds.csv</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>late_fusion_stacking.py; meta-learner trained on OUT-OF-FOLD base predictions</t>
+          <t>product answer: replace model confidence with a realised track record</t>
         </is>
       </c>
     </row>
@@ -8328,12 +8338,12 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Meta-learner weight allocation</t>
+          <t>News isolated - macro removed</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + HNB</t>
+          <t>BANKS composite + S&amp;P SL 20</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -8343,52 +8353,50 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds</t>
+          <t>6 walk-forward folds, 2016-2022 (news window)</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Logistic meta-learner on 3 base models</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>stacking</t>
+          <t>direct, h=1/5/10, P vs P+N</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Median weight share price/news/macro</t>
+          <t>Horizons where news helps</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>29% / 38% / 33%</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M101" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>0 of 6</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M101" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>CLEANEST VERSION OF THE CENTRAL FINDING. A model free to weight the three sources however it likes splits ~1/3 each and leans MOST on news. If price carried signal and news did not, it would load onto price. Even allocation = nothing to prefer.</t>
+          <t>CLEAN ISOLATION TEST. In Phase H news competed with ~30 other columns incl. macro, which Phase C showed can actively hurt. Stripped back to price+news only: news gain -1.25 to +2.60pp, nothing significant. Macro was NOT masking news.</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>results/late_fusion/meta_weights_summary.csv</t>
+          <t>results/price_news_hybrid/news_gain.csv</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>resolves the ambiguous early-fusion result (high importance, zero gain)</t>
+          <t>price_news_hybrid.py; window 2016-2022 not comparable to other phases</t>
         </is>
       </c>
     </row>
@@ -8403,17 +8411,17 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Early vs late fusion ruled out as explanation</t>
+          <t>Hybrid + news, no macro</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + HNB</t>
+          <t>BANKS composite + S&amp;P SL 20</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -8423,31 +8431,29 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>identical folds, both architectures</t>
+          <t>6 walk-forward folds</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>early (concatenated) vs late (stacked)</t>
+          <t>naive / ARIMA(2,1,0) / Hybrid / Hybrid+News</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>one-step-ahead</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>Late beats early significantly</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>1 of 6</t>
-        </is>
+          <t>Theil U2 (Hybrid+News, BANKS)</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>1.0003</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="M102" s="5" t="inlineStr">
         <is>
@@ -8456,17 +8462,17 @@
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
-          <t>Rules out one candidate explanation for why published papers report gains: 'early fusion drowned the weak signals'. Giving news and macro dedicated models surfaces nothing. Still open: missing naive baselines, no publication lag, single favourable split, decomposition hybrids.</t>
+          <t>Adding news to the hybrid makes it WORSE on both targets (BANKS 0.989-&gt;1.000, SPSL20 0.987-&gt;1.017). Plain ARIMA is the best model in the table and even it is not significant (DM p=0.30/0.46). Simplest wins again.</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>late_fusion_folds.csv</t>
+          <t>results/price_news_hybrid/price_summary.csv</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>late_fusion_stacking.py</t>
+          <t>supports cutting BOTH the news and hybrid stages from the production system</t>
         </is>
       </c>
     </row>
@@ -8481,17 +8487,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Reproduce-then-break ladder</t>
+          <t>LEAK #4 - SPSL20 calendar vs ASPI (again)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + BANKS composite</t>
+          <t>S&amp;P SL 20</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -8501,31 +8507,29 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>L0 paper-style -&gt; L3 walk-forward, one guard at a time</t>
+          <t>feature vs same-day and next-day return</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost (best reported)</t>
+          <t>correlation audit</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>next-day price</t>
+          <t>leak detection</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>L0 'macro improvement' %</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>+0.17 / -0.04</t>
-        </is>
+          <t>corr with next-day vs same-day</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0.871</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>0</v>
+        <v>0.227</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -8534,17 +8538,17 @@
       </c>
       <c r="N103" s="4" t="inlineStr">
         <is>
-          <t>REPRODUCTION FAILED - and that is the finding. Removing the publication lag, leaking the scaler and using a single split move the number by FRACTIONS OF A PERCENT. These three shortcuts are NOT the mechanism behind published macro gains.</t>
+          <t>The 'clean' SPSL20 file DELETED every flat day, misaligning it against ASPI (352 of 1505 rows drop). Removing .ffill() was NOT enough. Faked 82.8% accuracy / +20.7pp edge; a trivial 'copy sign of ASPI' rule scored 84.3%. Fixed by using the ASPI-calendar SPSL20 file AND dropping ASPI features for index targets.</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>results/reproduce_then_break/ladder_summary.md</t>
+          <t>results/price_news_hybrid/leak_scan.csv</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>reproduce_then_break.py; hypothesis was wrong, reported as such</t>
+          <t>corrected result: 56.8% accuracy, -5.5pp edge</t>
         </is>
       </c>
     </row>
@@ -8564,12 +8568,12 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>The likely real mechanism: no naive baseline</t>
+          <t>Leak guard now HALTS the run</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + BANKS composite</t>
+          <t>all targets</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -8579,29 +8583,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>all ladder levels</t>
+          <t>every feature set</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>all configs incl. naive</t>
+          <t>automated leak scan</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>next-day price</t>
+          <t>guard</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>R2 across every level</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="n">
-        <v>0.998</v>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0.9979</v>
+          <t>Runs aborted on leak detection</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>1 of 1</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>
@@ -8610,17 +8618,17 @@
       </c>
       <c r="N104" s="4" t="inlineStr">
         <is>
-          <t>R2 is 0.9978-0.9984 at EVERY level for EVERY config - and naive scores 0.9979. A paper running this exact setup would truthfully report 'R2=0.998, MAPE=0.83%, outperforms benchmark'. The gain is model-vs-weaker-model, reported with metrics that cannot distinguish either from a random walk.</t>
+          <t>The guard previously only wrote a CSV and the run continued, reporting a fake +20.7pp edge while the summary line claimed 'clean'. A guard that does not stop the run is not a guard. Now raises SystemExit.</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ladder_summary.csv</t>
+          <t>price_news_hybrid.py</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>DM p = 0.48-0.86 throughout; nothing significant</t>
+          <t>4th leak caught in this project; all four flattered the model</t>
         </is>
       </c>
     </row>
@@ -8635,17 +8643,17 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Single split is the shortcut that matters most</t>
+          <t>Late fusion (one model per source)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + BANKS composite</t>
+          <t>BANKS composite + HNB</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -8655,32 +8663,32 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>L0-L2 single split vs L3 walk-forward</t>
+          <t>6 walk-forward folds, chronological base/meta split</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>XGBoost bases + Logistic meta-learner</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>next-day price</t>
+          <t>stacking, h=1/5/10</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>MAPE(macro)/MAPE(naive)</t>
+          <t>Configurations beating baseline</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>0.96-0.98 -&gt; 1.027</t>
+          <t>0 of 6</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>majority / persistence</t>
         </is>
       </c>
       <c r="M105" s="5" t="inlineStr">
@@ -8690,17 +8698,17 @@
       </c>
       <c r="N105" s="4" t="inlineStr">
         <is>
-          <t>Under single-split levels price+macro sits BELOW naive (0.964-0.980); under walk-forward it crosses ABOVE 1.0 on both targets. Of the three shortcuts tested, the single split changes the conclusion; the other two do not. 4th confirmation of the window effect.</t>
+          <t>ARCHITECTURE WAS NOT THE CONSTRAINT. Separate models for price/news/macro combined by a meta-learner: 0/6 beat the baseline. Late fusion IS less bad than early fusion (better in 5/6) but beats it significantly in only 1/6 = chance.</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ladder_all.csv</t>
+          <t>results/late_fusion/late_fusion_summary.md</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>argues for walk-forward as the default reporting protocol</t>
+          <t>late_fusion_stacking.py; meta-learner trained on OUT-OF-FOLD base predictions</t>
         </is>
       </c>
     </row>
@@ -8715,17 +8723,17 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>DECOMPOSITION LEAK - the mechanism found</t>
+          <t>Meta-learner weight allocation</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + BANKS composite</t>
+          <t>BANKS composite + HNB</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -8735,32 +8743,32 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20, identical model/data, only pipeline ORDER differs</t>
+          <t>6 walk-forward folds</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>wavelet(db4,3) + CEEMDAN -&gt; Ridge/XGBoost</t>
+          <t>Logistic meta-learner on 3 base models</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead price</t>
+          <t>stacking</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>Improvement over naive: leaky vs honest</t>
+          <t>Median weight share price/news/macro</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>+19.2% vs -6.9%</t>
+          <t>29% / 38% / 33%</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>naive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M106" s="6" t="inlineStr">
@@ -8770,17 +8778,17 @@
       </c>
       <c r="N106" s="4" t="inlineStr">
         <is>
-          <t>★ THE MECHANISM. Decomposing the FULL series BEFORE splitting creates a 13-26pp improvement out of nothing. Wavelet/CEEMDAN are GLOBAL transforms: component values at time t are computed from the whole series, so training components carry test-period information and test components were built from their own future.</t>
+          <t>CLEANEST VERSION OF THE CENTRAL FINDING. A model free to weight the three sources however it likes splits ~1/3 each and leans MOST on news. If price carried signal and news did not, it would load onto price. Even allocation = nothing to prefer.</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>results/decomposition_leak/decomposition_summary.md</t>
+          <t>results/late_fusion/meta_weights_summary.csv</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>decomposition_leak_test.py; explains the gap between published hybrid results and this project</t>
+          <t>resolves the ambiguous early-fusion result (high importance, zero gain)</t>
         </is>
       </c>
     </row>
@@ -8800,12 +8808,12 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Leaky decomposition is highly significant</t>
+          <t>Early vs late fusion ruled out as explanation</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + BANKS composite</t>
+          <t>BANKS composite + HNB</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -8815,50 +8823,50 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20</t>
+          <t>identical folds, both architectures</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>wavelet + CEEMDAN, leaky pipeline</t>
+          <t>early (concatenated) vs late (stacked)</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead price</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>DM p vs naive (4 configs)</t>
+          <t>Late beats early significantly</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0.0000-0.0199</t>
+          <t>1 of 6</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="M107" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="M107" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N107" s="4" t="inlineStr">
         <is>
-          <t>ALL FOUR leaky configurations beat naive significantly (Theil U2 0.794-0.871, DM p&lt;0.02, two at p&lt;0.0001). These are exactly the numbers decomposition-hybrid papers report.</t>
+          <t>Rules out one candidate explanation for why published papers report gains: 'early fusion drowned the weak signals'. Giving news and macro dedicated models surfaces nothing. Still open: missing naive baselines, no publication lag, single favourable split, decomposition hybrids.</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>decomposition_results.csv</t>
+          <t>late_fusion_folds.csv</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>the result is real as computed - it is the pipeline that is wrong</t>
+          <t>late_fusion_stacking.py</t>
         </is>
       </c>
     </row>
@@ -8878,70 +8886,462 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
+          <t>Reproduce-then-break ladder</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>L0 paper-style -&gt; L3 walk-forward, one guard at a time</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Ridge + XGBoost (best reported)</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>next-day price</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>L0 'macro improvement' %</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>+0.17 / -0.04</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N108" s="4" t="inlineStr">
+        <is>
+          <t>REPRODUCTION FAILED - and that is the finding. Removing the publication lag, leaking the scaler and using a single split move the number by FRACTIONS OF A PERCENT. These three shortcuts are NOT the mechanism behind published macro gains.</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>results/reproduce_then_break/ladder_summary.md</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>reproduce_then_break.py; hypothesis was wrong, reported as such</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>The likely real mechanism: no naive baseline</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>all ladder levels</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>all configs incl. naive</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>next-day price</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>R2 across every level</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0.9979</v>
+      </c>
+      <c r="M109" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N109" s="4" t="inlineStr">
+        <is>
+          <t>R2 is 0.9978-0.9984 at EVERY level for EVERY config - and naive scores 0.9979. A paper running this exact setup would truthfully report 'R2=0.998, MAPE=0.83%, outperforms benchmark'. The gain is model-vs-weaker-model, reported with metrics that cannot distinguish either from a random walk.</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>ladder_summary.csv</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>DM p = 0.48-0.86 throughout; nothing significant</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Single split is the shortcut that matters most</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>L0-L2 single split vs L3 walk-forward</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Ridge + XGBoost</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>next-day price</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>MAPE(macro)/MAPE(naive)</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>0.96-0.98 -&gt; 1.027</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="M110" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>Under single-split levels price+macro sits BELOW naive (0.964-0.980); under walk-forward it crosses ABOVE 1.0 on both targets. Of the three shortcuts tested, the single split changes the conclusion; the other two do not. 4th confirmation of the window effect.</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>ladder_all.csv</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>argues for walk-forward as the default reporting protocol</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>DECOMPOSITION LEAK - the mechanism found</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>fixed 80/20, identical model/data, only pipeline ORDER differs</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>wavelet(db4,3) + CEEMDAN -&gt; Ridge/XGBoost</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>one-step-ahead price</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>Improvement over naive: leaky vs honest</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>+19.2% vs -6.9%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M111" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t>★ THE MECHANISM. Decomposing the FULL series BEFORE splitting creates a 13-26pp improvement out of nothing. Wavelet/CEEMDAN are GLOBAL transforms: component values at time t are computed from the whole series, so training components carry test-period information and test components were built from their own future.</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>results/decomposition_leak/decomposition_summary.md</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>decomposition_leak_test.py; explains the gap between published hybrid results and this project</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Leaky decomposition is highly significant</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>fixed 80/20</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>wavelet + CEEMDAN, leaky pipeline</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>one-step-ahead price</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>DM p vs naive (4 configs)</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0.0000-0.0199</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M112" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N112" s="4" t="inlineStr">
+        <is>
+          <t>ALL FOUR leaky configurations beat naive significantly (Theil U2 0.794-0.871, DM p&lt;0.02, two at p&lt;0.0001). These are exactly the numbers decomposition-hybrid papers report.</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>decomposition_results.csv</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>the result is real as computed - it is the pipeline that is wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
           <t>Honest decomposition loses to naive</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>S&amp;P SL 20 + BANKS composite</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>fixed 80/20, decompose only series[:t] at each t</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>wavelet + CEEMDAN, honest pipeline</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr">
         <is>
           <t>one-step-ahead price</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr">
+      <c r="J113" s="2" t="inlineStr">
         <is>
           <t>Theil U2 (4 configs)</t>
         </is>
       </c>
-      <c r="K108" s="2" t="inlineStr">
+      <c r="K113" s="2" t="inlineStr">
         <is>
           <t>1.008-1.028</t>
         </is>
       </c>
-      <c r="L108" s="2" t="n">
+      <c r="L113" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M108" s="5" t="inlineStr">
+      <c r="M113" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N108" s="4" t="inlineStr">
+      <c r="N113" s="4" t="inlineStr">
         <is>
           <t>Same models, same data, decomposition restricted to past data only: ALL FOUR configs are WORSE than a random walk and none significant (DM p 0.35-0.84). The decomposition advantage does not survive an honest pipeline.</t>
         </is>
       </c>
-      <c r="O108" s="2" t="inlineStr">
+      <c r="O113" s="2" t="inlineStr">
         <is>
           <t>decomposition_results.csv</t>
         </is>
       </c>
-      <c r="P108" s="2" t="inlineStr">
+      <c r="P113" s="2" t="inlineStr">
         <is>
           <t>honest CEEMDAN re-decomposes every 3rd point for runtime; wavelet every point</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P108"/>
+  <autoFilter ref="A1:P113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results_master_log.xlsx
+++ b/results_master_log.xlsx
@@ -11,7 +11,7 @@
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Results log'!$A$1:$P$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P113"/>
+  <dimension ref="A1:P119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3178,17 +3178,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Phase A multi-horizon direction</t>
+          <t>GARCH vol forecast (new phase)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3203,52 +3203,52 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge</t>
+          <t>80/20</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Constant / EWMA / GARCH(1,1)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons (1d-252d)</t>
+          <t>predict daily volatility</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Horizons beating baseline</t>
+          <t>corr w/ realized 10d vol (MAE)</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0 of 9</t>
+          <t>GARCH-daily 0.88</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>majority / persistence</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Constant 0.00</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>Yes — strong</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>NO EDGE AT ANY HORIZON. Best model always below best baseline; gap widens with horizon (-3.5pp @1d -&gt; -47.1pp @1yr) because long-horizon drift makes the dumb baseline huge (maj 78% @6mo, pers 77% @1yr).</t>
+          <t>POSITIVE RESULT. Price unpredictable but VOLATILITY is: GARCH daily-updated corr 0.876 (MAE 0.295) vs Constant 0.00 (MAE 0.599); EWMA 0.781. GARCH-blind(one-shot)=0.02 (flattens, fails like price). Skill needs daily updating (legit for risk: manager has today's data). Storms cluster -&gt; predictable.</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>results/direction/multi_horizon/mh_summary.md</t>
+          <t>results/volatility/HNB_vol_forecast.png</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>direction_multi_horizon.py; Tier-1 only; dead-zone +/-0.5%*sqrt(h)</t>
+          <t>vol_forecast.py HNB</t>
         </is>
       </c>
     </row>
@@ -3258,73 +3258,77 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Phase A best single horizon</t>
+          <t>GARCH vol forecast (new phase)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>HNB</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>daily 2000+</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge</t>
+          <t>80/20</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Logistic</t>
+          <t>Constant / EWMA / GARCH(1,1)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>direct, h=22d (1 month)</t>
+          <t>predict daily volatility</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Accuracy %</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>corr w/ realized 10d vol (MAE)</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>GARCH-daily 0.91</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Constant 0.00</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>Yes — strong</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Best model result of the sweep (1-month Logistic 40.1%) still loses to persistence 42.1%. Logistic &gt; XGBoost at every horizon -&gt; no nonlinear structure to find.</t>
+          <t>Confirms HNB on US market. GARCH daily-updated corr 0.914 (MAE 0.339) vs Constant 0.00 (MAE 1.196); GARCH-blind 0.05 (fails). Volatility predictability is market-independent. The project's positive finding: forecast RISK not RETURN.</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>mh_direction_table.csv</t>
+          <t>results/volatility/AAPL_vol_forecast.png</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>edge -2.0pp</t>
+          <t>vol_forecast.py AAPL</t>
         </is>
       </c>
     </row>
@@ -3334,73 +3338,77 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Phase A multi-horizon return %</t>
+          <t>Bull/Bear detector (rule-based v1)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>HNB</t>
+          <t>ASPI</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>daily 2012-2026</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge</t>
+          <t>real-time, past-only</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>3-signal (MA200+drawdown+momentum)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons (1d-252d)</t>
+          <t>nowcast regime vs 20% hindsight truth</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>RMSE ratio vs train-mean</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>Tie</t>
+          <t>accuracy / bear recall</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>67.0% / 53%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Always-bull 61.6%</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>Ridge beats naive-0 at 8/9 horizons BUT is only ~1% better than train-mean drift -&gt; it learned drift, NOT signal. XGBoost worse than naive everywhere (ratio 1.01-1.14).</t>
+          <t>REGIME HAS SIGNAL (price did not). Combined detector 67.0% acc BEATS always-bull base rate 61.6% and catches 53% of true bear days real-time; MA200-only 66.2%. Visual: fires during 2016-20 slump + 2022 crash. Foundation for agentic bull/bear system (add GARCH vol + news agent next).</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>mh_return_table.csv</t>
+          <t>results/regime/ASPI_regime.png</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>train-mean is the honest null, not naive-0</t>
+          <t>regime_detect.py ASPI</t>
         </is>
       </c>
     </row>
@@ -3410,22 +3418,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Phase A return sign accuracy</t>
+          <t>Bull/Bear detector (rule-based v1)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>HNB</t>
+          <t>SPSL20</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3435,52 +3443,52 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge</t>
+          <t>real-time, past-only</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>3-signal (MA200+drawdown+momentum)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>direct, sign of h-day return</t>
+          <t>nowcast regime vs 20% hindsight truth</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Horizons beating sign null</t>
+          <t>accuracy / bear recall</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2 of 9</t>
+          <t>66.1% / 62%</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>always-guess-winning-side</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Always-bull 67.8%</t>
+        </is>
+      </c>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>TRAP CHECK: 55-57% sign accuracy @1-3mo looks like the 52-58% target but 'always guess up' matches/beats it (test window drifted up 59-95%). Both 'wins' are +0.2pp = noise.</t>
+          <t>On S&amp;P SL20 combined 66.1% acc is just BELOW always-bull 67.8% (few bears, high base rate) BUT catches 62% of true bear days (always-bull catches 0%). Honest: warns of bears at some false-alarm cost. Regime detection more tractable than price everywhere.</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>mh_edge_vs_horizon.png</t>
+          <t>results/regime/SPSL20_regime.png</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>up-share null added to stop false positive</t>
+          <t>regime_detect.py SPSL20</t>
         </is>
       </c>
     </row>
@@ -3490,22 +3498,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Bugfix</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Phase B ablation (+Tier-2)</t>
+          <t>ARIMAX off-by-one alignment fix</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>HNB</t>
+          <t>9 tickers (mh)</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -3515,48 +3523,52 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds, A vs B</t>
+          <t>80/20 blind</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>ARIMAX (SARIMAX)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, ablation</t>
+          <t>direction re-scored h=1,5,22</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from Tier-2 (pp)</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>ARIMAX h=1 dir acc</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>all &gt;40% (assert passes)</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>chance 50</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>RSI+MACD+volume add NOTHING. Mean -0.9pp, 0/9 beat baseline. Technical indicators exhausted.</t>
+          <t>BUG: forecast conditioned on lp[:o] not lp[:o+1] -&gt; every ARIMAX horizon scored one step early (inverted at short h). Fixed to lp[:o+1], macro held at ex[o]. Old ARIMAX numbers VOID. Biggest corrections: ASPI h1 25.4-&gt;71.8, SPSL20 h1 36.2-&gt;62.3 (were below-chance inversions). HNB/JKH ~unchanged (already near chance). AFTER fix ARIMAX still near-chance ~50% at h=1/5/22 -&gt; no real directional skill; alignment was the bug, weak signal is the finding.</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>results/direction/phase_ablation/ablation_summary.md</t>
+          <t>results/mh_models/*_results.csv</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_ablation.py; 9 -&gt; 16 features; value restated on the 4-phase run (macro availability trims early rows)</t>
+          <t>mh_multimodel.py (all)</t>
         </is>
       </c>
     </row>
@@ -3566,22 +3578,22 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Ensemble</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Phase B feature attention check</t>
+          <t>AVG2 direction vs components</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>HNB</t>
+          <t>9 tickers (mh)</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3591,50 +3603,52 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>80/20 blind</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>XGBoost importance</t>
+          <t>AVG2 vs ARIMAX vs RF</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>directional accuracy</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Tier-2 share of importance %</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>41</v>
+          <t>AVG2 beats BOTH components</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>10/99 cells (10%)</t>
+        </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>components</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>XGBoost spends 41% of importance on Tier-2 (macd_signal is top feature at 6/9 horizons) yet accuracy does not improve -&gt; the model USES them but they carry no signal.</t>
+          <t>Added dir_per_h + majority row + SWITCH-dir. AVG2(ARIMAX+RF) beats BOTH components on direction in only 10 of 99 ticker-horizon cells (~10%), scattered, no pattern (ASPI/LOLC/SPSL20 = 0). Averaging gives NO reliable directional edge over its parts. AVG2 also loses to Majority baseline at most h=1/5/22 cells. Consistent with random-walk finding.</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ablation_tier2_importance.csv</t>
+          <t>results/mh_models/*_ensemble_direction.csv</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>strong evidence indicators are redundant with price</t>
+          <t>mh_ensemble.py (all)</t>
         </is>
       </c>
     </row>
@@ -3649,12 +3663,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Phase B return % (+Tier-2)</t>
+          <t>Phase A multi-horizon direction</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -3669,48 +3683,52 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>80/20 chrono + h-bar purge</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, 9 horizons (1d-252d)</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>RMSE ratio vs train-mean (B)</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>Tie</t>
+          <t>Horizons beating baseline</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>0 of 9</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>majority / persistence</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>Tier-2 made return RMSE slightly WORSE at 9/9 horizons (ratio gain +0.000 to +0.046). Sign edge stays negative everywhere.</t>
+          <t>NO EDGE AT ANY HORIZON. Best model always below best baseline; gap widens with horizon (-3.5pp @1d -&gt; -47.1pp @1yr) because long-horizon drift makes the dumb baseline huge (maj 78% @6mo, pers 77% @1yr).</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ablation_return_table.csv</t>
+          <t>results/direction/multi_horizon/mh_summary.md</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>A ratio 0.991 -&gt; B ratio 0.991-1.034</t>
+          <t>direction_multi_horizon.py; Tier-1 only; dead-zone +/-0.5%*sqrt(h)</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3748,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Phase C ablation (+macro rates)</t>
+          <t>Phase A best single horizon</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3745,29 +3763,29 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds, 35d publication lag</t>
+          <t>80/20 chrono + h-bar purge</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Logistic</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, ablation</t>
+          <t>direct, h=22d (1 month)</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from macro (pp)</t>
+          <t>Accuracy %</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
-        <v>-2.8</v>
+        <v>40.1</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>42.1</v>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
@@ -3776,17 +3794,17 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>Macro rates make it WORSE and unstable: gain swings -22.3 to +10.3 pp, 0/9 beat baseline. Not weak signal - overfitting.</t>
+          <t>Best model result of the sweep (1-month Logistic 40.1%) still loses to persistence 42.1%. Logistic &gt; XGBoost at every horizon -&gt; no nonlinear structure to find.</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>results/direction/phase_ablation/ablation_summary.md</t>
+          <t>mh_direction_table.csv</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_ablation.py; 16 -&gt; 29 features; inflation/FX/M2 still uncollected</t>
+          <t>edge -2.0pp</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3819,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Phase C2 diagnostic (macro changes only)</t>
+          <t>Phase A multi-horizon return %</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3821,48 +3839,48 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>80/20 chrono + h-bar purge</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, ablation</t>
+          <t>direct, 9 horizons (1d-252d)</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from macro d (pp)</t>
+          <t>RMSE ratio vs train-mean</t>
         </is>
       </c>
       <c r="K43" s="2" t="n">
-        <v>3.4</v>
+        <v>0.99</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="M43" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Tie</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>DROPPING RATE LEVELS FIXES THE DAMAGE (-2.8 -&gt; +3.4 pp; 1yr 4.5% -&gt; 49.7%). Non-stationary levels were being memorised. Still 0/9 beat baseline -&gt; form was wrong AND no signal.</t>
+          <t>Ridge beats naive-0 at 8/9 horizons BUT is only ~1% better than train-mean drift -&gt; it learned drift, NOT signal. XGBoost worse than naive everywhere (ratio 1.01-1.14).</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ablation_gain_table.csv</t>
+          <t>mh_return_table.csv</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>key methodology lesson: feed macro as changes, never levels</t>
+          <t>train-mean is the honest null, not naive-0</t>
         </is>
       </c>
     </row>
@@ -3877,12 +3895,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Phase C feature attention check</t>
+          <t>Phase A return sign accuracy</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3897,50 +3915,52 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>80/20 chrono + h-bar purge</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>XGBoost importance</t>
+          <t>Ridge</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, sign of h-day return</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Macro share of importance %</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>64</v>
+          <t>Horizons beating sign null</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>2 of 9</t>
+        </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M44" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>always-guess-winning-side</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>Macro importance rises 46% (1d) -&gt; 80% (1yr) while accuracy FALLS. Model fits rates as a trend proxy, not signal. tb_12m/spread/policy_rate are top features at 8/9 horizons.</t>
+          <t>TRAP CHECK: 55-57% sign accuracy @1-3mo looks like the 52-58% target but 'always guess up' matches/beats it (test window drifted up 59-95%). Both 'wins' are +0.2pp = noise.</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ablation_feature_importance.csv</t>
+          <t>mh_edge_vs_horizon.png</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>fingerprint of trending-variable overfit</t>
+          <t>up-share null added to stop false positive</t>
         </is>
       </c>
     </row>
@@ -3955,12 +3975,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Phase C return % (+macro)</t>
+          <t>Phase B ablation (+Tier-2)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3975,29 +3995,29 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>identical rows/split/seeds, A vs B</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, 9 horizons, ablation</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>RMSE ratio vs train-mean (C)</t>
+          <t>Mean gain from Tier-2 (pp)</t>
         </is>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1.37</v>
+        <v>-0.9</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0.995</v>
+        <v>0</v>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
@@ -4006,17 +4026,17 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>Macro blows out return RMSE to 1.29-1.37x the train-mean null (A/B sat at ~0.99). Clear damage, confirms the overfit reading.</t>
+          <t>RSI+MACD+volume add NOTHING. Mean -0.9pp, 0/9 beat baseline. Technical indicators exhausted.</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ablation_return_table.csv</t>
+          <t>results/direction/phase_ablation/ablation_summary.md</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>worst at 2-3 month horizons</t>
+          <t>direction_phase_ablation.py; 9 -&gt; 16 features; value restated on the 4-phase run (macro availability trims early rows)</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4056,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Phase D ablation (+sector)</t>
+          <t>Phase B feature attention check</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4056,43 +4076,45 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>XGBoost importance</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, ablation</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from sector (pp)</t>
+          <t>Tier-2 share of importance %</t>
         </is>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>41</v>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>FIRST consistently POSITIVE step: +2.6pp mean, positive at 6/9 horizons. Built on C2 (macro changes only). But still 0/9 beat baseline.</t>
+          <t>XGBoost spends 41% of importance on Tier-2 (macd_signal is top feature at 6/9 horizons) yet accuracy does not improve -&gt; the model USES them but they carry no signal.</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>results/direction/phase_ablation/ablation_summary.md</t>
+          <t>ablation_tier2_importance.csv</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_ablation.py; C2 16+7 -&gt; D 39 features; ASPI + COMB/SAMP + LOFC/LOLC/LFIN/CFIN</t>
+          <t>strong evidence indicators are redundant with price</t>
         </is>
       </c>
     </row>
@@ -4107,12 +4129,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Phase D best single horizon</t>
+          <t>Phase B return % (+Tier-2)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4132,43 +4154,43 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>direct, h=5d (1 week)</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Edge over baseline (pp)</t>
+          <t>RMSE ratio vs train-mean (B)</t>
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>-0.2</v>
+        <v>0.991</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>0.991</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Tie</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>Closest call of the whole study: 1-week Phase D 37.3% vs baseline 37.4%. Near-parity at short horizons (1d -1.7, 1wk -0.2, 2wk -1.6) but never crosses.</t>
+          <t>Tier-2 made return RMSE slightly WORSE at 9/9 horizons (ratio gain +0.000 to +0.046). Sign edge stays negative everywhere.</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ablation_gain_table.csv</t>
+          <t>ablation_return_table.csv</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>not a win; single split, one stock</t>
+          <t>A ratio 0.991 -&gt; B ratio 0.991-1.034</t>
         </is>
       </c>
     </row>
@@ -4183,12 +4205,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Return forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Phase D return sign edge (+sector)</t>
+          <t>Phase C ablation (+macro rates)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4203,52 +4225,48 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>identical rows/split/seeds, 35d publication lag</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>direct, sign of h-day return</t>
+          <t>direct, 9 horizons, ablation</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Sign edge 1wk/2wk/3wk (pp)</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>+1.7 / +1.7 / +1.1</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>always-guess-winning-side</t>
-        </is>
-      </c>
-      <c r="M48" s="3" t="inlineStr">
-        <is>
-          <t>Tie</t>
+          <t>Mean gain from macro (pp)</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>First POSITIVE sign edges in the study, and at 3 adjacent horizons (1-3 weeks). Tiny (~1-2pp) and one split only -&gt; flag as worth re-testing, NOT a finding.</t>
+          <t>Macro rates make it WORSE and unstable: gain swings -22.3 to +10.3 pp, 0/9 beat baseline. Not weak signal - overfitting.</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ablation_return_table.csv</t>
+          <t>results/direction/phase_ablation/ablation_summary.md</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>check on other tickers before claiming anything</t>
+          <t>direction_phase_ablation.py; 16 -&gt; 29 features; inflation/FX/M2 still uncollected</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4286,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Phase D feature attention check</t>
+          <t>Phase C2 diagnostic (macro changes only)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4288,45 +4306,43 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>XGBoost importance</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, 9 horizons, ablation</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Sector share of importance %</t>
+          <t>Mean gain from macro d (pp)</t>
         </is>
       </c>
       <c r="K49" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
+        <v>3.4</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="M49" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M49" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>Sector takes 34% avg (42% at 1 day, falling to 27% at 1yr) - mirror image of macro, which rises with horizon. Sector matters short, macro long, neither enough.</t>
+          <t>DROPPING RATE LEVELS FIXES THE DAMAGE (-2.8 -&gt; +3.4 pp; 1yr 4.5% -&gt; 49.7%). Non-stationary levels were being memorised. Still 0/9 beat baseline -&gt; form was wrong AND no signal.</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ablation_feature_importance.csv</t>
+          <t>ablation_gain_table.csv</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>vol_20 is top feature at 1d/1wk; d_tb3m dominates long</t>
+          <t>key methodology lesson: feed macro as changes, never levels</t>
         </is>
       </c>
     </row>
@@ -4346,12 +4362,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Sector sweep - replication test</t>
+          <t>Phase C feature attention check</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks (3 banks, 4 finance, 4 control)</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -4361,52 +4377,50 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge, per stock</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>XGBoost importance</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Cells beating baseline</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>27 of 99</t>
-        </is>
+          <t>Macro share of importance %</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>64</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>14 of 99 (Phase A)</t>
-        </is>
-      </c>
-      <c r="M50" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>Sector features nearly DOUBLE the win rate vs Tier-1 (14-&gt;27 of 99) but wins sit at exactly coin-flip at short horizons and collapse at long ones. No real edge.</t>
+          <t>Macro importance rises 46% (1d) -&gt; 80% (1yr) while accuracy FALLS. Model fits rates as a trend proxy, not signal. tb_12m/spread/policy_rate are top features at 8/9 horizons.</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>results/direction/sector_sweep/sweep_summary.md</t>
+          <t>ablation_feature_importance.csv</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>direction_sector_sweep.py; peer composites exclude the target stock</t>
+          <t>fingerprint of trending-variable overfit</t>
         </is>
       </c>
     </row>
@@ -4421,17 +4435,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Sector gain replication (HNB claim 3)</t>
+          <t>Phase C return % (+macro)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -4441,48 +4455,48 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>identical protocol per stock</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Phase D - Phase A</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Mean sector gain (pp)</t>
+          <t>RMSE ratio vs train-mean (C)</t>
         </is>
       </c>
       <c r="K51" s="2" t="n">
-        <v>3.8</v>
+        <v>1.37</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.995</v>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>REPLICATES: +3.8pp mean, positive in 66/99 cells (67%), 9 of 11 stocks positive. HNB was not a fluke - sector context genuinely helps the model. Best: LFIN +13.2, SAMP +9.4, LOFC +8.2. Worst: CTC -11.0.</t>
+          <t>Macro blows out return RMSE to 1.29-1.37x the train-mean null (A/B sat at ~0.99). Clear damage, confirms the overfit reading.</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>sweep_gain_by_ticker.csv</t>
+          <t>ablation_return_table.csv</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>helping is not the same as winning</t>
+          <t>worst at 2-3 month horizons</t>
         </is>
       </c>
     </row>
@@ -4502,12 +4516,12 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Sector sweep significance screen</t>
+          <t>Phase D ablation (+sector)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -4517,29 +4531,29 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>sign test + Wilcoxon across stocks, per horizon</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>binomial sign test (H0 p=0.5)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, 9 horizons, ablation</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Best sign-test p</t>
+          <t>Mean gain from sector (pp)</t>
         </is>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
@@ -4548,17 +4562,17 @@
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>NOTHING SIGNIFICANT AT ANY HORIZON. Best cells (1 day, 1 week) are 6/11 stocks positive = p=0.500, exactly a coin flip. Long horizons far worse (1yr 0/11).</t>
+          <t>FIRST consistently POSITIVE step: +2.6pp mean, positive at 6/9 horizons. Built on C2 (macro changes only). But still 0/9 beat baseline.</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>sweep_significance.csv</t>
+          <t>results/direction/phase_ablation/ablation_summary.md</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>stocks share a market factor so p-values are already optimistic</t>
+          <t>direction_phase_ablation.py; C2 16+7 -&gt; D 39 features; ASPI + COMB/SAMP + LOFC/LOLC/LFIN/CFIN</t>
         </is>
       </c>
     </row>
@@ -4578,12 +4592,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>HNB sign-edge claim retest (claim 2)</t>
+          <t>Phase D best single horizon</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -4593,33 +4607,29 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>identical protocol per stock</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>direct, sign of h-day return, 1-3 week horizons</t>
+          <t>direct, h=5d (1 week)</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Cells with positive sign edge</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>6 of 33</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>~17 of 33 (coin flip)</t>
-        </is>
+          <t>Edge over baseline (pp)</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
@@ -4628,17 +4638,17 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>REFUTED. HNB's positive 1-3 week sign edge did NOT replicate - 18% vs the ~50% chance would give. It was luck. Flagged as provisional when found, now closed.</t>
+          <t>Closest call of the whole study: 1-week Phase D 37.3% vs baseline 37.4%. Near-parity at short horizons (1d -1.7, 1wk -0.2, 2wk -1.6) but never crosses.</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>sweep_all_results.csv</t>
+          <t>ablation_gain_table.csv</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>value of naming a claim before retesting it</t>
+          <t>not a win; single split, one stock</t>
         </is>
       </c>
     </row>
@@ -4653,17 +4663,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Return forecast</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Phase E - daily USD/LKR</t>
+          <t>Phase D return sign edge (+sector)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -4673,48 +4683,52 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono + h-bar purge, 2015-2026 window</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, sign of h-day return</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from daily FX (pp)</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Sign edge 1wk/2wk/3wk (pp)</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>+1.7 / +1.7 / +1.1</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>always-guess-winning-side</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Tie</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>FREQUENCY WAS NOT THE PROBLEM. Daily FX gain is exactly 0.0pp (positive in 57/99 cells = coin flip). Macro fails daily exactly as it failed monthly.</t>
+          <t>First POSITIVE sign edges in the study, and at 3 adjacent horizons (1-3 weeks). Tiny (~1-2pp) and one split only -&gt; flag as worth re-testing, NOT a finding.</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>results/direction/daily_macro/daily_macro_summary.md</t>
+          <t>ablation_return_table.csv</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>direction_daily_macro.py; new cleaned_data/usd_lkr_daily.csv</t>
+          <t>check on other tickers before claiming anything</t>
         </is>
       </c>
     </row>
@@ -4734,12 +4748,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Phase E2 - daily global + CPI</t>
+          <t>Phase D feature attention check</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>HNB</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -4754,43 +4768,45 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>XGBoost importance</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from global+CPI (pp)</t>
+          <t>Sector share of importance %</t>
         </is>
       </c>
       <c r="K55" s="2" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>34</v>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>Oil, US 10Y, DXY and inflation make it WORSE (-1.9pp), worst at long horizons (-6.0pp at 1yr). Same trending-variable overfit as Phase C.</t>
+          <t>Sector takes 34% avg (42% at 1 day, falling to 27% at 1yr) - mirror image of macro, which rises with horizon. Sector matters short, macro long, neither enough.</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>daily_macro_gain.csv</t>
+          <t>ablation_feature_importance.csv</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>CPI spliced across 4 base years; money supply excluded (ends 2024-08, inside test window)</t>
+          <t>vol_20 is top feature at 1d/1wk; d_tb3m dominates long</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4826,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Phase E significance screen</t>
+          <t>Sector sweep - replication test</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>11 CSE stocks</t>
+          <t>11 CSE stocks (3 banks, 4 finance, 4 control)</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -4825,31 +4841,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>sign test across stocks, 4 phases x 9 horizons</t>
+          <t>80/20 chrono + h-bar purge, per stock</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>binomial sign test (H0 p=0.5)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Combinations with p&lt;0.05</t>
+          <t>Cells beating baseline</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0 of 36</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0.05</v>
+          <t>27 of 99</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>14 of 99 (Phase A)</t>
+        </is>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
@@ -4858,17 +4876,17 @@
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>NOTHING SIGNIFICANT ANYWHERE. Best cell is 1 day (6/11 stocks, p=0.500) - exact coin flip, same as the sector sweep. Cells beating baseline: A 17, D 27, E 24, E2 25 of 99.</t>
+          <t>Sector features nearly DOUBLE the win rate vs Tier-1 (14-&gt;27 of 99) but wins sit at exactly coin-flip at short horizons and collapse at long ones. No real edge.</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>daily_macro_significance.csv</t>
+          <t>results/direction/sector_sweep/sweep_summary.md</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>macro information source now closed at both frequencies</t>
+          <t>direction_sector_sweep.py; peer composites exclude the target stock</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4906,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Phase E feature attention check</t>
+          <t>Sector gain replication (HNB claim 3)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -4903,12 +4921,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>identical protocol per stock</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>XGBoost importance</t>
+          <t>Phase D - Phase A</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -4918,35 +4936,33 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>New-data share of importance %</t>
+          <t>Mean sector gain (pp)</t>
         </is>
       </c>
       <c r="K57" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
+        <v>3.8</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M57" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>Model spends 27% of importance on the new data (FX 7%, global 11%, CPI 9%) and gains nothing - third time this fingerprint has appeared (Tier-2 41%, macro 64%, now 27%).</t>
+          <t>REPLICATES: +3.8pp mean, positive in 66/99 cells (67%), 9 of 11 stocks positive. HNB was not a fluke - sector context genuinely helps the model. Best: LFIN +13.2, SAMP +9.4, LOFC +8.2. Worst: CTC -11.0.</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>daily_macro_all_results.csv</t>
+          <t>sweep_gain_by_ticker.csv</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>using a feature is not the same as profiting from it</t>
+          <t>helping is not the same as winning</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4982,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Phase F - money supply (M1/M2/M2b/M4)</t>
+          <t>Sector sweep significance screen</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -4981,29 +4997,29 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono, sample cut at 2024-08; test 2022-03 to 2024-08</t>
+          <t>sign test + Wilcoxon across stocks, per horizon</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>binomial sign test (H0 p=0.5)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from money supply (pp)</t>
+          <t>Best sign-test p</t>
         </is>
       </c>
       <c r="K58" s="2" t="n">
-        <v>-0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
@@ -5012,17 +5028,17 @@
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>Money supply adds NOTHING even on a crisis-era test window (positive in 50/99 cells = exact coin flip). Window moved back so M1/M2 could be tested fairly rather than excluded.</t>
+          <t>NOTHING SIGNIFICANT AT ANY HORIZON. Best cells (1 day, 1 week) are 6/11 stocks positive = p=0.500, exactly a coin flip. Long horizons far worse (1yr 0/11).</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>results/direction/money_supply/money_summary.md</t>
+          <t>sweep_significance.csv</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>direction_money_supply.py; 65-day publication lag per CBSL's own note; reserve money dropped (ends 2024-02)</t>
+          <t>stocks share a market factor so p-values are already optimistic</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5058,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Phase F - full classic macro set</t>
+          <t>HNB sign-edge claim retest (claim 2)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -5057,29 +5073,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>identical rows/split/seeds</t>
+          <t>identical protocol per stock</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct, sign of h-day return, 1-3 week horizons</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Mean gain money-&gt;full macro (pp)</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>Cells with positive sign edge</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>6 of 33</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>~17 of 33 (coin flip)</t>
+        </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
@@ -5088,17 +5108,17 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>Full classic set (money + rates + FX + inflation) = 4 of the 5 Naik-Padhi variables. Still 42/99 cells, below the money-only phase (51/99). Only industrial production remains uncollected.</t>
+          <t>REFUTED. HNB's positive 1-3 week sign edge did NOT replicate - 18% vs the ~50% chance would give. It was luck. Flagged as provisional when found, now closed.</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>money_gain.csv</t>
+          <t>sweep_all_results.csv</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>closes the macro chapter apart from IIP</t>
+          <t>value of naming a claim before retesting it</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5138,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Crisis-window effect (window sensitivity)</t>
+          <t>Phase E - daily USD/LKR</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5133,7 +5153,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>2022-03 to 2024-08 vs 2024-2026</t>
+          <t>80/20 chrono + h-bar purge, 2015-2026 window</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -5148,37 +5168,33 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Cells beating baseline</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>43-51 of 99</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>17-27 of 99 (calm window)</t>
-        </is>
-      </c>
-      <c r="M60" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Mean gain from daily FX (pp)</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>IMPORTANT METHOD FINDING: moving the test window into the 2022 crisis roughly DOUBLES the win rate for ALL phases including price-only. Results are window-dependent, not model-dependent.</t>
+          <t>FREQUENCY WAS NOT THE PROBLEM. Daily FX gain is exactly 0.0pp (positive in 57/99 cells = coin flip). Macro fails daily exactly as it failed monthly.</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>money_by_horizon.csv</t>
+          <t>results/direction/daily_macro/daily_macro_summary.md</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>argues for walk-forward / multi-window evaluation in the write-up</t>
+          <t>direction_daily_macro.py; new cleaned_data/usd_lkr_daily.csv</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5214,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>1-day significance - macro ruled out</t>
+          <t>Phase E2 - daily global + CPI</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -5213,33 +5229,29 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>sign test across stocks, 4 phases x 9 horizons</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>binomial sign test (H0 p=0.5)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Cells with p&lt;0.05</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>2 of 36</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>1.8 expected by chance</t>
-        </is>
+          <t>Mean gain from global+CPI (pp)</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
@@ -5248,17 +5260,17 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>Both hits are at 1 day, and the STRONGEST is Phase A (price only, 9/11, +3.9pp, p=0.033). Adding money supply SHRINKS it to +3.2pp. So it is the crisis window, not macro - and 2/36 is chance anyway.</t>
+          <t>Oil, US 10Y, DXY and inflation make it WORSE (-1.9pp), worst at long horizons (-6.0pp at 1yr). Same trending-variable overfit as Phase C.</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>money_significance.csv</t>
+          <t>daily_macro_gain.csv</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>checking the null model is what prevented a false claim</t>
+          <t>CPI spliced across 4 base years; money supply excluded (ends 2024-08, inside test window)</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5280,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5278,7 +5290,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Phase G - industrial production (IIP)</t>
+          <t>Phase E significance screen</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5293,29 +5305,31 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>80/20 chrono, sample 2016-2026 (IIP coverage)</t>
+          <t>sign test across stocks, 4 phases x 9 horizons</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>binomial sign test (H0 p=0.5)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons x 11 stocks</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from IIP (pp)</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="n">
-        <v>-6.4</v>
+          <t>Combinations with p&lt;0.05</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>0 of 36</t>
+        </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
@@ -5324,17 +5338,17 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>IIP makes it WORSE (-6.4pp, positive in only 25/99 cells, 0/36 significant). It was the STRONGEST variable in the Naik-Padhi reference paper, and it still does not predict direction.</t>
+          <t>NOTHING SIGNIFICANT ANYWHERE. Best cell is 1 day (6/11 stocks, p=0.500) - exact coin flip, same as the sector sweep. Cells beating baseline: A 17, D 27, E 24, E2 25 of 99.</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>results/direction/industrial_production/iip_summary.md</t>
+          <t>daily_macro_significance.csv</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>direction_industrial_production.py; DCS index entered by hand, 2016-01 to 2026-05; 50-day publication lag</t>
+          <t>macro information source now closed at both frequencies</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5358,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5354,7 +5368,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Phase G - full classic macro set complete</t>
+          <t>Phase E feature attention check</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -5374,7 +5388,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>XGBoost importance</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -5384,37 +5398,35 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Cells beating baseline</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>25 of 99</t>
-        </is>
+          <t>New-data share of importance %</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>27</v>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>27 of 99 (no macro)</t>
-        </is>
-      </c>
-      <c r="M63" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>ALL FIVE Naik-Padhi macro variables now tested (IIP, money supply, T-bill rate, exchange rate, inflation). NONE beats plain price history. Macro chapter complete.</t>
+          <t>Model spends 27% of importance on the new data (FX 7%, global 11%, CPI 9%) and gains nothing - third time this fingerprint has appeared (Tier-2 41%, macro 64%, now 27%).</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>iip_gain.csv</t>
+          <t>daily_macro_all_results.csv</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>adding all macro is WORSE than sector-only (27/99)</t>
+          <t>using a feature is not the same as profiting from it</t>
         </is>
       </c>
     </row>
@@ -5424,77 +5436,73 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>IIP seasonality guard</t>
+          <t>Phase F - money supply (M1/M2/M2b/M4)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Sri Lanka DCS IIP</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>monthly (125)</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>2016-01 to 2026-05</t>
+          <t>80/20 chrono, sample cut at 2024-08; test 2022-03 to 2024-08</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>seasonal inspection</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>April vs March gap (pts)</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>-10 to -34</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M64" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Mean gain from money supply (pp)</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>IIP is NOT seasonally adjusted - April falls 10-34 pts EVERY year (Sinhala/Tamil New Year), March always peaks. Month-on-month would be a calendar signal, so YoY-only features were used.</t>
+          <t>Money supply adds NOTHING even on a crisis-era test window (positive in 50/99 cells = exact coin flip). Window moved back so M1/M2 could be tested fairly rather than excluded.</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>cleaned_data/industrial_production_monthly.csv</t>
+          <t>results/direction/money_supply/money_summary.md</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>clean_macro_sources.py; mom column deliberately named _DO_NOT_USE</t>
+          <t>direction_money_supply.py; 65-day publication lag per CBSL's own note; reserve money dropped (ends 2024-02)</t>
         </is>
       </c>
     </row>
@@ -5504,22 +5512,22 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Correlation</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Co-movement lift table (no model)</t>
+          <t>Phase F - full classic macro set</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks (22,677 stock-days)</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -5529,48 +5537,48 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>full panel, 15 indicators x 9 horizons</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>conditional probability + 2-proportion z</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Median |lift| short horizons (pp)</t>
+          <t>Mean gain money-&gt;full macro (pp)</t>
         </is>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M65" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>'If indicator up, does stock go up?' answered by pure counting. Market/peer indicators give a real +6 to +10pp lift at 1d-1mo on huge samples. Macro lifts are near zero at short horizons.</t>
+          <t>Full classic set (money + rates + FX + inflation) = 4 of the 5 Naik-Padhi variables. Still 42/99 cells, below the money-only phase (51/99). Only industrial production remains uncollected.</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>results/direction/pooled_rules/comovement_table.csv</t>
+          <t>money_gain.csv</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>direction_pooled_and_rules.py; lift = P(up|ind up) - P(up|ind down)</t>
+          <t>closes the macro chapter apart from IIP</t>
         </is>
       </c>
     </row>
@@ -5580,22 +5588,22 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Correlation</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Co-movement - long-horizon lifts are artifacts</t>
+          <t>Crisis-window effect (window sensitivity)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -5605,52 +5613,52 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>panel, |lift|&gt;=10pp cells</t>
+          <t>2022-03 to 2024-08 vs 2024-2026</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>independent-window audit</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Independent windows behind biggest lifts</t>
+          <t>Cells beating baseline</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>7-24</t>
+          <t>43-51 of 99</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>hundreds needed</t>
-        </is>
-      </c>
-      <c r="M66" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>17-27 of 99 (calm window)</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>All 19 large lifts (T-bill -19.3, M2 +17.0, USD/LKR -15.3) sit at 3mo-1yr where only 7-24 INDEPENDENT windows exist. Overlapping windows inflate the z-test. Discard them.</t>
+          <t>IMPORTANT METHOD FINDING: moving the test window into the 2022 crisis roughly DOUBLES the win rate for ALL phases including price-only. Results are window-dependent, not model-dependent.</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>comovement_table.csv</t>
+          <t>money_by_horizon.csv</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>median |lift| long 4.2pp vs short 2.5pp is a sample-size illusion</t>
+          <t>argues for walk-forward / multi-window evaluation in the write-up</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5668,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5670,12 +5678,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Pooled panel model (sector-wide)</t>
+          <t>1-day significance - macro ruled out</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks pooled</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -5685,32 +5693,32 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>split by DATE not row, 17,770 train rows</t>
+          <t>sign test across stocks, 4 phases x 9 horizons</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>binomial sign test (H0 p=0.5)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons, one model for whole sector</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Horizons beating pooled baseline</t>
+          <t>Cells with p&lt;0.05</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>2 of 9</t>
+          <t>2 of 36</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>majority / persistence</t>
+          <t>1.8 expected by chance</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
@@ -5720,17 +5728,17 @@
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>7x more training data (17,770 vs ~2,700 per stock). Beats the POOLED baseline at 1 day (+3.3pp) and 1 week (+2.7pp) only.</t>
+          <t>Both hits are at 1 day, and the STRONGEST is Phase A (price only, 9/11, +3.9pp, p=0.033). Adding money supply SHRINKS it to +3.2pp. So it is the crisis window, not macro - and 2/36 is chance anyway.</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>results/direction/pooled_rules/pooled_model_results.csv</t>
+          <t>money_significance.csv</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>direction_pooled_and_rules.py</t>
+          <t>checking the null model is what prevented a false claim</t>
         </is>
       </c>
     </row>
@@ -5750,12 +5758,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Pooled model fairness check</t>
+          <t>Phase G - industrial production (IIP)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -5765,33 +5773,29 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>pooled model scored vs each stock's OWN baseline</t>
+          <t>80/20 chrono, sample 2016-2026 (IIP coverage)</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>binomial sign test (H0 p=0.5)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>direct, 9 horizons</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>1-day: stocks positive</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>6 of 7</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>p=0.062</t>
-        </is>
+          <t>Mean gain from IIP (pp)</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
@@ -5800,17 +5804,17 @@
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>STRONGEST RESULT OF THE PROJECT but still not significant. The 1-week +2.7pp was a POOLING ARTIFACT (-0.5pp vs own baselines). Only 1 day survives: median +2.5pp, p=0.062, 1 of 9 horizons, single window.</t>
+          <t>IIP makes it WORSE (-6.4pp, positive in only 25/99 cells, 0/36 significant). It was the STRONGEST variable in the Naik-Padhi reference paper, and it still does not predict direction.</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>pooled_vs_own_baseline.csv</t>
+          <t>results/direction/industrial_production/iip_summary.md</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>pooling stocks with different class balance weakens the majority baseline and fakes an edge</t>
+          <t>direction_industrial_production.py; DCS index entered by hand, 2016-01 to 2026-05; 50-day publication lag</t>
         </is>
       </c>
     </row>
@@ -5830,12 +5834,12 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Readable rules extracted</t>
+          <t>Phase G - full classic macro set complete</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks pooled</t>
+          <t>11 CSE stocks</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -5845,48 +5849,52 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>depth-3 tree, scored on unseen test set</t>
+          <t>identical rows/split/seeds</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Decision tree (depth 3)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/22</t>
+          <t>direct, 9 horizons x 11 stocks</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Best 1-day rule accuracy %</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="M69" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Cells beating baseline</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>25 of 99</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>27 of 99 (no macro)</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>17 plain-English rules with out-of-sample hit rates. Best 1-day rule: calm market + flat ASPI + no big drop -&gt; Hold, 49.3% (+11.3pp). Shows WHAT the model believes, not just that it fails.</t>
+          <t>ALL FIVE Naik-Padhi macro variables now tested (IIP, money supply, T-bill rate, exchange rate, inflation). NONE beats plain price history. Macro chapter complete.</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>readable_rules.csv</t>
+          <t>iip_gain.csv</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>1-month rule at 68.5% fires only 317 times - treat as noise</t>
+          <t>adding all macro is WORSE than sector-only (27/99)</t>
         </is>
       </c>
     </row>
@@ -5901,72 +5909,72 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1-day claim re-test (walk-forward)</t>
+          <t>IIP seasonality guard</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>Sri Lanka DCS IIP</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>monthly (125)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>21 non-overlapping 6-month windows, expanding train</t>
+          <t>2016-01 to 2026-05</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost (reported separately)</t>
+          <t>seasonal inspection</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>direct, walk-forward, h=1</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Folds with positive median edge</t>
+          <t>April vs March gap (pts)</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>6-7 of 21</t>
+          <t>-10 to -34</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>10.5 expected by chance</t>
-        </is>
-      </c>
-      <c r="M70" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>CLAIM REFUTED. Median of fold medians -1.8pp (Logistic) / -1.9pp (XGBoost), sign-test p=0.96 and 0.99. The single-split +2.5pp did not survive 21 independent windows.</t>
+          <t>IIP is NOT seasonally adjusted - April falls 10-34 pts EVERY year (Sinhala/Tamil New Year), March always peaks. Month-on-month would be a calendar signal, so YoY-only features were used.</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>results/direction/retest_1day/retest_summary.md</t>
+          <t>cleaned_data/industrial_production_monthly.csv</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>direction_1day_retest.py; verdict rule fixed IN ADVANCE; 1-week carried as control, also negative</t>
+          <t>clean_macro_sources.py; mom column deliberately named _DO_NOT_USE</t>
         </is>
       </c>
     </row>
@@ -5981,17 +5989,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Correlation</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>1-day re-test - window regime effect</t>
+          <t>Co-movement lift table (no model)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>7 bank/finance stocks (22,677 stock-days)</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -6001,52 +6009,48 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>21 walk-forward folds</t>
+          <t>full panel, 15 indicators x 9 horizons</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>conditional probability + 2-proportion z</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Positive folds 2016-2020 vs 2021-2024</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>1 of 10 vs 6 of 8</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
+          <t>Median |lift| short horizons (pp)</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M71" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>Confirms the crisis-window finding a second time: folds in 2021-2024 are mostly POSITIVE, 2016-2020 mostly negative. Apparent skill is a property of the period, not the model.</t>
+          <t>'If indicator up, does stock go up?' answered by pure counting. Market/peer indicators give a real +6 to +10pp lift at 1d-1mo on huge samples. Macro lifts are near zero at short horizons.</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>retest_by_fold.csv</t>
+          <t>results/direction/pooled_rules/comovement_table.csv</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>strong argument for walk-forward reporting in the dissertation</t>
+          <t>direction_pooled_and_rules.py; lift = P(up|ind up) - P(up|ind down)</t>
         </is>
       </c>
     </row>
@@ -6061,12 +6065,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Correlation</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1-day re-test - per stock consistency</t>
+          <t>Co-movement - long-horizon lifts are artifacts</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -6081,32 +6085,32 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>21 walk-forward folds each</t>
+          <t>panel, |lift|&gt;=10pp cells</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>independent-window audit</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Stocks positive in &gt;50% of folds</t>
+          <t>Independent windows behind biggest lifts</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>2 of 7</t>
+          <t>7-24</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>hundreds needed</t>
         </is>
       </c>
       <c r="M72" s="5" t="inlineStr">
@@ -6116,17 +6120,17 @@
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>No consistency: LOFC and CFIN positive in 62% of folds, HNB in only 19%. A real edge would show across the sector, not in two names.</t>
+          <t>All 19 large lifts (T-bill -19.3, M2 +17.0, USD/LKR -15.3) sit at 3mo-1yr where only 7-24 INDEPENDENT windows exist. Overlapping windows inflate the z-test. Discard them.</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>retest_by_stock.csv</t>
+          <t>comovement_table.csv</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>median edge per stock ranges +4.9 (LOFC) to -4.9 (SAMP)</t>
+          <t>median |lift| long 4.2pp vs short 2.5pp is a sample-size illusion</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6150,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>LSTM/GRU for direction</t>
+          <t>Pooled panel model (sector-wide)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -6156,37 +6160,37 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>daily (30-day sequences)</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>7 walk-forward 12-month folds, 3 seeds</t>
+          <t>split by DATE not row, 17,770 train rows</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>LSTM + GRU (PyTorch)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>direct, sequence input, h=1/5/22</t>
+          <t>direct, 9 horizons, one model for whole sector</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Folds positive (LSTM, h=1)</t>
+          <t>Horizons beating pooled baseline</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>5 of 7</t>
+          <t>2 of 9</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>p=0.227</t>
+          <t>majority / persistence</t>
         </is>
       </c>
       <c r="M73" s="5" t="inlineStr">
@@ -6196,17 +6200,17 @@
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>Recurrent nets do NOT beat the naive baseline at any horizon. Closes the 'did you try deep learning on direction?' question. LSTM finally applied to the direction target (project is named after it).</t>
+          <t>7x more training data (17,770 vs ~2,700 per stock). Beats the POOLED baseline at 1 day (+3.3pp) and 1 week (+2.7pp) only.</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>results/direction/lstm_gru/lstm_gru_summary.md</t>
+          <t>results/direction/pooled_rules/pooled_model_results.csv</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>direction_lstm_gru.py; monthly macro excluded (flat inside a 30-day window)</t>
+          <t>direction_pooled_and_rules.py</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6230,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Sequence vs flat control (LSTM value)</t>
+          <t>Pooled model fairness check</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks pooled</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -6241,52 +6245,52 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>identical sequences, flattened for the control</t>
+          <t>pooled model scored vs each stock's OWN baseline</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>LSTM vs Logistic on flattened sequences</t>
+          <t>binomial sign test (H0 p=0.5)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/22</t>
+          <t>direct, 9 horizons</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Median edge LSTM vs flat (pp)</t>
+          <t>1-day: stocks positive</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>+2.9 vs -1.7</t>
+          <t>6 of 7</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Logistic(flat)</t>
-        </is>
-      </c>
-      <c r="M74" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>p=0.062</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>REAL NUANCE: LSTM beats the FLATTENED same data at ALL 3 horizons (1d +2.9 vs -1.7, 1wk -0.4 vs -2.1, 1mo -5.4 vs -9.9). Order of recent days carries a little signal that summary features discard - first time added complexity helped. Still not enough to reach the baseline.</t>
+          <t>STRONGEST RESULT OF THE PROJECT but still not significant. The 1-week +2.7pp was a POOLING ARTIFACT (-0.5pp vs own baselines). Only 1 day survives: median +2.5pp, p=0.062, 1 of 9 horizons, single window.</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>lstm_gru_by_fold.csv</t>
+          <t>pooled_vs_own_baseline.csv</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>the flat control is what makes this interpretable</t>
+          <t>pooling stocks with different class balance weakens the majority baseline and fakes an edge</t>
         </is>
       </c>
     </row>
@@ -6306,12 +6310,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Regime effect - THIRD confirmation</t>
+          <t>Readable rules extracted</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>7 bank/finance stocks pooled</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -6321,52 +6325,48 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>7 walk-forward folds, LSTM h=1</t>
+          <t>depth-3 tree, scored on unseen test set</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>Decision tree (depth 3)</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, h=1/5/22</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Positive folds 2019-2020 vs 2021-2025</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>0 of 2 vs 5 of 5</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Best 1-day rule accuracy %</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="M75" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>Same window/regime pattern found for a THIRD time (after money supply and the 1-day retest). Every model looks skilled post-2021 and useless before, with identical code and features. Explains why 5/7 folds here is not convincing.</t>
+          <t>17 plain-English rules with out-of-sample hit rates. Best 1-day rule: calm market + flat ASPI + no big drop -&gt; Hold, 49.3% (+11.3pp). Shows WHAT the model believes, not just that it fails.</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>lstm_gru_by_fold.csv</t>
+          <t>readable_rules.csv</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>strongest methodological finding of the project</t>
+          <t>1-month rule at 68.5% fires only 317 times - treat as noise</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Phase H - news sentiment</t>
+          <t>1-day claim re-test (walk-forward)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6401,29 +6401,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>7 walk-forward 6-month folds, 2016-2022</t>
+          <t>21 non-overlapping 6-month windows, expanding train</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>Logistic + XGBoost (reported separately)</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/10/22</t>
+          <t>direct, walk-forward, h=1</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Mean gain from sentiment (pp)</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>0</v>
+          <t>Folds with positive median edge</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>6-7 of 21</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>10.5 expected by chance</t>
+        </is>
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
@@ -6432,17 +6436,17 @@
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>News sentiment does NOT improve direction. Gain positive at 2 of 4 horizons (-0.8, -0.7, +2.4, +1.6), nothing near significance (all p&gt;=0.50). No phase beats the naive baseline.</t>
+          <t>CLAIM REFUTED. Median of fold medians -1.8pp (Logistic) / -1.9pp (XGBoost), sign-test p=0.96 and 0.99. The single-split +2.5pp did not survive 21 independent windows.</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>results/direction/sentiment/sentiment_summary.md</t>
+          <t>results/direction/retest_1day/retest_summary.md</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>direction_phase_h_sentiment.py; 149k Dailymirror/Newsfirst articles, 9,785 market-relevant</t>
+          <t>direction_1day_retest.py; verdict rule fixed IN ADVANCE; 1-week carried as control, also negative</t>
         </is>
       </c>
     </row>
@@ -6462,12 +6466,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Phase H - lexicon disagreement</t>
+          <t>1-day re-test - window regime effect</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Dailymirror + Newsfirst news</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -6477,26 +6481,28 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>9,785 market-relevant articles 2016-2022</t>
+          <t>21 walk-forward folds</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>VADER vs Loughran-McDonald style</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>sentiment scoring</t>
+          <t>direct, h=1</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Correlation between lexicons</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="n">
-        <v>0.416</v>
+          <t>Positive folds 2016-2020 vs 2021-2024</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>1 of 10 vs 6 of 8</t>
+        </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
@@ -6510,17 +6516,17 @@
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>Two reasonable sentiment measures on the SAME articles correlate only 0.42. Direct evidence the sentiment signal is fragile, not merely weak. Running one lexicon alone would have hidden this.</t>
+          <t>Confirms the crisis-window finding a second time: folds in 2021-2024 are mostly POSITIVE, 2016-2020 mostly negative. Apparent skill is a property of the period, not the model.</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>sentiment_verdict.csv</t>
+          <t>retest_by_fold.csv</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>finance_lexicon.py; full LM dictionary can be dropped in without code change</t>
+          <t>strong argument for walk-forward reporting in the dissertation</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6546,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Phase H - regime confound ruled out</t>
+          <t>1-day re-test - per stock consistency</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -6555,27 +6561,27 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>folds split calm vs crisis</t>
+          <t>21 walk-forward folds each</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>direct, h=1</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Sentiment gain calm vs crisis (pp)</t>
+          <t>Stocks positive in &gt;50% of folds</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>+0.85 vs -0.45</t>
+          <t>2 of 7</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -6583,24 +6589,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M78" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>Expected sentiment to 'work' only in the 2022 crisis; the OPPOSITE happened (calm 9/16 folds positive, crisis 3/12). So this null is NOT a regime artifact - cleaner than the other phases.</t>
+          <t>No consistency: LOFC and CFIN positive in 62% of folds, HNB in only 19%. A real edge would show across the sector, not in two names.</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>sentiment_regime_split.csv</t>
+          <t>retest_by_stock.csv</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>first phase where the regime effect did not appear</t>
+          <t>median edge per stock ranges +4.9 (LOFC) to -4.9 (SAMP)</t>
         </is>
       </c>
     </row>
@@ -6615,70 +6621,72 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>News look-ahead guard</t>
+          <t>LSTM/GRU for direction</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Dailymirror + Newsfirst news</t>
+          <t>7 bank/finance stocks pooled</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>daily (30-day sequences)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>publication timestamps vs 14:30 CSE close</t>
+          <t>7 walk-forward 12-month folds, 3 seeds</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>time-of-day assignment</t>
+          <t>LSTM + GRU (PyTorch)</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>direct, sequence input, h=1/5/22</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Articles pushed to next trading day %</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="n">
-        <v>36</v>
+          <t>Folds positive (LSTM, h=1)</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>5 of 7</t>
+        </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>p=0.227</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>36% of articles were published AFTER the 14:30 close and were reassigned to the next trading day. Without this rule those articles report the very move being predicted and sentiment would look excellent and be worthless.</t>
+          <t>Recurrent nets do NOT beat the naive baseline at any horizon. Closes the 'did you try deep learning on direction?' question. LSTM finally applied to the direction target (project is named after it).</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>cleaned_data/news_sentiment_daily.csv</t>
+          <t>results/direction/lstm_gru/lstm_gru_summary.md</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>only 75 of 149,240 rows lacked a timestamp</t>
+          <t>direction_lstm_gru.py; monthly macro excluded (flat inside a 30-day window)</t>
         </is>
       </c>
     </row>
@@ -6698,12 +6706,12 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>POSITIVE CONTROL - pipeline validation</t>
+          <t>Sequence vs flat control (LSTM value)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>7 bank/finance stocks pooled</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -6713,48 +6721,52 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, same-day vs lagged info</t>
+          <t>identical sequences, flattened for the control</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>LSTM vs Logistic on flattened sequences</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>contemporaneous vs predictive</t>
+          <t>direct, h=1/5/22</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Edge over baseline (pp)</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="M80" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Median edge LSTM vs flat (pp)</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>+2.9 vs -1.7</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Logistic(flat)</t>
+        </is>
+      </c>
+      <c r="M80" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>DECISIVE: same code finds +8.2pp (17/19 folds, p=0.0004) using TODAY's market/macro/news, and -4.1pp using the SAME info one day earlier. Gap 13.7pp. The pipeline is NOT blind - this information EXPLAINS returns but does not PREDICT them.</t>
+          <t>REAL NUANCE: LSTM beats the FLATTENED same data at ALL 3 horizons (1d +2.9 vs -1.7, 1wk -0.4 vs -2.1, 1mo -5.4 vs -9.9). Order of recent days carries a little signal that summary features discard - first time added complexity helped. Still not enough to reach the baseline.</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>results/direction/diagnostics/diagnostics_summary.md</t>
+          <t>lstm_gru_by_fold.csv</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>direction_diagnostics.py; own-stock return excluded from contemporaneous features</t>
+          <t>the flat control is what makes this interpretable</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6786,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Binary up/down reformulation</t>
+          <t>Regime effect - THIRD confirmation</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -6789,48 +6801,52 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds</t>
+          <t>7 walk-forward folds, LSTM h=1</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>LSTM</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>binary, h=1/5/22</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Edge over baseline (pp)</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Positive folds 2019-2020 vs 2021-2025</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>0 of 2 vs 5 of 5</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>3-class dead-zone was NOT hiding a signal. Binary edge -4.8/-1.1/-2.1pp at 1d/1wk/1mo, positive in only 1/19, 7/19, 4/19 folds.</t>
+          <t>Same window/regime pattern found for a THIRD time (after money supply and the 1-day retest). Every model looks skilled post-2021 and useless before, with identical code and features. Explains why 5/7 folds here is not convincing.</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>diagnostics_verdict.csv</t>
+          <t>lstm_gru_by_fold.csv</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>rules out the Hold-majority explanation</t>
+          <t>strongest methodological finding of the project</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6866,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>MAGNITUDE-WEIGHTED edge (survives)</t>
+          <t>Phase H - news sentiment</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -6865,7 +6881,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds</t>
+          <t>7 walk-forward 6-month folds, 2016-2022</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6875,40 +6891,38 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>binary, |return|-weighted</t>
+          <t>direct, h=1/5/10/22</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Weighted edge 1d / 1wk (pp)</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>+7.9 / +13.2</t>
-        </is>
+          <t>Mean gain from sentiment (pp)</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0.6</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M82" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>FIRST RESULT TO SURVIVE. Model is WRONG more often than baseline on plain accuracy (-4.3pp) but RIGHT on the big moves: weighted edge +7.9pp (15/19 folds, p=0.0096) at 1 day and +13.2pp (15/19, p=0.0096) at 1 week. Accuracy was the wrong metric.</t>
+          <t>News sentiment does NOT improve direction. Gain positive at 2 of 4 horizons (-0.8, -0.7, +2.4, +1.6), nothing near significance (all p&gt;=0.50). No phase beats the naive baseline.</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>diagnostics_magnitude.csv</t>
+          <t>results/direction/sentiment/sentiment_summary.md</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>1-month +9.5pp but p=0.18</t>
+          <t>direction_phase_h_sentiment.py; 149k Dailymirror/Newsfirst articles, 9,785 market-relevant</t>
         </is>
       </c>
     </row>
@@ -6928,12 +6942,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Trading backtest with costs</t>
+          <t>Phase H - lexicon disagreement</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>Dailymirror + Newsfirst news</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -6943,48 +6957,50 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, h=1 only (non-overlapping)</t>
+          <t>9,785 market-relevant articles 2016-2022</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>long/short on model signal</t>
+          <t>VADER vs Loughran-McDonald style</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>economic evaluation</t>
+          <t>sentiment scoring</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Net return @50bps (%)</t>
+          <t>Correlation between lexicons</t>
         </is>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="M83" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>0.416</v>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M83" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>THE EDGE IS REAL BUT NOT EXPLOITABLE. Gross +22.19% vs buy-and-hold +6.49%, but median 40 position flips per 6-month fold: net +17.35% @10bps, +11.24% @25bps, +0.05% @50bps. At realistic CSE costs the edge is exactly zero (8/19 folds, p=0.82).</t>
+          <t>Two reasonable sentiment measures on the SAME articles correlate only 0.42. Direct evidence the sentiment signal is fragile, not merely weak. Running one lexicon alone would have hidden this.</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>diagnostics_backtest_h1.csv</t>
+          <t>sentiment_verdict.csv</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>h=5 and h=22 backtests omitted - overlapping returns cannot be summed</t>
+          <t>finance_lexicon.py; full LM dictionary can be dropped in without code change</t>
         </is>
       </c>
     </row>
@@ -6999,12 +7015,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Price + macro + news vs naive</t>
+          <t>Phase H - regime confound ruled out</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -7019,52 +7035,52 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>walk-forward 6-month folds, per stock</t>
+          <t>folds split calm vs crisis</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>naive / ARIMA(1,1,1) / Ridge / XGBoost</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>1-day and 5-day, return-then-reconstruct</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Cases beating naive (MAPE)</t>
+          <t>Sentiment gain calm vs crisis (pp)</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0 of 133</t>
+          <t>+0.85 vs -0.45</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>naive</t>
-        </is>
-      </c>
-      <c r="M84" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M84" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>NAIVE UNBEATEN. Best model ARIMA(1,1,1) at 1.004x naive MAPE. Stage 1's univariate conclusion survives the multivariate test - adding macro and news does not rescue price forecasting.</t>
+          <t>Expected sentiment to 'work' only in the 2022 crisis; the OPPOSITE happened (calm 9/16 folds positive, crisis 3/12). So this null is NOT a regime artifact - cleaner than the other phases.</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>results/price_macro_news/price_summary.md</t>
+          <t>sentiment_regime_split.csv</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>price_with_macro_news.py; models predict RETURN then reconstruct price to stop them echoing today's price</t>
+          <t>first phase where the regime effect did not appear</t>
         </is>
       </c>
     </row>
@@ -7079,17 +7095,17 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Does macro/news improve price forecasting?</t>
+          <t>News look-ahead guard</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>7 bank/finance stocks</t>
+          <t>Dailymirror + Newsfirst news</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -7099,48 +7115,50 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>nested feature sets P / P+M / P+M+N</t>
+          <t>publication timestamps vs 14:30 CSE close</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>time-of-day assignment</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>ablation on MAPE</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Median MAPE improvement (pp)</t>
+          <t>Articles pushed to next trading day %</t>
         </is>
       </c>
       <c r="K85" s="2" t="n">
-        <v>-0.019</v>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>36</v>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M85" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>ALL EIGHT combinations NEGATIVE (-0.008 to -0.078pp). Adding macro and news makes price forecasting WORSE, consistently across both algorithms and both horizons.</t>
+          <t>36% of articles were published AFTER the 14:30 close and were reassigned to the next trading day. Without this rule those articles report the very move being predicted and sentiment would look excellent and be worthless.</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>price_ablation_gain.csv</t>
+          <t>cleaned_data/news_sentiment_daily.csv</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>mirrors the direction chapter exactly</t>
+          <t>only 75 of 149,240 rows lacked a timestamp</t>
         </is>
       </c>
     </row>
@@ -7155,12 +7173,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>CSE flat-day share (illiquidity)</t>
+          <t>POSITIVE CONTROL - pipeline validation</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -7175,50 +7193,48 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>2017-2026</t>
+          <t>19 walk-forward folds, same-day vs lagged info</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>share of zero-return days</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>contemporaneous vs predictive</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Flat days at 1 day (%)</t>
+          <t>Edge over baseline (pp)</t>
         </is>
       </c>
       <c r="K86" s="2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M86" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="M86" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>~10% of bank/finance trading days close EXACTLY unchanged; LOFC 36.0%, HNB 12.9%, LOLC 7.2%. Illiquidity is part of why the naive baseline is so hard to beat and why the Hold class dominates.</t>
+          <t>DECISIVE: same code finds +8.2pp (17/19 folds, p=0.0004) using TODAY's market/macro/news, and -4.1pp using the SAME info one day earlier. Gap 13.7pp. The pipeline is NOT blind - this information EXPLAINS returns but does not PREDICT them.</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>price_all_results.csv</t>
+          <t>results/direction/diagnostics/diagnostics_summary.md</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>surfaced as an artefact of the naive model's directional-accuracy column</t>
+          <t>direction_diagnostics.py; own-stock return excluded from contemporaneous features</t>
         </is>
       </c>
     </row>
@@ -7233,17 +7249,17 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>LEAK CAUGHT - ASPI forward-fill</t>
+          <t>Binary up/down reformulation</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 index</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -7253,48 +7269,48 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>feature vs same-day and next-day return</t>
+          <t>19 walk-forward folds</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>correlation audit</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>leak detection</t>
+          <t>binary, h=1/5/22</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>corr with next-day vs same-day</t>
+          <t>Edge over baseline (pp)</t>
         </is>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.742</v>
+        <v>-4.8</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="M87" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0</v>
+      </c>
+      <c r="M87" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>SPSL20 and ASPI do not share a trading calendar (207 / 962 mismatched dates). Forward-filling ASPI across the gaps let it carry a move SPSL20 only recorded on its NEXT row. Halved MAPE for free: ratio 0.496 vs a true 0.970.</t>
+          <t>3-class dead-zone was NOT hiding a signal. Binary edge -4.8/-1.1/-2.1pp at 1d/1wk/1mo, positive in only 1/19, 7/19, 4/19 folds.</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>results/price_macro_news/leak_scan.csv</t>
+          <t>diagnostics_verdict.csv</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>fix: no ffill across calendars + no ASPI features for index targets</t>
+          <t>rules out the Hold-majority explanation</t>
         </is>
       </c>
     </row>
@@ -7309,17 +7325,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Automated leak scan added</t>
+          <t>MAGNITUDE-WEIGHTED edge (survives)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>all 9 targets</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -7329,50 +7345,50 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>every feature, every run</t>
+          <t>19 walk-forward folds</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>corr(feature, future) vs corr(feature, present)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>guard</t>
+          <t>binary, |return|-weighted</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Features flagged after fix</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="n">
+          <t>Weighted edge 1d / 1wk (pp)</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>+7.9 / +13.2</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M88" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M88" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>Permanent guard: any feature correlating MORE with the future than the present is flagged. Would have caught the ASPI bug instantly. Runs on every target automatically. THIRD leak-class bug in this project - all three flattered the model.</t>
+          <t>FIRST RESULT TO SURVIVE. Model is WRONG more often than baseline on plain accuracy (-4.3pp) but RIGHT on the big moves: weighted edge +7.9pp (15/19 folds, p=0.0096) at 1 day and +13.2pp (15/19, p=0.0096) at 1 week. Accuracy was the wrong metric.</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>price_with_macro_news.py</t>
+          <t>diagnostics_magnitude.csv</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>previous two: persistence baseline lookback, pooled baseline</t>
+          <t>1-month +9.5pp but p=0.18</t>
         </is>
       </c>
     </row>
@@ -7387,17 +7403,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 with macro + news (corrected)</t>
+          <t>Trading backtest with costs</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 index</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -7407,29 +7423,29 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>17 walk-forward 6-month folds</t>
+          <t>19 walk-forward folds, h=1 only (non-overlapping)</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>naive / ARIMA / Ridge / XGBoost</t>
+          <t>long/short on model signal</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>direct 1-day and 5-day</t>
+          <t>economic evaluation</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>MAPE ratio vs naive (best)</t>
+          <t>Net return @50bps (%)</t>
         </is>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.97</v>
+        <v>0.05</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>1</v>
+        <v>6.49</v>
       </c>
       <c r="M89" s="5" t="inlineStr">
         <is>
@@ -7438,17 +7454,17 @@
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>After the leak fix: best is Ridge price-only at 0.970 (1d) and 0.959 (5d), beating naive in only 10/17 and 9/17 folds. Macro and news make it WORSE (ratios 1.00-1.10).</t>
+          <t>THE EDGE IS REAL BUT NOT EXPLOITABLE. Gross +22.19% vs buy-and-hold +6.49%, but median 40 position flips per 6-month fold: net +17.35% @10bps, +11.24% @25bps, +0.05% @50bps. At realistic CSE costs the edge is exactly zero (8/19 folds, p=0.82).</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>results/price_macro_news/price_summary.md</t>
+          <t>diagnostics_backtest_h1.csv</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>pre-fix figure was 0.496 - entirely the ASPI leak</t>
+          <t>h=5 and h=22 backtests omitted - overlapping returns cannot be summed</t>
         </is>
       </c>
     </row>
@@ -7468,12 +7484,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Index vs stock autocorrelation</t>
+          <t>Price + macro + news vs naive</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>SPSL20, ASPI vs 7 stocks</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -7483,52 +7499,52 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>full sample</t>
+          <t>walk-forward 6-month folds, per stock</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>lag-1 return autocorrelation</t>
+          <t>naive / ARIMA(1,1,1) / Ridge / XGBoost</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>1-day and 5-day, return-then-reconstruct</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Lag-1 autocorr (index vs stock)</t>
+          <t>Cases beating naive (MAPE)</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>+0.24 vs +0.04</t>
+          <t>0 of 133</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M90" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M90" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>REAL EFFECT: indices show +0.237 (SPSL20) and +0.233 (ASPI) lag-1 return autocorrelation vs +0.038 for HNB. Non-synchronous trading - illiquid constituents (LOFC 37.8% flat days) reprice a day late, smearing shocks. A 1-parameter AR(1) captures the entire index 'edge'.</t>
+          <t>NAIVE UNBEATEN. Best model ARIMA(1,1,1) at 1.004x naive MAPE. Stage 1's univariate conclusion survives the multivariate test - adding macro and news does not rescue price forecasting.</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>price_all_results.csv</t>
+          <t>results/price_macro_news/price_summary.md</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>statistically real, economically useless - capturing it means trading the illiquid names that cause it</t>
+          <t>price_with_macro_news.py; models predict RETURN then reconstruct price to stop them echoing today's price</t>
         </is>
       </c>
     </row>
@@ -7548,12 +7564,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Hybrid ARIMA+LSTM (Zhang 2003)</t>
+          <t>Does macro/news improve price forecasting?</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + HNB</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -7563,29 +7579,29 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20 + 7 walk-forward folds</t>
+          <t>nested feature sets P / P+M / P+M+N</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>ARIMA(2,1,0) + LSTM on residuals</t>
+          <t>Ridge + XGBoost</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead, rolling ARIMA state</t>
+          <t>ablation on MAPE</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Theil U2 (fixed split)</t>
+          <t>Median MAPE improvement (pp)</t>
         </is>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1.012</v>
+        <v>-0.019</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
@@ -7594,17 +7610,17 @@
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>Hybrid built properly (Y=L+N, LSTM on ARIMA residuals, 3 seeds averaged) and it does NOT beat the naive random walk. SPSL20 U2=1.012, HNB U2=1.005. Marginally WORSE than plain ARIMA on both targets.</t>
+          <t>ALL EIGHT combinations NEGATIVE (-0.008 to -0.078pp). Adding macro and news makes price forecasting WORSE, consistently across both algorithms and both horizons.</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>results/hybrid_comparable/hybrid_summary.md</t>
+          <t>price_ablation_gain.csv</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>hybrid_arima_lstm_macro_news.py; supervisor-committed architecture, now tested</t>
+          <t>mirrors the direction chapter exactly</t>
         </is>
       </c>
     </row>
@@ -7619,17 +7635,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Hybrid + macro + news (extension)</t>
+          <t>CSE flat-day share (illiquidity)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + HNB</t>
+          <t>7 bank/finance stocks</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -7639,52 +7655,50 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20 + 7 walk-forward folds</t>
+          <t>2017-2026</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>ARIMA + LSTM on residuals WITH exogenous macro/news</t>
+          <t>share of zero-return days</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Folds better than naive (HNB)</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>0 of 7</t>
-        </is>
+          <t>Flat days at 1 day (%)</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>10.5</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>naive</t>
-        </is>
-      </c>
-      <c r="M92" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M92" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>THE PROJECT'S EXTENSION: macro+news fed into the residual model - the part ARIMA provably cannot explain. It makes things WORSE. SPSL20 U2 1.032, HNB U2 1.011, HNB walk-forward 0/7 folds.</t>
+          <t>~10% of bank/finance trading days close EXACTLY unchanged; LOFC 36.0%, HNB 12.9%, LOLC 7.2%. Illiquidity is part of why the naive baseline is so hard to beat and why the Hold class dominates.</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>hybrid_walkforward_table.csv</t>
+          <t>price_all_results.csv</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>best place to put macro if it carried information; it does not</t>
+          <t>surfaced as an artefact of the naive model's directional-accuracy column</t>
         </is>
       </c>
     </row>
@@ -7699,17 +7713,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Diebold-Mariano + Theil U added</t>
+          <t>LEAK CAUGHT - ASPI forward-fill</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + HNB</t>
+          <t>S&amp;P SL 20 index</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -7719,50 +7733,48 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20</t>
+          <t>feature vs same-day and next-day return</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>DM test (Newey-West HAC) + Theil U2</t>
+          <t>correlation audit</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>forecast comparison</t>
+          <t>leak detection</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Models significantly better than naive</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>0 of 8</t>
-        </is>
+          <t>corr with next-day vs same-day</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0.742</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M93" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>0.374</v>
+      </c>
+      <c r="M93" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>COMPARABILITY GAP CLOSED. Papers claim superiority with the DM test; this project had only baseline-relative edge. DM run vs naive AND vs ARIMA: ZERO models significant at p&lt;0.05. Only 1 of 8 has Theil U2&lt;1.</t>
+          <t>SPSL20 and ASPI do not share a trading calendar (207 / 962 mismatched dates). Forward-filling ASPI across the gaps let it carry a move SPSL20 only recorded on its NEXT row. Halved MAPE for free: ratio 0.496 vs a true 0.970.</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>hybrid_fixed_split_table.csv</t>
+          <t>results/price_macro_news/leak_scan.csv</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>the standard test reviewers expect; previously missing</t>
+          <t>fix: no ffill across calendars + no ASPI features for index targets</t>
         </is>
       </c>
     </row>
@@ -7782,12 +7794,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>R-squared on price levels is meaningless</t>
+          <t>Automated leak scan added</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + HNB</t>
+          <t>all 9 targets</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -7797,26 +7809,26 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20</t>
+          <t>every feature, every run</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>all models incl. naive</t>
+          <t>corr(feature, future) vs corr(feature, present)</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>descriptive</t>
+          <t>guard</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>R2 of the NAIVE model</t>
+          <t>Features flagged after fix</t>
         </is>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.9979</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
@@ -7830,17 +7842,17 @@
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>IMPORTANT FOR THE WRITE-UP: every model scores R2 0.9977-0.9980 - INCLUDING the naive random walk. Papers reporting R2~0.99 on price levels are reporting nothing. R2 on a level only measures being in the right magnitude.</t>
+          <t>Permanent guard: any feature correlating MORE with the future than the present is flagged. Would have caught the ASPI bug instantly. Runs on every target automatically. THIRD leak-class bug in this project - all three flattered the model.</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>hybrid_fixed_split_table.csv</t>
+          <t>price_with_macro_news.py</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>direct rebuttal to a common claim in this literature</t>
+          <t>previous two: persistence baseline lookback, pooled baseline</t>
         </is>
       </c>
     </row>
@@ -7855,17 +7867,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Fixed split vs walk-forward disagreement</t>
+          <t>S&amp;P SL 20 with macro + news (corrected)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + HNB</t>
+          <t>S&amp;P SL 20 index</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -7875,52 +7887,48 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>both protocols, same models</t>
+          <t>17 walk-forward 6-month folds</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>ARIMA / LSTM / Hybrid</t>
+          <t>naive / ARIMA / Ridge / XGBoost</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead</t>
+          <t>direct 1-day and 5-day</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>ARIMA SPSL20 U2 (fixed vs WF)</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>1.005 vs 0.985</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M95" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>MAPE ratio vs naive (best)</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>The two protocols DISAGREE: ARIMA is worse than naive on the SPSL20 fixed split (6/7 folds better in walk-forward), and the reverse pattern on HNB. Reporting only one protocol would mislead - hence both are published.</t>
+          <t>After the leak fix: best is Ridge price-only at 0.970 (1d) and 0.959 (5d), beating naive in only 10/17 and 9/17 folds. Macro and news make it WORSE (ratios 1.00-1.10).</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>hybrid_all_results.csv</t>
+          <t>results/price_macro_news/price_summary.md</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>4th demonstration that the test window drives the result</t>
+          <t>pre-fix figure was 0.496 - entirely the ASPI leak</t>
         </is>
       </c>
     </row>
@@ -7935,17 +7943,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Sector composite autocorrelation</t>
+          <t>Index vs stock autocorrelation</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>BANKS/FINANCE/SECTOR composites</t>
+          <t>SPSL20, ASPI vs 7 stocks</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -7960,7 +7968,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>lag-1 autocorrelation</t>
+          <t>lag-1 return autocorrelation</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -7970,12 +7978,12 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Composite vs constituent autocorr</t>
+          <t>Lag-1 autocorr (index vs stock)</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>BANKS +0.178 vs ~0.07</t>
+          <t>+0.24 vs +0.04</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -7990,17 +7998,17 @@
       </c>
       <c r="N96" s="4" t="inlineStr">
         <is>
-          <t>Averaging HELPS for banks (composite 0.178 &gt; every constituent) but FAILS for finance (0.017 - constituents have negative autocorrs that cancel). Mixing them is worse (0.078). SYSTEM DESIGN: build a BANKS index, not a banks+finance index.</t>
+          <t>REAL EFFECT: indices show +0.237 (SPSL20) and +0.233 (ASPI) lag-1 return autocorrelation vs +0.038 for HNB. Non-synchronous trading - illiquid constituents (LOFC 37.8% flat days) reprice a day late, smearing shocks. A 1-parameter AR(1) captures the entire index 'edge'.</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>results/sector_direction/autocorrelation.csv</t>
+          <t>price_all_results.csv</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>sector_direction.py; the '6x more predictable' estimate was too strong - 1.2x on average</t>
+          <t>statistically real, economically useless - capturing it means trading the illiquid names that cause it</t>
         </is>
       </c>
     </row>
@@ -8015,17 +8023,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Sector direction (the product target)</t>
+          <t>Hybrid ARIMA+LSTM (Zhang 2003)</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>BANKS/FINANCE/SECTOR composites</t>
+          <t>S&amp;P SL 20 + HNB</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -8035,33 +8043,29 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward 6-month folds</t>
+          <t>fixed 80/20 + 7 walk-forward folds</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>ARIMA(2,1,0) + LSTM on residuals</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/10/22, binary + 3-class</t>
+          <t>one-step-ahead, rolling ARIMA state</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Configurations beating baseline</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>0 of 24</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>majority / persistence</t>
-        </is>
+          <t>Theil U2 (fixed split)</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
@@ -8070,17 +8074,17 @@
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>The target the SYSTEM actually predicts, never tested before. Sector-level direction is NOT predictable on plain accuracy at any horizon or grouping. Leak scan clean.</t>
+          <t>Hybrid built properly (Y=L+N, LSTM on ARIMA residuals, 3 seeds averaged) and it does NOT beat the naive random walk. SPSL20 U2=1.012, HNB U2=1.005. Marginally WORSE than plain ARIMA on both targets.</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>results/sector_direction/sector_direction_summary.md</t>
+          <t>results/hybrid_comparable/hybrid_summary.md</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>sector_direction.py</t>
+          <t>hybrid_arima_lstm_macro_news.py; supervisor-committed architecture, now tested</t>
         </is>
       </c>
     </row>
@@ -8095,17 +8099,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Magnitude edge on BANKS composite</t>
+          <t>Hybrid + macro + news (extension)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite</t>
+          <t>S&amp;P SL 20 + HNB</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -8115,50 +8119,52 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, binary</t>
+          <t>fixed 80/20 + 7 walk-forward folds</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>ARIMA + LSTM on residuals WITH exogenous macro/news</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>|return|-weighted accuracy</t>
+          <t>one-step-ahead</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Weighted edge 1d/1wk/2wk (pp)</t>
+          <t>Folds better than naive (HNB)</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>+10.2 / +8.1 / +11.5</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>0 of 7</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M98" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N98" s="4" t="inlineStr">
         <is>
-          <t>THIRD independent replication of the magnitude edge (after single stocks and pooled panel). Consistent across 4 horizons, 14-15 of 19 folds each, while plain accuracy edge is NEGATIVE. Product: flag big-move periods, do not emit daily direction calls.</t>
+          <t>THE PROJECT'S EXTENSION: macro+news fed into the residual model - the part ARIMA provably cannot explain. It makes things WORSE. SPSL20 U2 1.032, HNB U2 1.011, HNB walk-forward 0/7 folds.</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>sector_direction_all.csv</t>
+          <t>hybrid_walkforward_table.csv</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>3-class magnitude figures (+34/+39pp) are INFLATED by a degenerate weighted-majority baseline - use the binary ones</t>
+          <t>best place to put macro if it carried information; it does not</t>
         </is>
       </c>
     </row>
@@ -8173,17 +8179,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Method study</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>PROBABILITY CALIBRATION (product-critical)</t>
+          <t>Diebold-Mariano + Theil U added</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>BANKS + SECTOR composites</t>
+          <t>S&amp;P SL 20 + HNB</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -8193,33 +8199,31 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds, calibrator fitted inside training window only</t>
+          <t>fixed 80/20</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Logistic/XGBoost x raw/Platt/isotonic</t>
+          <t>DM test (Newey-West HAC) + Theil U2</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>binary, h=5/10/22</t>
+          <t>forecast comparison</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>Configurations usable (skill&gt;0 &amp; ECE&lt;0.10)</t>
+          <t>Models significantly better than naive</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0 of 36</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>climatology (base rate)</t>
-        </is>
+          <t>0 of 8</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0.05</v>
       </c>
       <c r="M99" s="5" t="inlineStr">
         <is>
@@ -8228,17 +8232,17 @@
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>THE DASHBOARD CANNOT SHOW A MODEL CONFIDENCE NUMBER. Every Brier skill score is NEGATIVE; AUC 0.41-0.56 = coin flip. Calibration cannot fix a model that cannot rank.</t>
+          <t>COMPARABILITY GAP CLOSED. Papers claim superiority with the DM test; this project had only baseline-relative edge. DM run vs naive AND vs ARIMA: ZERO models significant at p&lt;0.05. Only 1 of 8 has Theil U2&lt;1.</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>results/sector_calibration/calibration_summary.md</t>
+          <t>hybrid_fixed_split_table.csv</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>sector_calibration.py; sklearn 1.9 removed cv='prefit', FrozenEstimator required</t>
+          <t>the standard test reviewers expect; previously missing</t>
         </is>
       </c>
     </row>
@@ -8253,17 +8257,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Method study</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Calibration removes error by removing information</t>
+          <t>R-squared on price levels is meaningless</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>BANKS + SECTOR composites</t>
+          <t>S&amp;P SL 20 + HNB</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -8273,28 +8277,26 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>19 walk-forward folds</t>
+          <t>fixed 80/20</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Platt vs raw probabilities</t>
+          <t>all models incl. naive</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>prob_std Platt vs raw</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>0.012-0.054 vs 0.164-0.232</t>
-        </is>
+          <t>R2 of the NAIVE model</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0.9979</v>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
@@ -8308,17 +8310,17 @@
       </c>
       <c r="N100" s="4" t="inlineStr">
         <is>
-          <t>Platt roughly HALVES calibration error by collapsing the forecast to near-constant. A model that says '54%' every day is perfectly calibrated and useless - no resolution. Calibration alone is not evidence of a usable forecast.</t>
+          <t>IMPORTANT FOR THE WRITE-UP: every model scores R2 0.9977-0.9980 - INCLUDING the naive random walk. Papers reporting R2~0.99 on price levels are reporting nothing. R2 on a level only measures being in the right magnitude.</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>calibration_all_folds.csv</t>
+          <t>hybrid_fixed_split_table.csv</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>product answer: replace model confidence with a realised track record</t>
+          <t>direct rebuttal to a common claim in this literature</t>
         </is>
       </c>
     </row>
@@ -8333,17 +8335,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Method study</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>News isolated - macro removed</t>
+          <t>Fixed split vs walk-forward disagreement</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + S&amp;P SL 20</t>
+          <t>S&amp;P SL 20 + HNB</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -8353,50 +8355,52 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds, 2016-2022 (news window)</t>
+          <t>both protocols, same models</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Logistic + XGBoost</t>
+          <t>ARIMA / LSTM / Hybrid</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>direct, h=1/5/10, P vs P+N</t>
+          <t>one-step-ahead</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Horizons where news helps</t>
+          <t>ARIMA SPSL20 U2 (fixed vs WF)</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0 of 6</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M101" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>1.005 vs 0.985</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>CLEAN ISOLATION TEST. In Phase H news competed with ~30 other columns incl. macro, which Phase C showed can actively hurt. Stripped back to price+news only: news gain -1.25 to +2.60pp, nothing significant. Macro was NOT masking news.</t>
+          <t>The two protocols DISAGREE: ARIMA is worse than naive on the SPSL20 fixed split (6/7 folds better in walk-forward), and the reverse pattern on HNB. Reporting only one protocol would mislead - hence both are published.</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>results/price_news_hybrid/news_gain.csv</t>
+          <t>hybrid_all_results.csv</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>price_news_hybrid.py; window 2016-2022 not comparable to other phases</t>
+          <t>4th demonstration that the test window drives the result</t>
         </is>
       </c>
     </row>
@@ -8411,17 +8415,17 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Price forecast</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Hybrid + news, no macro</t>
+          <t>Sector composite autocorrelation</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + S&amp;P SL 20</t>
+          <t>BANKS/FINANCE/SECTOR composites</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -8431,48 +8435,52 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds</t>
+          <t>full sample</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>naive / ARIMA(2,1,0) / Hybrid / Hybrid+News</t>
+          <t>lag-1 autocorrelation</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead</t>
+          <t>descriptive</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>Theil U2 (Hybrid+News, BANKS)</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>1.0003</v>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M102" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Composite vs constituent autocorr</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>BANKS +0.178 vs ~0.07</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M102" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
-          <t>Adding news to the hybrid makes it WORSE on both targets (BANKS 0.989-&gt;1.000, SPSL20 0.987-&gt;1.017). Plain ARIMA is the best model in the table and even it is not significant (DM p=0.30/0.46). Simplest wins again.</t>
+          <t>Averaging HELPS for banks (composite 0.178 &gt; every constituent) but FAILS for finance (0.017 - constituents have negative autocorrs that cancel). Mixing them is worse (0.078). SYSTEM DESIGN: build a BANKS index, not a banks+finance index.</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>results/price_news_hybrid/price_summary.csv</t>
+          <t>results/sector_direction/autocorrelation.csv</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>supports cutting BOTH the news and hybrid stages from the production system</t>
+          <t>sector_direction.py; the '6x more predictable' estimate was too strong - 1.2x on average</t>
         </is>
       </c>
     </row>
@@ -8487,17 +8495,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Data quality</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>LEAK #4 - SPSL20 calendar vs ASPI (again)</t>
+          <t>Sector direction (the product target)</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20</t>
+          <t>BANKS/FINANCE/SECTOR composites</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -8507,48 +8515,52 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>feature vs same-day and next-day return</t>
+          <t>19 walk-forward 6-month folds</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>correlation audit</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>leak detection</t>
+          <t>direct, h=1/5/10/22, binary + 3-class</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>corr with next-day vs same-day</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>0.871</v>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="M103" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Configurations beating baseline</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0 of 24</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>majority / persistence</t>
+        </is>
+      </c>
+      <c r="M103" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N103" s="4" t="inlineStr">
         <is>
-          <t>The 'clean' SPSL20 file DELETED every flat day, misaligning it against ASPI (352 of 1505 rows drop). Removing .ffill() was NOT enough. Faked 82.8% accuracy / +20.7pp edge; a trivial 'copy sign of ASPI' rule scored 84.3%. Fixed by using the ASPI-calendar SPSL20 file AND dropping ASPI features for index targets.</t>
+          <t>The target the SYSTEM actually predicts, never tested before. Sector-level direction is NOT predictable on plain accuracy at any horizon or grouping. Leak scan clean.</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>results/price_news_hybrid/leak_scan.csv</t>
+          <t>results/sector_direction/sector_direction_summary.md</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>corrected result: 56.8% accuracy, -5.5pp edge</t>
+          <t>sector_direction.py</t>
         </is>
       </c>
     </row>
@@ -8563,17 +8575,17 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Leak guard now HALTS the run</t>
+          <t>Magnitude edge on BANKS composite</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>all targets</t>
+          <t>BANKS composite</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -8583,52 +8595,50 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>every feature set</t>
+          <t>19 walk-forward folds, binary</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>automated leak scan</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>guard</t>
+          <t>|return|-weighted accuracy</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>Runs aborted on leak detection</t>
+          <t>Weighted edge 1d/1wk/2wk (pp)</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>1 of 1</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M104" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>+10.2 / +8.1 / +11.5</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N104" s="4" t="inlineStr">
         <is>
-          <t>The guard previously only wrote a CSV and the run continued, reporting a fake +20.7pp edge while the summary line claimed 'clean'. A guard that does not stop the run is not a guard. Now raises SystemExit.</t>
+          <t>THIRD independent replication of the magnitude edge (after single stocks and pooled panel). Consistent across 4 horizons, 14-15 of 19 folds each, while plain accuracy edge is NEGATIVE. Product: flag big-move periods, do not emit daily direction calls.</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>price_news_hybrid.py</t>
+          <t>sector_direction_all.csv</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>4th leak caught in this project; all four flattered the model</t>
+          <t>3-class magnitude figures (+34/+39pp) are INFLATED by a degenerate weighted-majority baseline - use the binary ones</t>
         </is>
       </c>
     </row>
@@ -8648,12 +8658,12 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Late fusion (one model per source)</t>
+          <t>PROBABILITY CALIBRATION (product-critical)</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + HNB</t>
+          <t>BANKS + SECTOR composites</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -8663,32 +8673,32 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds, chronological base/meta split</t>
+          <t>19 walk-forward folds, calibrator fitted inside training window only</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>XGBoost bases + Logistic meta-learner</t>
+          <t>Logistic/XGBoost x raw/Platt/isotonic</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>stacking, h=1/5/10</t>
+          <t>binary, h=5/10/22</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>Configurations beating baseline</t>
+          <t>Configurations usable (skill&gt;0 &amp; ECE&lt;0.10)</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>0 of 6</t>
+          <t>0 of 36</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>majority / persistence</t>
+          <t>climatology (base rate)</t>
         </is>
       </c>
       <c r="M105" s="5" t="inlineStr">
@@ -8698,17 +8708,17 @@
       </c>
       <c r="N105" s="4" t="inlineStr">
         <is>
-          <t>ARCHITECTURE WAS NOT THE CONSTRAINT. Separate models for price/news/macro combined by a meta-learner: 0/6 beat the baseline. Late fusion IS less bad than early fusion (better in 5/6) but beats it significantly in only 1/6 = chance.</t>
+          <t>THE DASHBOARD CANNOT SHOW A MODEL CONFIDENCE NUMBER. Every Brier skill score is NEGATIVE; AUC 0.41-0.56 = coin flip. Calibration cannot fix a model that cannot rank.</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>results/late_fusion/late_fusion_summary.md</t>
+          <t>results/sector_calibration/calibration_summary.md</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>late_fusion_stacking.py; meta-learner trained on OUT-OF-FOLD base predictions</t>
+          <t>sector_calibration.py; sklearn 1.9 removed cv='prefit', FrozenEstimator required</t>
         </is>
       </c>
     </row>
@@ -8728,12 +8738,12 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Meta-learner weight allocation</t>
+          <t>Calibration removes error by removing information</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + HNB</t>
+          <t>BANKS + SECTOR composites</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -8743,27 +8753,27 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>6 walk-forward folds</t>
+          <t>19 walk-forward folds</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Logistic meta-learner on 3 base models</t>
+          <t>Platt vs raw probabilities</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>stacking</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>Median weight share price/news/macro</t>
+          <t>prob_std Platt vs raw</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>29% / 38% / 33%</t>
+          <t>0.012-0.054 vs 0.164-0.232</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
@@ -8778,17 +8788,17 @@
       </c>
       <c r="N106" s="4" t="inlineStr">
         <is>
-          <t>CLEANEST VERSION OF THE CENTRAL FINDING. A model free to weight the three sources however it likes splits ~1/3 each and leans MOST on news. If price carried signal and news did not, it would load onto price. Even allocation = nothing to prefer.</t>
+          <t>Platt roughly HALVES calibration error by collapsing the forecast to near-constant. A model that says '54%' every day is perfectly calibrated and useless - no resolution. Calibration alone is not evidence of a usable forecast.</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>results/late_fusion/meta_weights_summary.csv</t>
+          <t>calibration_all_folds.csv</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>resolves the ambiguous early-fusion result (high importance, zero gain)</t>
+          <t>product answer: replace model confidence with a realised track record</t>
         </is>
       </c>
     </row>
@@ -8803,17 +8813,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Early vs late fusion ruled out as explanation</t>
+          <t>News isolated - macro removed</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>BANKS composite + HNB</t>
+          <t>BANKS composite + S&amp;P SL 20</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -8823,27 +8833,27 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>identical folds, both architectures</t>
+          <t>6 walk-forward folds, 2016-2022 (news window)</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>early (concatenated) vs late (stacked)</t>
+          <t>Logistic + XGBoost</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>direct, h=1/5/10, P vs P+N</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>Late beats early significantly</t>
+          <t>Horizons where news helps</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>1 of 6</t>
+          <t>0 of 6</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
@@ -8856,17 +8866,17 @@
       </c>
       <c r="N107" s="4" t="inlineStr">
         <is>
-          <t>Rules out one candidate explanation for why published papers report gains: 'early fusion drowned the weak signals'. Giving news and macro dedicated models surfaces nothing. Still open: missing naive baselines, no publication lag, single favourable split, decomposition hybrids.</t>
+          <t>CLEAN ISOLATION TEST. In Phase H news competed with ~30 other columns incl. macro, which Phase C showed can actively hurt. Stripped back to price+news only: news gain -1.25 to +2.60pp, nothing significant. Macro was NOT masking news.</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>late_fusion_folds.csv</t>
+          <t>results/price_news_hybrid/news_gain.csv</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>late_fusion_stacking.py</t>
+          <t>price_news_hybrid.py; window 2016-2022 not comparable to other phases</t>
         </is>
       </c>
     </row>
@@ -8881,17 +8891,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Price forecast</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Reproduce-then-break ladder</t>
+          <t>Hybrid + news, no macro</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + BANKS composite</t>
+          <t>BANKS composite + S&amp;P SL 20</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -8901,50 +8911,48 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>L0 paper-style -&gt; L3 walk-forward, one guard at a time</t>
+          <t>6 walk-forward folds</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost (best reported)</t>
+          <t>naive / ARIMA(2,1,0) / Hybrid / Hybrid+News</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>next-day price</t>
+          <t>one-step-ahead</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>L0 'macro improvement' %</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>+0.17 / -0.04</t>
-        </is>
+          <t>Theil U2 (Hybrid+News, BANKS)</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>1.0003</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>1</v>
+      </c>
+      <c r="M108" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N108" s="4" t="inlineStr">
         <is>
-          <t>REPRODUCTION FAILED - and that is the finding. Removing the publication lag, leaking the scaler and using a single split move the number by FRACTIONS OF A PERCENT. These three shortcuts are NOT the mechanism behind published macro gains.</t>
+          <t>Adding news to the hybrid makes it WORSE on both targets (BANKS 0.989-&gt;1.000, SPSL20 0.987-&gt;1.017). Plain ARIMA is the best model in the table and even it is not significant (DM p=0.30/0.46). Simplest wins again.</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>results/reproduce_then_break/ladder_summary.md</t>
+          <t>results/price_news_hybrid/price_summary.csv</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>reproduce_then_break.py; hypothesis was wrong, reported as such</t>
+          <t>supports cutting BOTH the news and hybrid stages from the production system</t>
         </is>
       </c>
     </row>
@@ -8959,17 +8967,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Data quality</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>The likely real mechanism: no naive baseline</t>
+          <t>LEAK #4 - SPSL20 calendar vs ASPI (again)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + BANKS composite</t>
+          <t>S&amp;P SL 20</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -8979,29 +8987,29 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>all ladder levels</t>
+          <t>feature vs same-day and next-day return</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>all configs incl. naive</t>
+          <t>correlation audit</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>next-day price</t>
+          <t>leak detection</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>R2 across every level</t>
+          <t>corr with next-day vs same-day</t>
         </is>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.998</v>
+        <v>0.871</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>0.9979</v>
+        <v>0.227</v>
       </c>
       <c r="M109" s="6" t="inlineStr">
         <is>
@@ -9010,17 +9018,17 @@
       </c>
       <c r="N109" s="4" t="inlineStr">
         <is>
-          <t>R2 is 0.9978-0.9984 at EVERY level for EVERY config - and naive scores 0.9979. A paper running this exact setup would truthfully report 'R2=0.998, MAPE=0.83%, outperforms benchmark'. The gain is model-vs-weaker-model, reported with metrics that cannot distinguish either from a random walk.</t>
+          <t>The 'clean' SPSL20 file DELETED every flat day, misaligning it against ASPI (352 of 1505 rows drop). Removing .ffill() was NOT enough. Faked 82.8% accuracy / +20.7pp edge; a trivial 'copy sign of ASPI' rule scored 84.3%. Fixed by using the ASPI-calendar SPSL20 file AND dropping ASPI features for index targets.</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ladder_summary.csv</t>
+          <t>results/price_news_hybrid/leak_scan.csv</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>DM p = 0.48-0.86 throughout; nothing significant</t>
+          <t>corrected result: 56.8% accuracy, -5.5pp edge</t>
         </is>
       </c>
     </row>
@@ -9040,12 +9048,12 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Single split is the shortcut that matters most</t>
+          <t>Leak guard now HALTS the run</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + BANKS composite</t>
+          <t>all targets</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -9055,52 +9063,52 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>L0-L2 single split vs L3 walk-forward</t>
+          <t>every feature set</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Ridge + XGBoost</t>
+          <t>automated leak scan</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>next-day price</t>
+          <t>guard</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>MAPE(macro)/MAPE(naive)</t>
+          <t>Runs aborted on leak detection</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0.96-0.98 -&gt; 1.027</t>
+          <t>1 of 1</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="M110" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M110" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N110" s="4" t="inlineStr">
         <is>
-          <t>Under single-split levels price+macro sits BELOW naive (0.964-0.980); under walk-forward it crosses ABOVE 1.0 on both targets. Of the three shortcuts tested, the single split changes the conclusion; the other two do not. 4th confirmation of the window effect.</t>
+          <t>The guard previously only wrote a CSV and the run continued, reporting a fake +20.7pp edge while the summary line claimed 'clean'. A guard that does not stop the run is not a guard. Now raises SystemExit.</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ladder_all.csv</t>
+          <t>price_news_hybrid.py</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>argues for walk-forward as the default reporting protocol</t>
+          <t>4th leak caught in this project; all four flattered the model</t>
         </is>
       </c>
     </row>
@@ -9115,17 +9123,17 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>DECOMPOSITION LEAK - the mechanism found</t>
+          <t>Late fusion (one model per source)</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + BANKS composite</t>
+          <t>BANKS composite + HNB</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -9135,52 +9143,52 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20, identical model/data, only pipeline ORDER differs</t>
+          <t>6 walk-forward folds, chronological base/meta split</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>wavelet(db4,3) + CEEMDAN -&gt; Ridge/XGBoost</t>
+          <t>XGBoost bases + Logistic meta-learner</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead price</t>
+          <t>stacking, h=1/5/10</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>Improvement over naive: leaky vs honest</t>
+          <t>Configurations beating baseline</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>+19.2% vs -6.9%</t>
+          <t>0 of 6</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>naive</t>
-        </is>
-      </c>
-      <c r="M111" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>majority / persistence</t>
+        </is>
+      </c>
+      <c r="M111" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="N111" s="4" t="inlineStr">
         <is>
-          <t>★ THE MECHANISM. Decomposing the FULL series BEFORE splitting creates a 13-26pp improvement out of nothing. Wavelet/CEEMDAN are GLOBAL transforms: component values at time t are computed from the whole series, so training components carry test-period information and test components were built from their own future.</t>
+          <t>ARCHITECTURE WAS NOT THE CONSTRAINT. Separate models for price/news/macro combined by a meta-learner: 0/6 beat the baseline. Late fusion IS less bad than early fusion (better in 5/6) but beats it significantly in only 1/6 = chance.</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>results/decomposition_leak/decomposition_summary.md</t>
+          <t>results/late_fusion/late_fusion_summary.md</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>decomposition_leak_test.py; explains the gap between published hybrid results and this project</t>
+          <t>late_fusion_stacking.py; meta-learner trained on OUT-OF-FOLD base predictions</t>
         </is>
       </c>
     </row>
@@ -9195,17 +9203,17 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Method study</t>
+          <t>Direction</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Leaky decomposition is highly significant</t>
+          <t>Meta-learner weight allocation</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>S&amp;P SL 20 + BANKS composite</t>
+          <t>BANKS composite + HNB</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -9215,50 +9223,52 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>fixed 80/20</t>
+          <t>6 walk-forward folds</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>wavelet + CEEMDAN, leaky pipeline</t>
+          <t>Logistic meta-learner on 3 base models</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>one-step-ahead price</t>
+          <t>stacking</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>DM p vs naive (4 configs)</t>
+          <t>Median weight share price/news/macro</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0.0000-0.0199</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M112" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>29% / 38% / 33%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M112" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="N112" s="4" t="inlineStr">
         <is>
-          <t>ALL FOUR leaky configurations beat naive significantly (Theil U2 0.794-0.871, DM p&lt;0.02, two at p&lt;0.0001). These are exactly the numbers decomposition-hybrid papers report.</t>
+          <t>CLEANEST VERSION OF THE CENTRAL FINDING. A model free to weight the three sources however it likes splits ~1/3 each and leans MOST on news. If price carried signal and news did not, it would load onto price. Even allocation = nothing to prefer.</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>decomposition_results.csv</t>
+          <t>results/late_fusion/meta_weights_summary.csv</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>the result is real as computed - it is the pipeline that is wrong</t>
+          <t>resolves the ambiguous early-fusion result (high importance, zero gain)</t>
         </is>
       </c>
     </row>
@@ -9278,70 +9288,540 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
+          <t>Early vs late fusion ruled out as explanation</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>BANKS composite + HNB</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>identical folds, both architectures</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>early (concatenated) vs late (stacked)</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Late beats early significantly</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>1 of 6</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M113" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N113" s="4" t="inlineStr">
+        <is>
+          <t>Rules out one candidate explanation for why published papers report gains: 'early fusion drowned the weak signals'. Giving news and macro dedicated models surfaces nothing. Still open: missing naive baselines, no publication lag, single favourable split, decomposition hybrids.</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>late_fusion_folds.csv</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>late_fusion_stacking.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Reproduce-then-break ladder</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>L0 paper-style -&gt; L3 walk-forward, one guard at a time</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Ridge + XGBoost (best reported)</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>next-day price</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>L0 'macro improvement' %</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>+0.17 / -0.04</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t>REPRODUCTION FAILED - and that is the finding. Removing the publication lag, leaking the scaler and using a single split move the number by FRACTIONS OF A PERCENT. These three shortcuts are NOT the mechanism behind published macro gains.</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>results/reproduce_then_break/ladder_summary.md</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>reproduce_then_break.py; hypothesis was wrong, reported as such</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>The likely real mechanism: no naive baseline</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>all ladder levels</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>all configs incl. naive</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>next-day price</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>R2 across every level</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0.9979</v>
+      </c>
+      <c r="M115" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>R2 is 0.9978-0.9984 at EVERY level for EVERY config - and naive scores 0.9979. A paper running this exact setup would truthfully report 'R2=0.998, MAPE=0.83%, outperforms benchmark'. The gain is model-vs-weaker-model, reported with metrics that cannot distinguish either from a random walk.</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>ladder_summary.csv</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>DM p = 0.48-0.86 throughout; nothing significant</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Single split is the shortcut that matters most</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>L0-L2 single split vs L3 walk-forward</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Ridge + XGBoost</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>next-day price</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>MAPE(macro)/MAPE(naive)</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>0.96-0.98 -&gt; 1.027</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="M116" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N116" s="4" t="inlineStr">
+        <is>
+          <t>Under single-split levels price+macro sits BELOW naive (0.964-0.980); under walk-forward it crosses ABOVE 1.0 on both targets. Of the three shortcuts tested, the single split changes the conclusion; the other two do not. 4th confirmation of the window effect.</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>ladder_all.csv</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>argues for walk-forward as the default reporting protocol</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>DECOMPOSITION LEAK - the mechanism found</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>fixed 80/20, identical model/data, only pipeline ORDER differs</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>wavelet(db4,3) + CEEMDAN -&gt; Ridge/XGBoost</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>one-step-ahead price</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>Improvement over naive: leaky vs honest</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>+19.2% vs -6.9%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="M117" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>★ THE MECHANISM. Decomposing the FULL series BEFORE splitting creates a 13-26pp improvement out of nothing. Wavelet/CEEMDAN are GLOBAL transforms: component values at time t are computed from the whole series, so training components carry test-period information and test components were built from their own future.</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>results/decomposition_leak/decomposition_summary.md</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>decomposition_leak_test.py; explains the gap between published hybrid results and this project</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Leaky decomposition is highly significant</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>S&amp;P SL 20 + BANKS composite</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>fixed 80/20</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>wavelet + CEEMDAN, leaky pipeline</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>one-step-ahead price</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>DM p vs naive (4 configs)</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0.0000-0.0199</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M118" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N118" s="4" t="inlineStr">
+        <is>
+          <t>ALL FOUR leaky configurations beat naive significantly (Theil U2 0.794-0.871, DM p&lt;0.02, two at p&lt;0.0001). These are exactly the numbers decomposition-hybrid papers report.</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>decomposition_results.csv</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>the result is real as computed - it is the pipeline that is wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Method study</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
           <t>Honest decomposition loses to naive</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>S&amp;P SL 20 + BANKS composite</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>fixed 80/20, decompose only series[:t] at each t</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>wavelet + CEEMDAN, honest pipeline</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr">
         <is>
           <t>one-step-ahead price</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr">
+      <c r="J119" s="2" t="inlineStr">
         <is>
           <t>Theil U2 (4 configs)</t>
         </is>
       </c>
-      <c r="K113" s="2" t="inlineStr">
+      <c r="K119" s="2" t="inlineStr">
         <is>
           <t>1.008-1.028</t>
         </is>
       </c>
-      <c r="L113" s="2" t="n">
+      <c r="L119" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M113" s="5" t="inlineStr">
+      <c r="M119" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N113" s="4" t="inlineStr">
+      <c r="N119" s="4" t="inlineStr">
         <is>
           <t>Same models, same data, decomposition restricted to past data only: ALL FOUR configs are WORSE than a random walk and none significant (DM p 0.35-0.84). The decomposition advantage does not survive an honest pipeline.</t>
         </is>
       </c>
-      <c r="O113" s="2" t="inlineStr">
+      <c r="O119" s="2" t="inlineStr">
         <is>
           <t>decomposition_results.csv</t>
         </is>
       </c>
-      <c r="P113" s="2" t="inlineStr">
+      <c r="P119" s="2" t="inlineStr">
         <is>
           <t>honest CEEMDAN re-decomposes every 3rd point for runtime; wavelet every point</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P113"/>
+  <autoFilter ref="A1:P119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
